--- a/api/2/clv3/xlsx/en/HumanitarianPlan.xlsx
+++ b/api/2/clv3/xlsx/en/HumanitarianPlan.xlsx
@@ -25,15 +25,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:plan-start-date</t>
+  </si>
+  <si>
+    <t>codeforiati:plan-end-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-year</t>
   </si>
   <si>
-    <t>codeforiati:plan-end-date</t>
-  </si>
-  <si>
-    <t>codeforiati:plan-start-date</t>
-  </si>
-  <si>
     <t>codeforiati:plan-type</t>
   </si>
   <si>
@@ -46,15 +46,15 @@
     <t>active</t>
   </si>
   <si>
+    <t>2025-01-01</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
     <t>2025</t>
   </si>
   <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
@@ -355,15 +355,15 @@
     <t>Afghanistan Humanitarian Needs and Response Plan 2024</t>
   </si>
   <si>
+    <t>2024-01-01</t>
+  </si>
+  <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
-    <t>2024-01-01</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -712,15 +712,15 @@
     <t>Afghanistan Humanitarian Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-01-01</t>
+  </si>
+  <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
     <t>2023</t>
   </si>
   <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
-    <t>2023-01-01</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -841,24 +841,24 @@
     <t>Mongolia Dzud Early Action and Response Plan 2023</t>
   </si>
   <si>
+    <t>2022-12-01</t>
+  </si>
+  <si>
     <t>2023-05-31</t>
   </si>
   <si>
-    <t>2022-12-01</t>
-  </si>
-  <si>
     <t>OMOZ23</t>
   </si>
   <si>
     <t>Mozambique Cyclone Freddy, Floods and Cholera Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-03-01</t>
+  </si>
+  <si>
     <t>2023-09-30</t>
   </si>
   <si>
-    <t>2023-03-01</t>
-  </si>
-  <si>
     <t>HMOZ23</t>
   </si>
   <si>
@@ -946,12 +946,12 @@
     <t>Sudan Emergency: Regional Refugee Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-05-01</t>
+  </si>
+  <si>
     <t>2023-10-31</t>
   </si>
   <si>
-    <t>2023-05-01</t>
-  </si>
-  <si>
     <t>HSDN23</t>
   </si>
   <si>
@@ -1030,15 +1030,15 @@
     <t>Afghanistan Humanitarian Response Plan 2022</t>
   </si>
   <si>
+    <t>2022-01-01</t>
+  </si>
+  <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
     <t>2022</t>
   </si>
   <si>
-    <t>2022-12-31</t>
-  </si>
-  <si>
-    <t>2022-01-01</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -1081,12 +1081,12 @@
     <t>Cuba Hurricane Ian Response - Plan of Action 2022</t>
   </si>
   <si>
+    <t>2022-10-20</t>
+  </si>
+  <si>
     <t>2023-03-31</t>
   </si>
   <si>
-    <t>2022-10-20</t>
-  </si>
-  <si>
     <t>RDRCRRP22</t>
   </si>
   <si>
@@ -1117,12 +1117,12 @@
     <t>Haïti Choléra+ Appel Éclair 2022</t>
   </si>
   <si>
+    <t>2022-10-16</t>
+  </si>
+  <si>
     <t>2023-04-15</t>
   </si>
   <si>
-    <t>2022-10-16</t>
-  </si>
-  <si>
     <t>FHTI22</t>
   </si>
   <si>
@@ -1180,12 +1180,12 @@
     <t>Malawi Flash Appeal 2022</t>
   </si>
   <si>
+    <t>2022-02-26</t>
+  </si>
+  <si>
     <t>2022-05-31</t>
   </si>
   <si>
-    <t>2022-02-26</t>
-  </si>
-  <si>
     <t>HMLI22</t>
   </si>
   <si>
@@ -1198,12 +1198,12 @@
     <t>Mozambique Gombe Emergency Response Plan 2022</t>
   </si>
   <si>
+    <t>2022-04-01</t>
+  </si>
+  <si>
     <t>2022-09-30</t>
   </si>
   <si>
-    <t>2022-04-01</t>
-  </si>
-  <si>
     <t>HMOZ22</t>
   </si>
   <si>
@@ -1255,12 +1255,12 @@
     <t>Philippines Super Typhoon Rai (Odette) Humanitarian Needs and Priorities 2022</t>
   </si>
   <si>
+    <t>2021-12-24</t>
+  </si>
+  <si>
     <t>2022-06-30</t>
   </si>
   <si>
-    <t>2021-12-24</t>
-  </si>
-  <si>
     <t>RREG22</t>
   </si>
   <si>
@@ -1378,15 +1378,15 @@
     <t>Afghanistan Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
     <t>2021</t>
   </si>
   <si>
-    <t>2021-12-31</t>
-  </si>
-  <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -1477,12 +1477,12 @@
     <t>Escalation of Hostilities in the OPT Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-05-27</t>
+  </si>
+  <si>
     <t>2021-08-27</t>
   </si>
   <si>
-    <t>2021-05-27</t>
-  </si>
-  <si>
     <t>HETH21</t>
   </si>
   <si>
@@ -1507,12 +1507,12 @@
     <t>Haiti Earthquake Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-08-16</t>
+  </si>
+  <si>
     <t>2022-02-15</t>
   </si>
   <si>
-    <t>2021-08-16</t>
-  </si>
-  <si>
     <t>HHTI21</t>
   </si>
   <si>
@@ -1525,12 +1525,12 @@
     <t>Honduras Tropical Storm Eta Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2020-11-15</t>
+  </si>
+  <si>
     <t>2021-06-30</t>
   </si>
   <si>
-    <t>2020-11-15</t>
-  </si>
-  <si>
     <t>HHND21</t>
   </si>
   <si>
@@ -1564,12 +1564,12 @@
     <t>Lebanon Emergency Response Plan 2021</t>
   </si>
   <si>
+    <t>2021-08-03</t>
+  </si>
+  <si>
     <t>2022-07-31</t>
   </si>
   <si>
-    <t>2021-08-03</t>
-  </si>
-  <si>
     <t>HLBY21</t>
   </si>
   <si>
@@ -1735,15 +1735,15 @@
     <t>Afghanistan Humanitarian Response Plan 2020</t>
   </si>
   <si>
+    <t>2020-01-01</t>
+  </si>
+  <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
     <t>2020</t>
   </si>
   <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2020-01-01</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -1858,12 +1858,12 @@
     <t>Djibouti Flash Appeal 2020</t>
   </si>
   <si>
+    <t>2019-12-17</t>
+  </si>
+  <si>
     <t>2020-03-31</t>
   </si>
   <si>
-    <t>2019-12-17</t>
-  </si>
-  <si>
     <t>ODJI20</t>
   </si>
   <si>
@@ -1957,12 +1957,12 @@
     <t>Lebanon Flash Appeal 2020</t>
   </si>
   <si>
+    <t>2020-08-05</t>
+  </si>
+  <si>
     <t>2020-11-13</t>
   </si>
   <si>
-    <t>2020-08-05</t>
-  </si>
-  <si>
     <t>OLBN20</t>
   </si>
   <si>
@@ -1975,12 +1975,12 @@
     <t>Lesotho Flash Appeal 2019-2020</t>
   </si>
   <si>
+    <t>2019-11-01</t>
+  </si>
+  <si>
     <t>2020-04-30</t>
   </si>
   <si>
-    <t>2019-11-01</t>
-  </si>
-  <si>
     <t>OLBR20</t>
   </si>
   <si>
@@ -2170,15 +2170,15 @@
     <t>Afghanistan Humanitarian Response Plan 2019</t>
   </si>
   <si>
+    <t>2019-01-01</t>
+  </si>
+  <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
     <t>2019</t>
   </si>
   <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
-    <t>2019-01-01</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -2386,12 +2386,12 @@
     <t>Zimbabwe Flash Appeal 2019</t>
   </si>
   <si>
+    <t>2019-02-01</t>
+  </si>
+  <si>
     <t>2020-04-29</t>
   </si>
   <si>
-    <t>2019-02-01</t>
-  </si>
-  <si>
     <t>FZWE1820</t>
   </si>
   <si>
@@ -2407,15 +2407,15 @@
     <t>Afghanistan Humanitarian Response Plan 2018</t>
   </si>
   <si>
+    <t>2018-01-01</t>
+  </si>
+  <si>
+    <t>2018-12-31</t>
+  </si>
+  <si>
     <t>2018</t>
   </si>
   <si>
-    <t>2018-12-31</t>
-  </si>
-  <si>
-    <t>2018-01-01</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -2590,12 +2590,12 @@
     <t>Syrian Arab Republic Humanitarian Response Plan 2018</t>
   </si>
   <si>
+    <t>2018-11-30</t>
+  </si>
+  <si>
     <t>2018-12-30</t>
   </si>
   <si>
-    <t>2018-11-30</t>
-  </si>
-  <si>
     <t>RSYR18</t>
   </si>
   <si>
@@ -2632,15 +2632,15 @@
     <t>2017 Europe Situation - Regional Refugee and Migrant Response</t>
   </si>
   <si>
+    <t>2017-01-01</t>
+  </si>
+  <si>
+    <t>2017-12-31</t>
+  </si>
+  <si>
     <t>2017</t>
   </si>
   <si>
-    <t>2017-12-31</t>
-  </si>
-  <si>
-    <t>2017-01-01</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -2716,12 +2716,12 @@
     <t>Dominica Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-09-28</t>
+  </si>
+  <si>
     <t>2017-12-29</t>
   </si>
   <si>
-    <t>2017-09-28</t>
-  </si>
-  <si>
     <t>OPRK17</t>
   </si>
   <si>
@@ -2761,12 +2761,12 @@
     <t>Kenya Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
     <t>2017-11-30</t>
   </si>
   <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
     <t>HLBY17</t>
   </si>
   <si>
@@ -2779,12 +2779,12 @@
     <t>Madagascar Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-03-20</t>
+  </si>
+  <si>
     <t>2017-06-20</t>
   </si>
   <si>
-    <t>2017-03-20</t>
-  </si>
-  <si>
     <t>HMLI17</t>
   </si>
   <si>
@@ -2803,12 +2803,12 @@
     <t>Mozambique Cyclone Dineo Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-02-28</t>
+  </si>
+  <si>
     <t>2017-05-31</t>
   </si>
   <si>
-    <t>2017-02-28</t>
-  </si>
-  <si>
     <t>HMMR17</t>
   </si>
   <si>
@@ -2845,12 +2845,12 @@
     <t>Peru Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-04-01</t>
+  </si>
+  <si>
     <t>2017-10-31</t>
   </si>
   <si>
-    <t>2017-04-01</t>
-  </si>
-  <si>
     <t>HCOG17</t>
   </si>
   <si>
@@ -2920,15 +2920,15 @@
     <t>2016 Europe Situation -Regional Refugee and Migrant Response</t>
   </si>
   <si>
+    <t>2016-01-01</t>
+  </si>
+  <si>
+    <t>2016-12-31</t>
+  </si>
+  <si>
     <t>2016</t>
   </si>
   <si>
-    <t>2016-12-31</t>
-  </si>
-  <si>
-    <t>2016-01-01</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -3001,24 +3001,24 @@
     <t>Ecuador Earthquake Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-04-16</t>
+  </si>
+  <si>
     <t>2016-10-31</t>
   </si>
   <si>
-    <t>2016-04-16</t>
-  </si>
-  <si>
     <t>FFJI16</t>
   </si>
   <si>
     <t>Fiji Tropical Cyclone Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-02-20</t>
+  </si>
+  <si>
     <t>2016-05-30</t>
   </si>
   <si>
-    <t>2016-02-20</t>
-  </si>
-  <si>
     <t>HGMB16</t>
   </si>
   <si>
@@ -3094,12 +3094,12 @@
     <t>Mosul Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-07-20</t>
+  </si>
+  <si>
     <t>2016-10-01</t>
   </si>
   <si>
-    <t>2016-07-20</t>
-  </si>
-  <si>
     <t>HMMR16</t>
   </si>
   <si>
@@ -3184,27 +3184,27 @@
     <t>Zimbabwe Humanitarian Response Plan 2016</t>
   </si>
   <si>
+    <t>2016-04-01</t>
+  </si>
+  <si>
     <t>2017-03-31</t>
   </si>
   <si>
-    <t>2016-04-01</t>
-  </si>
-  <si>
     <t>HAFG15</t>
   </si>
   <si>
     <t>Afghanistan Strategic Response Plan 2015</t>
   </si>
   <si>
+    <t>2015-01-01</t>
+  </si>
+  <si>
+    <t>2015-12-31</t>
+  </si>
+  <si>
     <t>2015</t>
   </si>
   <si>
-    <t>2015-12-31</t>
-  </si>
-  <si>
-    <t>2015-01-01</t>
-  </si>
-  <si>
     <t>Strategic response plan</t>
   </si>
   <si>
@@ -3262,12 +3262,12 @@
     <t>Guatemala Plan de Respuesta Sequia 2015</t>
   </si>
   <si>
+    <t>2014-11-03</t>
+  </si>
+  <si>
     <t>2015-09-30</t>
   </si>
   <si>
-    <t>2014-11-03</t>
-  </si>
-  <si>
     <t>FHTI15</t>
   </si>
   <si>
@@ -3292,12 +3292,12 @@
     <t>Vanuatu Emergency Response Plan for Tropical Cyclone PAM 2015</t>
   </si>
   <si>
+    <t>2015-03-24</t>
+  </si>
+  <si>
     <t>2015-10-31</t>
   </si>
   <si>
-    <t>2015-03-24</t>
-  </si>
-  <si>
     <t>HIRQ15</t>
   </si>
   <si>
@@ -3310,12 +3310,12 @@
     <t>Libya Humanitarian Appeal 2014- 2015</t>
   </si>
   <si>
+    <t>2014-10-01</t>
+  </si>
+  <si>
     <t>2015-05-31</t>
   </si>
   <si>
-    <t>2014-10-01</t>
-  </si>
-  <si>
     <t>HMLI15</t>
   </si>
   <si>
@@ -3427,15 +3427,15 @@
     <t>Afghanistan Strategic Response Plan 2014</t>
   </si>
   <si>
+    <t>2014-01-01</t>
+  </si>
+  <si>
+    <t>2014-12-31</t>
+  </si>
+  <si>
     <t>2014</t>
   </si>
   <si>
-    <t>2014-12-31</t>
-  </si>
-  <si>
-    <t>2014-01-01</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -3571,24 +3571,24 @@
     <t>Philippines Bohol Earthquake Flash Appeal 2014</t>
   </si>
   <si>
+    <t>2013-10-22</t>
+  </si>
+  <si>
     <t>2014-04-22</t>
   </si>
   <si>
-    <t>2013-10-22</t>
-  </si>
-  <si>
     <t>SPHL1314</t>
   </si>
   <si>
     <t>Philippines Typhoon Haiyan Strategic Response Plan 2014</t>
   </si>
   <si>
+    <t>2013-11-08</t>
+  </si>
+  <si>
     <t>2014-11-07</t>
   </si>
   <si>
-    <t>2013-11-08</t>
-  </si>
-  <si>
     <t>HPHL1314</t>
   </si>
   <si>
@@ -3604,12 +3604,12 @@
     <t>Philippines Zamboanga Crisis Flash Appeal 2014</t>
   </si>
   <si>
+    <t>2013-10-01</t>
+  </si>
+  <si>
     <t>2014-08-31</t>
   </si>
   <si>
-    <t>2013-10-01</t>
-  </si>
-  <si>
     <t>SCOD14</t>
   </si>
   <si>
@@ -3715,12 +3715,12 @@
     <t>Afghanistan 2013</t>
   </si>
   <si>
+    <t>2013-12-31</t>
+  </si>
+  <si>
     <t>2013</t>
   </si>
   <si>
-    <t>2013-12-31</t>
-  </si>
-  <si>
     <t>Consolidated appeals process</t>
   </si>
   <si>
@@ -3877,15 +3877,15 @@
     <t>2012+ Kenya Emergency Humanitarian Response Plan</t>
   </si>
   <si>
+    <t>2012-01-01</t>
+  </si>
+  <si>
+    <t>2012-12-31</t>
+  </si>
+  <si>
     <t>2012</t>
   </si>
   <si>
-    <t>2012-12-31</t>
-  </si>
-  <si>
-    <t>2012-01-01</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -3955,12 +3955,12 @@
     <t>Lesotho Food Insecurity (September 2012 - March 2013)</t>
   </si>
   <si>
+    <t>2012-09-18</t>
+  </si>
+  <si>
     <t>2013-03-25</t>
   </si>
   <si>
-    <t>2012-09-18</t>
-  </si>
-  <si>
     <t>CLBR12</t>
   </si>
   <si>
@@ -4033,12 +4033,12 @@
     <t>Syria Humanitarian Assistance Response Plan (SHARP) 2012</t>
   </si>
   <si>
+    <t>2012-06-05</t>
+  </si>
+  <si>
     <t>2012-12-05</t>
   </si>
   <si>
-    <t>2012-06-05</t>
-  </si>
-  <si>
     <t>CYEM12</t>
   </si>
   <si>
@@ -4063,12 +4063,12 @@
     <t>2011+ Kenya Emergency Humanitarian Response Plan</t>
   </si>
   <si>
+    <t>2011-01-01</t>
+  </si>
+  <si>
     <t>2011</t>
   </si>
   <si>
-    <t>2011-01-01</t>
-  </si>
-  <si>
     <t>CAFG11</t>
   </si>
   <si>
@@ -4111,12 +4111,12 @@
     <t>El Salvador Flash Appeal (October 2011 - April 2012)</t>
   </si>
   <si>
+    <t>2011-10-25</t>
+  </si>
+  <si>
     <t>2012-04-25</t>
   </si>
   <si>
-    <t>2011-10-25</t>
-  </si>
-  <si>
     <t>CHTI1011</t>
   </si>
   <si>
@@ -4147,24 +4147,24 @@
     <t>Namibia Flash Appeal (April - October 2011)</t>
   </si>
   <si>
+    <t>2011-04-11</t>
+  </si>
+  <si>
     <t>2011-10-11</t>
   </si>
   <si>
-    <t>2011-04-11</t>
-  </si>
-  <si>
     <t>FNIC1112</t>
   </si>
   <si>
     <t>Nicaragua Flash Appeal (October 2011 - April 2012)</t>
   </si>
   <si>
+    <t>2011-10-27</t>
+  </si>
+  <si>
     <t>2012-04-26</t>
   </si>
   <si>
-    <t>2011-10-27</t>
-  </si>
-  <si>
     <t>CNER11</t>
   </si>
   <si>
@@ -4177,12 +4177,12 @@
     <t>Pakistan Rapid Response Plan Floods 2011 (September - March 2012)</t>
   </si>
   <si>
+    <t>2011-09-15</t>
+  </si>
+  <si>
     <t>2012-06-30</t>
   </si>
   <si>
-    <t>2011-09-15</t>
-  </si>
-  <si>
     <t>FXLBYREG11</t>
   </si>
   <si>
@@ -4258,27 +4258,27 @@
     <t>Afghanistan Humanitarian Action Plan 2010</t>
   </si>
   <si>
+    <t>2010-01-01</t>
+  </si>
+  <si>
+    <t>2010-12-31</t>
+  </si>
+  <si>
     <t>2010</t>
   </si>
   <si>
-    <t>2010-12-31</t>
-  </si>
-  <si>
-    <t>2010-01-01</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
     <t>Burkina Faso Emergency Humanitarian Action Plan 2010</t>
   </si>
   <si>
+    <t>2010-08-01</t>
+  </si>
+  <si>
     <t>2011-01-31</t>
   </si>
   <si>
-    <t>2010-08-01</t>
-  </si>
-  <si>
     <t>CCAF10</t>
   </si>
   <si>
@@ -4303,36 +4303,36 @@
     <t>El Salvador Flash Appeal (Revised) (November 2009 - May 2010)</t>
   </si>
   <si>
+    <t>2009-11-01</t>
+  </si>
+  <si>
     <t>2010-05-31</t>
   </si>
   <si>
-    <t>2009-11-01</t>
-  </si>
-  <si>
     <t>FGTM10</t>
   </si>
   <si>
     <t>Guatemala Flash Appeal (Revised) (June - December 2010)</t>
   </si>
   <si>
+    <t>2010-06-10</t>
+  </si>
+  <si>
     <t>2010-12-09</t>
   </si>
   <si>
-    <t>2010-06-10</t>
-  </si>
-  <si>
     <t>CGTM10</t>
   </si>
   <si>
     <t>Guatemala Food Insecurity and Acute Malnutrition Appeal 2010</t>
   </si>
   <si>
+    <t>2010-02-12</t>
+  </si>
+  <si>
     <t>2010-08-11</t>
   </si>
   <si>
-    <t>2010-02-12</t>
-  </si>
-  <si>
     <t>FHTI10</t>
   </si>
   <si>
@@ -4360,12 +4360,12 @@
     <t>Kyrgyzstan Flash Appeal (Revised) (June 2010 - June 2011)</t>
   </si>
   <si>
+    <t>2010-06-01</t>
+  </si>
+  <si>
     <t>2011-06-30</t>
   </si>
   <si>
-    <t>2010-06-01</t>
-  </si>
-  <si>
     <t>CMNG1011</t>
   </si>
   <si>
@@ -4468,27 +4468,27 @@
     <t>Afghanistan Humanitarian Action Plan 2009</t>
   </si>
   <si>
+    <t>2009-01-01</t>
+  </si>
+  <si>
+    <t>2009-12-31</t>
+  </si>
+  <si>
     <t>2009</t>
   </si>
   <si>
-    <t>2009-12-31</t>
-  </si>
-  <si>
-    <t>2009-01-01</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
     <t>Burkina Faso Flash Appeal (September 2009 - February 2010)</t>
   </si>
   <si>
+    <t>2009-09-10</t>
+  </si>
+  <si>
     <t>2010-03-09</t>
   </si>
   <si>
-    <t>2009-09-10</t>
-  </si>
-  <si>
     <t>CCAF09</t>
   </si>
   <si>
@@ -4552,24 +4552,24 @@
     <t>Madagascar Flash Appeal (Revised) (April - October 2009)</t>
   </si>
   <si>
+    <t>2009-04-01</t>
+  </si>
+  <si>
     <t>2009-10-31</t>
   </si>
   <si>
-    <t>2009-04-01</t>
-  </si>
-  <si>
     <t>FNAM09</t>
   </si>
   <si>
     <t>Namibia Flash Appeal (Revised) (March - November 2009)</t>
   </si>
   <si>
+    <t>2009-03-20</t>
+  </si>
+  <si>
     <t>2009-09-30</t>
   </si>
   <si>
-    <t>2009-03-20</t>
-  </si>
-  <si>
     <t>ONPL09</t>
   </si>
   <si>
@@ -4591,12 +4591,12 @@
     <t>Philippines Flash Appeal (Revised) (October 2009 - March 2010)</t>
   </si>
   <si>
+    <t>2009-10-03</t>
+  </si>
+  <si>
     <t>2010-03-31</t>
   </si>
   <si>
-    <t>2009-10-03</t>
-  </si>
-  <si>
     <t>CSOM09</t>
   </si>
   <si>
@@ -4621,12 +4621,12 @@
     <t>Syria Drought Response Plan (Revised) (July 2009 - June 2010)</t>
   </si>
   <si>
+    <t>2009-07-15</t>
+  </si>
+  <si>
     <t>2010-06-14</t>
   </si>
   <si>
-    <t>2009-07-15</t>
-  </si>
-  <si>
     <t>OTJK09</t>
   </si>
   <si>
@@ -4684,27 +4684,27 @@
     <t>Afghanistan Joint Appeal 2008: Humanitarian Consequences of Rise in Food Prices (February - June 2008)</t>
   </si>
   <si>
+    <t>2008-02-01</t>
+  </si>
+  <si>
+    <t>2008-06-30</t>
+  </si>
+  <si>
     <t>2008</t>
   </si>
   <si>
-    <t>2008-06-30</t>
-  </si>
-  <si>
-    <t>2008-02-01</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
     <t>Afghanistan Joint Emergency Appeal 2008: High Food Price and Drought Crisis (July 2008 - June 2009)</t>
   </si>
   <si>
+    <t>2008-07-01</t>
+  </si>
+  <si>
     <t>2009-06-30</t>
   </si>
   <si>
-    <t>2008-07-01</t>
-  </si>
-  <si>
     <t>FBOL08</t>
   </si>
   <si>
@@ -4720,12 +4720,12 @@
     <t>Central African Republic 2008</t>
   </si>
   <si>
+    <t>2008-01-01</t>
+  </si>
+  <si>
     <t>2008-12-31</t>
   </si>
   <si>
-    <t>2008-01-01</t>
-  </si>
-  <si>
     <t>CTCD08</t>
   </si>
   <si>
@@ -4756,24 +4756,24 @@
     <t>Djibouti Joint Appeal 2008: Response Plan for Drought, Food and Nutrition Crisis</t>
   </si>
   <si>
+    <t>2008-08-01</t>
+  </si>
+  <si>
     <t>2009-02-28</t>
   </si>
   <si>
-    <t>2008-08-01</t>
-  </si>
-  <si>
     <t>FGEO0809</t>
   </si>
   <si>
     <t>Georgia Crisis Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2008-08-09</t>
+  </si>
+  <si>
     <t>2009-02-09</t>
   </si>
   <si>
-    <t>2008-08-09</t>
-  </si>
-  <si>
     <t>FHTI0809</t>
   </si>
   <si>
@@ -4789,12 +4789,12 @@
     <t>Honduras Flash Appeal (Updated) (November - April) 2008</t>
   </si>
   <si>
+    <t>2008-11-01</t>
+  </si>
+  <si>
     <t>2009-04-30</t>
   </si>
   <si>
-    <t>2008-11-01</t>
-  </si>
-  <si>
     <t>CIRQ08</t>
   </si>
   <si>
@@ -4813,12 +4813,12 @@
     <t>Kyrgyzstan Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2008-12-01</t>
+  </si>
+  <si>
     <t>2009-05-31</t>
   </si>
   <si>
-    <t>2008-12-01</t>
-  </si>
-  <si>
     <t>OLAO0809</t>
   </si>
   <si>
@@ -4849,12 +4849,12 @@
     <t>Myanmar Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2008-05-01</t>
+  </si>
+  <si>
     <t>2008-11-30</t>
   </si>
   <si>
-    <t>2008-05-01</t>
-  </si>
-  <si>
     <t>ONPL08</t>
   </si>
   <si>
@@ -4951,39 +4951,39 @@
     <t>Bolivia Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-02-22</t>
+  </si>
+  <si>
+    <t>2007-08-21</t>
+  </si>
+  <si>
     <t>2007</t>
   </si>
   <si>
-    <t>2007-08-21</t>
-  </si>
-  <si>
-    <t>2007-02-22</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
     <t>Burkina Faso Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-11-01</t>
+  </si>
+  <si>
     <t>2008-01-31</t>
   </si>
   <si>
-    <t>2007-11-01</t>
-  </si>
-  <si>
     <t>CBDI07</t>
   </si>
   <si>
     <t>Burundi 2007</t>
   </si>
   <si>
+    <t>2007-01-01</t>
+  </si>
+  <si>
     <t>2007-12-31</t>
   </si>
   <si>
-    <t>2007-01-01</t>
-  </si>
-  <si>
     <t>CCAF07</t>
   </si>
   <si>
@@ -5023,12 +5023,12 @@
     <t>Ghana Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-09-01</t>
+  </si>
+  <si>
     <t>2008-03-31</t>
   </si>
   <si>
-    <t>2007-09-01</t>
-  </si>
-  <si>
     <t>CXGLR07</t>
   </si>
   <si>
@@ -5050,36 +5050,36 @@
     <t>Korea DPR Flash Appeal: Floods Emergency 2007</t>
   </si>
   <si>
+    <t>2007-08-28</t>
+  </si>
+  <si>
     <t>2007-11-30</t>
   </si>
   <si>
-    <t>2007-08-28</t>
-  </si>
-  <si>
     <t>OLBN07</t>
   </si>
   <si>
     <t>Lebanon Crisis Appeal 2007</t>
   </si>
   <si>
+    <t>2007-06-04</t>
+  </si>
+  <si>
     <t>2007-09-03</t>
   </si>
   <si>
-    <t>2007-06-04</t>
-  </si>
-  <si>
     <t>FLSO0708</t>
   </si>
   <si>
     <t>Lesotho Drought Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-07-28</t>
+  </si>
+  <si>
     <t>2008-01-28</t>
   </si>
   <si>
-    <t>2007-07-28</t>
-  </si>
-  <si>
     <t>CLBR07</t>
   </si>
   <si>
@@ -5092,24 +5092,24 @@
     <t>Madagascar Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-03-15</t>
+  </si>
+  <si>
     <t>2007-09-15</t>
   </si>
   <si>
-    <t>2007-03-15</t>
-  </si>
-  <si>
     <t>FMOZ07</t>
   </si>
   <si>
     <t>Mozambique Floods and Cyclone Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-03-01</t>
+  </si>
+  <si>
     <t>2007-06-30</t>
   </si>
   <si>
-    <t>2007-03-01</t>
-  </si>
-  <si>
     <t>ONPL07</t>
   </si>
   <si>
@@ -5122,12 +5122,12 @@
     <t>Nicaragua Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-09-07</t>
+  </si>
+  <si>
     <t>2008-02-28</t>
   </si>
   <si>
-    <t>2007-09-07</t>
-  </si>
-  <si>
     <t>ORUS07</t>
   </si>
   <si>
@@ -5140,12 +5140,12 @@
     <t>Pakistan Cyclone and Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-07-15</t>
+  </si>
+  <si>
     <t>2007-10-31</t>
   </si>
   <si>
-    <t>2007-07-15</t>
-  </si>
-  <si>
     <t>FPER0708</t>
   </si>
   <si>
@@ -5203,12 +5203,12 @@
     <t>Swaziland Drought Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-07-20</t>
+  </si>
+  <si>
     <t>2008-01-20</t>
   </si>
   <si>
-    <t>2007-07-20</t>
-  </si>
-  <si>
     <t>CTLS07</t>
   </si>
   <si>
@@ -5257,15 +5257,15 @@
     <t>Afghanistan Drought Joint Appeal 2006</t>
   </si>
   <si>
+    <t>2006-07-01</t>
+  </si>
+  <si>
+    <t>2006-12-31</t>
+  </si>
+  <si>
     <t>2006</t>
   </si>
   <si>
-    <t>2006-12-31</t>
-  </si>
-  <si>
-    <t>2006-07-01</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -5311,24 +5311,24 @@
     <t>Ethiopia Floods Joint Appeal 2006</t>
   </si>
   <si>
+    <t>2006-08-25</t>
+  </si>
+  <si>
     <t>2006-11-25</t>
   </si>
   <si>
-    <t>2006-08-25</t>
-  </si>
-  <si>
     <t>OETH0607</t>
   </si>
   <si>
     <t>Ethiopia: 2006 Govt-UN Joint Emergency Flood Appeal for Somali Region</t>
   </si>
   <si>
+    <t>2006-11-23</t>
+  </si>
+  <si>
     <t>2007-01-22</t>
   </si>
   <si>
-    <t>2006-11-23</t>
-  </si>
-  <si>
     <t>CXGLR06</t>
   </si>
   <si>
@@ -5347,12 +5347,12 @@
     <t>Guinea-Bissau 2006</t>
   </si>
   <si>
+    <t>2006-05-01</t>
+  </si>
+  <si>
     <t>2006-11-30</t>
   </si>
   <si>
-    <t>2006-05-01</t>
-  </si>
-  <si>
     <t>CXHAF06</t>
   </si>
   <si>
@@ -5371,12 +5371,12 @@
     <t>Kenya 2006</t>
   </si>
   <si>
+    <t>2006-10-16</t>
+  </si>
+  <si>
     <t>2007-04-15</t>
   </si>
   <si>
-    <t>2006-10-16</t>
-  </si>
-  <si>
     <t>FKEN06</t>
   </si>
   <si>
@@ -5392,12 +5392,12 @@
     <t>Lebanon Crisis 2006</t>
   </si>
   <si>
+    <t>2006-07-24</t>
+  </si>
+  <si>
     <t>2006-10-23</t>
   </si>
   <si>
-    <t>2006-07-24</t>
-  </si>
-  <si>
     <t>CLBR06</t>
   </si>
   <si>
@@ -5446,12 +5446,12 @@
     <t>Somalia: 2006 Flood Response Plan</t>
   </si>
   <si>
+    <t>2006-12-05</t>
+  </si>
+  <si>
     <t>2007-03-05</t>
   </si>
   <si>
-    <t>2006-12-05</t>
-  </si>
-  <si>
     <t>OLKA06</t>
   </si>
   <si>
@@ -5512,39 +5512,39 @@
     <t>Angola Marburg VHF 2005</t>
   </si>
   <si>
+    <t>2005-04-01</t>
+  </si>
+  <si>
+    <t>2005-06-30</t>
+  </si>
+  <si>
     <t>2005</t>
   </si>
   <si>
-    <t>2005-06-30</t>
-  </si>
-  <si>
-    <t>2005-04-01</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
     <t>Benin 2005</t>
   </si>
   <si>
+    <t>2005-05-01</t>
+  </si>
+  <si>
     <t>2005-10-31</t>
   </si>
   <si>
-    <t>2005-05-01</t>
-  </si>
-  <si>
     <t>CBDI05</t>
   </si>
   <si>
     <t>Burundi 2005</t>
   </si>
   <si>
+    <t>2005-01-01</t>
+  </si>
+  <si>
     <t>2005-12-31</t>
   </si>
   <si>
-    <t>2005-01-01</t>
-  </si>
-  <si>
     <t>CCAF05</t>
   </si>
   <si>
@@ -5620,12 +5620,12 @@
     <t>Guyana 2005</t>
   </si>
   <si>
+    <t>2005-02-01</t>
+  </si>
+  <si>
     <t>2005-08-01</t>
   </si>
   <si>
-    <t>2005-02-01</t>
-  </si>
-  <si>
     <t>FXINDTSU05</t>
   </si>
   <si>
@@ -5647,12 +5647,12 @@
     <t>Niger 2005</t>
   </si>
   <si>
+    <t>2005-06-01</t>
+  </si>
+  <si>
     <t>2005-09-30</t>
   </si>
   <si>
-    <t>2005-06-01</t>
-  </si>
-  <si>
     <t>CCOG05</t>
   </si>
   <si>
@@ -5671,12 +5671,12 @@
     <t>South Asia Earthquake 2005</t>
   </si>
   <si>
+    <t>2005-10-11</t>
+  </si>
+  <si>
     <t>2006-04-10</t>
   </si>
   <si>
-    <t>2005-10-11</t>
-  </si>
-  <si>
     <t>CSDN05</t>
   </si>
   <si>
@@ -5701,12 +5701,12 @@
     <t>West and Central Africa Region Cholera 2005</t>
   </si>
   <si>
+    <t>2005-11-01</t>
+  </si>
+  <si>
     <t>2006-05-31</t>
   </si>
   <si>
-    <t>2005-11-01</t>
-  </si>
-  <si>
     <t>CPSE05</t>
   </si>
   <si>
@@ -5719,15 +5719,15 @@
     <t>Afghanistan UN-Government Drought Appeal 2004</t>
   </si>
   <si>
+    <t>2004-09-01</t>
+  </si>
+  <si>
+    <t>2004-12-31</t>
+  </si>
+  <si>
     <t>2004</t>
   </si>
   <si>
-    <t>2004-12-31</t>
-  </si>
-  <si>
-    <t>2004-09-01</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -5743,24 +5743,24 @@
     <t>Bangladesh 2004</t>
   </si>
   <si>
+    <t>2004-08-01</t>
+  </si>
+  <si>
     <t>2005-01-31</t>
   </si>
   <si>
-    <t>2004-08-01</t>
-  </si>
-  <si>
     <t>FBOL0405</t>
   </si>
   <si>
     <t>Bolivia 2004</t>
   </si>
   <si>
+    <t>2004-11-01</t>
+  </si>
+  <si>
     <t>2005-05-31</t>
   </si>
   <si>
-    <t>2004-11-01</t>
-  </si>
-  <si>
     <t>CBDI04</t>
   </si>
   <si>
@@ -5887,24 +5887,24 @@
     <t>Madagascar 2004</t>
   </si>
   <si>
+    <t>2004-03-19</t>
+  </si>
+  <si>
     <t>2004-06-19</t>
   </si>
   <si>
-    <t>2004-03-19</t>
-  </si>
-  <si>
     <t>FPHL0405</t>
   </si>
   <si>
     <t>Philippines 2004</t>
   </si>
   <si>
+    <t>2004-12-15</t>
+  </si>
+  <si>
     <t>2005-03-15</t>
   </si>
   <si>
-    <t>2004-12-15</t>
-  </si>
-  <si>
     <t>CSLE04</t>
   </si>
   <si>
@@ -5965,15 +5965,15 @@
     <t>Afghanistan TAPA 2003</t>
   </si>
   <si>
+    <t>2003-01-01</t>
+  </si>
+  <si>
+    <t>2003-12-31</t>
+  </si>
+  <si>
     <t>2003</t>
   </si>
   <si>
-    <t>2003-12-31</t>
-  </si>
-  <si>
-    <t>2003-01-01</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -5992,12 +5992,12 @@
     <t>Central African Republic 2003</t>
   </si>
   <si>
+    <t>2003-04-01</t>
+  </si>
+  <si>
     <t>2003-06-30</t>
   </si>
   <si>
-    <t>2003-04-01</t>
-  </si>
-  <si>
     <t>CRUS03</t>
   </si>
   <si>
@@ -6022,12 +6022,12 @@
     <t>Côte d'Ivoire and the West Africa Sub-Region 2002-2003</t>
   </si>
   <si>
+    <t>2002-11-01</t>
+  </si>
+  <si>
     <t>2003-01-31</t>
   </si>
   <si>
-    <t>2002-11-01</t>
-  </si>
-  <si>
     <t>CPRK03</t>
   </si>
   <si>
@@ -6064,24 +6064,24 @@
     <t>Haiti (PIR) 2003</t>
   </si>
   <si>
+    <t>2003-03-01</t>
+  </si>
+  <si>
     <t>2003-08-31</t>
   </si>
   <si>
-    <t>2003-03-01</t>
-  </si>
-  <si>
     <t>CLSO0304</t>
   </si>
   <si>
     <t>Humanitarian Crisis in Southern Africa - LESOTHO (July 2003 - June 2004)</t>
   </si>
   <si>
+    <t>2003-07-01</t>
+  </si>
+  <si>
     <t>2004-06-30</t>
   </si>
   <si>
-    <t>2003-07-01</t>
-  </si>
-  <si>
     <t>CMWI03</t>
   </si>
   <si>
@@ -6184,15 +6184,15 @@
     <t>Afghanistan 2002 (ITAP for the Afghan People)</t>
   </si>
   <si>
+    <t>2001-10-01</t>
+  </si>
+  <si>
+    <t>2002-12-31</t>
+  </si>
+  <si>
     <t>2002</t>
   </si>
   <si>
-    <t>2002-12-31</t>
-  </si>
-  <si>
-    <t>2001-10-01</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -6370,15 +6370,15 @@
     <t>Afghanistan 2001</t>
   </si>
   <si>
+    <t>2001-01-01</t>
+  </si>
+  <si>
+    <t>2001-09-30</t>
+  </si>
+  <si>
     <t>2001</t>
   </si>
   <si>
-    <t>2001-09-30</t>
-  </si>
-  <si>
-    <t>2001-01-01</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -6520,15 +6520,15 @@
     <t>Angola 2000</t>
   </si>
   <si>
+    <t>2000-01-01</t>
+  </si>
+  <si>
+    <t>2000-12-31</t>
+  </si>
+  <si>
     <t>2000</t>
   </si>
   <si>
-    <t>2000-12-31</t>
-  </si>
-  <si>
-    <t>2000-01-01</t>
-  </si>
-  <si>
     <t>CBDI00</t>
   </si>
   <si>
@@ -6616,10 +6616,10 @@
     <t>East Timor 1999</t>
   </si>
   <si>
+    <t>1999-10-01</t>
+  </si>
+  <si>
     <t>1999</t>
-  </si>
-  <si>
-    <t>1999-10-01</t>
   </si>
   <si>
     <t>CRUS9900</t>
@@ -7417,13 +7417,13 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="E20" t="s">
         <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -7739,13 +7739,13 @@
         <v>9</v>
       </c>
       <c r="D34" t="s">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="E34" t="s">
         <v>11</v>
       </c>
       <c r="F34" t="s">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="G34" t="s">
         <v>34</v>
@@ -8061,13 +8061,13 @@
         <v>9</v>
       </c>
       <c r="D48" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E48" t="s">
         <v>114</v>
       </c>
       <c r="F48" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G48" t="s">
         <v>20</v>
@@ -8107,13 +8107,13 @@
         <v>9</v>
       </c>
       <c r="D50" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E50" t="s">
         <v>114</v>
       </c>
       <c r="F50" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G50" t="s">
         <v>20</v>
@@ -8268,13 +8268,13 @@
         <v>9</v>
       </c>
       <c r="D57" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="E57" t="s">
         <v>114</v>
       </c>
       <c r="F57" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="G57" t="s">
         <v>34</v>
@@ -8360,13 +8360,13 @@
         <v>9</v>
       </c>
       <c r="D61" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="E61" t="s">
         <v>114</v>
       </c>
       <c r="F61" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="G61" t="s">
         <v>20</v>
@@ -8383,13 +8383,13 @@
         <v>9</v>
       </c>
       <c r="D62" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="E62" t="s">
         <v>114</v>
       </c>
       <c r="F62" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="G62" t="s">
         <v>34</v>
@@ -8452,13 +8452,13 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>113</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
         <v>114</v>
       </c>
       <c r="F65" t="s">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="G65" t="s">
         <v>34</v>
@@ -8498,13 +8498,13 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="E67" t="s">
         <v>157</v>
       </c>
       <c r="F67" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="G67" t="s">
         <v>20</v>
@@ -8521,13 +8521,13 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="E68" t="s">
         <v>114</v>
       </c>
       <c r="F68" t="s">
-        <v>168</v>
+        <v>115</v>
       </c>
       <c r="G68" t="s">
         <v>34</v>
@@ -8590,13 +8590,13 @@
         <v>9</v>
       </c>
       <c r="D71" t="s">
-        <v>113</v>
+        <v>175</v>
       </c>
       <c r="E71" t="s">
         <v>114</v>
       </c>
       <c r="F71" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
       <c r="G71" t="s">
         <v>20</v>
@@ -8659,13 +8659,13 @@
         <v>9</v>
       </c>
       <c r="D74" t="s">
-        <v>113</v>
+        <v>182</v>
       </c>
       <c r="E74" t="s">
         <v>114</v>
       </c>
       <c r="F74" t="s">
-        <v>182</v>
+        <v>115</v>
       </c>
       <c r="G74" t="s">
         <v>20</v>
@@ -8797,13 +8797,13 @@
         <v>9</v>
       </c>
       <c r="D80" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="E80" t="s">
         <v>114</v>
       </c>
       <c r="F80" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="G80" t="s">
         <v>34</v>
@@ -9096,13 +9096,13 @@
         <v>9</v>
       </c>
       <c r="D93" t="s">
-        <v>113</v>
+        <v>222</v>
       </c>
       <c r="E93" t="s">
         <v>114</v>
       </c>
       <c r="F93" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="G93" t="s">
         <v>20</v>
@@ -9142,13 +9142,13 @@
         <v>9</v>
       </c>
       <c r="D95" t="s">
-        <v>113</v>
+        <v>227</v>
       </c>
       <c r="E95" t="s">
         <v>114</v>
       </c>
       <c r="F95" t="s">
-        <v>227</v>
+        <v>115</v>
       </c>
       <c r="G95" t="s">
         <v>34</v>
@@ -9165,13 +9165,13 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>113</v>
+        <v>227</v>
       </c>
       <c r="E96" t="s">
         <v>114</v>
       </c>
       <c r="F96" t="s">
-        <v>227</v>
+        <v>115</v>
       </c>
       <c r="G96" t="s">
         <v>34</v>
@@ -9372,13 +9372,13 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="E105" t="s">
         <v>233</v>
       </c>
       <c r="F105" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="G105" t="s">
         <v>34</v>
@@ -9556,13 +9556,13 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="E113" t="s">
         <v>233</v>
       </c>
       <c r="F113" t="s">
-        <v>268</v>
+        <v>234</v>
       </c>
       <c r="G113" t="s">
         <v>34</v>
@@ -9625,13 +9625,13 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="E116" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F116" t="s">
-        <v>276</v>
+        <v>234</v>
       </c>
       <c r="G116" t="s">
         <v>20</v>
@@ -9648,13 +9648,13 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>232</v>
+        <v>279</v>
       </c>
       <c r="E117" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F117" t="s">
-        <v>280</v>
+        <v>234</v>
       </c>
       <c r="G117" t="s">
         <v>20</v>
@@ -9766,7 +9766,7 @@
         <v>232</v>
       </c>
       <c r="E122" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F122" t="s">
         <v>234</v>
@@ -9789,7 +9789,7 @@
         <v>232</v>
       </c>
       <c r="E123" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F123" t="s">
         <v>234</v>
@@ -9993,13 +9993,13 @@
         <v>9</v>
       </c>
       <c r="D132" t="s">
-        <v>232</v>
+        <v>310</v>
       </c>
       <c r="E132" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F132" t="s">
-        <v>311</v>
+        <v>234</v>
       </c>
       <c r="G132" t="s">
         <v>16</v>
@@ -10039,13 +10039,13 @@
         <v>9</v>
       </c>
       <c r="D134" t="s">
-        <v>232</v>
+        <v>316</v>
       </c>
       <c r="E134" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F134" t="s">
-        <v>316</v>
+        <v>234</v>
       </c>
       <c r="G134" t="s">
         <v>34</v>
@@ -10085,13 +10085,13 @@
         <v>9</v>
       </c>
       <c r="D136" t="s">
-        <v>232</v>
+        <v>321</v>
       </c>
       <c r="E136" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F136" t="s">
-        <v>321</v>
+        <v>234</v>
       </c>
       <c r="G136" t="s">
         <v>34</v>
@@ -10430,13 +10430,13 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="E151" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F151" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="G151" t="s">
         <v>20</v>
@@ -10545,13 +10545,13 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="E156" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F156" t="s">
-        <v>368</v>
+        <v>340</v>
       </c>
       <c r="G156" t="s">
         <v>34</v>
@@ -10568,13 +10568,13 @@
         <v>185</v>
       </c>
       <c r="D157" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="E157" t="s">
         <v>339</v>
       </c>
       <c r="F157" t="s">
-        <v>368</v>
+        <v>340</v>
       </c>
       <c r="G157" t="s">
         <v>34</v>
@@ -10752,13 +10752,13 @@
         <v>9</v>
       </c>
       <c r="D165" t="s">
-        <v>338</v>
+        <v>388</v>
       </c>
       <c r="E165" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F165" t="s">
-        <v>389</v>
+        <v>340</v>
       </c>
       <c r="G165" t="s">
         <v>34</v>
@@ -10798,13 +10798,13 @@
         <v>9</v>
       </c>
       <c r="D167" t="s">
-        <v>338</v>
+        <v>394</v>
       </c>
       <c r="E167" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F167" t="s">
-        <v>395</v>
+        <v>340</v>
       </c>
       <c r="G167" t="s">
         <v>34</v>
@@ -10936,13 +10936,13 @@
         <v>9</v>
       </c>
       <c r="D173" t="s">
-        <v>338</v>
+        <v>408</v>
       </c>
       <c r="E173" t="s">
         <v>339</v>
       </c>
       <c r="F173" t="s">
-        <v>408</v>
+        <v>340</v>
       </c>
       <c r="G173" t="s">
         <v>20</v>
@@ -10959,13 +10959,13 @@
         <v>185</v>
       </c>
       <c r="D174" t="s">
-        <v>338</v>
+        <v>408</v>
       </c>
       <c r="E174" t="s">
         <v>410</v>
       </c>
       <c r="F174" t="s">
-        <v>408</v>
+        <v>340</v>
       </c>
       <c r="G174" t="s">
         <v>20</v>
@@ -10982,13 +10982,13 @@
         <v>9</v>
       </c>
       <c r="D175" t="s">
-        <v>338</v>
+        <v>413</v>
       </c>
       <c r="E175" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F175" t="s">
-        <v>414</v>
+        <v>340</v>
       </c>
       <c r="G175" t="s">
         <v>20</v>
@@ -11166,13 +11166,13 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>338</v>
+        <v>431</v>
       </c>
       <c r="E183" t="s">
         <v>339</v>
       </c>
       <c r="F183" t="s">
-        <v>431</v>
+        <v>340</v>
       </c>
       <c r="G183" t="s">
         <v>20</v>
@@ -11281,13 +11281,13 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>338</v>
+        <v>442</v>
       </c>
       <c r="E188" t="s">
         <v>339</v>
       </c>
       <c r="F188" t="s">
-        <v>442</v>
+        <v>340</v>
       </c>
       <c r="G188" t="s">
         <v>34</v>
@@ -11327,13 +11327,13 @@
         <v>9</v>
       </c>
       <c r="D190" t="s">
-        <v>338</v>
+        <v>442</v>
       </c>
       <c r="E190" t="s">
         <v>447</v>
       </c>
       <c r="F190" t="s">
-        <v>442</v>
+        <v>340</v>
       </c>
       <c r="G190" t="s">
         <v>16</v>
@@ -11419,13 +11419,13 @@
         <v>9</v>
       </c>
       <c r="D194" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E194" t="s">
         <v>455</v>
       </c>
       <c r="F194" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G194" t="s">
         <v>25</v>
@@ -11442,13 +11442,13 @@
         <v>9</v>
       </c>
       <c r="D195" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E195" t="s">
         <v>455</v>
       </c>
       <c r="F195" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G195" t="s">
         <v>16</v>
@@ -11465,13 +11465,13 @@
         <v>9</v>
       </c>
       <c r="D196" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E196" t="s">
         <v>455</v>
       </c>
       <c r="F196" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G196" t="s">
         <v>25</v>
@@ -11488,13 +11488,13 @@
         <v>9</v>
       </c>
       <c r="D197" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E197" t="s">
         <v>455</v>
       </c>
       <c r="F197" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G197" t="s">
         <v>25</v>
@@ -11511,13 +11511,13 @@
         <v>9</v>
       </c>
       <c r="D198" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E198" t="s">
         <v>455</v>
       </c>
       <c r="F198" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G198" t="s">
         <v>16</v>
@@ -11534,13 +11534,13 @@
         <v>9</v>
       </c>
       <c r="D199" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E199" t="s">
         <v>455</v>
       </c>
       <c r="F199" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G199" t="s">
         <v>25</v>
@@ -11557,13 +11557,13 @@
         <v>9</v>
       </c>
       <c r="D200" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E200" t="s">
         <v>455</v>
       </c>
       <c r="F200" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G200" t="s">
         <v>25</v>
@@ -11580,13 +11580,13 @@
         <v>9</v>
       </c>
       <c r="D201" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E201" t="s">
         <v>455</v>
       </c>
       <c r="F201" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G201" t="s">
         <v>25</v>
@@ -11603,13 +11603,13 @@
         <v>9</v>
       </c>
       <c r="D202" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E202" t="s">
         <v>455</v>
       </c>
       <c r="F202" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G202" t="s">
         <v>25</v>
@@ -11626,13 +11626,13 @@
         <v>9</v>
       </c>
       <c r="D203" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E203" t="s">
         <v>455</v>
       </c>
       <c r="F203" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G203" t="s">
         <v>25</v>
@@ -11649,13 +11649,13 @@
         <v>9</v>
       </c>
       <c r="D204" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E204" t="s">
         <v>455</v>
       </c>
       <c r="F204" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G204" t="s">
         <v>16</v>
@@ -11672,13 +11672,13 @@
         <v>9</v>
       </c>
       <c r="D205" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="E205" t="s">
         <v>455</v>
       </c>
       <c r="F205" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G205" t="s">
         <v>25</v>
@@ -11695,13 +11695,13 @@
         <v>185</v>
       </c>
       <c r="D206" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="E206" t="s">
         <v>339</v>
       </c>
       <c r="F206" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G206" t="s">
         <v>25</v>
@@ -11718,13 +11718,13 @@
         <v>9</v>
       </c>
       <c r="D207" t="s">
-        <v>454</v>
+        <v>487</v>
       </c>
       <c r="E207" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F207" t="s">
-        <v>488</v>
+        <v>456</v>
       </c>
       <c r="G207" t="s">
         <v>34</v>
@@ -11741,13 +11741,13 @@
         <v>9</v>
       </c>
       <c r="D208" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E208" t="s">
         <v>455</v>
       </c>
       <c r="F208" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G208" t="s">
         <v>25</v>
@@ -11764,13 +11764,13 @@
         <v>9</v>
       </c>
       <c r="D209" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="E209" t="s">
         <v>455</v>
       </c>
       <c r="F209" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G209" t="s">
         <v>25</v>
@@ -11787,13 +11787,13 @@
         <v>185</v>
       </c>
       <c r="D210" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="E210" t="s">
         <v>339</v>
       </c>
       <c r="F210" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G210" t="s">
         <v>25</v>
@@ -11810,13 +11810,13 @@
         <v>9</v>
       </c>
       <c r="D211" t="s">
-        <v>454</v>
+        <v>497</v>
       </c>
       <c r="E211" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F211" t="s">
-        <v>498</v>
+        <v>456</v>
       </c>
       <c r="G211" t="s">
         <v>34</v>
@@ -11833,13 +11833,13 @@
         <v>9</v>
       </c>
       <c r="D212" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E212" t="s">
         <v>455</v>
       </c>
       <c r="F212" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G212" t="s">
         <v>25</v>
@@ -11856,13 +11856,13 @@
         <v>9</v>
       </c>
       <c r="D213" t="s">
-        <v>454</v>
+        <v>503</v>
       </c>
       <c r="E213" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F213" t="s">
-        <v>504</v>
+        <v>456</v>
       </c>
       <c r="G213" t="s">
         <v>34</v>
@@ -11879,13 +11879,13 @@
         <v>9</v>
       </c>
       <c r="D214" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="E214" t="s">
         <v>455</v>
       </c>
       <c r="F214" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G214" t="s">
         <v>25</v>
@@ -11902,13 +11902,13 @@
         <v>185</v>
       </c>
       <c r="D215" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="E215" t="s">
         <v>339</v>
       </c>
       <c r="F215" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G215" t="s">
         <v>25</v>
@@ -11925,13 +11925,13 @@
         <v>9</v>
       </c>
       <c r="D216" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E216" t="s">
         <v>455</v>
       </c>
       <c r="F216" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G216" t="s">
         <v>25</v>
@@ -11948,13 +11948,13 @@
         <v>9</v>
       </c>
       <c r="D217" t="s">
-        <v>454</v>
+        <v>513</v>
       </c>
       <c r="E217" t="s">
         <v>455</v>
       </c>
       <c r="F217" t="s">
-        <v>513</v>
+        <v>456</v>
       </c>
       <c r="G217" t="s">
         <v>34</v>
@@ -11971,13 +11971,13 @@
         <v>9</v>
       </c>
       <c r="D218" t="s">
-        <v>454</v>
+        <v>516</v>
       </c>
       <c r="E218" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F218" t="s">
-        <v>517</v>
+        <v>456</v>
       </c>
       <c r="G218" t="s">
         <v>20</v>
@@ -11994,13 +11994,13 @@
         <v>9</v>
       </c>
       <c r="D219" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E219" t="s">
         <v>455</v>
       </c>
       <c r="F219" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G219" t="s">
         <v>25</v>
@@ -12017,13 +12017,13 @@
         <v>185</v>
       </c>
       <c r="D220" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E220" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F220" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G220" t="s">
         <v>34</v>
@@ -12040,13 +12040,13 @@
         <v>9</v>
       </c>
       <c r="D221" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E221" t="s">
         <v>455</v>
       </c>
       <c r="F221" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G221" t="s">
         <v>34</v>
@@ -12063,13 +12063,13 @@
         <v>9</v>
       </c>
       <c r="D222" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E222" t="s">
         <v>455</v>
       </c>
       <c r="F222" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G222" t="s">
         <v>25</v>
@@ -12086,13 +12086,13 @@
         <v>9</v>
       </c>
       <c r="D223" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E223" t="s">
         <v>455</v>
       </c>
       <c r="F223" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G223" t="s">
         <v>25</v>
@@ -12109,13 +12109,13 @@
         <v>9</v>
       </c>
       <c r="D224" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E224" t="s">
         <v>455</v>
       </c>
       <c r="F224" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G224" t="s">
         <v>25</v>
@@ -12132,13 +12132,13 @@
         <v>9</v>
       </c>
       <c r="D225" t="s">
-        <v>454</v>
+        <v>532</v>
       </c>
       <c r="E225" t="s">
         <v>455</v>
       </c>
       <c r="F225" t="s">
-        <v>532</v>
+        <v>456</v>
       </c>
       <c r="G225" t="s">
         <v>20</v>
@@ -12155,13 +12155,13 @@
         <v>9</v>
       </c>
       <c r="D226" t="s">
-        <v>454</v>
+        <v>535</v>
       </c>
       <c r="E226" t="s">
         <v>455</v>
       </c>
       <c r="F226" t="s">
-        <v>535</v>
+        <v>456</v>
       </c>
       <c r="G226" t="s">
         <v>20</v>
@@ -12178,13 +12178,13 @@
         <v>9</v>
       </c>
       <c r="D227" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E227" t="s">
         <v>455</v>
       </c>
       <c r="F227" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G227" t="s">
         <v>25</v>
@@ -12201,13 +12201,13 @@
         <v>9</v>
       </c>
       <c r="D228" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E228" t="s">
         <v>455</v>
       </c>
       <c r="F228" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G228" t="s">
         <v>25</v>
@@ -12224,13 +12224,13 @@
         <v>9</v>
       </c>
       <c r="D229" t="s">
-        <v>454</v>
+        <v>535</v>
       </c>
       <c r="E229" t="s">
         <v>455</v>
       </c>
       <c r="F229" t="s">
-        <v>535</v>
+        <v>456</v>
       </c>
       <c r="G229" t="s">
         <v>34</v>
@@ -12247,13 +12247,13 @@
         <v>185</v>
       </c>
       <c r="D230" t="s">
-        <v>454</v>
+        <v>535</v>
       </c>
       <c r="E230" t="s">
         <v>455</v>
       </c>
       <c r="F230" t="s">
-        <v>535</v>
+        <v>456</v>
       </c>
       <c r="G230" t="s">
         <v>20</v>
@@ -12270,13 +12270,13 @@
         <v>9</v>
       </c>
       <c r="D231" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E231" t="s">
         <v>455</v>
       </c>
       <c r="F231" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G231" t="s">
         <v>25</v>
@@ -12293,13 +12293,13 @@
         <v>9</v>
       </c>
       <c r="D232" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E232" t="s">
         <v>455</v>
       </c>
       <c r="F232" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G232" t="s">
         <v>25</v>
@@ -12316,13 +12316,13 @@
         <v>9</v>
       </c>
       <c r="D233" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E233" t="s">
         <v>455</v>
       </c>
       <c r="F233" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G233" t="s">
         <v>16</v>
@@ -12339,13 +12339,13 @@
         <v>9</v>
       </c>
       <c r="D234" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E234" t="s">
         <v>455</v>
       </c>
       <c r="F234" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G234" t="s">
         <v>16</v>
@@ -12362,13 +12362,13 @@
         <v>9</v>
       </c>
       <c r="D235" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E235" t="s">
         <v>455</v>
       </c>
       <c r="F235" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G235" t="s">
         <v>25</v>
@@ -12385,13 +12385,13 @@
         <v>9</v>
       </c>
       <c r="D236" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E236" t="s">
         <v>455</v>
       </c>
       <c r="F236" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G236" t="s">
         <v>25</v>
@@ -12408,13 +12408,13 @@
         <v>9</v>
       </c>
       <c r="D237" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E237" t="s">
         <v>455</v>
       </c>
       <c r="F237" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G237" t="s">
         <v>16</v>
@@ -12431,13 +12431,13 @@
         <v>9</v>
       </c>
       <c r="D238" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E238" t="s">
         <v>455</v>
       </c>
       <c r="F238" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G238" t="s">
         <v>25</v>
@@ -12454,13 +12454,13 @@
         <v>9</v>
       </c>
       <c r="D239" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E239" t="s">
         <v>455</v>
       </c>
       <c r="F239" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G239" t="s">
         <v>25</v>
@@ -12477,13 +12477,13 @@
         <v>9</v>
       </c>
       <c r="D240" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E240" t="s">
         <v>455</v>
       </c>
       <c r="F240" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G240" t="s">
         <v>16</v>
@@ -12500,13 +12500,13 @@
         <v>9</v>
       </c>
       <c r="D241" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E241" t="s">
         <v>455</v>
       </c>
       <c r="F241" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G241" t="s">
         <v>25</v>
@@ -12523,13 +12523,13 @@
         <v>9</v>
       </c>
       <c r="D242" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E242" t="s">
         <v>455</v>
       </c>
       <c r="F242" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G242" t="s">
         <v>25</v>
@@ -12546,13 +12546,13 @@
         <v>9</v>
       </c>
       <c r="D243" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E243" t="s">
         <v>455</v>
       </c>
       <c r="F243" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G243" t="s">
         <v>25</v>
@@ -12569,13 +12569,13 @@
         <v>9</v>
       </c>
       <c r="D244" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E244" t="s">
         <v>455</v>
       </c>
       <c r="F244" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G244" t="s">
         <v>25</v>
@@ -12615,13 +12615,13 @@
         <v>9</v>
       </c>
       <c r="D246" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E246" t="s">
         <v>574</v>
       </c>
       <c r="F246" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G246" t="s">
         <v>20</v>
@@ -12661,13 +12661,13 @@
         <v>9</v>
       </c>
       <c r="D248" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E248" t="s">
         <v>574</v>
       </c>
       <c r="F248" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G248" t="s">
         <v>20</v>
@@ -12753,13 +12753,13 @@
         <v>9</v>
       </c>
       <c r="D252" t="s">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="E252" t="s">
         <v>574</v>
       </c>
       <c r="F252" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="G252" t="s">
         <v>20</v>
@@ -12799,13 +12799,13 @@
         <v>9</v>
       </c>
       <c r="D254" t="s">
-        <v>573</v>
+        <v>596</v>
       </c>
       <c r="E254" t="s">
         <v>459</v>
       </c>
       <c r="F254" t="s">
-        <v>596</v>
+        <v>575</v>
       </c>
       <c r="G254" t="s">
         <v>25</v>
@@ -12868,13 +12868,13 @@
         <v>9</v>
       </c>
       <c r="D257" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E257" t="s">
         <v>574</v>
       </c>
       <c r="F257" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G257" t="s">
         <v>20</v>
@@ -12891,13 +12891,13 @@
         <v>9</v>
       </c>
       <c r="D258" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E258" t="s">
         <v>574</v>
       </c>
       <c r="F258" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G258" t="s">
         <v>20</v>
@@ -12914,13 +12914,13 @@
         <v>185</v>
       </c>
       <c r="D259" t="s">
-        <v>573</v>
+        <v>607</v>
       </c>
       <c r="E259" t="s">
         <v>574</v>
       </c>
       <c r="F259" t="s">
-        <v>607</v>
+        <v>575</v>
       </c>
       <c r="G259" t="s">
         <v>25</v>
@@ -12983,13 +12983,13 @@
         <v>9</v>
       </c>
       <c r="D262" t="s">
-        <v>573</v>
+        <v>614</v>
       </c>
       <c r="E262" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F262" t="s">
-        <v>615</v>
+        <v>575</v>
       </c>
       <c r="G262" t="s">
         <v>34</v>
@@ -13006,13 +13006,13 @@
         <v>9</v>
       </c>
       <c r="D263" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E263" t="s">
         <v>574</v>
       </c>
       <c r="F263" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G263" t="s">
         <v>20</v>
@@ -13029,13 +13029,13 @@
         <v>185</v>
       </c>
       <c r="D264" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E264" t="s">
         <v>574</v>
       </c>
       <c r="F264" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G264" t="s">
         <v>20</v>
@@ -13075,13 +13075,13 @@
         <v>9</v>
       </c>
       <c r="D266" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E266" t="s">
         <v>574</v>
       </c>
       <c r="F266" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G266" t="s">
         <v>20</v>
@@ -13121,13 +13121,13 @@
         <v>9</v>
       </c>
       <c r="D268" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E268" t="s">
         <v>574</v>
       </c>
       <c r="F268" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G268" t="s">
         <v>20</v>
@@ -13144,13 +13144,13 @@
         <v>9</v>
       </c>
       <c r="D269" t="s">
-        <v>573</v>
+        <v>607</v>
       </c>
       <c r="E269" t="s">
         <v>574</v>
       </c>
       <c r="F269" t="s">
-        <v>607</v>
+        <v>575</v>
       </c>
       <c r="G269" t="s">
         <v>20</v>
@@ -13167,13 +13167,13 @@
         <v>185</v>
       </c>
       <c r="D270" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E270" t="s">
         <v>574</v>
       </c>
       <c r="F270" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G270" t="s">
         <v>20</v>
@@ -13190,13 +13190,13 @@
         <v>9</v>
       </c>
       <c r="D271" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E271" t="s">
         <v>574</v>
       </c>
       <c r="F271" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G271" t="s">
         <v>20</v>
@@ -13236,13 +13236,13 @@
         <v>9</v>
       </c>
       <c r="D273" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E273" t="s">
         <v>574</v>
       </c>
       <c r="F273" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G273" t="s">
         <v>20</v>
@@ -13282,13 +13282,13 @@
         <v>9</v>
       </c>
       <c r="D275" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E275" t="s">
         <v>574</v>
       </c>
       <c r="F275" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G275" t="s">
         <v>20</v>
@@ -13305,13 +13305,13 @@
         <v>9</v>
       </c>
       <c r="D276" t="s">
-        <v>573</v>
+        <v>644</v>
       </c>
       <c r="E276" t="s">
         <v>574</v>
       </c>
       <c r="F276" t="s">
-        <v>644</v>
+        <v>575</v>
       </c>
       <c r="G276" t="s">
         <v>20</v>
@@ -13328,13 +13328,13 @@
         <v>9</v>
       </c>
       <c r="D277" t="s">
-        <v>573</v>
+        <v>647</v>
       </c>
       <c r="E277" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F277" t="s">
-        <v>648</v>
+        <v>575</v>
       </c>
       <c r="G277" t="s">
         <v>34</v>
@@ -13351,13 +13351,13 @@
         <v>9</v>
       </c>
       <c r="D278" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E278" t="s">
         <v>574</v>
       </c>
       <c r="F278" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G278" t="s">
         <v>20</v>
@@ -13374,13 +13374,13 @@
         <v>9</v>
       </c>
       <c r="D279" t="s">
-        <v>573</v>
+        <v>653</v>
       </c>
       <c r="E279" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F279" t="s">
-        <v>654</v>
+        <v>575</v>
       </c>
       <c r="G279" t="s">
         <v>34</v>
@@ -13397,13 +13397,13 @@
         <v>9</v>
       </c>
       <c r="D280" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E280" t="s">
         <v>574</v>
       </c>
       <c r="F280" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G280" t="s">
         <v>20</v>
@@ -13466,13 +13466,13 @@
         <v>9</v>
       </c>
       <c r="D283" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E283" t="s">
         <v>574</v>
       </c>
       <c r="F283" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G283" t="s">
         <v>20</v>
@@ -13581,13 +13581,13 @@
         <v>9</v>
       </c>
       <c r="D288" t="s">
-        <v>573</v>
+        <v>644</v>
       </c>
       <c r="E288" t="s">
         <v>574</v>
       </c>
       <c r="F288" t="s">
-        <v>644</v>
+        <v>575</v>
       </c>
       <c r="G288" t="s">
         <v>20</v>
@@ -13604,13 +13604,13 @@
         <v>9</v>
       </c>
       <c r="D289" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E289" t="s">
         <v>574</v>
       </c>
       <c r="F289" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G289" t="s">
         <v>20</v>
@@ -13673,13 +13673,13 @@
         <v>9</v>
       </c>
       <c r="D292" t="s">
-        <v>573</v>
+        <v>644</v>
       </c>
       <c r="E292" t="s">
         <v>574</v>
       </c>
       <c r="F292" t="s">
-        <v>644</v>
+        <v>575</v>
       </c>
       <c r="G292" t="s">
         <v>20</v>
@@ -13696,13 +13696,13 @@
         <v>9</v>
       </c>
       <c r="D293" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E293" t="s">
         <v>574</v>
       </c>
       <c r="F293" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G293" t="s">
         <v>20</v>
@@ -13857,13 +13857,13 @@
         <v>9</v>
       </c>
       <c r="D300" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E300" t="s">
         <v>574</v>
       </c>
       <c r="F300" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G300" t="s">
         <v>20</v>
@@ -13880,13 +13880,13 @@
         <v>9</v>
       </c>
       <c r="D301" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E301" t="s">
         <v>574</v>
       </c>
       <c r="F301" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G301" t="s">
         <v>20</v>
@@ -13903,13 +13903,13 @@
         <v>9</v>
       </c>
       <c r="D302" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E302" t="s">
         <v>574</v>
       </c>
       <c r="F302" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G302" t="s">
         <v>20</v>
@@ -13949,13 +13949,13 @@
         <v>9</v>
       </c>
       <c r="D304" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E304" t="s">
         <v>574</v>
       </c>
       <c r="F304" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G304" t="s">
         <v>20</v>
@@ -14018,13 +14018,13 @@
         <v>9</v>
       </c>
       <c r="D307" t="s">
-        <v>573</v>
+        <v>711</v>
       </c>
       <c r="E307" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F307" t="s">
-        <v>711</v>
+        <v>575</v>
       </c>
       <c r="G307" t="s">
         <v>20</v>
@@ -14041,13 +14041,13 @@
         <v>9</v>
       </c>
       <c r="D308" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E308" t="s">
         <v>574</v>
       </c>
       <c r="F308" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G308" t="s">
         <v>20</v>
@@ -14386,13 +14386,13 @@
         <v>9</v>
       </c>
       <c r="D323" t="s">
-        <v>718</v>
+        <v>747</v>
       </c>
       <c r="E323" t="s">
         <v>719</v>
       </c>
       <c r="F323" t="s">
-        <v>747</v>
+        <v>720</v>
       </c>
       <c r="G323" t="s">
         <v>20</v>
@@ -14846,13 +14846,13 @@
         <v>9</v>
       </c>
       <c r="D343" t="s">
-        <v>718</v>
+        <v>790</v>
       </c>
       <c r="E343" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="F343" t="s">
-        <v>791</v>
+        <v>720</v>
       </c>
       <c r="G343" t="s">
         <v>34</v>
@@ -14869,13 +14869,13 @@
         <v>185</v>
       </c>
       <c r="D344" t="s">
-        <v>718</v>
+        <v>794</v>
       </c>
       <c r="E344" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="F344" t="s">
-        <v>794</v>
+        <v>720</v>
       </c>
       <c r="G344" t="s">
         <v>34</v>
@@ -14915,13 +14915,13 @@
         <v>185</v>
       </c>
       <c r="D346" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="E346" t="s">
         <v>798</v>
       </c>
       <c r="F346" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="G346" t="s">
         <v>20</v>
@@ -15145,13 +15145,13 @@
         <v>9</v>
       </c>
       <c r="D356" t="s">
-        <v>797</v>
+        <v>823</v>
       </c>
       <c r="E356" t="s">
         <v>798</v>
       </c>
       <c r="F356" t="s">
-        <v>823</v>
+        <v>799</v>
       </c>
       <c r="G356" t="s">
         <v>20</v>
@@ -15375,13 +15375,13 @@
         <v>9</v>
       </c>
       <c r="D366" t="s">
-        <v>797</v>
+        <v>844</v>
       </c>
       <c r="E366" t="s">
         <v>798</v>
       </c>
       <c r="F366" t="s">
-        <v>844</v>
+        <v>799</v>
       </c>
       <c r="G366" t="s">
         <v>20</v>
@@ -15398,13 +15398,13 @@
         <v>9</v>
       </c>
       <c r="D367" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="E367" t="s">
         <v>798</v>
       </c>
       <c r="F367" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="G367" t="s">
         <v>16</v>
@@ -15513,13 +15513,13 @@
         <v>9</v>
       </c>
       <c r="D372" t="s">
-        <v>797</v>
+        <v>858</v>
       </c>
       <c r="E372" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F372" t="s">
-        <v>859</v>
+        <v>799</v>
       </c>
       <c r="G372" t="s">
         <v>25</v>
@@ -15559,13 +15559,13 @@
         <v>185</v>
       </c>
       <c r="D374" t="s">
-        <v>797</v>
+        <v>858</v>
       </c>
       <c r="E374" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F374" t="s">
-        <v>859</v>
+        <v>799</v>
       </c>
       <c r="G374" t="s">
         <v>25</v>
@@ -15697,13 +15697,13 @@
         <v>9</v>
       </c>
       <c r="D380" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="E380" t="s">
         <v>873</v>
       </c>
       <c r="F380" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="G380" t="s">
         <v>16</v>
@@ -15835,13 +15835,13 @@
         <v>9</v>
       </c>
       <c r="D386" t="s">
-        <v>872</v>
+        <v>892</v>
       </c>
       <c r="E386" t="s">
         <v>873</v>
       </c>
       <c r="F386" t="s">
-        <v>892</v>
+        <v>874</v>
       </c>
       <c r="G386" t="s">
         <v>20</v>
@@ -15858,13 +15858,13 @@
         <v>9</v>
       </c>
       <c r="D387" t="s">
-        <v>872</v>
+        <v>895</v>
       </c>
       <c r="E387" t="s">
         <v>873</v>
       </c>
       <c r="F387" t="s">
-        <v>895</v>
+        <v>874</v>
       </c>
       <c r="G387" t="s">
         <v>25</v>
@@ -15904,13 +15904,13 @@
         <v>9</v>
       </c>
       <c r="D389" t="s">
-        <v>872</v>
+        <v>900</v>
       </c>
       <c r="E389" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="F389" t="s">
-        <v>901</v>
+        <v>874</v>
       </c>
       <c r="G389" t="s">
         <v>34</v>
@@ -15996,13 +15996,13 @@
         <v>9</v>
       </c>
       <c r="D393" t="s">
-        <v>872</v>
+        <v>910</v>
       </c>
       <c r="E393" t="s">
         <v>873</v>
       </c>
       <c r="F393" t="s">
-        <v>910</v>
+        <v>874</v>
       </c>
       <c r="G393" t="s">
         <v>20</v>
@@ -16042,13 +16042,13 @@
         <v>9</v>
       </c>
       <c r="D395" t="s">
-        <v>872</v>
+        <v>915</v>
       </c>
       <c r="E395" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="F395" t="s">
-        <v>916</v>
+        <v>874</v>
       </c>
       <c r="G395" t="s">
         <v>34</v>
@@ -16088,13 +16088,13 @@
         <v>9</v>
       </c>
       <c r="D397" t="s">
-        <v>872</v>
+        <v>921</v>
       </c>
       <c r="E397" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="F397" t="s">
-        <v>922</v>
+        <v>874</v>
       </c>
       <c r="G397" t="s">
         <v>34</v>
@@ -16157,13 +16157,13 @@
         <v>9</v>
       </c>
       <c r="D400" t="s">
-        <v>872</v>
+        <v>929</v>
       </c>
       <c r="E400" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="F400" t="s">
-        <v>930</v>
+        <v>874</v>
       </c>
       <c r="G400" t="s">
         <v>34</v>
@@ -16295,13 +16295,13 @@
         <v>9</v>
       </c>
       <c r="D406" t="s">
-        <v>872</v>
+        <v>943</v>
       </c>
       <c r="E406" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="F406" t="s">
-        <v>944</v>
+        <v>874</v>
       </c>
       <c r="G406" t="s">
         <v>34</v>
@@ -16318,13 +16318,13 @@
         <v>9</v>
       </c>
       <c r="D407" t="s">
-        <v>872</v>
+        <v>947</v>
       </c>
       <c r="E407" t="s">
         <v>873</v>
       </c>
       <c r="F407" t="s">
-        <v>947</v>
+        <v>874</v>
       </c>
       <c r="G407" t="s">
         <v>25</v>
@@ -16594,13 +16594,13 @@
         <v>9</v>
       </c>
       <c r="D419" t="s">
-        <v>968</v>
+        <v>975</v>
       </c>
       <c r="E419" t="s">
         <v>969</v>
       </c>
       <c r="F419" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="G419" t="s">
         <v>34</v>
@@ -16640,13 +16640,13 @@
         <v>9</v>
       </c>
       <c r="D421" t="s">
-        <v>968</v>
+        <v>980</v>
       </c>
       <c r="E421" t="s">
         <v>969</v>
       </c>
       <c r="F421" t="s">
-        <v>980</v>
+        <v>970</v>
       </c>
       <c r="G421" t="s">
         <v>25</v>
@@ -16801,13 +16801,13 @@
         <v>9</v>
       </c>
       <c r="D428" t="s">
-        <v>968</v>
+        <v>995</v>
       </c>
       <c r="E428" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="F428" t="s">
-        <v>996</v>
+        <v>970</v>
       </c>
       <c r="G428" t="s">
         <v>34</v>
@@ -16824,13 +16824,13 @@
         <v>9</v>
       </c>
       <c r="D429" t="s">
-        <v>968</v>
+        <v>999</v>
       </c>
       <c r="E429" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="F429" t="s">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="G429" t="s">
         <v>34</v>
@@ -16916,13 +16916,13 @@
         <v>9</v>
       </c>
       <c r="D433" t="s">
-        <v>968</v>
+        <v>1009</v>
       </c>
       <c r="E433" t="s">
         <v>969</v>
       </c>
       <c r="F433" t="s">
-        <v>1009</v>
+        <v>970</v>
       </c>
       <c r="G433" t="s">
         <v>34</v>
@@ -16985,13 +16985,13 @@
         <v>9</v>
       </c>
       <c r="D436" t="s">
-        <v>968</v>
+        <v>1016</v>
       </c>
       <c r="E436" t="s">
         <v>969</v>
       </c>
       <c r="F436" t="s">
-        <v>1016</v>
+        <v>970</v>
       </c>
       <c r="G436" t="s">
         <v>34</v>
@@ -17008,13 +17008,13 @@
         <v>9</v>
       </c>
       <c r="D437" t="s">
-        <v>968</v>
+        <v>1019</v>
       </c>
       <c r="E437" t="s">
         <v>969</v>
       </c>
       <c r="F437" t="s">
-        <v>1019</v>
+        <v>970</v>
       </c>
       <c r="G437" t="s">
         <v>25</v>
@@ -17077,13 +17077,13 @@
         <v>9</v>
       </c>
       <c r="D440" t="s">
-        <v>968</v>
+        <v>1026</v>
       </c>
       <c r="E440" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="F440" t="s">
-        <v>1027</v>
+        <v>970</v>
       </c>
       <c r="G440" t="s">
         <v>34</v>
@@ -17399,13 +17399,13 @@
         <v>9</v>
       </c>
       <c r="D454" t="s">
-        <v>968</v>
+        <v>1056</v>
       </c>
       <c r="E454" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="F454" t="s">
-        <v>1057</v>
+        <v>970</v>
       </c>
       <c r="G454" t="s">
         <v>25</v>
@@ -17629,13 +17629,13 @@
         <v>9</v>
       </c>
       <c r="D464" t="s">
-        <v>1060</v>
+        <v>1082</v>
       </c>
       <c r="E464" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="F464" t="s">
-        <v>1083</v>
+        <v>1062</v>
       </c>
       <c r="G464" t="s">
         <v>34</v>
@@ -17652,13 +17652,13 @@
         <v>9</v>
       </c>
       <c r="D465" t="s">
-        <v>1060</v>
+        <v>1086</v>
       </c>
       <c r="E465" t="s">
         <v>1061</v>
       </c>
       <c r="F465" t="s">
-        <v>1086</v>
+        <v>1062</v>
       </c>
       <c r="G465" t="s">
         <v>34</v>
@@ -17675,13 +17675,13 @@
         <v>9</v>
       </c>
       <c r="D466" t="s">
-        <v>1060</v>
+        <v>1089</v>
       </c>
       <c r="E466" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="F466" t="s">
-        <v>1089</v>
+        <v>1062</v>
       </c>
       <c r="G466" t="s">
         <v>34</v>
@@ -17698,13 +17698,13 @@
         <v>9</v>
       </c>
       <c r="D467" t="s">
-        <v>1060</v>
+        <v>1092</v>
       </c>
       <c r="E467" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F467" t="s">
-        <v>1093</v>
+        <v>1062</v>
       </c>
       <c r="G467" t="s">
         <v>34</v>
@@ -17744,13 +17744,13 @@
         <v>9</v>
       </c>
       <c r="D469" t="s">
-        <v>1060</v>
+        <v>1098</v>
       </c>
       <c r="E469" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="F469" t="s">
-        <v>1099</v>
+        <v>1062</v>
       </c>
       <c r="G469" t="s">
         <v>34</v>
@@ -17836,13 +17836,13 @@
         <v>9</v>
       </c>
       <c r="D473" t="s">
-        <v>1060</v>
+        <v>1108</v>
       </c>
       <c r="E473" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="F473" t="s">
-        <v>1108</v>
+        <v>1062</v>
       </c>
       <c r="G473" t="s">
         <v>34</v>
@@ -18181,13 +18181,13 @@
         <v>9</v>
       </c>
       <c r="D488" t="s">
-        <v>1137</v>
+        <v>1142</v>
       </c>
       <c r="E488" t="s">
         <v>1138</v>
       </c>
       <c r="F488" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="G488" t="s">
         <v>1063</v>
@@ -18319,13 +18319,13 @@
         <v>9</v>
       </c>
       <c r="D494" t="s">
-        <v>1137</v>
+        <v>1098</v>
       </c>
       <c r="E494" t="s">
         <v>1156</v>
       </c>
       <c r="F494" t="s">
-        <v>1099</v>
+        <v>1139</v>
       </c>
       <c r="G494" t="s">
         <v>16</v>
@@ -18342,13 +18342,13 @@
         <v>185</v>
       </c>
       <c r="D495" t="s">
-        <v>1137</v>
+        <v>1098</v>
       </c>
       <c r="E495" t="s">
         <v>1156</v>
       </c>
       <c r="F495" t="s">
-        <v>1099</v>
+        <v>1139</v>
       </c>
       <c r="G495" t="s">
         <v>20</v>
@@ -18411,13 +18411,13 @@
         <v>9</v>
       </c>
       <c r="D498" t="s">
-        <v>1137</v>
+        <v>1165</v>
       </c>
       <c r="E498" t="s">
         <v>1138</v>
       </c>
       <c r="F498" t="s">
-        <v>1165</v>
+        <v>1139</v>
       </c>
       <c r="G498" t="s">
         <v>1063</v>
@@ -18503,13 +18503,13 @@
         <v>185</v>
       </c>
       <c r="D502" t="s">
-        <v>1137</v>
+        <v>1174</v>
       </c>
       <c r="E502" t="s">
         <v>1138</v>
       </c>
       <c r="F502" t="s">
-        <v>1174</v>
+        <v>1139</v>
       </c>
       <c r="G502" t="s">
         <v>25</v>
@@ -18618,13 +18618,13 @@
         <v>9</v>
       </c>
       <c r="D507" t="s">
-        <v>1137</v>
+        <v>1185</v>
       </c>
       <c r="E507" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="F507" t="s">
-        <v>1186</v>
+        <v>1139</v>
       </c>
       <c r="G507" t="s">
         <v>34</v>
@@ -18641,13 +18641,13 @@
         <v>9</v>
       </c>
       <c r="D508" t="s">
-        <v>1137</v>
+        <v>1189</v>
       </c>
       <c r="E508" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="F508" t="s">
-        <v>1190</v>
+        <v>1139</v>
       </c>
       <c r="G508" t="s">
         <v>1063</v>
@@ -18664,13 +18664,13 @@
         <v>185</v>
       </c>
       <c r="D509" t="s">
-        <v>1137</v>
+        <v>1189</v>
       </c>
       <c r="E509" t="s">
         <v>1193</v>
       </c>
       <c r="F509" t="s">
-        <v>1190</v>
+        <v>1139</v>
       </c>
       <c r="G509" t="s">
         <v>25</v>
@@ -18687,13 +18687,13 @@
         <v>9</v>
       </c>
       <c r="D510" t="s">
-        <v>1137</v>
+        <v>1196</v>
       </c>
       <c r="E510" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="F510" t="s">
-        <v>1197</v>
+        <v>1139</v>
       </c>
       <c r="G510" t="s">
         <v>34</v>
@@ -18733,13 +18733,13 @@
         <v>9</v>
       </c>
       <c r="D512" t="s">
-        <v>1137</v>
+        <v>1202</v>
       </c>
       <c r="E512" t="s">
         <v>1138</v>
       </c>
       <c r="F512" t="s">
-        <v>1202</v>
+        <v>1139</v>
       </c>
       <c r="G512" t="s">
         <v>20</v>
@@ -18940,13 +18940,13 @@
         <v>185</v>
       </c>
       <c r="D521" t="s">
-        <v>1137</v>
+        <v>1222</v>
       </c>
       <c r="E521" t="s">
         <v>1138</v>
       </c>
       <c r="F521" t="s">
-        <v>1222</v>
+        <v>1139</v>
       </c>
       <c r="G521" t="s">
         <v>25</v>
@@ -18963,13 +18963,13 @@
         <v>185</v>
       </c>
       <c r="D522" t="s">
-        <v>1137</v>
+        <v>1225</v>
       </c>
       <c r="E522" t="s">
         <v>1138</v>
       </c>
       <c r="F522" t="s">
-        <v>1225</v>
+        <v>1139</v>
       </c>
       <c r="G522" t="s">
         <v>16</v>
@@ -18986,13 +18986,13 @@
         <v>9</v>
       </c>
       <c r="D523" t="s">
-        <v>1137</v>
+        <v>1228</v>
       </c>
       <c r="E523" t="s">
         <v>1138</v>
       </c>
       <c r="F523" t="s">
-        <v>1228</v>
+        <v>1139</v>
       </c>
       <c r="G523" t="s">
         <v>34</v>
@@ -19032,13 +19032,13 @@
         <v>9</v>
       </c>
       <c r="D525" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E525" t="s">
         <v>1233</v>
       </c>
-      <c r="E525" t="s">
+      <c r="F525" t="s">
         <v>1234</v>
-      </c>
-      <c r="F525" t="s">
-        <v>1142</v>
       </c>
       <c r="G525" t="s">
         <v>1235</v>
@@ -19055,13 +19055,13 @@
         <v>9</v>
       </c>
       <c r="D526" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E526" t="s">
         <v>1233</v>
       </c>
-      <c r="E526" t="s">
+      <c r="F526" t="s">
         <v>1234</v>
-      </c>
-      <c r="F526" t="s">
-        <v>1142</v>
       </c>
       <c r="G526" t="s">
         <v>1235</v>
@@ -19078,13 +19078,13 @@
         <v>9</v>
       </c>
       <c r="D527" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E527" t="s">
         <v>1233</v>
       </c>
-      <c r="E527" t="s">
+      <c r="F527" t="s">
         <v>1234</v>
-      </c>
-      <c r="F527" t="s">
-        <v>1142</v>
       </c>
       <c r="G527" t="s">
         <v>1235</v>
@@ -19101,13 +19101,13 @@
         <v>9</v>
       </c>
       <c r="D528" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E528" t="s">
         <v>1233</v>
       </c>
-      <c r="E528" t="s">
+      <c r="F528" t="s">
         <v>1234</v>
-      </c>
-      <c r="F528" t="s">
-        <v>1142</v>
       </c>
       <c r="G528" t="s">
         <v>1235</v>
@@ -19124,13 +19124,13 @@
         <v>9</v>
       </c>
       <c r="D529" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E529" t="s">
         <v>1233</v>
       </c>
-      <c r="E529" t="s">
+      <c r="F529" t="s">
         <v>1234</v>
-      </c>
-      <c r="F529" t="s">
-        <v>1244</v>
       </c>
       <c r="G529" t="s">
         <v>20</v>
@@ -19147,13 +19147,13 @@
         <v>9</v>
       </c>
       <c r="D530" t="s">
-        <v>1233</v>
+        <v>1142</v>
       </c>
       <c r="E530" t="s">
         <v>1247</v>
       </c>
       <c r="F530" t="s">
-        <v>1142</v>
+        <v>1234</v>
       </c>
       <c r="G530" t="s">
         <v>1235</v>
@@ -19170,13 +19170,13 @@
         <v>9</v>
       </c>
       <c r="D531" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E531" t="s">
         <v>1233</v>
       </c>
-      <c r="E531" t="s">
+      <c r="F531" t="s">
         <v>1234</v>
-      </c>
-      <c r="F531" t="s">
-        <v>1142</v>
       </c>
       <c r="G531" t="s">
         <v>1235</v>
@@ -19193,13 +19193,13 @@
         <v>9</v>
       </c>
       <c r="D532" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E532" t="s">
         <v>1233</v>
       </c>
-      <c r="E532" t="s">
+      <c r="F532" t="s">
         <v>1234</v>
-      </c>
-      <c r="F532" t="s">
-        <v>1142</v>
       </c>
       <c r="G532" t="s">
         <v>1235</v>
@@ -19216,13 +19216,13 @@
         <v>9</v>
       </c>
       <c r="D533" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E533" t="s">
         <v>1233</v>
       </c>
-      <c r="E533" t="s">
+      <c r="F533" t="s">
         <v>1234</v>
-      </c>
-      <c r="F533" t="s">
-        <v>1142</v>
       </c>
       <c r="G533" t="s">
         <v>1235</v>
@@ -19239,13 +19239,13 @@
         <v>9</v>
       </c>
       <c r="D534" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E534" t="s">
         <v>1233</v>
       </c>
-      <c r="E534" t="s">
+      <c r="F534" t="s">
         <v>1234</v>
-      </c>
-      <c r="F534" t="s">
-        <v>1142</v>
       </c>
       <c r="G534" t="s">
         <v>1235</v>
@@ -19262,13 +19262,13 @@
         <v>9</v>
       </c>
       <c r="D535" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E535" t="s">
         <v>1233</v>
       </c>
-      <c r="E535" t="s">
+      <c r="F535" t="s">
         <v>1234</v>
-      </c>
-      <c r="F535" t="s">
-        <v>1142</v>
       </c>
       <c r="G535" t="s">
         <v>1235</v>
@@ -19285,13 +19285,13 @@
         <v>9</v>
       </c>
       <c r="D536" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E536" t="s">
         <v>1233</v>
       </c>
-      <c r="E536" t="s">
+      <c r="F536" t="s">
         <v>1234</v>
-      </c>
-      <c r="F536" t="s">
-        <v>1260</v>
       </c>
       <c r="G536" t="s">
         <v>20</v>
@@ -19308,13 +19308,13 @@
         <v>9</v>
       </c>
       <c r="D537" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E537" t="s">
         <v>1233</v>
       </c>
-      <c r="E537" t="s">
+      <c r="F537" t="s">
         <v>1234</v>
-      </c>
-      <c r="F537" t="s">
-        <v>1263</v>
       </c>
       <c r="G537" t="s">
         <v>20</v>
@@ -19331,13 +19331,13 @@
         <v>9</v>
       </c>
       <c r="D538" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E538" t="s">
         <v>1233</v>
       </c>
-      <c r="E538" t="s">
+      <c r="F538" t="s">
         <v>1234</v>
-      </c>
-      <c r="F538" t="s">
-        <v>1142</v>
       </c>
       <c r="G538" t="s">
         <v>1235</v>
@@ -19354,13 +19354,13 @@
         <v>9</v>
       </c>
       <c r="D539" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E539" t="s">
         <v>1233</v>
       </c>
-      <c r="E539" t="s">
+      <c r="F539" t="s">
         <v>1234</v>
-      </c>
-      <c r="F539" t="s">
-        <v>1142</v>
       </c>
       <c r="G539" t="s">
         <v>1235</v>
@@ -19377,13 +19377,13 @@
         <v>9</v>
       </c>
       <c r="D540" t="s">
-        <v>1233</v>
+        <v>1142</v>
       </c>
       <c r="E540" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="F540" t="s">
-        <v>1142</v>
+        <v>1234</v>
       </c>
       <c r="G540" t="s">
         <v>1235</v>
@@ -19400,13 +19400,13 @@
         <v>9</v>
       </c>
       <c r="D541" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E541" t="s">
         <v>1233</v>
       </c>
-      <c r="E541" t="s">
+      <c r="F541" t="s">
         <v>1234</v>
-      </c>
-      <c r="F541" t="s">
-        <v>1142</v>
       </c>
       <c r="G541" t="s">
         <v>1235</v>
@@ -19423,13 +19423,13 @@
         <v>9</v>
       </c>
       <c r="D542" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E542" t="s">
         <v>1233</v>
       </c>
-      <c r="E542" t="s">
+      <c r="F542" t="s">
         <v>1234</v>
-      </c>
-      <c r="F542" t="s">
-        <v>1142</v>
       </c>
       <c r="G542" t="s">
         <v>1235</v>
@@ -19446,13 +19446,13 @@
         <v>9</v>
       </c>
       <c r="D543" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E543" t="s">
         <v>1233</v>
       </c>
-      <c r="E543" t="s">
+      <c r="F543" t="s">
         <v>1234</v>
-      </c>
-      <c r="F543" t="s">
-        <v>1142</v>
       </c>
       <c r="G543" t="s">
         <v>1235</v>
@@ -19469,13 +19469,13 @@
         <v>9</v>
       </c>
       <c r="D544" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E544" t="s">
         <v>1233</v>
       </c>
-      <c r="E544" t="s">
+      <c r="F544" t="s">
         <v>1234</v>
-      </c>
-      <c r="F544" t="s">
-        <v>1142</v>
       </c>
       <c r="G544" t="s">
         <v>1235</v>
@@ -19492,13 +19492,13 @@
         <v>9</v>
       </c>
       <c r="D545" t="s">
-        <v>1233</v>
+        <v>1142</v>
       </c>
       <c r="E545" t="s">
         <v>1280</v>
       </c>
       <c r="F545" t="s">
-        <v>1142</v>
+        <v>1234</v>
       </c>
       <c r="G545" t="s">
         <v>16</v>
@@ -19515,13 +19515,13 @@
         <v>9</v>
       </c>
       <c r="D546" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E546" t="s">
         <v>1233</v>
       </c>
-      <c r="E546" t="s">
+      <c r="F546" t="s">
         <v>1234</v>
-      </c>
-      <c r="F546" t="s">
-        <v>1142</v>
       </c>
       <c r="G546" t="s">
         <v>1235</v>
@@ -19538,13 +19538,13 @@
         <v>9</v>
       </c>
       <c r="D547" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E547" t="s">
         <v>1233</v>
       </c>
-      <c r="E547" t="s">
+      <c r="F547" t="s">
         <v>1234</v>
-      </c>
-      <c r="F547" t="s">
-        <v>1142</v>
       </c>
       <c r="G547" t="s">
         <v>20</v>
@@ -19584,13 +19584,13 @@
         <v>9</v>
       </c>
       <c r="D549" t="s">
-        <v>1287</v>
+        <v>1292</v>
       </c>
       <c r="E549" t="s">
         <v>1288</v>
       </c>
       <c r="F549" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="G549" t="s">
         <v>1235</v>
@@ -19607,13 +19607,13 @@
         <v>9</v>
       </c>
       <c r="D550" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
       <c r="E550" t="s">
         <v>1288</v>
       </c>
       <c r="F550" t="s">
-        <v>1295</v>
+        <v>1289</v>
       </c>
       <c r="G550" t="s">
         <v>1235</v>
@@ -19791,13 +19791,13 @@
         <v>9</v>
       </c>
       <c r="D558" t="s">
-        <v>1287</v>
+        <v>1313</v>
       </c>
       <c r="E558" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="F558" t="s">
-        <v>1314</v>
+        <v>1289</v>
       </c>
       <c r="G558" t="s">
         <v>34</v>
@@ -19837,13 +19837,13 @@
         <v>9</v>
       </c>
       <c r="D560" t="s">
-        <v>1287</v>
+        <v>1319</v>
       </c>
       <c r="E560" t="s">
         <v>1288</v>
       </c>
       <c r="F560" t="s">
-        <v>1319</v>
+        <v>1289</v>
       </c>
       <c r="G560" t="s">
         <v>1235</v>
@@ -19860,13 +19860,13 @@
         <v>9</v>
       </c>
       <c r="D561" t="s">
-        <v>1287</v>
+        <v>1319</v>
       </c>
       <c r="E561" t="s">
         <v>1288</v>
       </c>
       <c r="F561" t="s">
-        <v>1319</v>
+        <v>1289</v>
       </c>
       <c r="G561" t="s">
         <v>1235</v>
@@ -20044,13 +20044,13 @@
         <v>9</v>
       </c>
       <c r="D569" t="s">
-        <v>1287</v>
+        <v>1339</v>
       </c>
       <c r="E569" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="F569" t="s">
-        <v>1340</v>
+        <v>1289</v>
       </c>
       <c r="G569" t="s">
         <v>1235</v>
@@ -20139,7 +20139,7 @@
         <v>1349</v>
       </c>
       <c r="E573" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="F573" t="s">
         <v>1350</v>
@@ -20251,13 +20251,13 @@
         <v>9</v>
       </c>
       <c r="D578" t="s">
-        <v>1349</v>
+        <v>1362</v>
       </c>
       <c r="E578" t="s">
         <v>1353</v>
       </c>
       <c r="F578" t="s">
-        <v>1362</v>
+        <v>1350</v>
       </c>
       <c r="G578" t="s">
         <v>1235</v>
@@ -20274,13 +20274,13 @@
         <v>9</v>
       </c>
       <c r="D579" t="s">
-        <v>1349</v>
+        <v>1365</v>
       </c>
       <c r="E579" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="F579" t="s">
-        <v>1366</v>
+        <v>1350</v>
       </c>
       <c r="G579" t="s">
         <v>34</v>
@@ -20297,13 +20297,13 @@
         <v>9</v>
       </c>
       <c r="D580" t="s">
-        <v>1349</v>
+        <v>1369</v>
       </c>
       <c r="E580" t="s">
         <v>1353</v>
       </c>
       <c r="F580" t="s">
-        <v>1369</v>
+        <v>1350</v>
       </c>
       <c r="G580" t="s">
         <v>1235</v>
@@ -20320,13 +20320,13 @@
         <v>9</v>
       </c>
       <c r="D581" t="s">
-        <v>1349</v>
+        <v>1372</v>
       </c>
       <c r="E581" t="s">
         <v>1353</v>
       </c>
       <c r="F581" t="s">
-        <v>1372</v>
+        <v>1350</v>
       </c>
       <c r="G581" t="s">
         <v>20</v>
@@ -20366,13 +20366,13 @@
         <v>9</v>
       </c>
       <c r="D583" t="s">
-        <v>1349</v>
+        <v>1377</v>
       </c>
       <c r="E583" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="F583" t="s">
-        <v>1378</v>
+        <v>1350</v>
       </c>
       <c r="G583" t="s">
         <v>34</v>
@@ -20389,13 +20389,13 @@
         <v>9</v>
       </c>
       <c r="D584" t="s">
-        <v>1349</v>
+        <v>1381</v>
       </c>
       <c r="E584" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="F584" t="s">
-        <v>1382</v>
+        <v>1350</v>
       </c>
       <c r="G584" t="s">
         <v>34</v>
@@ -20435,13 +20435,13 @@
         <v>9</v>
       </c>
       <c r="D586" t="s">
-        <v>1349</v>
+        <v>1387</v>
       </c>
       <c r="E586" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="F586" t="s">
-        <v>1388</v>
+        <v>1350</v>
       </c>
       <c r="G586" t="s">
         <v>34</v>
@@ -20458,13 +20458,13 @@
         <v>9</v>
       </c>
       <c r="D587" t="s">
-        <v>1349</v>
+        <v>1391</v>
       </c>
       <c r="E587" t="s">
         <v>1353</v>
       </c>
       <c r="F587" t="s">
-        <v>1391</v>
+        <v>1350</v>
       </c>
       <c r="G587" t="s">
         <v>16</v>
@@ -20481,13 +20481,13 @@
         <v>9</v>
       </c>
       <c r="D588" t="s">
-        <v>1349</v>
+        <v>1394</v>
       </c>
       <c r="E588" t="s">
         <v>1353</v>
       </c>
       <c r="F588" t="s">
-        <v>1394</v>
+        <v>1350</v>
       </c>
       <c r="G588" t="s">
         <v>1235</v>
@@ -20711,13 +20711,13 @@
         <v>9</v>
       </c>
       <c r="D598" t="s">
-        <v>1414</v>
+        <v>1419</v>
       </c>
       <c r="E598" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="F598" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="G598" t="s">
         <v>20</v>
@@ -20803,13 +20803,13 @@
         <v>9</v>
       </c>
       <c r="D602" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="E602" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="F602" t="s">
-        <v>1430</v>
+        <v>1416</v>
       </c>
       <c r="G602" t="s">
         <v>34</v>
@@ -20826,13 +20826,13 @@
         <v>9</v>
       </c>
       <c r="D603" t="s">
-        <v>1414</v>
+        <v>1433</v>
       </c>
       <c r="E603" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="F603" t="s">
-        <v>1434</v>
+        <v>1416</v>
       </c>
       <c r="G603" t="s">
         <v>34</v>
@@ -20849,13 +20849,13 @@
         <v>9</v>
       </c>
       <c r="D604" t="s">
-        <v>1414</v>
+        <v>1437</v>
       </c>
       <c r="E604" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="F604" t="s">
-        <v>1438</v>
+        <v>1416</v>
       </c>
       <c r="G604" t="s">
         <v>1235</v>
@@ -20872,13 +20872,13 @@
         <v>9</v>
       </c>
       <c r="D605" t="s">
-        <v>1414</v>
+        <v>1441</v>
       </c>
       <c r="E605" t="s">
         <v>1415</v>
       </c>
       <c r="F605" t="s">
-        <v>1441</v>
+        <v>1416</v>
       </c>
       <c r="G605" t="s">
         <v>34</v>
@@ -20941,13 +20941,13 @@
         <v>9</v>
       </c>
       <c r="D608" t="s">
-        <v>1414</v>
+        <v>1448</v>
       </c>
       <c r="E608" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="F608" t="s">
-        <v>1449</v>
+        <v>1416</v>
       </c>
       <c r="G608" t="s">
         <v>34</v>
@@ -20964,13 +20964,13 @@
         <v>9</v>
       </c>
       <c r="D609" t="s">
-        <v>1414</v>
+        <v>1452</v>
       </c>
       <c r="E609" t="s">
         <v>1391</v>
       </c>
       <c r="F609" t="s">
-        <v>1452</v>
+        <v>1416</v>
       </c>
       <c r="G609" t="s">
         <v>1235</v>
@@ -21010,13 +21010,13 @@
         <v>9</v>
       </c>
       <c r="D611" t="s">
-        <v>1414</v>
+        <v>1419</v>
       </c>
       <c r="E611" t="s">
         <v>1457</v>
       </c>
       <c r="F611" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="G611" t="s">
         <v>34</v>
@@ -21033,13 +21033,13 @@
         <v>9</v>
       </c>
       <c r="D612" t="s">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="E612" t="s">
         <v>1415</v>
       </c>
       <c r="F612" t="s">
-        <v>1460</v>
+        <v>1416</v>
       </c>
       <c r="G612" t="s">
         <v>20</v>
@@ -21079,13 +21079,13 @@
         <v>9</v>
       </c>
       <c r="D614" t="s">
-        <v>1414</v>
+        <v>1465</v>
       </c>
       <c r="E614" t="s">
         <v>1415</v>
       </c>
       <c r="F614" t="s">
-        <v>1465</v>
+        <v>1416</v>
       </c>
       <c r="G614" t="s">
         <v>1235</v>
@@ -21309,13 +21309,13 @@
         <v>9</v>
       </c>
       <c r="D624" t="s">
-        <v>1484</v>
+        <v>1489</v>
       </c>
       <c r="E624" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="F624" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
       <c r="G624" t="s">
         <v>34</v>
@@ -21424,13 +21424,13 @@
         <v>9</v>
       </c>
       <c r="D629" t="s">
-        <v>1484</v>
+        <v>1502</v>
       </c>
       <c r="E629" t="s">
         <v>1485</v>
       </c>
       <c r="F629" t="s">
-        <v>1502</v>
+        <v>1486</v>
       </c>
       <c r="G629" t="s">
         <v>34</v>
@@ -21493,13 +21493,13 @@
         <v>9</v>
       </c>
       <c r="D632" t="s">
-        <v>1484</v>
+        <v>1502</v>
       </c>
       <c r="E632" t="s">
         <v>1509</v>
       </c>
       <c r="F632" t="s">
-        <v>1502</v>
+        <v>1486</v>
       </c>
       <c r="G632" t="s">
         <v>34</v>
@@ -21516,13 +21516,13 @@
         <v>9</v>
       </c>
       <c r="D633" t="s">
-        <v>1484</v>
+        <v>1512</v>
       </c>
       <c r="E633" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="F633" t="s">
-        <v>1513</v>
+        <v>1486</v>
       </c>
       <c r="G633" t="s">
         <v>34</v>
@@ -21539,13 +21539,13 @@
         <v>9</v>
       </c>
       <c r="D634" t="s">
-        <v>1484</v>
+        <v>1516</v>
       </c>
       <c r="E634" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="F634" t="s">
-        <v>1517</v>
+        <v>1486</v>
       </c>
       <c r="G634" t="s">
         <v>34</v>
@@ -21585,13 +21585,13 @@
         <v>9</v>
       </c>
       <c r="D636" t="s">
-        <v>1484</v>
+        <v>1522</v>
       </c>
       <c r="E636" t="s">
         <v>1485</v>
       </c>
       <c r="F636" t="s">
-        <v>1522</v>
+        <v>1486</v>
       </c>
       <c r="G636" t="s">
         <v>1235</v>
@@ -21608,13 +21608,13 @@
         <v>9</v>
       </c>
       <c r="D637" t="s">
-        <v>1484</v>
+        <v>1525</v>
       </c>
       <c r="E637" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="F637" t="s">
-        <v>1526</v>
+        <v>1486</v>
       </c>
       <c r="G637" t="s">
         <v>34</v>
@@ -21700,13 +21700,13 @@
         <v>9</v>
       </c>
       <c r="D641" t="s">
-        <v>1484</v>
+        <v>1535</v>
       </c>
       <c r="E641" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="F641" t="s">
-        <v>1536</v>
+        <v>1486</v>
       </c>
       <c r="G641" t="s">
         <v>20</v>
@@ -21723,13 +21723,13 @@
         <v>9</v>
       </c>
       <c r="D642" t="s">
-        <v>1484</v>
+        <v>1539</v>
       </c>
       <c r="E642" t="s">
         <v>1485</v>
       </c>
       <c r="F642" t="s">
-        <v>1539</v>
+        <v>1486</v>
       </c>
       <c r="G642" t="s">
         <v>20</v>
@@ -21746,13 +21746,13 @@
         <v>9</v>
       </c>
       <c r="D643" t="s">
-        <v>1484</v>
+        <v>1542</v>
       </c>
       <c r="E643" t="s">
         <v>1485</v>
       </c>
       <c r="F643" t="s">
-        <v>1542</v>
+        <v>1486</v>
       </c>
       <c r="G643" t="s">
         <v>20</v>
@@ -21815,13 +21815,13 @@
         <v>9</v>
       </c>
       <c r="D646" t="s">
-        <v>1484</v>
+        <v>1549</v>
       </c>
       <c r="E646" t="s">
         <v>1485</v>
       </c>
       <c r="F646" t="s">
-        <v>1549</v>
+        <v>1486</v>
       </c>
       <c r="G646" t="s">
         <v>34</v>
@@ -21907,13 +21907,13 @@
         <v>9</v>
       </c>
       <c r="D650" t="s">
-        <v>1556</v>
+        <v>1561</v>
       </c>
       <c r="E650" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="F650" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="G650" t="s">
         <v>20</v>
@@ -21953,13 +21953,13 @@
         <v>9</v>
       </c>
       <c r="D652" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="E652" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="F652" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G652" t="s">
         <v>1235</v>
@@ -21976,13 +21976,13 @@
         <v>9</v>
       </c>
       <c r="D653" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="E653" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="F653" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G653" t="s">
         <v>1235</v>
@@ -21999,13 +21999,13 @@
         <v>9</v>
       </c>
       <c r="D654" t="s">
-        <v>1556</v>
+        <v>1542</v>
       </c>
       <c r="E654" t="s">
         <v>1485</v>
       </c>
       <c r="F654" t="s">
-        <v>1542</v>
+        <v>1558</v>
       </c>
       <c r="G654" t="s">
         <v>20</v>
@@ -22022,13 +22022,13 @@
         <v>9</v>
       </c>
       <c r="D655" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="E655" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="F655" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G655" t="s">
         <v>1235</v>
@@ -22045,13 +22045,13 @@
         <v>9</v>
       </c>
       <c r="D656" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="E656" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="F656" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G656" t="s">
         <v>1235</v>
@@ -22068,13 +22068,13 @@
         <v>9</v>
       </c>
       <c r="D657" t="s">
-        <v>1556</v>
+        <v>1580</v>
       </c>
       <c r="E657" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="F657" t="s">
-        <v>1581</v>
+        <v>1558</v>
       </c>
       <c r="G657" t="s">
         <v>20</v>
@@ -22091,13 +22091,13 @@
         <v>9</v>
       </c>
       <c r="D658" t="s">
-        <v>1556</v>
+        <v>1584</v>
       </c>
       <c r="E658" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="F658" t="s">
-        <v>1585</v>
+        <v>1558</v>
       </c>
       <c r="G658" t="s">
         <v>34</v>
@@ -22114,13 +22114,13 @@
         <v>9</v>
       </c>
       <c r="D659" t="s">
-        <v>1556</v>
+        <v>1522</v>
       </c>
       <c r="E659" t="s">
         <v>1588</v>
       </c>
       <c r="F659" t="s">
-        <v>1522</v>
+        <v>1558</v>
       </c>
       <c r="G659" t="s">
         <v>34</v>
@@ -22137,13 +22137,13 @@
         <v>9</v>
       </c>
       <c r="D660" t="s">
-        <v>1556</v>
+        <v>1591</v>
       </c>
       <c r="E660" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="F660" t="s">
-        <v>1592</v>
+        <v>1558</v>
       </c>
       <c r="G660" t="s">
         <v>34</v>
@@ -22160,13 +22160,13 @@
         <v>9</v>
       </c>
       <c r="D661" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="E661" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="F661" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G661" t="s">
         <v>1235</v>
@@ -22183,13 +22183,13 @@
         <v>9</v>
       </c>
       <c r="D662" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="E662" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="F662" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G662" t="s">
         <v>34</v>
@@ -22206,13 +22206,13 @@
         <v>9</v>
       </c>
       <c r="D663" t="s">
-        <v>1556</v>
+        <v>1599</v>
       </c>
       <c r="E663" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="F663" t="s">
-        <v>1600</v>
+        <v>1558</v>
       </c>
       <c r="G663" t="s">
         <v>34</v>
@@ -22229,13 +22229,13 @@
         <v>9</v>
       </c>
       <c r="D664" t="s">
-        <v>1556</v>
+        <v>1542</v>
       </c>
       <c r="E664" t="s">
         <v>1603</v>
       </c>
       <c r="F664" t="s">
-        <v>1542</v>
+        <v>1558</v>
       </c>
       <c r="G664" t="s">
         <v>20</v>
@@ -22252,13 +22252,13 @@
         <v>9</v>
       </c>
       <c r="D665" t="s">
-        <v>1556</v>
+        <v>1606</v>
       </c>
       <c r="E665" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="F665" t="s">
-        <v>1606</v>
+        <v>1558</v>
       </c>
       <c r="G665" t="s">
         <v>1235</v>
@@ -22275,13 +22275,13 @@
         <v>9</v>
       </c>
       <c r="D666" t="s">
-        <v>1556</v>
+        <v>1606</v>
       </c>
       <c r="E666" t="s">
         <v>1557</v>
       </c>
       <c r="F666" t="s">
-        <v>1606</v>
+        <v>1558</v>
       </c>
       <c r="G666" t="s">
         <v>34</v>
@@ -22298,13 +22298,13 @@
         <v>9</v>
       </c>
       <c r="D667" t="s">
-        <v>1556</v>
+        <v>1611</v>
       </c>
       <c r="E667" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="F667" t="s">
-        <v>1612</v>
+        <v>1558</v>
       </c>
       <c r="G667" t="s">
         <v>34</v>
@@ -22321,13 +22321,13 @@
         <v>9</v>
       </c>
       <c r="D668" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="E668" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="F668" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G668" t="s">
         <v>20</v>
@@ -22344,13 +22344,13 @@
         <v>9</v>
       </c>
       <c r="D669" t="s">
-        <v>1556</v>
+        <v>1542</v>
       </c>
       <c r="E669" t="s">
         <v>1588</v>
       </c>
       <c r="F669" t="s">
-        <v>1542</v>
+        <v>1558</v>
       </c>
       <c r="G669" t="s">
         <v>20</v>
@@ -22367,13 +22367,13 @@
         <v>9</v>
       </c>
       <c r="D670" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="E670" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="F670" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G670" t="s">
         <v>1235</v>
@@ -22413,13 +22413,13 @@
         <v>9</v>
       </c>
       <c r="D672" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="E672" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="F672" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G672" t="s">
         <v>20</v>
@@ -22436,13 +22436,13 @@
         <v>9</v>
       </c>
       <c r="D673" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="E673" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="F673" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G673" t="s">
         <v>1235</v>
@@ -22459,13 +22459,13 @@
         <v>9</v>
       </c>
       <c r="D674" t="s">
-        <v>1556</v>
+        <v>1542</v>
       </c>
       <c r="E674" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="F674" t="s">
-        <v>1542</v>
+        <v>1558</v>
       </c>
       <c r="G674" t="s">
         <v>20</v>
@@ -22505,13 +22505,13 @@
         <v>9</v>
       </c>
       <c r="D676" t="s">
-        <v>1556</v>
+        <v>1632</v>
       </c>
       <c r="E676" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="F676" t="s">
-        <v>1632</v>
+        <v>1558</v>
       </c>
       <c r="G676" t="s">
         <v>20</v>
@@ -22528,13 +22528,13 @@
         <v>9</v>
       </c>
       <c r="D677" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="E677" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="F677" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G677" t="s">
         <v>1235</v>
@@ -22551,13 +22551,13 @@
         <v>9</v>
       </c>
       <c r="D678" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="E678" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="F678" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G678" t="s">
         <v>1235</v>
@@ -22574,13 +22574,13 @@
         <v>9</v>
       </c>
       <c r="D679" t="s">
-        <v>1556</v>
+        <v>1591</v>
       </c>
       <c r="E679" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="F679" t="s">
-        <v>1592</v>
+        <v>1558</v>
       </c>
       <c r="G679" t="s">
         <v>34</v>
@@ -22597,13 +22597,13 @@
         <v>9</v>
       </c>
       <c r="D680" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="E680" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="F680" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G680" t="s">
         <v>1235</v>
@@ -22620,13 +22620,13 @@
         <v>9</v>
       </c>
       <c r="D681" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="E681" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="F681" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G681" t="s">
         <v>1235</v>
@@ -22666,13 +22666,13 @@
         <v>9</v>
       </c>
       <c r="D683" t="s">
-        <v>1645</v>
+        <v>1650</v>
       </c>
       <c r="E683" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="F683" t="s">
-        <v>1651</v>
+        <v>1647</v>
       </c>
       <c r="G683" t="s">
         <v>34</v>
@@ -22689,13 +22689,13 @@
         <v>9</v>
       </c>
       <c r="D684" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="E684" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="F684" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G684" t="s">
         <v>1235</v>
@@ -22712,13 +22712,13 @@
         <v>9</v>
       </c>
       <c r="D685" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="E685" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="F685" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G685" t="s">
         <v>1235</v>
@@ -22735,13 +22735,13 @@
         <v>9</v>
       </c>
       <c r="D686" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="E686" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="F686" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G686" t="s">
         <v>1235</v>
@@ -22758,13 +22758,13 @@
         <v>9</v>
       </c>
       <c r="D687" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="E687" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="F687" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G687" t="s">
         <v>1235</v>
@@ -22781,13 +22781,13 @@
         <v>9</v>
       </c>
       <c r="D688" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="E688" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="F688" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G688" t="s">
         <v>1235</v>
@@ -22804,13 +22804,13 @@
         <v>9</v>
       </c>
       <c r="D689" t="s">
-        <v>1645</v>
+        <v>1650</v>
       </c>
       <c r="E689" t="s">
         <v>1666</v>
       </c>
       <c r="F689" t="s">
-        <v>1651</v>
+        <v>1647</v>
       </c>
       <c r="G689" t="s">
         <v>34</v>
@@ -22827,13 +22827,13 @@
         <v>9</v>
       </c>
       <c r="D690" t="s">
-        <v>1645</v>
+        <v>1669</v>
       </c>
       <c r="E690" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="F690" t="s">
-        <v>1670</v>
+        <v>1647</v>
       </c>
       <c r="G690" t="s">
         <v>34</v>
@@ -22850,13 +22850,13 @@
         <v>9</v>
       </c>
       <c r="D691" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="E691" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="F691" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G691" t="s">
         <v>16</v>
@@ -22873,13 +22873,13 @@
         <v>9</v>
       </c>
       <c r="D692" t="s">
-        <v>1645</v>
+        <v>1675</v>
       </c>
       <c r="E692" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="F692" t="s">
-        <v>1675</v>
+        <v>1647</v>
       </c>
       <c r="G692" t="s">
         <v>20</v>
@@ -22896,13 +22896,13 @@
         <v>9</v>
       </c>
       <c r="D693" t="s">
-        <v>1645</v>
+        <v>1678</v>
       </c>
       <c r="E693" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="F693" t="s">
-        <v>1679</v>
+        <v>1647</v>
       </c>
       <c r="G693" t="s">
         <v>34</v>
@@ -22919,13 +22919,13 @@
         <v>9</v>
       </c>
       <c r="D694" t="s">
-        <v>1645</v>
+        <v>1682</v>
       </c>
       <c r="E694" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="F694" t="s">
-        <v>1683</v>
+        <v>1647</v>
       </c>
       <c r="G694" t="s">
         <v>20</v>
@@ -22942,13 +22942,13 @@
         <v>9</v>
       </c>
       <c r="D695" t="s">
-        <v>1645</v>
+        <v>1686</v>
       </c>
       <c r="E695" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="F695" t="s">
-        <v>1687</v>
+        <v>1647</v>
       </c>
       <c r="G695" t="s">
         <v>34</v>
@@ -22965,13 +22965,13 @@
         <v>9</v>
       </c>
       <c r="D696" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="E696" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="F696" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G696" t="s">
         <v>1235</v>
@@ -22988,13 +22988,13 @@
         <v>9</v>
       </c>
       <c r="D697" t="s">
-        <v>1645</v>
+        <v>1692</v>
       </c>
       <c r="E697" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="F697" t="s">
-        <v>1693</v>
+        <v>1647</v>
       </c>
       <c r="G697" t="s">
         <v>34</v>
@@ -23011,13 +23011,13 @@
         <v>9</v>
       </c>
       <c r="D698" t="s">
-        <v>1645</v>
+        <v>1696</v>
       </c>
       <c r="E698" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="F698" t="s">
-        <v>1697</v>
+        <v>1647</v>
       </c>
       <c r="G698" t="s">
         <v>34</v>
@@ -23034,13 +23034,13 @@
         <v>9</v>
       </c>
       <c r="D699" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="E699" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="F699" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G699" t="s">
         <v>20</v>
@@ -23057,13 +23057,13 @@
         <v>9</v>
       </c>
       <c r="D700" t="s">
-        <v>1645</v>
+        <v>1702</v>
       </c>
       <c r="E700" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="F700" t="s">
-        <v>1703</v>
+        <v>1647</v>
       </c>
       <c r="G700" t="s">
         <v>34</v>
@@ -23080,13 +23080,13 @@
         <v>9</v>
       </c>
       <c r="D701" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="E701" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="F701" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G701" t="s">
         <v>20</v>
@@ -23103,13 +23103,13 @@
         <v>9</v>
       </c>
       <c r="D702" t="s">
-        <v>1645</v>
+        <v>1708</v>
       </c>
       <c r="E702" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="F702" t="s">
-        <v>1709</v>
+        <v>1647</v>
       </c>
       <c r="G702" t="s">
         <v>34</v>
@@ -23126,13 +23126,13 @@
         <v>9</v>
       </c>
       <c r="D703" t="s">
-        <v>1645</v>
+        <v>1712</v>
       </c>
       <c r="E703" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="F703" t="s">
-        <v>1712</v>
+        <v>1647</v>
       </c>
       <c r="G703" t="s">
         <v>34</v>
@@ -23149,13 +23149,13 @@
         <v>9</v>
       </c>
       <c r="D704" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="E704" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="F704" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G704" t="s">
         <v>1235</v>
@@ -23172,13 +23172,13 @@
         <v>9</v>
       </c>
       <c r="D705" t="s">
-        <v>1645</v>
+        <v>1717</v>
       </c>
       <c r="E705" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="F705" t="s">
-        <v>1717</v>
+        <v>1647</v>
       </c>
       <c r="G705" t="s">
         <v>20</v>
@@ -23195,13 +23195,13 @@
         <v>9</v>
       </c>
       <c r="D706" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="E706" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="F706" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G706" t="s">
         <v>1235</v>
@@ -23218,13 +23218,13 @@
         <v>9</v>
       </c>
       <c r="D707" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="E707" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="F707" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G707" t="s">
         <v>20</v>
@@ -23241,13 +23241,13 @@
         <v>9</v>
       </c>
       <c r="D708" t="s">
-        <v>1645</v>
+        <v>1724</v>
       </c>
       <c r="E708" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="F708" t="s">
-        <v>1724</v>
+        <v>1647</v>
       </c>
       <c r="G708" t="s">
         <v>34</v>
@@ -23264,13 +23264,13 @@
         <v>9</v>
       </c>
       <c r="D709" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="E709" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="F709" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G709" t="s">
         <v>1235</v>
@@ -23287,13 +23287,13 @@
         <v>9</v>
       </c>
       <c r="D710" t="s">
-        <v>1645</v>
+        <v>1729</v>
       </c>
       <c r="E710" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="F710" t="s">
-        <v>1730</v>
+        <v>1647</v>
       </c>
       <c r="G710" t="s">
         <v>34</v>
@@ -23310,13 +23310,13 @@
         <v>9</v>
       </c>
       <c r="D711" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="E711" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="F711" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G711" t="s">
         <v>1235</v>
@@ -23333,13 +23333,13 @@
         <v>9</v>
       </c>
       <c r="D712" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="E712" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="F712" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G712" t="s">
         <v>1235</v>
@@ -23356,13 +23356,13 @@
         <v>9</v>
       </c>
       <c r="D713" t="s">
-        <v>1645</v>
+        <v>1669</v>
       </c>
       <c r="E713" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="F713" t="s">
-        <v>1670</v>
+        <v>1647</v>
       </c>
       <c r="G713" t="s">
         <v>34</v>
@@ -23379,13 +23379,13 @@
         <v>9</v>
       </c>
       <c r="D714" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="E714" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="F714" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G714" t="s">
         <v>1235</v>
@@ -23402,13 +23402,13 @@
         <v>9</v>
       </c>
       <c r="D715" t="s">
-        <v>1645</v>
+        <v>1692</v>
       </c>
       <c r="E715" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="F715" t="s">
-        <v>1693</v>
+        <v>1647</v>
       </c>
       <c r="G715" t="s">
         <v>34</v>
@@ -23425,13 +23425,13 @@
         <v>9</v>
       </c>
       <c r="D716" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="E716" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="F716" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G716" t="s">
         <v>1235</v>
@@ -23448,13 +23448,13 @@
         <v>9</v>
       </c>
       <c r="D717" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="E717" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="F717" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G717" t="s">
         <v>1235</v>
@@ -23494,13 +23494,13 @@
         <v>9</v>
       </c>
       <c r="D719" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E719" t="s">
         <v>1748</v>
       </c>
       <c r="F719" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G719" t="s">
         <v>1235</v>
@@ -23517,13 +23517,13 @@
         <v>9</v>
       </c>
       <c r="D720" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E720" t="s">
         <v>1748</v>
       </c>
       <c r="F720" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G720" t="s">
         <v>1235</v>
@@ -23540,13 +23540,13 @@
         <v>9</v>
       </c>
       <c r="D721" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E721" t="s">
         <v>1748</v>
       </c>
       <c r="F721" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G721" t="s">
         <v>1235</v>
@@ -23563,13 +23563,13 @@
         <v>9</v>
       </c>
       <c r="D722" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E722" t="s">
         <v>1748</v>
       </c>
       <c r="F722" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G722" t="s">
         <v>1235</v>
@@ -23586,13 +23586,13 @@
         <v>9</v>
       </c>
       <c r="D723" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E723" t="s">
         <v>1748</v>
       </c>
       <c r="F723" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G723" t="s">
         <v>1235</v>
@@ -23609,13 +23609,13 @@
         <v>9</v>
       </c>
       <c r="D724" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E724" t="s">
         <v>1748</v>
       </c>
       <c r="F724" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G724" t="s">
         <v>20</v>
@@ -23632,13 +23632,13 @@
         <v>9</v>
       </c>
       <c r="D725" t="s">
-        <v>1747</v>
+        <v>1765</v>
       </c>
       <c r="E725" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="F725" t="s">
-        <v>1766</v>
+        <v>1749</v>
       </c>
       <c r="G725" t="s">
         <v>20</v>
@@ -23655,13 +23655,13 @@
         <v>9</v>
       </c>
       <c r="D726" t="s">
-        <v>1747</v>
+        <v>1769</v>
       </c>
       <c r="E726" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="F726" t="s">
-        <v>1770</v>
+        <v>1749</v>
       </c>
       <c r="G726" t="s">
         <v>20</v>
@@ -23678,13 +23678,13 @@
         <v>9</v>
       </c>
       <c r="D727" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E727" t="s">
         <v>1748</v>
       </c>
       <c r="F727" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G727" t="s">
         <v>1235</v>
@@ -23701,13 +23701,13 @@
         <v>9</v>
       </c>
       <c r="D728" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E728" t="s">
         <v>1748</v>
       </c>
       <c r="F728" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G728" t="s">
         <v>1235</v>
@@ -23724,13 +23724,13 @@
         <v>9</v>
       </c>
       <c r="D729" t="s">
-        <v>1747</v>
+        <v>1777</v>
       </c>
       <c r="E729" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="F729" t="s">
-        <v>1778</v>
+        <v>1749</v>
       </c>
       <c r="G729" t="s">
         <v>34</v>
@@ -23747,13 +23747,13 @@
         <v>9</v>
       </c>
       <c r="D730" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E730" t="s">
         <v>1748</v>
       </c>
       <c r="F730" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G730" t="s">
         <v>16</v>
@@ -23770,13 +23770,13 @@
         <v>9</v>
       </c>
       <c r="D731" t="s">
-        <v>1747</v>
+        <v>1777</v>
       </c>
       <c r="E731" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="F731" t="s">
-        <v>1778</v>
+        <v>1749</v>
       </c>
       <c r="G731" t="s">
         <v>34</v>
@@ -23793,13 +23793,13 @@
         <v>9</v>
       </c>
       <c r="D732" t="s">
-        <v>1747</v>
+        <v>1785</v>
       </c>
       <c r="E732" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="F732" t="s">
-        <v>1786</v>
+        <v>1749</v>
       </c>
       <c r="G732" t="s">
         <v>34</v>
@@ -23816,13 +23816,13 @@
         <v>9</v>
       </c>
       <c r="D733" t="s">
-        <v>1747</v>
+        <v>1789</v>
       </c>
       <c r="E733" t="s">
         <v>1748</v>
       </c>
       <c r="F733" t="s">
-        <v>1789</v>
+        <v>1749</v>
       </c>
       <c r="G733" t="s">
         <v>34</v>
@@ -23839,13 +23839,13 @@
         <v>9</v>
       </c>
       <c r="D734" t="s">
-        <v>1747</v>
+        <v>1792</v>
       </c>
       <c r="E734" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="F734" t="s">
-        <v>1793</v>
+        <v>1749</v>
       </c>
       <c r="G734" t="s">
         <v>34</v>
@@ -23862,13 +23862,13 @@
         <v>9</v>
       </c>
       <c r="D735" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E735" t="s">
         <v>1748</v>
       </c>
       <c r="F735" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G735" t="s">
         <v>1235</v>
@@ -23885,13 +23885,13 @@
         <v>9</v>
       </c>
       <c r="D736" t="s">
-        <v>1747</v>
+        <v>1798</v>
       </c>
       <c r="E736" t="s">
         <v>1748</v>
       </c>
       <c r="F736" t="s">
-        <v>1798</v>
+        <v>1749</v>
       </c>
       <c r="G736" t="s">
         <v>1235</v>
@@ -23908,13 +23908,13 @@
         <v>9</v>
       </c>
       <c r="D737" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E737" t="s">
         <v>1748</v>
       </c>
       <c r="F737" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G737" t="s">
         <v>20</v>
@@ -23931,13 +23931,13 @@
         <v>9</v>
       </c>
       <c r="D738" t="s">
-        <v>1747</v>
+        <v>1803</v>
       </c>
       <c r="E738" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="F738" t="s">
-        <v>1803</v>
+        <v>1749</v>
       </c>
       <c r="G738" t="s">
         <v>20</v>
@@ -23954,13 +23954,13 @@
         <v>9</v>
       </c>
       <c r="D739" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E739" t="s">
         <v>1748</v>
       </c>
       <c r="F739" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G739" t="s">
         <v>1235</v>
@@ -23977,13 +23977,13 @@
         <v>9</v>
       </c>
       <c r="D740" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E740" t="s">
         <v>1748</v>
       </c>
       <c r="F740" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G740" t="s">
         <v>1235</v>
@@ -24000,13 +24000,13 @@
         <v>9</v>
       </c>
       <c r="D741" t="s">
-        <v>1747</v>
+        <v>1810</v>
       </c>
       <c r="E741" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="F741" t="s">
-        <v>1811</v>
+        <v>1749</v>
       </c>
       <c r="G741" t="s">
         <v>34</v>
@@ -24023,13 +24023,13 @@
         <v>9</v>
       </c>
       <c r="D742" t="s">
-        <v>1747</v>
+        <v>1814</v>
       </c>
       <c r="E742" t="s">
         <v>1748</v>
       </c>
       <c r="F742" t="s">
-        <v>1814</v>
+        <v>1749</v>
       </c>
       <c r="G742" t="s">
         <v>20</v>
@@ -24046,13 +24046,13 @@
         <v>9</v>
       </c>
       <c r="D743" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E743" t="s">
         <v>1748</v>
       </c>
       <c r="F743" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G743" t="s">
         <v>1235</v>
@@ -24092,13 +24092,13 @@
         <v>9</v>
       </c>
       <c r="D745" t="s">
-        <v>1747</v>
+        <v>1821</v>
       </c>
       <c r="E745" t="s">
         <v>1748</v>
       </c>
       <c r="F745" t="s">
-        <v>1821</v>
+        <v>1749</v>
       </c>
       <c r="G745" t="s">
         <v>34</v>
@@ -24115,13 +24115,13 @@
         <v>9</v>
       </c>
       <c r="D746" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E746" t="s">
         <v>1748</v>
       </c>
       <c r="F746" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G746" t="s">
         <v>1235</v>
@@ -24138,13 +24138,13 @@
         <v>9</v>
       </c>
       <c r="D747" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E747" t="s">
         <v>1748</v>
       </c>
       <c r="F747" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G747" t="s">
         <v>1235</v>
@@ -24161,13 +24161,13 @@
         <v>9</v>
       </c>
       <c r="D748" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E748" t="s">
         <v>1748</v>
       </c>
       <c r="F748" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G748" t="s">
         <v>1235</v>
@@ -24184,13 +24184,13 @@
         <v>9</v>
       </c>
       <c r="D749" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E749" t="s">
         <v>1748</v>
       </c>
       <c r="F749" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G749" t="s">
         <v>1235</v>
@@ -24230,13 +24230,13 @@
         <v>9</v>
       </c>
       <c r="D751" t="s">
-        <v>1832</v>
+        <v>1837</v>
       </c>
       <c r="E751" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="F751" t="s">
-        <v>1838</v>
+        <v>1834</v>
       </c>
       <c r="G751" t="s">
         <v>34</v>
@@ -24253,13 +24253,13 @@
         <v>9</v>
       </c>
       <c r="D752" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="E752" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="F752" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G752" t="s">
         <v>1235</v>
@@ -24276,13 +24276,13 @@
         <v>9</v>
       </c>
       <c r="D753" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="E753" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="F753" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G753" t="s">
         <v>1235</v>
@@ -24299,13 +24299,13 @@
         <v>9</v>
       </c>
       <c r="D754" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="E754" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="F754" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G754" t="s">
         <v>1235</v>
@@ -24322,13 +24322,13 @@
         <v>9</v>
       </c>
       <c r="D755" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="E755" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="F755" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G755" t="s">
         <v>1235</v>
@@ -24345,13 +24345,13 @@
         <v>9</v>
       </c>
       <c r="D756" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="E756" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="F756" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G756" t="s">
         <v>1235</v>
@@ -24368,13 +24368,13 @@
         <v>9</v>
       </c>
       <c r="D757" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="E757" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="F757" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G757" t="s">
         <v>1235</v>
@@ -24394,7 +24394,7 @@
         <v>1832</v>
       </c>
       <c r="E758" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="F758" t="s">
         <v>1834</v>
@@ -24414,13 +24414,13 @@
         <v>9</v>
       </c>
       <c r="D759" t="s">
-        <v>1832</v>
+        <v>1798</v>
       </c>
       <c r="E759" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="F759" t="s">
-        <v>1798</v>
+        <v>1834</v>
       </c>
       <c r="G759" t="s">
         <v>20</v>
@@ -24437,13 +24437,13 @@
         <v>9</v>
       </c>
       <c r="D760" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="E760" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="F760" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G760" t="s">
         <v>1235</v>
@@ -24460,13 +24460,13 @@
         <v>9</v>
       </c>
       <c r="D761" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="E761" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="F761" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G761" t="s">
         <v>1235</v>
@@ -24483,13 +24483,13 @@
         <v>9</v>
       </c>
       <c r="D762" t="s">
-        <v>1832</v>
+        <v>1798</v>
       </c>
       <c r="E762" t="s">
         <v>1863</v>
       </c>
       <c r="F762" t="s">
-        <v>1798</v>
+        <v>1834</v>
       </c>
       <c r="G762" t="s">
         <v>34</v>
@@ -24506,13 +24506,13 @@
         <v>9</v>
       </c>
       <c r="D763" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="E763" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="F763" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G763" t="s">
         <v>1235</v>
@@ -24529,13 +24529,13 @@
         <v>9</v>
       </c>
       <c r="D764" t="s">
-        <v>1832</v>
+        <v>1868</v>
       </c>
       <c r="E764" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="F764" t="s">
-        <v>1869</v>
+        <v>1834</v>
       </c>
       <c r="G764" t="s">
         <v>34</v>
@@ -24552,13 +24552,13 @@
         <v>9</v>
       </c>
       <c r="D765" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="E765" t="s">
         <v>1833</v>
       </c>
       <c r="F765" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G765" t="s">
         <v>34</v>
@@ -24575,13 +24575,13 @@
         <v>9</v>
       </c>
       <c r="D766" t="s">
-        <v>1832</v>
+        <v>1874</v>
       </c>
       <c r="E766" t="s">
         <v>1863</v>
       </c>
       <c r="F766" t="s">
-        <v>1874</v>
+        <v>1834</v>
       </c>
       <c r="G766" t="s">
         <v>34</v>
@@ -24598,13 +24598,13 @@
         <v>9</v>
       </c>
       <c r="D767" t="s">
-        <v>1832</v>
+        <v>1877</v>
       </c>
       <c r="E767" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="F767" t="s">
-        <v>1878</v>
+        <v>1834</v>
       </c>
       <c r="G767" t="s">
         <v>34</v>
@@ -24621,13 +24621,13 @@
         <v>9</v>
       </c>
       <c r="D768" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="E768" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="F768" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G768" t="s">
         <v>1235</v>
@@ -24644,13 +24644,13 @@
         <v>9</v>
       </c>
       <c r="D769" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="E769" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="F769" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G769" t="s">
         <v>1235</v>
@@ -24667,13 +24667,13 @@
         <v>9</v>
       </c>
       <c r="D770" t="s">
-        <v>1832</v>
+        <v>1885</v>
       </c>
       <c r="E770" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="F770" t="s">
-        <v>1886</v>
+        <v>1834</v>
       </c>
       <c r="G770" t="s">
         <v>34</v>
@@ -24690,13 +24690,13 @@
         <v>9</v>
       </c>
       <c r="D771" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="E771" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="F771" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G771" t="s">
         <v>1235</v>
@@ -24713,13 +24713,13 @@
         <v>9</v>
       </c>
       <c r="D772" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="E772" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="F772" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G772" t="s">
         <v>1235</v>
@@ -24736,13 +24736,13 @@
         <v>9</v>
       </c>
       <c r="D773" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="E773" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="F773" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G773" t="s">
         <v>1235</v>
@@ -24759,13 +24759,13 @@
         <v>9</v>
       </c>
       <c r="D774" t="s">
-        <v>1832</v>
+        <v>1895</v>
       </c>
       <c r="E774" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="F774" t="s">
-        <v>1896</v>
+        <v>1834</v>
       </c>
       <c r="G774" t="s">
         <v>34</v>
@@ -24782,13 +24782,13 @@
         <v>9</v>
       </c>
       <c r="D775" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="E775" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="F775" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G775" t="s">
         <v>1235</v>
@@ -24828,13 +24828,13 @@
         <v>9</v>
       </c>
       <c r="D777" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E777" t="s">
         <v>1902</v>
       </c>
       <c r="F777" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G777" t="s">
         <v>1235</v>
@@ -24851,13 +24851,13 @@
         <v>9</v>
       </c>
       <c r="D778" t="s">
-        <v>1901</v>
+        <v>1909</v>
       </c>
       <c r="E778" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="F778" t="s">
-        <v>1910</v>
+        <v>1903</v>
       </c>
       <c r="G778" t="s">
         <v>34</v>
@@ -24874,13 +24874,13 @@
         <v>9</v>
       </c>
       <c r="D779" t="s">
-        <v>1901</v>
+        <v>1913</v>
       </c>
       <c r="E779" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="F779" t="s">
-        <v>1914</v>
+        <v>1903</v>
       </c>
       <c r="G779" t="s">
         <v>34</v>
@@ -24897,13 +24897,13 @@
         <v>9</v>
       </c>
       <c r="D780" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E780" t="s">
         <v>1902</v>
       </c>
       <c r="F780" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G780" t="s">
         <v>1235</v>
@@ -24920,13 +24920,13 @@
         <v>9</v>
       </c>
       <c r="D781" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E781" t="s">
         <v>1902</v>
       </c>
       <c r="F781" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G781" t="s">
         <v>1235</v>
@@ -24943,13 +24943,13 @@
         <v>9</v>
       </c>
       <c r="D782" t="s">
-        <v>1901</v>
+        <v>1921</v>
       </c>
       <c r="E782" t="s">
         <v>1902</v>
       </c>
       <c r="F782" t="s">
-        <v>1921</v>
+        <v>1903</v>
       </c>
       <c r="G782" t="s">
         <v>1235</v>
@@ -24966,13 +24966,13 @@
         <v>9</v>
       </c>
       <c r="D783" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E783" t="s">
         <v>1902</v>
       </c>
       <c r="F783" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G783" t="s">
         <v>1235</v>
@@ -24989,13 +24989,13 @@
         <v>9</v>
       </c>
       <c r="D784" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E784" t="s">
         <v>1902</v>
       </c>
       <c r="F784" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G784" t="s">
         <v>1235</v>
@@ -25012,13 +25012,13 @@
         <v>9</v>
       </c>
       <c r="D785" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E785" t="s">
         <v>1902</v>
       </c>
       <c r="F785" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G785" t="s">
         <v>1235</v>
@@ -25035,13 +25035,13 @@
         <v>9</v>
       </c>
       <c r="D786" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E786" t="s">
         <v>1902</v>
       </c>
       <c r="F786" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G786" t="s">
         <v>1235</v>
@@ -25058,13 +25058,13 @@
         <v>9</v>
       </c>
       <c r="D787" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E787" t="s">
         <v>1902</v>
       </c>
       <c r="F787" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G787" t="s">
         <v>1235</v>
@@ -25081,13 +25081,13 @@
         <v>9</v>
       </c>
       <c r="D788" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E788" t="s">
         <v>1902</v>
       </c>
       <c r="F788" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G788" t="s">
         <v>1235</v>
@@ -25127,13 +25127,13 @@
         <v>9</v>
       </c>
       <c r="D790" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E790" t="s">
         <v>1902</v>
       </c>
       <c r="F790" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G790" t="s">
         <v>1235</v>
@@ -25150,13 +25150,13 @@
         <v>9</v>
       </c>
       <c r="D791" t="s">
-        <v>1901</v>
+        <v>1921</v>
       </c>
       <c r="E791" t="s">
         <v>1941</v>
       </c>
       <c r="F791" t="s">
-        <v>1921</v>
+        <v>1903</v>
       </c>
       <c r="G791" t="s">
         <v>34</v>
@@ -25173,13 +25173,13 @@
         <v>9</v>
       </c>
       <c r="D792" t="s">
-        <v>1901</v>
+        <v>1944</v>
       </c>
       <c r="E792" t="s">
         <v>1936</v>
       </c>
       <c r="F792" t="s">
-        <v>1944</v>
+        <v>1903</v>
       </c>
       <c r="G792" t="s">
         <v>34</v>
@@ -25196,13 +25196,13 @@
         <v>9</v>
       </c>
       <c r="D793" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E793" t="s">
         <v>1902</v>
       </c>
       <c r="F793" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G793" t="s">
         <v>1235</v>
@@ -25219,13 +25219,13 @@
         <v>9</v>
       </c>
       <c r="D794" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E794" t="s">
         <v>1949</v>
       </c>
       <c r="F794" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G794" t="s">
         <v>34</v>
@@ -25242,13 +25242,13 @@
         <v>9</v>
       </c>
       <c r="D795" t="s">
-        <v>1901</v>
+        <v>1952</v>
       </c>
       <c r="E795" t="s">
         <v>1902</v>
       </c>
       <c r="F795" t="s">
-        <v>1952</v>
+        <v>1903</v>
       </c>
       <c r="G795" t="s">
         <v>34</v>
@@ -25265,13 +25265,13 @@
         <v>9</v>
       </c>
       <c r="D796" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E796" t="s">
         <v>1902</v>
       </c>
       <c r="F796" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G796" t="s">
         <v>1235</v>
@@ -25288,13 +25288,13 @@
         <v>9</v>
       </c>
       <c r="D797" t="s">
-        <v>1901</v>
+        <v>1957</v>
       </c>
       <c r="E797" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="F797" t="s">
-        <v>1958</v>
+        <v>1903</v>
       </c>
       <c r="G797" t="s">
         <v>34</v>
@@ -25311,13 +25311,13 @@
         <v>9</v>
       </c>
       <c r="D798" t="s">
-        <v>1901</v>
+        <v>1961</v>
       </c>
       <c r="E798" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="F798" t="s">
-        <v>1962</v>
+        <v>1903</v>
       </c>
       <c r="G798" t="s">
         <v>34</v>
@@ -25334,13 +25334,13 @@
         <v>9</v>
       </c>
       <c r="D799" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E799" t="s">
         <v>1902</v>
       </c>
       <c r="F799" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G799" t="s">
         <v>1235</v>
@@ -25357,13 +25357,13 @@
         <v>9</v>
       </c>
       <c r="D800" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E800" t="s">
         <v>1902</v>
       </c>
       <c r="F800" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G800" t="s">
         <v>1235</v>
@@ -25380,13 +25380,13 @@
         <v>9</v>
       </c>
       <c r="D801" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E801" t="s">
         <v>1902</v>
       </c>
       <c r="F801" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G801" t="s">
         <v>1235</v>
@@ -25403,13 +25403,13 @@
         <v>9</v>
       </c>
       <c r="D802" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E802" t="s">
         <v>1902</v>
       </c>
       <c r="F802" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G802" t="s">
         <v>1235</v>
@@ -25426,13 +25426,13 @@
         <v>9</v>
       </c>
       <c r="D803" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E803" t="s">
         <v>1902</v>
       </c>
       <c r="F803" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G803" t="s">
         <v>1235</v>
@@ -25449,13 +25449,13 @@
         <v>9</v>
       </c>
       <c r="D804" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E804" t="s">
         <v>1902</v>
       </c>
       <c r="F804" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G804" t="s">
         <v>1235</v>
@@ -25472,13 +25472,13 @@
         <v>9</v>
       </c>
       <c r="D805" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E805" t="s">
         <v>1902</v>
       </c>
       <c r="F805" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G805" t="s">
         <v>1235</v>
@@ -25495,13 +25495,13 @@
         <v>9</v>
       </c>
       <c r="D806" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E806" t="s">
         <v>1902</v>
       </c>
       <c r="F806" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G806" t="s">
         <v>1235</v>
@@ -25518,13 +25518,13 @@
         <v>9</v>
       </c>
       <c r="D807" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E807" t="s">
         <v>1902</v>
       </c>
       <c r="F807" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G807" t="s">
         <v>1235</v>
@@ -25610,13 +25610,13 @@
         <v>9</v>
       </c>
       <c r="D811" t="s">
-        <v>1983</v>
+        <v>1992</v>
       </c>
       <c r="E811" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="F811" t="s">
-        <v>1993</v>
+        <v>1985</v>
       </c>
       <c r="G811" t="s">
         <v>34</v>
@@ -25679,13 +25679,13 @@
         <v>9</v>
       </c>
       <c r="D814" t="s">
-        <v>1983</v>
+        <v>1992</v>
       </c>
       <c r="E814" t="s">
         <v>1984</v>
       </c>
       <c r="F814" t="s">
-        <v>1993</v>
+        <v>1985</v>
       </c>
       <c r="G814" t="s">
         <v>1235</v>
@@ -25702,13 +25702,13 @@
         <v>9</v>
       </c>
       <c r="D815" t="s">
-        <v>1983</v>
+        <v>2002</v>
       </c>
       <c r="E815" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="F815" t="s">
-        <v>2003</v>
+        <v>1985</v>
       </c>
       <c r="G815" t="s">
         <v>34</v>
@@ -25840,13 +25840,13 @@
         <v>9</v>
       </c>
       <c r="D821" t="s">
-        <v>1983</v>
+        <v>2016</v>
       </c>
       <c r="E821" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="F821" t="s">
-        <v>2017</v>
+        <v>1985</v>
       </c>
       <c r="G821" t="s">
         <v>20</v>
@@ -25863,13 +25863,13 @@
         <v>9</v>
       </c>
       <c r="D822" t="s">
-        <v>1983</v>
+        <v>2020</v>
       </c>
       <c r="E822" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="F822" t="s">
-        <v>2021</v>
+        <v>1985</v>
       </c>
       <c r="G822" t="s">
         <v>1235</v>
@@ -25886,13 +25886,13 @@
         <v>9</v>
       </c>
       <c r="D823" t="s">
-        <v>1983</v>
+        <v>2020</v>
       </c>
       <c r="E823" t="s">
         <v>1984</v>
       </c>
       <c r="F823" t="s">
-        <v>2021</v>
+        <v>1985</v>
       </c>
       <c r="G823" t="s">
         <v>1235</v>
@@ -25909,13 +25909,13 @@
         <v>9</v>
       </c>
       <c r="D824" t="s">
-        <v>1983</v>
+        <v>2020</v>
       </c>
       <c r="E824" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="F824" t="s">
-        <v>2021</v>
+        <v>1985</v>
       </c>
       <c r="G824" t="s">
         <v>1235</v>
@@ -25932,13 +25932,13 @@
         <v>9</v>
       </c>
       <c r="D825" t="s">
-        <v>1983</v>
+        <v>2020</v>
       </c>
       <c r="E825" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="F825" t="s">
-        <v>2021</v>
+        <v>1985</v>
       </c>
       <c r="G825" t="s">
         <v>1235</v>
@@ -25955,13 +25955,13 @@
         <v>9</v>
       </c>
       <c r="D826" t="s">
-        <v>1983</v>
+        <v>2020</v>
       </c>
       <c r="E826" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="F826" t="s">
-        <v>2021</v>
+        <v>1985</v>
       </c>
       <c r="G826" t="s">
         <v>1235</v>
@@ -25978,13 +25978,13 @@
         <v>9</v>
       </c>
       <c r="D827" t="s">
-        <v>1983</v>
+        <v>2020</v>
       </c>
       <c r="E827" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="F827" t="s">
-        <v>2021</v>
+        <v>1985</v>
       </c>
       <c r="G827" t="s">
         <v>1235</v>
@@ -26001,13 +26001,13 @@
         <v>9</v>
       </c>
       <c r="D828" t="s">
-        <v>1983</v>
+        <v>2020</v>
       </c>
       <c r="E828" t="s">
         <v>1984</v>
       </c>
       <c r="F828" t="s">
-        <v>2021</v>
+        <v>1985</v>
       </c>
       <c r="G828" t="s">
         <v>1235</v>
@@ -26047,13 +26047,13 @@
         <v>9</v>
       </c>
       <c r="D830" t="s">
-        <v>1983</v>
+        <v>1992</v>
       </c>
       <c r="E830" t="s">
         <v>1984</v>
       </c>
       <c r="F830" t="s">
-        <v>1993</v>
+        <v>1985</v>
       </c>
       <c r="G830" t="s">
         <v>1235</v>
@@ -26277,13 +26277,13 @@
         <v>9</v>
       </c>
       <c r="D840" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E840" t="s">
         <v>2057</v>
       </c>
       <c r="F840" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G840" t="s">
         <v>1235</v>
@@ -26300,13 +26300,13 @@
         <v>9</v>
       </c>
       <c r="D841" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E841" t="s">
         <v>2057</v>
       </c>
       <c r="F841" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G841" t="s">
         <v>1235</v>
@@ -26323,13 +26323,13 @@
         <v>9</v>
       </c>
       <c r="D842" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E842" t="s">
         <v>2057</v>
       </c>
       <c r="F842" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G842" t="s">
         <v>1235</v>
@@ -26346,13 +26346,13 @@
         <v>9</v>
       </c>
       <c r="D843" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E843" t="s">
         <v>2057</v>
       </c>
       <c r="F843" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G843" t="s">
         <v>1235</v>
@@ -26369,13 +26369,13 @@
         <v>9</v>
       </c>
       <c r="D844" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E844" t="s">
         <v>2057</v>
       </c>
       <c r="F844" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G844" t="s">
         <v>1235</v>
@@ -26392,13 +26392,13 @@
         <v>9</v>
       </c>
       <c r="D845" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E845" t="s">
         <v>2057</v>
       </c>
       <c r="F845" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G845" t="s">
         <v>1235</v>
@@ -26415,13 +26415,13 @@
         <v>9</v>
       </c>
       <c r="D846" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E846" t="s">
         <v>2057</v>
       </c>
       <c r="F846" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G846" t="s">
         <v>1235</v>
@@ -26438,13 +26438,13 @@
         <v>9</v>
       </c>
       <c r="D847" t="s">
-        <v>2056</v>
+        <v>2076</v>
       </c>
       <c r="E847" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="F847" t="s">
-        <v>2076</v>
+        <v>2058</v>
       </c>
       <c r="G847" t="s">
         <v>1235</v>
@@ -26461,13 +26461,13 @@
         <v>9</v>
       </c>
       <c r="D848" t="s">
-        <v>2056</v>
+        <v>2076</v>
       </c>
       <c r="E848" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="F848" t="s">
-        <v>2076</v>
+        <v>2058</v>
       </c>
       <c r="G848" t="s">
         <v>1235</v>
@@ -26484,13 +26484,13 @@
         <v>9</v>
       </c>
       <c r="D849" t="s">
-        <v>2056</v>
+        <v>2076</v>
       </c>
       <c r="E849" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="F849" t="s">
-        <v>2076</v>
+        <v>2058</v>
       </c>
       <c r="G849" t="s">
         <v>1235</v>
@@ -26507,13 +26507,13 @@
         <v>9</v>
       </c>
       <c r="D850" t="s">
-        <v>2056</v>
+        <v>2076</v>
       </c>
       <c r="E850" t="s">
         <v>2083</v>
       </c>
       <c r="F850" t="s">
-        <v>2076</v>
+        <v>2058</v>
       </c>
       <c r="G850" t="s">
         <v>1235</v>
@@ -26530,13 +26530,13 @@
         <v>9</v>
       </c>
       <c r="D851" t="s">
-        <v>2056</v>
+        <v>2076</v>
       </c>
       <c r="E851" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="F851" t="s">
-        <v>2076</v>
+        <v>2058</v>
       </c>
       <c r="G851" t="s">
         <v>1235</v>
@@ -26553,13 +26553,13 @@
         <v>9</v>
       </c>
       <c r="D852" t="s">
-        <v>2056</v>
+        <v>2076</v>
       </c>
       <c r="E852" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="F852" t="s">
-        <v>2076</v>
+        <v>2058</v>
       </c>
       <c r="G852" t="s">
         <v>1235</v>
@@ -26576,13 +26576,13 @@
         <v>9</v>
       </c>
       <c r="D853" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E853" t="s">
         <v>2057</v>
       </c>
       <c r="F853" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G853" t="s">
         <v>1235</v>
@@ -26599,13 +26599,13 @@
         <v>9</v>
       </c>
       <c r="D854" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E854" t="s">
         <v>2057</v>
       </c>
       <c r="F854" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G854" t="s">
         <v>20</v>
@@ -26622,13 +26622,13 @@
         <v>9</v>
       </c>
       <c r="D855" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E855" t="s">
         <v>2057</v>
       </c>
       <c r="F855" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G855" t="s">
         <v>20</v>
@@ -26645,13 +26645,13 @@
         <v>9</v>
       </c>
       <c r="D856" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E856" t="s">
         <v>2057</v>
       </c>
       <c r="F856" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G856" t="s">
         <v>20</v>
@@ -26668,13 +26668,13 @@
         <v>9</v>
       </c>
       <c r="D857" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E857" t="s">
         <v>2057</v>
       </c>
       <c r="F857" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G857" t="s">
         <v>1235</v>
@@ -26691,13 +26691,13 @@
         <v>9</v>
       </c>
       <c r="D858" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E858" t="s">
         <v>2057</v>
       </c>
       <c r="F858" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G858" t="s">
         <v>1235</v>
@@ -26714,13 +26714,13 @@
         <v>9</v>
       </c>
       <c r="D859" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E859" t="s">
         <v>2057</v>
       </c>
       <c r="F859" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G859" t="s">
         <v>20</v>
@@ -26737,13 +26737,13 @@
         <v>9</v>
       </c>
       <c r="D860" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E860" t="s">
         <v>2057</v>
       </c>
       <c r="F860" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G860" t="s">
         <v>1235</v>
@@ -26760,13 +26760,13 @@
         <v>9</v>
       </c>
       <c r="D861" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E861" t="s">
         <v>2057</v>
       </c>
       <c r="F861" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G861" t="s">
         <v>1235</v>
@@ -26783,13 +26783,13 @@
         <v>9</v>
       </c>
       <c r="D862" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E862" t="s">
         <v>2057</v>
       </c>
       <c r="F862" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G862" t="s">
         <v>1235</v>
@@ -26806,13 +26806,13 @@
         <v>9</v>
       </c>
       <c r="D863" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E863" t="s">
         <v>2057</v>
       </c>
       <c r="F863" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G863" t="s">
         <v>1235</v>
@@ -26829,13 +26829,13 @@
         <v>9</v>
       </c>
       <c r="D864" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E864" t="s">
         <v>2057</v>
       </c>
       <c r="F864" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G864" t="s">
         <v>1235</v>
@@ -26852,13 +26852,13 @@
         <v>9</v>
       </c>
       <c r="D865" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E865" t="s">
         <v>2057</v>
       </c>
       <c r="F865" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G865" t="s">
         <v>1235</v>
@@ -26875,13 +26875,13 @@
         <v>9</v>
       </c>
       <c r="D866" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E866" t="s">
         <v>2057</v>
       </c>
       <c r="F866" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G866" t="s">
         <v>1235</v>
@@ -27542,13 +27542,13 @@
         <v>9</v>
       </c>
       <c r="D895" t="s">
-        <v>2168</v>
+        <v>2181</v>
       </c>
       <c r="E895" t="s">
         <v>2169</v>
       </c>
       <c r="F895" t="s">
-        <v>2181</v>
+        <v>2170</v>
       </c>
       <c r="G895" t="s">
         <v>1235</v>
@@ -27772,13 +27772,13 @@
         <v>9</v>
       </c>
       <c r="D905" t="s">
-        <v>2200</v>
+        <v>2204</v>
       </c>
       <c r="E905" t="s">
         <v>2169</v>
       </c>
       <c r="F905" t="s">
-        <v>2204</v>
+        <v>2201</v>
       </c>
       <c r="G905" t="s">
         <v>1235</v>

--- a/api/2/clv3/xlsx/en/HumanitarianPlan.xlsx
+++ b/api/2/clv3/xlsx/en/HumanitarianPlan.xlsx
@@ -25,12 +25,12 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:plan-end-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-start-date</t>
   </si>
   <si>
-    <t>codeforiati:plan-end-date</t>
-  </si>
-  <si>
     <t>codeforiati:plan-year</t>
   </si>
   <si>
@@ -46,12 +46,12 @@
     <t>active</t>
   </si>
   <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
     <t>2025-01-01</t>
   </si>
   <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
     <t>2025</t>
   </si>
   <si>
@@ -355,12 +355,12 @@
     <t>Afghanistan Humanitarian Needs and Response Plan 2024</t>
   </si>
   <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
     <t>2024-01-01</t>
   </si>
   <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
     <t>2024</t>
   </si>
   <si>
@@ -712,12 +712,12 @@
     <t>Afghanistan Humanitarian Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
     <t>2023-01-01</t>
   </si>
   <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
     <t>2023</t>
   </si>
   <si>
@@ -841,24 +841,24 @@
     <t>Mongolia Dzud Early Action and Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-05-31</t>
+  </si>
+  <si>
     <t>2022-12-01</t>
   </si>
   <si>
-    <t>2023-05-31</t>
-  </si>
-  <si>
     <t>OMOZ23</t>
   </si>
   <si>
     <t>Mozambique Cyclone Freddy, Floods and Cholera Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-09-30</t>
+  </si>
+  <si>
     <t>2023-03-01</t>
   </si>
   <si>
-    <t>2023-09-30</t>
-  </si>
-  <si>
     <t>HMOZ23</t>
   </si>
   <si>
@@ -946,12 +946,12 @@
     <t>Sudan Emergency: Regional Refugee Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-10-31</t>
+  </si>
+  <si>
     <t>2023-05-01</t>
   </si>
   <si>
-    <t>2023-10-31</t>
-  </si>
-  <si>
     <t>HSDN23</t>
   </si>
   <si>
@@ -1030,12 +1030,12 @@
     <t>Afghanistan Humanitarian Response Plan 2022</t>
   </si>
   <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
     <t>2022-01-01</t>
   </si>
   <si>
-    <t>2022-12-31</t>
-  </si>
-  <si>
     <t>2022</t>
   </si>
   <si>
@@ -1081,12 +1081,12 @@
     <t>Cuba Hurricane Ian Response - Plan of Action 2022</t>
   </si>
   <si>
+    <t>2023-03-31</t>
+  </si>
+  <si>
     <t>2022-10-20</t>
   </si>
   <si>
-    <t>2023-03-31</t>
-  </si>
-  <si>
     <t>RDRCRRP22</t>
   </si>
   <si>
@@ -1117,12 +1117,12 @@
     <t>Haïti Choléra+ Appel Éclair 2022</t>
   </si>
   <si>
+    <t>2023-04-15</t>
+  </si>
+  <si>
     <t>2022-10-16</t>
   </si>
   <si>
-    <t>2023-04-15</t>
-  </si>
-  <si>
     <t>FHTI22</t>
   </si>
   <si>
@@ -1180,12 +1180,12 @@
     <t>Malawi Flash Appeal 2022</t>
   </si>
   <si>
+    <t>2022-05-31</t>
+  </si>
+  <si>
     <t>2022-02-26</t>
   </si>
   <si>
-    <t>2022-05-31</t>
-  </si>
-  <si>
     <t>HMLI22</t>
   </si>
   <si>
@@ -1198,12 +1198,12 @@
     <t>Mozambique Gombe Emergency Response Plan 2022</t>
   </si>
   <si>
+    <t>2022-09-30</t>
+  </si>
+  <si>
     <t>2022-04-01</t>
   </si>
   <si>
-    <t>2022-09-30</t>
-  </si>
-  <si>
     <t>HMOZ22</t>
   </si>
   <si>
@@ -1255,12 +1255,12 @@
     <t>Philippines Super Typhoon Rai (Odette) Humanitarian Needs and Priorities 2022</t>
   </si>
   <si>
+    <t>2022-06-30</t>
+  </si>
+  <si>
     <t>2021-12-24</t>
   </si>
   <si>
-    <t>2022-06-30</t>
-  </si>
-  <si>
     <t>RREG22</t>
   </si>
   <si>
@@ -1378,12 +1378,12 @@
     <t>Afghanistan Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021-12-31</t>
-  </si>
-  <si>
     <t>2021</t>
   </si>
   <si>
@@ -1477,12 +1477,12 @@
     <t>Escalation of Hostilities in the OPT Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-08-27</t>
+  </si>
+  <si>
     <t>2021-05-27</t>
   </si>
   <si>
-    <t>2021-08-27</t>
-  </si>
-  <si>
     <t>HETH21</t>
   </si>
   <si>
@@ -1507,12 +1507,12 @@
     <t>Haiti Earthquake Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2022-02-15</t>
+  </si>
+  <si>
     <t>2021-08-16</t>
   </si>
   <si>
-    <t>2022-02-15</t>
-  </si>
-  <si>
     <t>HHTI21</t>
   </si>
   <si>
@@ -1525,12 +1525,12 @@
     <t>Honduras Tropical Storm Eta Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
     <t>2020-11-15</t>
   </si>
   <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
     <t>HHND21</t>
   </si>
   <si>
@@ -1564,12 +1564,12 @@
     <t>Lebanon Emergency Response Plan 2021</t>
   </si>
   <si>
+    <t>2022-07-31</t>
+  </si>
+  <si>
     <t>2021-08-03</t>
   </si>
   <si>
-    <t>2022-07-31</t>
-  </si>
-  <si>
     <t>HLBY21</t>
   </si>
   <si>
@@ -1735,12 +1735,12 @@
     <t>Afghanistan Humanitarian Response Plan 2020</t>
   </si>
   <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
     <t>2020-01-01</t>
   </si>
   <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
     <t>2020</t>
   </si>
   <si>
@@ -1858,12 +1858,12 @@
     <t>Djibouti Flash Appeal 2020</t>
   </si>
   <si>
+    <t>2020-03-31</t>
+  </si>
+  <si>
     <t>2019-12-17</t>
   </si>
   <si>
-    <t>2020-03-31</t>
-  </si>
-  <si>
     <t>ODJI20</t>
   </si>
   <si>
@@ -1957,12 +1957,12 @@
     <t>Lebanon Flash Appeal 2020</t>
   </si>
   <si>
+    <t>2020-11-13</t>
+  </si>
+  <si>
     <t>2020-08-05</t>
   </si>
   <si>
-    <t>2020-11-13</t>
-  </si>
-  <si>
     <t>OLBN20</t>
   </si>
   <si>
@@ -1975,12 +1975,12 @@
     <t>Lesotho Flash Appeal 2019-2020</t>
   </si>
   <si>
+    <t>2020-04-30</t>
+  </si>
+  <si>
     <t>2019-11-01</t>
   </si>
   <si>
-    <t>2020-04-30</t>
-  </si>
-  <si>
     <t>OLBR20</t>
   </si>
   <si>
@@ -2170,12 +2170,12 @@
     <t>Afghanistan Humanitarian Response Plan 2019</t>
   </si>
   <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
     <t>2019-01-01</t>
   </si>
   <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
     <t>2019</t>
   </si>
   <si>
@@ -2386,12 +2386,12 @@
     <t>Zimbabwe Flash Appeal 2019</t>
   </si>
   <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
     <t>2019-02-01</t>
   </si>
   <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
     <t>FZWE1820</t>
   </si>
   <si>
@@ -2407,12 +2407,12 @@
     <t>Afghanistan Humanitarian Response Plan 2018</t>
   </si>
   <si>
+    <t>2018-12-31</t>
+  </si>
+  <si>
     <t>2018-01-01</t>
   </si>
   <si>
-    <t>2018-12-31</t>
-  </si>
-  <si>
     <t>2018</t>
   </si>
   <si>
@@ -2590,12 +2590,12 @@
     <t>Syrian Arab Republic Humanitarian Response Plan 2018</t>
   </si>
   <si>
+    <t>2018-12-30</t>
+  </si>
+  <si>
     <t>2018-11-30</t>
   </si>
   <si>
-    <t>2018-12-30</t>
-  </si>
-  <si>
     <t>RSYR18</t>
   </si>
   <si>
@@ -2632,12 +2632,12 @@
     <t>2017 Europe Situation - Regional Refugee and Migrant Response</t>
   </si>
   <si>
+    <t>2017-12-31</t>
+  </si>
+  <si>
     <t>2017-01-01</t>
   </si>
   <si>
-    <t>2017-12-31</t>
-  </si>
-  <si>
     <t>2017</t>
   </si>
   <si>
@@ -2716,12 +2716,12 @@
     <t>Dominica Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-12-29</t>
+  </si>
+  <si>
     <t>2017-09-28</t>
   </si>
   <si>
-    <t>2017-12-29</t>
-  </si>
-  <si>
     <t>OPRK17</t>
   </si>
   <si>
@@ -2761,12 +2761,12 @@
     <t>Kenya Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-11-30</t>
+  </si>
+  <si>
     <t>2017-02-10</t>
   </si>
   <si>
-    <t>2017-11-30</t>
-  </si>
-  <si>
     <t>HLBY17</t>
   </si>
   <si>
@@ -2779,12 +2779,12 @@
     <t>Madagascar Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
     <t>2017-03-20</t>
   </si>
   <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
     <t>HMLI17</t>
   </si>
   <si>
@@ -2803,12 +2803,12 @@
     <t>Mozambique Cyclone Dineo Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-05-31</t>
+  </si>
+  <si>
     <t>2017-02-28</t>
   </si>
   <si>
-    <t>2017-05-31</t>
-  </si>
-  <si>
     <t>HMMR17</t>
   </si>
   <si>
@@ -2845,12 +2845,12 @@
     <t>Peru Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-10-31</t>
+  </si>
+  <si>
     <t>2017-04-01</t>
   </si>
   <si>
-    <t>2017-10-31</t>
-  </si>
-  <si>
     <t>HCOG17</t>
   </si>
   <si>
@@ -2920,12 +2920,12 @@
     <t>2016 Europe Situation -Regional Refugee and Migrant Response</t>
   </si>
   <si>
+    <t>2016-12-31</t>
+  </si>
+  <si>
     <t>2016-01-01</t>
   </si>
   <si>
-    <t>2016-12-31</t>
-  </si>
-  <si>
     <t>2016</t>
   </si>
   <si>
@@ -3001,24 +3001,24 @@
     <t>Ecuador Earthquake Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-10-31</t>
+  </si>
+  <si>
     <t>2016-04-16</t>
   </si>
   <si>
-    <t>2016-10-31</t>
-  </si>
-  <si>
     <t>FFJI16</t>
   </si>
   <si>
     <t>Fiji Tropical Cyclone Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-05-30</t>
+  </si>
+  <si>
     <t>2016-02-20</t>
   </si>
   <si>
-    <t>2016-05-30</t>
-  </si>
-  <si>
     <t>HGMB16</t>
   </si>
   <si>
@@ -3094,12 +3094,12 @@
     <t>Mosul Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-10-01</t>
+  </si>
+  <si>
     <t>2016-07-20</t>
   </si>
   <si>
-    <t>2016-10-01</t>
-  </si>
-  <si>
     <t>HMMR16</t>
   </si>
   <si>
@@ -3184,24 +3184,24 @@
     <t>Zimbabwe Humanitarian Response Plan 2016</t>
   </si>
   <si>
+    <t>2017-03-31</t>
+  </si>
+  <si>
     <t>2016-04-01</t>
   </si>
   <si>
-    <t>2017-03-31</t>
-  </si>
-  <si>
     <t>HAFG15</t>
   </si>
   <si>
     <t>Afghanistan Strategic Response Plan 2015</t>
   </si>
   <si>
+    <t>2015-12-31</t>
+  </si>
+  <si>
     <t>2015-01-01</t>
   </si>
   <si>
-    <t>2015-12-31</t>
-  </si>
-  <si>
     <t>2015</t>
   </si>
   <si>
@@ -3262,12 +3262,12 @@
     <t>Guatemala Plan de Respuesta Sequia 2015</t>
   </si>
   <si>
+    <t>2015-09-30</t>
+  </si>
+  <si>
     <t>2014-11-03</t>
   </si>
   <si>
-    <t>2015-09-30</t>
-  </si>
-  <si>
     <t>FHTI15</t>
   </si>
   <si>
@@ -3292,12 +3292,12 @@
     <t>Vanuatu Emergency Response Plan for Tropical Cyclone PAM 2015</t>
   </si>
   <si>
+    <t>2015-10-31</t>
+  </si>
+  <si>
     <t>2015-03-24</t>
   </si>
   <si>
-    <t>2015-10-31</t>
-  </si>
-  <si>
     <t>HIRQ15</t>
   </si>
   <si>
@@ -3310,12 +3310,12 @@
     <t>Libya Humanitarian Appeal 2014- 2015</t>
   </si>
   <si>
+    <t>2015-05-31</t>
+  </si>
+  <si>
     <t>2014-10-01</t>
   </si>
   <si>
-    <t>2015-05-31</t>
-  </si>
-  <si>
     <t>HMLI15</t>
   </si>
   <si>
@@ -3427,12 +3427,12 @@
     <t>Afghanistan Strategic Response Plan 2014</t>
   </si>
   <si>
+    <t>2014-12-31</t>
+  </si>
+  <si>
     <t>2014-01-01</t>
   </si>
   <si>
-    <t>2014-12-31</t>
-  </si>
-  <si>
     <t>2014</t>
   </si>
   <si>
@@ -3571,24 +3571,24 @@
     <t>Philippines Bohol Earthquake Flash Appeal 2014</t>
   </si>
   <si>
+    <t>2014-04-22</t>
+  </si>
+  <si>
     <t>2013-10-22</t>
   </si>
   <si>
-    <t>2014-04-22</t>
-  </si>
-  <si>
     <t>SPHL1314</t>
   </si>
   <si>
     <t>Philippines Typhoon Haiyan Strategic Response Plan 2014</t>
   </si>
   <si>
+    <t>2014-11-07</t>
+  </si>
+  <si>
     <t>2013-11-08</t>
   </si>
   <si>
-    <t>2014-11-07</t>
-  </si>
-  <si>
     <t>HPHL1314</t>
   </si>
   <si>
@@ -3604,12 +3604,12 @@
     <t>Philippines Zamboanga Crisis Flash Appeal 2014</t>
   </si>
   <si>
+    <t>2014-08-31</t>
+  </si>
+  <si>
     <t>2013-10-01</t>
   </si>
   <si>
-    <t>2014-08-31</t>
-  </si>
-  <si>
     <t>SCOD14</t>
   </si>
   <si>
@@ -3877,12 +3877,12 @@
     <t>2012+ Kenya Emergency Humanitarian Response Plan</t>
   </si>
   <si>
+    <t>2012-12-31</t>
+  </si>
+  <si>
     <t>2012-01-01</t>
   </si>
   <si>
-    <t>2012-12-31</t>
-  </si>
-  <si>
     <t>2012</t>
   </si>
   <si>
@@ -3955,12 +3955,12 @@
     <t>Lesotho Food Insecurity (September 2012 - March 2013)</t>
   </si>
   <si>
+    <t>2013-03-25</t>
+  </si>
+  <si>
     <t>2012-09-18</t>
   </si>
   <si>
-    <t>2013-03-25</t>
-  </si>
-  <si>
     <t>CLBR12</t>
   </si>
   <si>
@@ -4033,12 +4033,12 @@
     <t>Syria Humanitarian Assistance Response Plan (SHARP) 2012</t>
   </si>
   <si>
+    <t>2012-12-05</t>
+  </si>
+  <si>
     <t>2012-06-05</t>
   </si>
   <si>
-    <t>2012-12-05</t>
-  </si>
-  <si>
     <t>CYEM12</t>
   </si>
   <si>
@@ -4111,12 +4111,12 @@
     <t>El Salvador Flash Appeal (October 2011 - April 2012)</t>
   </si>
   <si>
+    <t>2012-04-25</t>
+  </si>
+  <si>
     <t>2011-10-25</t>
   </si>
   <si>
-    <t>2012-04-25</t>
-  </si>
-  <si>
     <t>CHTI1011</t>
   </si>
   <si>
@@ -4147,24 +4147,24 @@
     <t>Namibia Flash Appeal (April - October 2011)</t>
   </si>
   <si>
+    <t>2011-10-11</t>
+  </si>
+  <si>
     <t>2011-04-11</t>
   </si>
   <si>
-    <t>2011-10-11</t>
-  </si>
-  <si>
     <t>FNIC1112</t>
   </si>
   <si>
     <t>Nicaragua Flash Appeal (October 2011 - April 2012)</t>
   </si>
   <si>
+    <t>2012-04-26</t>
+  </si>
+  <si>
     <t>2011-10-27</t>
   </si>
   <si>
-    <t>2012-04-26</t>
-  </si>
-  <si>
     <t>CNER11</t>
   </si>
   <si>
@@ -4177,12 +4177,12 @@
     <t>Pakistan Rapid Response Plan Floods 2011 (September - March 2012)</t>
   </si>
   <si>
+    <t>2012-06-30</t>
+  </si>
+  <si>
     <t>2011-09-15</t>
   </si>
   <si>
-    <t>2012-06-30</t>
-  </si>
-  <si>
     <t>FXLBYREG11</t>
   </si>
   <si>
@@ -4258,12 +4258,12 @@
     <t>Afghanistan Humanitarian Action Plan 2010</t>
   </si>
   <si>
+    <t>2010-12-31</t>
+  </si>
+  <si>
     <t>2010-01-01</t>
   </si>
   <si>
-    <t>2010-12-31</t>
-  </si>
-  <si>
     <t>2010</t>
   </si>
   <si>
@@ -4273,12 +4273,12 @@
     <t>Burkina Faso Emergency Humanitarian Action Plan 2010</t>
   </si>
   <si>
+    <t>2011-01-31</t>
+  </si>
+  <si>
     <t>2010-08-01</t>
   </si>
   <si>
-    <t>2011-01-31</t>
-  </si>
-  <si>
     <t>CCAF10</t>
   </si>
   <si>
@@ -4303,36 +4303,36 @@
     <t>El Salvador Flash Appeal (Revised) (November 2009 - May 2010)</t>
   </si>
   <si>
+    <t>2010-05-31</t>
+  </si>
+  <si>
     <t>2009-11-01</t>
   </si>
   <si>
-    <t>2010-05-31</t>
-  </si>
-  <si>
     <t>FGTM10</t>
   </si>
   <si>
     <t>Guatemala Flash Appeal (Revised) (June - December 2010)</t>
   </si>
   <si>
+    <t>2010-12-09</t>
+  </si>
+  <si>
     <t>2010-06-10</t>
   </si>
   <si>
-    <t>2010-12-09</t>
-  </si>
-  <si>
     <t>CGTM10</t>
   </si>
   <si>
     <t>Guatemala Food Insecurity and Acute Malnutrition Appeal 2010</t>
   </si>
   <si>
+    <t>2010-08-11</t>
+  </si>
+  <si>
     <t>2010-02-12</t>
   </si>
   <si>
-    <t>2010-08-11</t>
-  </si>
-  <si>
     <t>FHTI10</t>
   </si>
   <si>
@@ -4360,12 +4360,12 @@
     <t>Kyrgyzstan Flash Appeal (Revised) (June 2010 - June 2011)</t>
   </si>
   <si>
+    <t>2011-06-30</t>
+  </si>
+  <si>
     <t>2010-06-01</t>
   </si>
   <si>
-    <t>2011-06-30</t>
-  </si>
-  <si>
     <t>CMNG1011</t>
   </si>
   <si>
@@ -4468,12 +4468,12 @@
     <t>Afghanistan Humanitarian Action Plan 2009</t>
   </si>
   <si>
+    <t>2009-12-31</t>
+  </si>
+  <si>
     <t>2009-01-01</t>
   </si>
   <si>
-    <t>2009-12-31</t>
-  </si>
-  <si>
     <t>2009</t>
   </si>
   <si>
@@ -4483,12 +4483,12 @@
     <t>Burkina Faso Flash Appeal (September 2009 - February 2010)</t>
   </si>
   <si>
+    <t>2010-03-09</t>
+  </si>
+  <si>
     <t>2009-09-10</t>
   </si>
   <si>
-    <t>2010-03-09</t>
-  </si>
-  <si>
     <t>CCAF09</t>
   </si>
   <si>
@@ -4552,24 +4552,24 @@
     <t>Madagascar Flash Appeal (Revised) (April - October 2009)</t>
   </si>
   <si>
+    <t>2009-10-31</t>
+  </si>
+  <si>
     <t>2009-04-01</t>
   </si>
   <si>
-    <t>2009-10-31</t>
-  </si>
-  <si>
     <t>FNAM09</t>
   </si>
   <si>
     <t>Namibia Flash Appeal (Revised) (March - November 2009)</t>
   </si>
   <si>
+    <t>2009-09-30</t>
+  </si>
+  <si>
     <t>2009-03-20</t>
   </si>
   <si>
-    <t>2009-09-30</t>
-  </si>
-  <si>
     <t>ONPL09</t>
   </si>
   <si>
@@ -4591,12 +4591,12 @@
     <t>Philippines Flash Appeal (Revised) (October 2009 - March 2010)</t>
   </si>
   <si>
+    <t>2010-03-31</t>
+  </si>
+  <si>
     <t>2009-10-03</t>
   </si>
   <si>
-    <t>2010-03-31</t>
-  </si>
-  <si>
     <t>CSOM09</t>
   </si>
   <si>
@@ -4621,12 +4621,12 @@
     <t>Syria Drought Response Plan (Revised) (July 2009 - June 2010)</t>
   </si>
   <si>
+    <t>2010-06-14</t>
+  </si>
+  <si>
     <t>2009-07-15</t>
   </si>
   <si>
-    <t>2010-06-14</t>
-  </si>
-  <si>
     <t>OTJK09</t>
   </si>
   <si>
@@ -4684,12 +4684,12 @@
     <t>Afghanistan Joint Appeal 2008: Humanitarian Consequences of Rise in Food Prices (February - June 2008)</t>
   </si>
   <si>
+    <t>2008-06-30</t>
+  </si>
+  <si>
     <t>2008-02-01</t>
   </si>
   <si>
-    <t>2008-06-30</t>
-  </si>
-  <si>
     <t>2008</t>
   </si>
   <si>
@@ -4699,12 +4699,12 @@
     <t>Afghanistan Joint Emergency Appeal 2008: High Food Price and Drought Crisis (July 2008 - June 2009)</t>
   </si>
   <si>
+    <t>2009-06-30</t>
+  </si>
+  <si>
     <t>2008-07-01</t>
   </si>
   <si>
-    <t>2009-06-30</t>
-  </si>
-  <si>
     <t>FBOL08</t>
   </si>
   <si>
@@ -4720,12 +4720,12 @@
     <t>Central African Republic 2008</t>
   </si>
   <si>
+    <t>2008-12-31</t>
+  </si>
+  <si>
     <t>2008-01-01</t>
   </si>
   <si>
-    <t>2008-12-31</t>
-  </si>
-  <si>
     <t>CTCD08</t>
   </si>
   <si>
@@ -4756,24 +4756,24 @@
     <t>Djibouti Joint Appeal 2008: Response Plan for Drought, Food and Nutrition Crisis</t>
   </si>
   <si>
+    <t>2009-02-28</t>
+  </si>
+  <si>
     <t>2008-08-01</t>
   </si>
   <si>
-    <t>2009-02-28</t>
-  </si>
-  <si>
     <t>FGEO0809</t>
   </si>
   <si>
     <t>Georgia Crisis Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2009-02-09</t>
+  </si>
+  <si>
     <t>2008-08-09</t>
   </si>
   <si>
-    <t>2009-02-09</t>
-  </si>
-  <si>
     <t>FHTI0809</t>
   </si>
   <si>
@@ -4789,12 +4789,12 @@
     <t>Honduras Flash Appeal (Updated) (November - April) 2008</t>
   </si>
   <si>
+    <t>2009-04-30</t>
+  </si>
+  <si>
     <t>2008-11-01</t>
   </si>
   <si>
-    <t>2009-04-30</t>
-  </si>
-  <si>
     <t>CIRQ08</t>
   </si>
   <si>
@@ -4813,12 +4813,12 @@
     <t>Kyrgyzstan Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2009-05-31</t>
+  </si>
+  <si>
     <t>2008-12-01</t>
   </si>
   <si>
-    <t>2009-05-31</t>
-  </si>
-  <si>
     <t>OLAO0809</t>
   </si>
   <si>
@@ -4849,12 +4849,12 @@
     <t>Myanmar Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2008-11-30</t>
+  </si>
+  <si>
     <t>2008-05-01</t>
   </si>
   <si>
-    <t>2008-11-30</t>
-  </si>
-  <si>
     <t>ONPL08</t>
   </si>
   <si>
@@ -4951,12 +4951,12 @@
     <t>Bolivia Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-08-21</t>
+  </si>
+  <si>
     <t>2007-02-22</t>
   </si>
   <si>
-    <t>2007-08-21</t>
-  </si>
-  <si>
     <t>2007</t>
   </si>
   <si>
@@ -4966,24 +4966,24 @@
     <t>Burkina Faso Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2008-01-31</t>
+  </si>
+  <si>
     <t>2007-11-01</t>
   </si>
   <si>
-    <t>2008-01-31</t>
-  </si>
-  <si>
     <t>CBDI07</t>
   </si>
   <si>
     <t>Burundi 2007</t>
   </si>
   <si>
+    <t>2007-12-31</t>
+  </si>
+  <si>
     <t>2007-01-01</t>
   </si>
   <si>
-    <t>2007-12-31</t>
-  </si>
-  <si>
     <t>CCAF07</t>
   </si>
   <si>
@@ -5023,12 +5023,12 @@
     <t>Ghana Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2008-03-31</t>
+  </si>
+  <si>
     <t>2007-09-01</t>
   </si>
   <si>
-    <t>2008-03-31</t>
-  </si>
-  <si>
     <t>CXGLR07</t>
   </si>
   <si>
@@ -5050,36 +5050,36 @@
     <t>Korea DPR Flash Appeal: Floods Emergency 2007</t>
   </si>
   <si>
+    <t>2007-11-30</t>
+  </si>
+  <si>
     <t>2007-08-28</t>
   </si>
   <si>
-    <t>2007-11-30</t>
-  </si>
-  <si>
     <t>OLBN07</t>
   </si>
   <si>
     <t>Lebanon Crisis Appeal 2007</t>
   </si>
   <si>
+    <t>2007-09-03</t>
+  </si>
+  <si>
     <t>2007-06-04</t>
   </si>
   <si>
-    <t>2007-09-03</t>
-  </si>
-  <si>
     <t>FLSO0708</t>
   </si>
   <si>
     <t>Lesotho Drought Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2008-01-28</t>
+  </si>
+  <si>
     <t>2007-07-28</t>
   </si>
   <si>
-    <t>2008-01-28</t>
-  </si>
-  <si>
     <t>CLBR07</t>
   </si>
   <si>
@@ -5092,24 +5092,24 @@
     <t>Madagascar Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-09-15</t>
+  </si>
+  <si>
     <t>2007-03-15</t>
   </si>
   <si>
-    <t>2007-09-15</t>
-  </si>
-  <si>
     <t>FMOZ07</t>
   </si>
   <si>
     <t>Mozambique Floods and Cyclone Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-06-30</t>
+  </si>
+  <si>
     <t>2007-03-01</t>
   </si>
   <si>
-    <t>2007-06-30</t>
-  </si>
-  <si>
     <t>ONPL07</t>
   </si>
   <si>
@@ -5122,12 +5122,12 @@
     <t>Nicaragua Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2008-02-28</t>
+  </si>
+  <si>
     <t>2007-09-07</t>
   </si>
   <si>
-    <t>2008-02-28</t>
-  </si>
-  <si>
     <t>ORUS07</t>
   </si>
   <si>
@@ -5140,12 +5140,12 @@
     <t>Pakistan Cyclone and Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-10-31</t>
+  </si>
+  <si>
     <t>2007-07-15</t>
   </si>
   <si>
-    <t>2007-10-31</t>
-  </si>
-  <si>
     <t>FPER0708</t>
   </si>
   <si>
@@ -5203,12 +5203,12 @@
     <t>Swaziland Drought Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2008-01-20</t>
+  </si>
+  <si>
     <t>2007-07-20</t>
   </si>
   <si>
-    <t>2008-01-20</t>
-  </si>
-  <si>
     <t>CTLS07</t>
   </si>
   <si>
@@ -5257,12 +5257,12 @@
     <t>Afghanistan Drought Joint Appeal 2006</t>
   </si>
   <si>
+    <t>2006-12-31</t>
+  </si>
+  <si>
     <t>2006-07-01</t>
   </si>
   <si>
-    <t>2006-12-31</t>
-  </si>
-  <si>
     <t>2006</t>
   </si>
   <si>
@@ -5311,24 +5311,24 @@
     <t>Ethiopia Floods Joint Appeal 2006</t>
   </si>
   <si>
+    <t>2006-11-25</t>
+  </si>
+  <si>
     <t>2006-08-25</t>
   </si>
   <si>
-    <t>2006-11-25</t>
-  </si>
-  <si>
     <t>OETH0607</t>
   </si>
   <si>
     <t>Ethiopia: 2006 Govt-UN Joint Emergency Flood Appeal for Somali Region</t>
   </si>
   <si>
+    <t>2007-01-22</t>
+  </si>
+  <si>
     <t>2006-11-23</t>
   </si>
   <si>
-    <t>2007-01-22</t>
-  </si>
-  <si>
     <t>CXGLR06</t>
   </si>
   <si>
@@ -5347,12 +5347,12 @@
     <t>Guinea-Bissau 2006</t>
   </si>
   <si>
+    <t>2006-11-30</t>
+  </si>
+  <si>
     <t>2006-05-01</t>
   </si>
   <si>
-    <t>2006-11-30</t>
-  </si>
-  <si>
     <t>CXHAF06</t>
   </si>
   <si>
@@ -5371,12 +5371,12 @@
     <t>Kenya 2006</t>
   </si>
   <si>
+    <t>2007-04-15</t>
+  </si>
+  <si>
     <t>2006-10-16</t>
   </si>
   <si>
-    <t>2007-04-15</t>
-  </si>
-  <si>
     <t>FKEN06</t>
   </si>
   <si>
@@ -5392,12 +5392,12 @@
     <t>Lebanon Crisis 2006</t>
   </si>
   <si>
+    <t>2006-10-23</t>
+  </si>
+  <si>
     <t>2006-07-24</t>
   </si>
   <si>
-    <t>2006-10-23</t>
-  </si>
-  <si>
     <t>CLBR06</t>
   </si>
   <si>
@@ -5446,12 +5446,12 @@
     <t>Somalia: 2006 Flood Response Plan</t>
   </si>
   <si>
+    <t>2007-03-05</t>
+  </si>
+  <si>
     <t>2006-12-05</t>
   </si>
   <si>
-    <t>2007-03-05</t>
-  </si>
-  <si>
     <t>OLKA06</t>
   </si>
   <si>
@@ -5512,12 +5512,12 @@
     <t>Angola Marburg VHF 2005</t>
   </si>
   <si>
+    <t>2005-06-30</t>
+  </si>
+  <si>
     <t>2005-04-01</t>
   </si>
   <si>
-    <t>2005-06-30</t>
-  </si>
-  <si>
     <t>2005</t>
   </si>
   <si>
@@ -5527,24 +5527,24 @@
     <t>Benin 2005</t>
   </si>
   <si>
+    <t>2005-10-31</t>
+  </si>
+  <si>
     <t>2005-05-01</t>
   </si>
   <si>
-    <t>2005-10-31</t>
-  </si>
-  <si>
     <t>CBDI05</t>
   </si>
   <si>
     <t>Burundi 2005</t>
   </si>
   <si>
+    <t>2005-12-31</t>
+  </si>
+  <si>
     <t>2005-01-01</t>
   </si>
   <si>
-    <t>2005-12-31</t>
-  </si>
-  <si>
     <t>CCAF05</t>
   </si>
   <si>
@@ -5620,12 +5620,12 @@
     <t>Guyana 2005</t>
   </si>
   <si>
+    <t>2005-08-01</t>
+  </si>
+  <si>
     <t>2005-02-01</t>
   </si>
   <si>
-    <t>2005-08-01</t>
-  </si>
-  <si>
     <t>FXINDTSU05</t>
   </si>
   <si>
@@ -5647,12 +5647,12 @@
     <t>Niger 2005</t>
   </si>
   <si>
+    <t>2005-09-30</t>
+  </si>
+  <si>
     <t>2005-06-01</t>
   </si>
   <si>
-    <t>2005-09-30</t>
-  </si>
-  <si>
     <t>CCOG05</t>
   </si>
   <si>
@@ -5671,12 +5671,12 @@
     <t>South Asia Earthquake 2005</t>
   </si>
   <si>
+    <t>2006-04-10</t>
+  </si>
+  <si>
     <t>2005-10-11</t>
   </si>
   <si>
-    <t>2006-04-10</t>
-  </si>
-  <si>
     <t>CSDN05</t>
   </si>
   <si>
@@ -5701,12 +5701,12 @@
     <t>West and Central Africa Region Cholera 2005</t>
   </si>
   <si>
+    <t>2006-05-31</t>
+  </si>
+  <si>
     <t>2005-11-01</t>
   </si>
   <si>
-    <t>2006-05-31</t>
-  </si>
-  <si>
     <t>CPSE05</t>
   </si>
   <si>
@@ -5719,12 +5719,12 @@
     <t>Afghanistan UN-Government Drought Appeal 2004</t>
   </si>
   <si>
+    <t>2004-12-31</t>
+  </si>
+  <si>
     <t>2004-09-01</t>
   </si>
   <si>
-    <t>2004-12-31</t>
-  </si>
-  <si>
     <t>2004</t>
   </si>
   <si>
@@ -5743,24 +5743,24 @@
     <t>Bangladesh 2004</t>
   </si>
   <si>
+    <t>2005-01-31</t>
+  </si>
+  <si>
     <t>2004-08-01</t>
   </si>
   <si>
-    <t>2005-01-31</t>
-  </si>
-  <si>
     <t>FBOL0405</t>
   </si>
   <si>
     <t>Bolivia 2004</t>
   </si>
   <si>
+    <t>2005-05-31</t>
+  </si>
+  <si>
     <t>2004-11-01</t>
   </si>
   <si>
-    <t>2005-05-31</t>
-  </si>
-  <si>
     <t>CBDI04</t>
   </si>
   <si>
@@ -5887,24 +5887,24 @@
     <t>Madagascar 2004</t>
   </si>
   <si>
+    <t>2004-06-19</t>
+  </si>
+  <si>
     <t>2004-03-19</t>
   </si>
   <si>
-    <t>2004-06-19</t>
-  </si>
-  <si>
     <t>FPHL0405</t>
   </si>
   <si>
     <t>Philippines 2004</t>
   </si>
   <si>
+    <t>2005-03-15</t>
+  </si>
+  <si>
     <t>2004-12-15</t>
   </si>
   <si>
-    <t>2005-03-15</t>
-  </si>
-  <si>
     <t>CSLE04</t>
   </si>
   <si>
@@ -5965,12 +5965,12 @@
     <t>Afghanistan TAPA 2003</t>
   </si>
   <si>
+    <t>2003-12-31</t>
+  </si>
+  <si>
     <t>2003-01-01</t>
   </si>
   <si>
-    <t>2003-12-31</t>
-  </si>
-  <si>
     <t>2003</t>
   </si>
   <si>
@@ -5992,12 +5992,12 @@
     <t>Central African Republic 2003</t>
   </si>
   <si>
+    <t>2003-06-30</t>
+  </si>
+  <si>
     <t>2003-04-01</t>
   </si>
   <si>
-    <t>2003-06-30</t>
-  </si>
-  <si>
     <t>CRUS03</t>
   </si>
   <si>
@@ -6022,12 +6022,12 @@
     <t>Côte d'Ivoire and the West Africa Sub-Region 2002-2003</t>
   </si>
   <si>
+    <t>2003-01-31</t>
+  </si>
+  <si>
     <t>2002-11-01</t>
   </si>
   <si>
-    <t>2003-01-31</t>
-  </si>
-  <si>
     <t>CPRK03</t>
   </si>
   <si>
@@ -6064,24 +6064,24 @@
     <t>Haiti (PIR) 2003</t>
   </si>
   <si>
+    <t>2003-08-31</t>
+  </si>
+  <si>
     <t>2003-03-01</t>
   </si>
   <si>
-    <t>2003-08-31</t>
-  </si>
-  <si>
     <t>CLSO0304</t>
   </si>
   <si>
     <t>Humanitarian Crisis in Southern Africa - LESOTHO (July 2003 - June 2004)</t>
   </si>
   <si>
+    <t>2004-06-30</t>
+  </si>
+  <si>
     <t>2003-07-01</t>
   </si>
   <si>
-    <t>2004-06-30</t>
-  </si>
-  <si>
     <t>CMWI03</t>
   </si>
   <si>
@@ -6184,12 +6184,12 @@
     <t>Afghanistan 2002 (ITAP for the Afghan People)</t>
   </si>
   <si>
+    <t>2002-12-31</t>
+  </si>
+  <si>
     <t>2001-10-01</t>
   </si>
   <si>
-    <t>2002-12-31</t>
-  </si>
-  <si>
     <t>2002</t>
   </si>
   <si>
@@ -6370,12 +6370,12 @@
     <t>Afghanistan 2001</t>
   </si>
   <si>
+    <t>2001-09-30</t>
+  </si>
+  <si>
     <t>2001-01-01</t>
   </si>
   <si>
-    <t>2001-09-30</t>
-  </si>
-  <si>
     <t>2001</t>
   </si>
   <si>
@@ -6520,10 +6520,10 @@
     <t>Angola 2000</t>
   </si>
   <si>
+    <t>2000-12-31</t>
+  </si>
+  <si>
     <t>2000-01-01</t>
-  </si>
-  <si>
-    <t>2000-12-31</t>
   </si>
   <si>
     <t>2000</t>
@@ -7049,10 +7049,10 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
@@ -7279,10 +7279,10 @@
         <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
@@ -7302,10 +7302,10 @@
         <v>9</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
@@ -7348,10 +7348,10 @@
         <v>9</v>
       </c>
       <c r="D17" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E17" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
@@ -7394,10 +7394,10 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="E19" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="F19" t="s">
         <v>12</v>
@@ -7417,10 +7417,10 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
         <v>58</v>
-      </c>
-      <c r="E20" t="s">
-        <v>11</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
@@ -7509,10 +7509,10 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="E24" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="F24" t="s">
         <v>12</v>
@@ -7739,10 +7739,10 @@
         <v>9</v>
       </c>
       <c r="D34" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" t="s">
         <v>88</v>
-      </c>
-      <c r="E34" t="s">
-        <v>11</v>
       </c>
       <c r="F34" t="s">
         <v>12</v>
@@ -7923,10 +7923,10 @@
         <v>9</v>
       </c>
       <c r="D42" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="E42" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="F42" t="s">
         <v>12</v>
@@ -7969,10 +7969,10 @@
         <v>9</v>
       </c>
       <c r="D44" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="E44" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="F44" t="s">
         <v>12</v>
@@ -7992,10 +7992,10 @@
         <v>9</v>
       </c>
       <c r="D45" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="E45" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="F45" t="s">
         <v>12</v>
@@ -8061,10 +8061,10 @@
         <v>9</v>
       </c>
       <c r="D48" t="s">
+        <v>113</v>
+      </c>
+      <c r="E48" t="s">
         <v>120</v>
-      </c>
-      <c r="E48" t="s">
-        <v>114</v>
       </c>
       <c r="F48" t="s">
         <v>115</v>
@@ -8107,10 +8107,10 @@
         <v>9</v>
       </c>
       <c r="D50" t="s">
+        <v>113</v>
+      </c>
+      <c r="E50" t="s">
         <v>125</v>
-      </c>
-      <c r="E50" t="s">
-        <v>114</v>
       </c>
       <c r="F50" t="s">
         <v>115</v>
@@ -8268,10 +8268,10 @@
         <v>9</v>
       </c>
       <c r="D57" t="s">
+        <v>113</v>
+      </c>
+      <c r="E57" t="s">
         <v>140</v>
-      </c>
-      <c r="E57" t="s">
-        <v>114</v>
       </c>
       <c r="F57" t="s">
         <v>115</v>
@@ -8360,10 +8360,10 @@
         <v>9</v>
       </c>
       <c r="D61" t="s">
+        <v>113</v>
+      </c>
+      <c r="E61" t="s">
         <v>149</v>
-      </c>
-      <c r="E61" t="s">
-        <v>114</v>
       </c>
       <c r="F61" t="s">
         <v>115</v>
@@ -8383,10 +8383,10 @@
         <v>9</v>
       </c>
       <c r="D62" t="s">
+        <v>113</v>
+      </c>
+      <c r="E62" t="s">
         <v>149</v>
-      </c>
-      <c r="E62" t="s">
-        <v>114</v>
       </c>
       <c r="F62" t="s">
         <v>115</v>
@@ -8406,10 +8406,10 @@
         <v>9</v>
       </c>
       <c r="D63" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="E63" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="F63" t="s">
         <v>115</v>
@@ -8429,10 +8429,10 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="E64" t="s">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="F64" t="s">
         <v>115</v>
@@ -8452,10 +8452,10 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
+        <v>113</v>
+      </c>
+      <c r="E65" t="s">
         <v>160</v>
-      </c>
-      <c r="E65" t="s">
-        <v>114</v>
       </c>
       <c r="F65" t="s">
         <v>115</v>
@@ -8498,10 +8498,10 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
+        <v>157</v>
+      </c>
+      <c r="E67" t="s">
         <v>165</v>
-      </c>
-      <c r="E67" t="s">
-        <v>157</v>
       </c>
       <c r="F67" t="s">
         <v>115</v>
@@ -8521,10 +8521,10 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
+        <v>113</v>
+      </c>
+      <c r="E68" t="s">
         <v>168</v>
-      </c>
-      <c r="E68" t="s">
-        <v>114</v>
       </c>
       <c r="F68" t="s">
         <v>115</v>
@@ -8590,10 +8590,10 @@
         <v>9</v>
       </c>
       <c r="D71" t="s">
+        <v>113</v>
+      </c>
+      <c r="E71" t="s">
         <v>175</v>
-      </c>
-      <c r="E71" t="s">
-        <v>114</v>
       </c>
       <c r="F71" t="s">
         <v>115</v>
@@ -8659,10 +8659,10 @@
         <v>9</v>
       </c>
       <c r="D74" t="s">
+        <v>113</v>
+      </c>
+      <c r="E74" t="s">
         <v>182</v>
-      </c>
-      <c r="E74" t="s">
-        <v>114</v>
       </c>
       <c r="F74" t="s">
         <v>115</v>
@@ -8797,10 +8797,10 @@
         <v>9</v>
       </c>
       <c r="D80" t="s">
+        <v>113</v>
+      </c>
+      <c r="E80" t="s">
         <v>140</v>
-      </c>
-      <c r="E80" t="s">
-        <v>114</v>
       </c>
       <c r="F80" t="s">
         <v>115</v>
@@ -9096,10 +9096,10 @@
         <v>9</v>
       </c>
       <c r="D93" t="s">
+        <v>113</v>
+      </c>
+      <c r="E93" t="s">
         <v>222</v>
-      </c>
-      <c r="E93" t="s">
-        <v>114</v>
       </c>
       <c r="F93" t="s">
         <v>115</v>
@@ -9142,10 +9142,10 @@
         <v>9</v>
       </c>
       <c r="D95" t="s">
+        <v>113</v>
+      </c>
+      <c r="E95" t="s">
         <v>227</v>
-      </c>
-      <c r="E95" t="s">
-        <v>114</v>
       </c>
       <c r="F95" t="s">
         <v>115</v>
@@ -9165,10 +9165,10 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
+        <v>113</v>
+      </c>
+      <c r="E96" t="s">
         <v>227</v>
-      </c>
-      <c r="E96" t="s">
-        <v>114</v>
       </c>
       <c r="F96" t="s">
         <v>115</v>
@@ -9372,10 +9372,10 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
+        <v>232</v>
+      </c>
+      <c r="E105" t="s">
         <v>251</v>
-      </c>
-      <c r="E105" t="s">
-        <v>233</v>
       </c>
       <c r="F105" t="s">
         <v>234</v>
@@ -9556,10 +9556,10 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
+        <v>232</v>
+      </c>
+      <c r="E113" t="s">
         <v>268</v>
-      </c>
-      <c r="E113" t="s">
-        <v>233</v>
       </c>
       <c r="F113" t="s">
         <v>234</v>
@@ -9763,10 +9763,10 @@
         <v>9</v>
       </c>
       <c r="D122" t="s">
-        <v>232</v>
+        <v>279</v>
       </c>
       <c r="E122" t="s">
-        <v>280</v>
+        <v>233</v>
       </c>
       <c r="F122" t="s">
         <v>234</v>
@@ -9786,10 +9786,10 @@
         <v>9</v>
       </c>
       <c r="D123" t="s">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="E123" t="s">
-        <v>276</v>
+        <v>233</v>
       </c>
       <c r="F123" t="s">
         <v>234</v>
@@ -10039,10 +10039,10 @@
         <v>9</v>
       </c>
       <c r="D134" t="s">
+        <v>275</v>
+      </c>
+      <c r="E134" t="s">
         <v>316</v>
-      </c>
-      <c r="E134" t="s">
-        <v>276</v>
       </c>
       <c r="F134" t="s">
         <v>234</v>
@@ -10085,10 +10085,10 @@
         <v>9</v>
       </c>
       <c r="D136" t="s">
+        <v>275</v>
+      </c>
+      <c r="E136" t="s">
         <v>321</v>
-      </c>
-      <c r="E136" t="s">
-        <v>276</v>
       </c>
       <c r="F136" t="s">
         <v>234</v>
@@ -10568,10 +10568,10 @@
         <v>185</v>
       </c>
       <c r="D157" t="s">
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="E157" t="s">
-        <v>339</v>
+        <v>368</v>
       </c>
       <c r="F157" t="s">
         <v>340</v>
@@ -10660,10 +10660,10 @@
         <v>9</v>
       </c>
       <c r="D161" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="E161" t="s">
-        <v>379</v>
+        <v>339</v>
       </c>
       <c r="F161" t="s">
         <v>340</v>
@@ -10936,10 +10936,10 @@
         <v>9</v>
       </c>
       <c r="D173" t="s">
+        <v>338</v>
+      </c>
+      <c r="E173" t="s">
         <v>408</v>
-      </c>
-      <c r="E173" t="s">
-        <v>339</v>
       </c>
       <c r="F173" t="s">
         <v>340</v>
@@ -10959,10 +10959,10 @@
         <v>185</v>
       </c>
       <c r="D174" t="s">
+        <v>410</v>
+      </c>
+      <c r="E174" t="s">
         <v>408</v>
-      </c>
-      <c r="E174" t="s">
-        <v>410</v>
       </c>
       <c r="F174" t="s">
         <v>340</v>
@@ -11166,10 +11166,10 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
+        <v>338</v>
+      </c>
+      <c r="E183" t="s">
         <v>431</v>
-      </c>
-      <c r="E183" t="s">
-        <v>339</v>
       </c>
       <c r="F183" t="s">
         <v>340</v>
@@ -11281,10 +11281,10 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
+        <v>338</v>
+      </c>
+      <c r="E188" t="s">
         <v>442</v>
-      </c>
-      <c r="E188" t="s">
-        <v>339</v>
       </c>
       <c r="F188" t="s">
         <v>340</v>
@@ -11327,10 +11327,10 @@
         <v>9</v>
       </c>
       <c r="D190" t="s">
+        <v>447</v>
+      </c>
+      <c r="E190" t="s">
         <v>442</v>
-      </c>
-      <c r="E190" t="s">
-        <v>447</v>
       </c>
       <c r="F190" t="s">
         <v>340</v>
@@ -11419,10 +11419,10 @@
         <v>9</v>
       </c>
       <c r="D194" t="s">
+        <v>454</v>
+      </c>
+      <c r="E194" t="s">
         <v>459</v>
-      </c>
-      <c r="E194" t="s">
-        <v>455</v>
       </c>
       <c r="F194" t="s">
         <v>456</v>
@@ -11442,10 +11442,10 @@
         <v>9</v>
       </c>
       <c r="D195" t="s">
+        <v>454</v>
+      </c>
+      <c r="E195" t="s">
         <v>459</v>
-      </c>
-      <c r="E195" t="s">
-        <v>455</v>
       </c>
       <c r="F195" t="s">
         <v>456</v>
@@ -11465,10 +11465,10 @@
         <v>9</v>
       </c>
       <c r="D196" t="s">
+        <v>454</v>
+      </c>
+      <c r="E196" t="s">
         <v>459</v>
-      </c>
-      <c r="E196" t="s">
-        <v>455</v>
       </c>
       <c r="F196" t="s">
         <v>456</v>
@@ -11488,10 +11488,10 @@
         <v>9</v>
       </c>
       <c r="D197" t="s">
+        <v>454</v>
+      </c>
+      <c r="E197" t="s">
         <v>459</v>
-      </c>
-      <c r="E197" t="s">
-        <v>455</v>
       </c>
       <c r="F197" t="s">
         <v>456</v>
@@ -11511,10 +11511,10 @@
         <v>9</v>
       </c>
       <c r="D198" t="s">
+        <v>454</v>
+      </c>
+      <c r="E198" t="s">
         <v>459</v>
-      </c>
-      <c r="E198" t="s">
-        <v>455</v>
       </c>
       <c r="F198" t="s">
         <v>456</v>
@@ -11534,10 +11534,10 @@
         <v>9</v>
       </c>
       <c r="D199" t="s">
+        <v>454</v>
+      </c>
+      <c r="E199" t="s">
         <v>459</v>
-      </c>
-      <c r="E199" t="s">
-        <v>455</v>
       </c>
       <c r="F199" t="s">
         <v>456</v>
@@ -11557,10 +11557,10 @@
         <v>9</v>
       </c>
       <c r="D200" t="s">
+        <v>454</v>
+      </c>
+      <c r="E200" t="s">
         <v>459</v>
-      </c>
-      <c r="E200" t="s">
-        <v>455</v>
       </c>
       <c r="F200" t="s">
         <v>456</v>
@@ -11580,10 +11580,10 @@
         <v>9</v>
       </c>
       <c r="D201" t="s">
+        <v>454</v>
+      </c>
+      <c r="E201" t="s">
         <v>459</v>
-      </c>
-      <c r="E201" t="s">
-        <v>455</v>
       </c>
       <c r="F201" t="s">
         <v>456</v>
@@ -11603,10 +11603,10 @@
         <v>9</v>
       </c>
       <c r="D202" t="s">
+        <v>454</v>
+      </c>
+      <c r="E202" t="s">
         <v>459</v>
-      </c>
-      <c r="E202" t="s">
-        <v>455</v>
       </c>
       <c r="F202" t="s">
         <v>456</v>
@@ -11626,10 +11626,10 @@
         <v>9</v>
       </c>
       <c r="D203" t="s">
+        <v>454</v>
+      </c>
+      <c r="E203" t="s">
         <v>459</v>
-      </c>
-      <c r="E203" t="s">
-        <v>455</v>
       </c>
       <c r="F203" t="s">
         <v>456</v>
@@ -11649,10 +11649,10 @@
         <v>9</v>
       </c>
       <c r="D204" t="s">
+        <v>454</v>
+      </c>
+      <c r="E204" t="s">
         <v>459</v>
-      </c>
-      <c r="E204" t="s">
-        <v>455</v>
       </c>
       <c r="F204" t="s">
         <v>456</v>
@@ -11672,10 +11672,10 @@
         <v>9</v>
       </c>
       <c r="D205" t="s">
+        <v>454</v>
+      </c>
+      <c r="E205" t="s">
         <v>482</v>
-      </c>
-      <c r="E205" t="s">
-        <v>455</v>
       </c>
       <c r="F205" t="s">
         <v>456</v>
@@ -11695,10 +11695,10 @@
         <v>185</v>
       </c>
       <c r="D206" t="s">
+        <v>338</v>
+      </c>
+      <c r="E206" t="s">
         <v>482</v>
-      </c>
-      <c r="E206" t="s">
-        <v>339</v>
       </c>
       <c r="F206" t="s">
         <v>456</v>
@@ -11741,10 +11741,10 @@
         <v>9</v>
       </c>
       <c r="D208" t="s">
+        <v>454</v>
+      </c>
+      <c r="E208" t="s">
         <v>459</v>
-      </c>
-      <c r="E208" t="s">
-        <v>455</v>
       </c>
       <c r="F208" t="s">
         <v>456</v>
@@ -11764,10 +11764,10 @@
         <v>9</v>
       </c>
       <c r="D209" t="s">
+        <v>454</v>
+      </c>
+      <c r="E209" t="s">
         <v>482</v>
-      </c>
-      <c r="E209" t="s">
-        <v>455</v>
       </c>
       <c r="F209" t="s">
         <v>456</v>
@@ -11787,10 +11787,10 @@
         <v>185</v>
       </c>
       <c r="D210" t="s">
+        <v>338</v>
+      </c>
+      <c r="E210" t="s">
         <v>482</v>
-      </c>
-      <c r="E210" t="s">
-        <v>339</v>
       </c>
       <c r="F210" t="s">
         <v>456</v>
@@ -11833,10 +11833,10 @@
         <v>9</v>
       </c>
       <c r="D212" t="s">
+        <v>454</v>
+      </c>
+      <c r="E212" t="s">
         <v>459</v>
-      </c>
-      <c r="E212" t="s">
-        <v>455</v>
       </c>
       <c r="F212" t="s">
         <v>456</v>
@@ -11879,10 +11879,10 @@
         <v>9</v>
       </c>
       <c r="D214" t="s">
+        <v>454</v>
+      </c>
+      <c r="E214" t="s">
         <v>482</v>
-      </c>
-      <c r="E214" t="s">
-        <v>455</v>
       </c>
       <c r="F214" t="s">
         <v>456</v>
@@ -11902,10 +11902,10 @@
         <v>185</v>
       </c>
       <c r="D215" t="s">
+        <v>338</v>
+      </c>
+      <c r="E215" t="s">
         <v>482</v>
-      </c>
-      <c r="E215" t="s">
-        <v>339</v>
       </c>
       <c r="F215" t="s">
         <v>456</v>
@@ -11925,10 +11925,10 @@
         <v>9</v>
       </c>
       <c r="D216" t="s">
+        <v>454</v>
+      </c>
+      <c r="E216" t="s">
         <v>459</v>
-      </c>
-      <c r="E216" t="s">
-        <v>455</v>
       </c>
       <c r="F216" t="s">
         <v>456</v>
@@ -11948,10 +11948,10 @@
         <v>9</v>
       </c>
       <c r="D217" t="s">
+        <v>454</v>
+      </c>
+      <c r="E217" t="s">
         <v>513</v>
-      </c>
-      <c r="E217" t="s">
-        <v>455</v>
       </c>
       <c r="F217" t="s">
         <v>456</v>
@@ -11994,10 +11994,10 @@
         <v>9</v>
       </c>
       <c r="D219" t="s">
+        <v>454</v>
+      </c>
+      <c r="E219" t="s">
         <v>459</v>
-      </c>
-      <c r="E219" t="s">
-        <v>455</v>
       </c>
       <c r="F219" t="s">
         <v>456</v>
@@ -12017,10 +12017,10 @@
         <v>185</v>
       </c>
       <c r="D220" t="s">
+        <v>388</v>
+      </c>
+      <c r="E220" t="s">
         <v>459</v>
-      </c>
-      <c r="E220" t="s">
-        <v>389</v>
       </c>
       <c r="F220" t="s">
         <v>456</v>
@@ -12040,10 +12040,10 @@
         <v>9</v>
       </c>
       <c r="D221" t="s">
+        <v>454</v>
+      </c>
+      <c r="E221" t="s">
         <v>459</v>
-      </c>
-      <c r="E221" t="s">
-        <v>455</v>
       </c>
       <c r="F221" t="s">
         <v>456</v>
@@ -12063,10 +12063,10 @@
         <v>9</v>
       </c>
       <c r="D222" t="s">
+        <v>454</v>
+      </c>
+      <c r="E222" t="s">
         <v>459</v>
-      </c>
-      <c r="E222" t="s">
-        <v>455</v>
       </c>
       <c r="F222" t="s">
         <v>456</v>
@@ -12086,10 +12086,10 @@
         <v>9</v>
       </c>
       <c r="D223" t="s">
+        <v>454</v>
+      </c>
+      <c r="E223" t="s">
         <v>459</v>
-      </c>
-      <c r="E223" t="s">
-        <v>455</v>
       </c>
       <c r="F223" t="s">
         <v>456</v>
@@ -12109,10 +12109,10 @@
         <v>9</v>
       </c>
       <c r="D224" t="s">
+        <v>454</v>
+      </c>
+      <c r="E224" t="s">
         <v>459</v>
-      </c>
-      <c r="E224" t="s">
-        <v>455</v>
       </c>
       <c r="F224" t="s">
         <v>456</v>
@@ -12132,10 +12132,10 @@
         <v>9</v>
       </c>
       <c r="D225" t="s">
+        <v>454</v>
+      </c>
+      <c r="E225" t="s">
         <v>532</v>
-      </c>
-      <c r="E225" t="s">
-        <v>455</v>
       </c>
       <c r="F225" t="s">
         <v>456</v>
@@ -12155,10 +12155,10 @@
         <v>9</v>
       </c>
       <c r="D226" t="s">
+        <v>454</v>
+      </c>
+      <c r="E226" t="s">
         <v>535</v>
-      </c>
-      <c r="E226" t="s">
-        <v>455</v>
       </c>
       <c r="F226" t="s">
         <v>456</v>
@@ -12178,10 +12178,10 @@
         <v>9</v>
       </c>
       <c r="D227" t="s">
+        <v>454</v>
+      </c>
+      <c r="E227" t="s">
         <v>459</v>
-      </c>
-      <c r="E227" t="s">
-        <v>455</v>
       </c>
       <c r="F227" t="s">
         <v>456</v>
@@ -12201,10 +12201,10 @@
         <v>9</v>
       </c>
       <c r="D228" t="s">
+        <v>454</v>
+      </c>
+      <c r="E228" t="s">
         <v>459</v>
-      </c>
-      <c r="E228" t="s">
-        <v>455</v>
       </c>
       <c r="F228" t="s">
         <v>456</v>
@@ -12224,10 +12224,10 @@
         <v>9</v>
       </c>
       <c r="D229" t="s">
+        <v>454</v>
+      </c>
+      <c r="E229" t="s">
         <v>535</v>
-      </c>
-      <c r="E229" t="s">
-        <v>455</v>
       </c>
       <c r="F229" t="s">
         <v>456</v>
@@ -12247,10 +12247,10 @@
         <v>185</v>
       </c>
       <c r="D230" t="s">
+        <v>454</v>
+      </c>
+      <c r="E230" t="s">
         <v>535</v>
-      </c>
-      <c r="E230" t="s">
-        <v>455</v>
       </c>
       <c r="F230" t="s">
         <v>456</v>
@@ -12270,10 +12270,10 @@
         <v>9</v>
       </c>
       <c r="D231" t="s">
+        <v>454</v>
+      </c>
+      <c r="E231" t="s">
         <v>459</v>
-      </c>
-      <c r="E231" t="s">
-        <v>455</v>
       </c>
       <c r="F231" t="s">
         <v>456</v>
@@ -12293,10 +12293,10 @@
         <v>9</v>
       </c>
       <c r="D232" t="s">
+        <v>454</v>
+      </c>
+      <c r="E232" t="s">
         <v>459</v>
-      </c>
-      <c r="E232" t="s">
-        <v>455</v>
       </c>
       <c r="F232" t="s">
         <v>456</v>
@@ -12316,10 +12316,10 @@
         <v>9</v>
       </c>
       <c r="D233" t="s">
+        <v>454</v>
+      </c>
+      <c r="E233" t="s">
         <v>459</v>
-      </c>
-      <c r="E233" t="s">
-        <v>455</v>
       </c>
       <c r="F233" t="s">
         <v>456</v>
@@ -12339,10 +12339,10 @@
         <v>9</v>
       </c>
       <c r="D234" t="s">
+        <v>454</v>
+      </c>
+      <c r="E234" t="s">
         <v>459</v>
-      </c>
-      <c r="E234" t="s">
-        <v>455</v>
       </c>
       <c r="F234" t="s">
         <v>456</v>
@@ -12362,10 +12362,10 @@
         <v>9</v>
       </c>
       <c r="D235" t="s">
+        <v>454</v>
+      </c>
+      <c r="E235" t="s">
         <v>459</v>
-      </c>
-      <c r="E235" t="s">
-        <v>455</v>
       </c>
       <c r="F235" t="s">
         <v>456</v>
@@ -12385,10 +12385,10 @@
         <v>9</v>
       </c>
       <c r="D236" t="s">
+        <v>454</v>
+      </c>
+      <c r="E236" t="s">
         <v>459</v>
-      </c>
-      <c r="E236" t="s">
-        <v>455</v>
       </c>
       <c r="F236" t="s">
         <v>456</v>
@@ -12408,10 +12408,10 @@
         <v>9</v>
       </c>
       <c r="D237" t="s">
+        <v>454</v>
+      </c>
+      <c r="E237" t="s">
         <v>459</v>
-      </c>
-      <c r="E237" t="s">
-        <v>455</v>
       </c>
       <c r="F237" t="s">
         <v>456</v>
@@ -12431,10 +12431,10 @@
         <v>9</v>
       </c>
       <c r="D238" t="s">
+        <v>454</v>
+      </c>
+      <c r="E238" t="s">
         <v>459</v>
-      </c>
-      <c r="E238" t="s">
-        <v>455</v>
       </c>
       <c r="F238" t="s">
         <v>456</v>
@@ -12454,10 +12454,10 @@
         <v>9</v>
       </c>
       <c r="D239" t="s">
+        <v>454</v>
+      </c>
+      <c r="E239" t="s">
         <v>459</v>
-      </c>
-      <c r="E239" t="s">
-        <v>455</v>
       </c>
       <c r="F239" t="s">
         <v>456</v>
@@ -12477,10 +12477,10 @@
         <v>9</v>
       </c>
       <c r="D240" t="s">
+        <v>454</v>
+      </c>
+      <c r="E240" t="s">
         <v>459</v>
-      </c>
-      <c r="E240" t="s">
-        <v>455</v>
       </c>
       <c r="F240" t="s">
         <v>456</v>
@@ -12500,10 +12500,10 @@
         <v>9</v>
       </c>
       <c r="D241" t="s">
+        <v>454</v>
+      </c>
+      <c r="E241" t="s">
         <v>459</v>
-      </c>
-      <c r="E241" t="s">
-        <v>455</v>
       </c>
       <c r="F241" t="s">
         <v>456</v>
@@ -12523,10 +12523,10 @@
         <v>9</v>
       </c>
       <c r="D242" t="s">
+        <v>454</v>
+      </c>
+      <c r="E242" t="s">
         <v>459</v>
-      </c>
-      <c r="E242" t="s">
-        <v>455</v>
       </c>
       <c r="F242" t="s">
         <v>456</v>
@@ -12546,10 +12546,10 @@
         <v>9</v>
       </c>
       <c r="D243" t="s">
+        <v>454</v>
+      </c>
+      <c r="E243" t="s">
         <v>459</v>
-      </c>
-      <c r="E243" t="s">
-        <v>455</v>
       </c>
       <c r="F243" t="s">
         <v>456</v>
@@ -12569,10 +12569,10 @@
         <v>9</v>
       </c>
       <c r="D244" t="s">
+        <v>454</v>
+      </c>
+      <c r="E244" t="s">
         <v>459</v>
-      </c>
-      <c r="E244" t="s">
-        <v>455</v>
       </c>
       <c r="F244" t="s">
         <v>456</v>
@@ -12615,10 +12615,10 @@
         <v>9</v>
       </c>
       <c r="D246" t="s">
+        <v>573</v>
+      </c>
+      <c r="E246" t="s">
         <v>578</v>
-      </c>
-      <c r="E246" t="s">
-        <v>574</v>
       </c>
       <c r="F246" t="s">
         <v>575</v>
@@ -12661,10 +12661,10 @@
         <v>9</v>
       </c>
       <c r="D248" t="s">
+        <v>573</v>
+      </c>
+      <c r="E248" t="s">
         <v>578</v>
-      </c>
-      <c r="E248" t="s">
-        <v>574</v>
       </c>
       <c r="F248" t="s">
         <v>575</v>
@@ -12753,10 +12753,10 @@
         <v>9</v>
       </c>
       <c r="D252" t="s">
+        <v>573</v>
+      </c>
+      <c r="E252" t="s">
         <v>591</v>
-      </c>
-      <c r="E252" t="s">
-        <v>574</v>
       </c>
       <c r="F252" t="s">
         <v>575</v>
@@ -12799,10 +12799,10 @@
         <v>9</v>
       </c>
       <c r="D254" t="s">
+        <v>459</v>
+      </c>
+      <c r="E254" t="s">
         <v>596</v>
-      </c>
-      <c r="E254" t="s">
-        <v>459</v>
       </c>
       <c r="F254" t="s">
         <v>575</v>
@@ -12868,10 +12868,10 @@
         <v>9</v>
       </c>
       <c r="D257" t="s">
+        <v>573</v>
+      </c>
+      <c r="E257" t="s">
         <v>578</v>
-      </c>
-      <c r="E257" t="s">
-        <v>574</v>
       </c>
       <c r="F257" t="s">
         <v>575</v>
@@ -12891,10 +12891,10 @@
         <v>9</v>
       </c>
       <c r="D258" t="s">
+        <v>573</v>
+      </c>
+      <c r="E258" t="s">
         <v>578</v>
-      </c>
-      <c r="E258" t="s">
-        <v>574</v>
       </c>
       <c r="F258" t="s">
         <v>575</v>
@@ -12914,10 +12914,10 @@
         <v>185</v>
       </c>
       <c r="D259" t="s">
+        <v>573</v>
+      </c>
+      <c r="E259" t="s">
         <v>607</v>
-      </c>
-      <c r="E259" t="s">
-        <v>574</v>
       </c>
       <c r="F259" t="s">
         <v>575</v>
@@ -13006,10 +13006,10 @@
         <v>9</v>
       </c>
       <c r="D263" t="s">
+        <v>573</v>
+      </c>
+      <c r="E263" t="s">
         <v>578</v>
-      </c>
-      <c r="E263" t="s">
-        <v>574</v>
       </c>
       <c r="F263" t="s">
         <v>575</v>
@@ -13029,10 +13029,10 @@
         <v>185</v>
       </c>
       <c r="D264" t="s">
+        <v>573</v>
+      </c>
+      <c r="E264" t="s">
         <v>578</v>
-      </c>
-      <c r="E264" t="s">
-        <v>574</v>
       </c>
       <c r="F264" t="s">
         <v>575</v>
@@ -13075,10 +13075,10 @@
         <v>9</v>
       </c>
       <c r="D266" t="s">
+        <v>573</v>
+      </c>
+      <c r="E266" t="s">
         <v>578</v>
-      </c>
-      <c r="E266" t="s">
-        <v>574</v>
       </c>
       <c r="F266" t="s">
         <v>575</v>
@@ -13121,10 +13121,10 @@
         <v>9</v>
       </c>
       <c r="D268" t="s">
+        <v>573</v>
+      </c>
+      <c r="E268" t="s">
         <v>578</v>
-      </c>
-      <c r="E268" t="s">
-        <v>574</v>
       </c>
       <c r="F268" t="s">
         <v>575</v>
@@ -13144,10 +13144,10 @@
         <v>9</v>
       </c>
       <c r="D269" t="s">
+        <v>573</v>
+      </c>
+      <c r="E269" t="s">
         <v>607</v>
-      </c>
-      <c r="E269" t="s">
-        <v>574</v>
       </c>
       <c r="F269" t="s">
         <v>575</v>
@@ -13167,10 +13167,10 @@
         <v>185</v>
       </c>
       <c r="D270" t="s">
+        <v>573</v>
+      </c>
+      <c r="E270" t="s">
         <v>578</v>
-      </c>
-      <c r="E270" t="s">
-        <v>574</v>
       </c>
       <c r="F270" t="s">
         <v>575</v>
@@ -13190,10 +13190,10 @@
         <v>9</v>
       </c>
       <c r="D271" t="s">
+        <v>573</v>
+      </c>
+      <c r="E271" t="s">
         <v>578</v>
-      </c>
-      <c r="E271" t="s">
-        <v>574</v>
       </c>
       <c r="F271" t="s">
         <v>575</v>
@@ -13236,10 +13236,10 @@
         <v>9</v>
       </c>
       <c r="D273" t="s">
+        <v>573</v>
+      </c>
+      <c r="E273" t="s">
         <v>578</v>
-      </c>
-      <c r="E273" t="s">
-        <v>574</v>
       </c>
       <c r="F273" t="s">
         <v>575</v>
@@ -13282,10 +13282,10 @@
         <v>9</v>
       </c>
       <c r="D275" t="s">
+        <v>573</v>
+      </c>
+      <c r="E275" t="s">
         <v>578</v>
-      </c>
-      <c r="E275" t="s">
-        <v>574</v>
       </c>
       <c r="F275" t="s">
         <v>575</v>
@@ -13305,10 +13305,10 @@
         <v>9</v>
       </c>
       <c r="D276" t="s">
+        <v>573</v>
+      </c>
+      <c r="E276" t="s">
         <v>644</v>
-      </c>
-      <c r="E276" t="s">
-        <v>574</v>
       </c>
       <c r="F276" t="s">
         <v>575</v>
@@ -13351,10 +13351,10 @@
         <v>9</v>
       </c>
       <c r="D278" t="s">
+        <v>573</v>
+      </c>
+      <c r="E278" t="s">
         <v>578</v>
-      </c>
-      <c r="E278" t="s">
-        <v>574</v>
       </c>
       <c r="F278" t="s">
         <v>575</v>
@@ -13397,10 +13397,10 @@
         <v>9</v>
       </c>
       <c r="D280" t="s">
+        <v>573</v>
+      </c>
+      <c r="E280" t="s">
         <v>578</v>
-      </c>
-      <c r="E280" t="s">
-        <v>574</v>
       </c>
       <c r="F280" t="s">
         <v>575</v>
@@ -13466,10 +13466,10 @@
         <v>9</v>
       </c>
       <c r="D283" t="s">
+        <v>573</v>
+      </c>
+      <c r="E283" t="s">
         <v>578</v>
-      </c>
-      <c r="E283" t="s">
-        <v>574</v>
       </c>
       <c r="F283" t="s">
         <v>575</v>
@@ -13581,10 +13581,10 @@
         <v>9</v>
       </c>
       <c r="D288" t="s">
+        <v>573</v>
+      </c>
+      <c r="E288" t="s">
         <v>644</v>
-      </c>
-      <c r="E288" t="s">
-        <v>574</v>
       </c>
       <c r="F288" t="s">
         <v>575</v>
@@ -13604,10 +13604,10 @@
         <v>9</v>
       </c>
       <c r="D289" t="s">
+        <v>573</v>
+      </c>
+      <c r="E289" t="s">
         <v>578</v>
-      </c>
-      <c r="E289" t="s">
-        <v>574</v>
       </c>
       <c r="F289" t="s">
         <v>575</v>
@@ -13673,10 +13673,10 @@
         <v>9</v>
       </c>
       <c r="D292" t="s">
+        <v>573</v>
+      </c>
+      <c r="E292" t="s">
         <v>644</v>
-      </c>
-      <c r="E292" t="s">
-        <v>574</v>
       </c>
       <c r="F292" t="s">
         <v>575</v>
@@ -13696,10 +13696,10 @@
         <v>9</v>
       </c>
       <c r="D293" t="s">
+        <v>573</v>
+      </c>
+      <c r="E293" t="s">
         <v>578</v>
-      </c>
-      <c r="E293" t="s">
-        <v>574</v>
       </c>
       <c r="F293" t="s">
         <v>575</v>
@@ -13857,10 +13857,10 @@
         <v>9</v>
       </c>
       <c r="D300" t="s">
+        <v>573</v>
+      </c>
+      <c r="E300" t="s">
         <v>578</v>
-      </c>
-      <c r="E300" t="s">
-        <v>574</v>
       </c>
       <c r="F300" t="s">
         <v>575</v>
@@ -13880,10 +13880,10 @@
         <v>9</v>
       </c>
       <c r="D301" t="s">
+        <v>573</v>
+      </c>
+      <c r="E301" t="s">
         <v>578</v>
-      </c>
-      <c r="E301" t="s">
-        <v>574</v>
       </c>
       <c r="F301" t="s">
         <v>575</v>
@@ -13903,10 +13903,10 @@
         <v>9</v>
       </c>
       <c r="D302" t="s">
+        <v>573</v>
+      </c>
+      <c r="E302" t="s">
         <v>578</v>
-      </c>
-      <c r="E302" t="s">
-        <v>574</v>
       </c>
       <c r="F302" t="s">
         <v>575</v>
@@ -13949,10 +13949,10 @@
         <v>9</v>
       </c>
       <c r="D304" t="s">
+        <v>573</v>
+      </c>
+      <c r="E304" t="s">
         <v>578</v>
-      </c>
-      <c r="E304" t="s">
-        <v>574</v>
       </c>
       <c r="F304" t="s">
         <v>575</v>
@@ -14018,10 +14018,10 @@
         <v>9</v>
       </c>
       <c r="D307" t="s">
+        <v>614</v>
+      </c>
+      <c r="E307" t="s">
         <v>711</v>
-      </c>
-      <c r="E307" t="s">
-        <v>615</v>
       </c>
       <c r="F307" t="s">
         <v>575</v>
@@ -14041,10 +14041,10 @@
         <v>9</v>
       </c>
       <c r="D308" t="s">
+        <v>573</v>
+      </c>
+      <c r="E308" t="s">
         <v>578</v>
-      </c>
-      <c r="E308" t="s">
-        <v>574</v>
       </c>
       <c r="F308" t="s">
         <v>575</v>
@@ -14386,10 +14386,10 @@
         <v>9</v>
       </c>
       <c r="D323" t="s">
+        <v>718</v>
+      </c>
+      <c r="E323" t="s">
         <v>747</v>
-      </c>
-      <c r="E323" t="s">
-        <v>719</v>
       </c>
       <c r="F323" t="s">
         <v>720</v>
@@ -14432,10 +14432,10 @@
         <v>9</v>
       </c>
       <c r="D325" t="s">
-        <v>718</v>
+        <v>752</v>
       </c>
       <c r="E325" t="s">
-        <v>752</v>
+        <v>719</v>
       </c>
       <c r="F325" t="s">
         <v>720</v>
@@ -14570,10 +14570,10 @@
         <v>9</v>
       </c>
       <c r="D331" t="s">
-        <v>718</v>
+        <v>765</v>
       </c>
       <c r="E331" t="s">
-        <v>765</v>
+        <v>719</v>
       </c>
       <c r="F331" t="s">
         <v>720</v>
@@ -14869,10 +14869,10 @@
         <v>185</v>
       </c>
       <c r="D344" t="s">
+        <v>790</v>
+      </c>
+      <c r="E344" t="s">
         <v>794</v>
-      </c>
-      <c r="E344" t="s">
-        <v>791</v>
       </c>
       <c r="F344" t="s">
         <v>720</v>
@@ -14915,10 +14915,10 @@
         <v>185</v>
       </c>
       <c r="D346" t="s">
+        <v>797</v>
+      </c>
+      <c r="E346" t="s">
         <v>802</v>
-      </c>
-      <c r="E346" t="s">
-        <v>798</v>
       </c>
       <c r="F346" t="s">
         <v>799</v>
@@ -15145,10 +15145,10 @@
         <v>9</v>
       </c>
       <c r="D356" t="s">
+        <v>797</v>
+      </c>
+      <c r="E356" t="s">
         <v>823</v>
-      </c>
-      <c r="E356" t="s">
-        <v>798</v>
       </c>
       <c r="F356" t="s">
         <v>799</v>
@@ -15375,10 +15375,10 @@
         <v>9</v>
       </c>
       <c r="D366" t="s">
+        <v>797</v>
+      </c>
+      <c r="E366" t="s">
         <v>844</v>
-      </c>
-      <c r="E366" t="s">
-        <v>798</v>
       </c>
       <c r="F366" t="s">
         <v>799</v>
@@ -15398,10 +15398,10 @@
         <v>9</v>
       </c>
       <c r="D367" t="s">
+        <v>797</v>
+      </c>
+      <c r="E367" t="s">
         <v>802</v>
-      </c>
-      <c r="E367" t="s">
-        <v>798</v>
       </c>
       <c r="F367" t="s">
         <v>799</v>
@@ -15490,10 +15490,10 @@
         <v>9</v>
       </c>
       <c r="D371" t="s">
-        <v>797</v>
+        <v>855</v>
       </c>
       <c r="E371" t="s">
-        <v>855</v>
+        <v>798</v>
       </c>
       <c r="F371" t="s">
         <v>799</v>
@@ -15697,10 +15697,10 @@
         <v>9</v>
       </c>
       <c r="D380" t="s">
+        <v>872</v>
+      </c>
+      <c r="E380" t="s">
         <v>879</v>
-      </c>
-      <c r="E380" t="s">
-        <v>873</v>
       </c>
       <c r="F380" t="s">
         <v>874</v>
@@ -15835,10 +15835,10 @@
         <v>9</v>
       </c>
       <c r="D386" t="s">
+        <v>872</v>
+      </c>
+      <c r="E386" t="s">
         <v>892</v>
-      </c>
-      <c r="E386" t="s">
-        <v>873</v>
       </c>
       <c r="F386" t="s">
         <v>874</v>
@@ -15858,10 +15858,10 @@
         <v>9</v>
       </c>
       <c r="D387" t="s">
+        <v>872</v>
+      </c>
+      <c r="E387" t="s">
         <v>895</v>
-      </c>
-      <c r="E387" t="s">
-        <v>873</v>
       </c>
       <c r="F387" t="s">
         <v>874</v>
@@ -15996,10 +15996,10 @@
         <v>9</v>
       </c>
       <c r="D393" t="s">
+        <v>872</v>
+      </c>
+      <c r="E393" t="s">
         <v>910</v>
-      </c>
-      <c r="E393" t="s">
-        <v>873</v>
       </c>
       <c r="F393" t="s">
         <v>874</v>
@@ -16318,10 +16318,10 @@
         <v>9</v>
       </c>
       <c r="D407" t="s">
+        <v>872</v>
+      </c>
+      <c r="E407" t="s">
         <v>947</v>
-      </c>
-      <c r="E407" t="s">
-        <v>873</v>
       </c>
       <c r="F407" t="s">
         <v>874</v>
@@ -16594,10 +16594,10 @@
         <v>9</v>
       </c>
       <c r="D419" t="s">
+        <v>968</v>
+      </c>
+      <c r="E419" t="s">
         <v>975</v>
-      </c>
-      <c r="E419" t="s">
-        <v>969</v>
       </c>
       <c r="F419" t="s">
         <v>970</v>
@@ -16640,10 +16640,10 @@
         <v>9</v>
       </c>
       <c r="D421" t="s">
+        <v>968</v>
+      </c>
+      <c r="E421" t="s">
         <v>980</v>
-      </c>
-      <c r="E421" t="s">
-        <v>969</v>
       </c>
       <c r="F421" t="s">
         <v>970</v>
@@ -16916,10 +16916,10 @@
         <v>9</v>
       </c>
       <c r="D433" t="s">
+        <v>968</v>
+      </c>
+      <c r="E433" t="s">
         <v>1009</v>
-      </c>
-      <c r="E433" t="s">
-        <v>969</v>
       </c>
       <c r="F433" t="s">
         <v>970</v>
@@ -16985,10 +16985,10 @@
         <v>9</v>
       </c>
       <c r="D436" t="s">
+        <v>968</v>
+      </c>
+      <c r="E436" t="s">
         <v>1016</v>
-      </c>
-      <c r="E436" t="s">
-        <v>969</v>
       </c>
       <c r="F436" t="s">
         <v>970</v>
@@ -17008,10 +17008,10 @@
         <v>9</v>
       </c>
       <c r="D437" t="s">
+        <v>968</v>
+      </c>
+      <c r="E437" t="s">
         <v>1019</v>
-      </c>
-      <c r="E437" t="s">
-        <v>969</v>
       </c>
       <c r="F437" t="s">
         <v>970</v>
@@ -17652,10 +17652,10 @@
         <v>9</v>
       </c>
       <c r="D465" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E465" t="s">
         <v>1086</v>
-      </c>
-      <c r="E465" t="s">
-        <v>1061</v>
       </c>
       <c r="F465" t="s">
         <v>1062</v>
@@ -17675,10 +17675,10 @@
         <v>9</v>
       </c>
       <c r="D466" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E466" t="s">
         <v>1089</v>
-      </c>
-      <c r="E466" t="s">
-        <v>1083</v>
       </c>
       <c r="F466" t="s">
         <v>1062</v>
@@ -17836,10 +17836,10 @@
         <v>9</v>
       </c>
       <c r="D473" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E473" t="s">
         <v>1108</v>
-      </c>
-      <c r="E473" t="s">
-        <v>1083</v>
       </c>
       <c r="F473" t="s">
         <v>1062</v>
@@ -18181,10 +18181,10 @@
         <v>9</v>
       </c>
       <c r="D488" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E488" t="s">
         <v>1142</v>
-      </c>
-      <c r="E488" t="s">
-        <v>1138</v>
       </c>
       <c r="F488" t="s">
         <v>1139</v>
@@ -18273,10 +18273,10 @@
         <v>185</v>
       </c>
       <c r="D492" t="s">
-        <v>1137</v>
+        <v>1151</v>
       </c>
       <c r="E492" t="s">
-        <v>1151</v>
+        <v>1138</v>
       </c>
       <c r="F492" t="s">
         <v>1139</v>
@@ -18319,10 +18319,10 @@
         <v>9</v>
       </c>
       <c r="D494" t="s">
-        <v>1098</v>
+        <v>1156</v>
       </c>
       <c r="E494" t="s">
-        <v>1156</v>
+        <v>1099</v>
       </c>
       <c r="F494" t="s">
         <v>1139</v>
@@ -18342,10 +18342,10 @@
         <v>185</v>
       </c>
       <c r="D495" t="s">
-        <v>1098</v>
+        <v>1156</v>
       </c>
       <c r="E495" t="s">
-        <v>1156</v>
+        <v>1099</v>
       </c>
       <c r="F495" t="s">
         <v>1139</v>
@@ -18411,10 +18411,10 @@
         <v>9</v>
       </c>
       <c r="D498" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E498" t="s">
         <v>1165</v>
-      </c>
-      <c r="E498" t="s">
-        <v>1138</v>
       </c>
       <c r="F498" t="s">
         <v>1139</v>
@@ -18503,10 +18503,10 @@
         <v>185</v>
       </c>
       <c r="D502" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E502" t="s">
         <v>1174</v>
-      </c>
-      <c r="E502" t="s">
-        <v>1138</v>
       </c>
       <c r="F502" t="s">
         <v>1139</v>
@@ -18664,10 +18664,10 @@
         <v>185</v>
       </c>
       <c r="D509" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="E509" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="F509" t="s">
         <v>1139</v>
@@ -18733,10 +18733,10 @@
         <v>9</v>
       </c>
       <c r="D512" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E512" t="s">
         <v>1202</v>
-      </c>
-      <c r="E512" t="s">
-        <v>1138</v>
       </c>
       <c r="F512" t="s">
         <v>1139</v>
@@ -18756,10 +18756,10 @@
         <v>185</v>
       </c>
       <c r="D513" t="s">
-        <v>1137</v>
+        <v>1205</v>
       </c>
       <c r="E513" t="s">
-        <v>1205</v>
+        <v>1138</v>
       </c>
       <c r="F513" t="s">
         <v>1139</v>
@@ -18940,10 +18940,10 @@
         <v>185</v>
       </c>
       <c r="D521" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E521" t="s">
         <v>1222</v>
-      </c>
-      <c r="E521" t="s">
-        <v>1138</v>
       </c>
       <c r="F521" t="s">
         <v>1139</v>
@@ -18963,10 +18963,10 @@
         <v>185</v>
       </c>
       <c r="D522" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E522" t="s">
         <v>1225</v>
-      </c>
-      <c r="E522" t="s">
-        <v>1138</v>
       </c>
       <c r="F522" t="s">
         <v>1139</v>
@@ -18986,10 +18986,10 @@
         <v>9</v>
       </c>
       <c r="D523" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E523" t="s">
         <v>1228</v>
-      </c>
-      <c r="E523" t="s">
-        <v>1138</v>
       </c>
       <c r="F523" t="s">
         <v>1139</v>
@@ -19032,10 +19032,10 @@
         <v>9</v>
       </c>
       <c r="D525" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E525" t="s">
         <v>1142</v>
-      </c>
-      <c r="E525" t="s">
-        <v>1233</v>
       </c>
       <c r="F525" t="s">
         <v>1234</v>
@@ -19055,10 +19055,10 @@
         <v>9</v>
       </c>
       <c r="D526" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E526" t="s">
         <v>1142</v>
-      </c>
-      <c r="E526" t="s">
-        <v>1233</v>
       </c>
       <c r="F526" t="s">
         <v>1234</v>
@@ -19078,10 +19078,10 @@
         <v>9</v>
       </c>
       <c r="D527" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E527" t="s">
         <v>1142</v>
-      </c>
-      <c r="E527" t="s">
-        <v>1233</v>
       </c>
       <c r="F527" t="s">
         <v>1234</v>
@@ -19101,10 +19101,10 @@
         <v>9</v>
       </c>
       <c r="D528" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E528" t="s">
         <v>1142</v>
-      </c>
-      <c r="E528" t="s">
-        <v>1233</v>
       </c>
       <c r="F528" t="s">
         <v>1234</v>
@@ -19124,10 +19124,10 @@
         <v>9</v>
       </c>
       <c r="D529" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E529" t="s">
         <v>1244</v>
-      </c>
-      <c r="E529" t="s">
-        <v>1233</v>
       </c>
       <c r="F529" t="s">
         <v>1234</v>
@@ -19147,10 +19147,10 @@
         <v>9</v>
       </c>
       <c r="D530" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E530" t="s">
         <v>1142</v>
-      </c>
-      <c r="E530" t="s">
-        <v>1247</v>
       </c>
       <c r="F530" t="s">
         <v>1234</v>
@@ -19170,10 +19170,10 @@
         <v>9</v>
       </c>
       <c r="D531" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E531" t="s">
         <v>1142</v>
-      </c>
-      <c r="E531" t="s">
-        <v>1233</v>
       </c>
       <c r="F531" t="s">
         <v>1234</v>
@@ -19193,10 +19193,10 @@
         <v>9</v>
       </c>
       <c r="D532" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E532" t="s">
         <v>1142</v>
-      </c>
-      <c r="E532" t="s">
-        <v>1233</v>
       </c>
       <c r="F532" t="s">
         <v>1234</v>
@@ -19216,10 +19216,10 @@
         <v>9</v>
       </c>
       <c r="D533" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E533" t="s">
         <v>1142</v>
-      </c>
-      <c r="E533" t="s">
-        <v>1233</v>
       </c>
       <c r="F533" t="s">
         <v>1234</v>
@@ -19239,10 +19239,10 @@
         <v>9</v>
       </c>
       <c r="D534" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E534" t="s">
         <v>1142</v>
-      </c>
-      <c r="E534" t="s">
-        <v>1233</v>
       </c>
       <c r="F534" t="s">
         <v>1234</v>
@@ -19262,10 +19262,10 @@
         <v>9</v>
       </c>
       <c r="D535" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E535" t="s">
         <v>1142</v>
-      </c>
-      <c r="E535" t="s">
-        <v>1233</v>
       </c>
       <c r="F535" t="s">
         <v>1234</v>
@@ -19285,10 +19285,10 @@
         <v>9</v>
       </c>
       <c r="D536" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E536" t="s">
         <v>1260</v>
-      </c>
-      <c r="E536" t="s">
-        <v>1233</v>
       </c>
       <c r="F536" t="s">
         <v>1234</v>
@@ -19308,10 +19308,10 @@
         <v>9</v>
       </c>
       <c r="D537" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E537" t="s">
         <v>1263</v>
-      </c>
-      <c r="E537" t="s">
-        <v>1233</v>
       </c>
       <c r="F537" t="s">
         <v>1234</v>
@@ -19331,10 +19331,10 @@
         <v>9</v>
       </c>
       <c r="D538" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E538" t="s">
         <v>1142</v>
-      </c>
-      <c r="E538" t="s">
-        <v>1233</v>
       </c>
       <c r="F538" t="s">
         <v>1234</v>
@@ -19354,10 +19354,10 @@
         <v>9</v>
       </c>
       <c r="D539" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E539" t="s">
         <v>1142</v>
-      </c>
-      <c r="E539" t="s">
-        <v>1233</v>
       </c>
       <c r="F539" t="s">
         <v>1234</v>
@@ -19377,10 +19377,10 @@
         <v>9</v>
       </c>
       <c r="D540" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E540" t="s">
         <v>1142</v>
-      </c>
-      <c r="E540" t="s">
-        <v>1197</v>
       </c>
       <c r="F540" t="s">
         <v>1234</v>
@@ -19400,10 +19400,10 @@
         <v>9</v>
       </c>
       <c r="D541" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E541" t="s">
         <v>1142</v>
-      </c>
-      <c r="E541" t="s">
-        <v>1233</v>
       </c>
       <c r="F541" t="s">
         <v>1234</v>
@@ -19423,10 +19423,10 @@
         <v>9</v>
       </c>
       <c r="D542" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E542" t="s">
         <v>1142</v>
-      </c>
-      <c r="E542" t="s">
-        <v>1233</v>
       </c>
       <c r="F542" t="s">
         <v>1234</v>
@@ -19446,10 +19446,10 @@
         <v>9</v>
       </c>
       <c r="D543" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E543" t="s">
         <v>1142</v>
-      </c>
-      <c r="E543" t="s">
-        <v>1233</v>
       </c>
       <c r="F543" t="s">
         <v>1234</v>
@@ -19469,10 +19469,10 @@
         <v>9</v>
       </c>
       <c r="D544" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E544" t="s">
         <v>1142</v>
-      </c>
-      <c r="E544" t="s">
-        <v>1233</v>
       </c>
       <c r="F544" t="s">
         <v>1234</v>
@@ -19492,10 +19492,10 @@
         <v>9</v>
       </c>
       <c r="D545" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E545" t="s">
         <v>1142</v>
-      </c>
-      <c r="E545" t="s">
-        <v>1280</v>
       </c>
       <c r="F545" t="s">
         <v>1234</v>
@@ -19515,10 +19515,10 @@
         <v>9</v>
       </c>
       <c r="D546" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E546" t="s">
         <v>1142</v>
-      </c>
-      <c r="E546" t="s">
-        <v>1233</v>
       </c>
       <c r="F546" t="s">
         <v>1234</v>
@@ -19538,10 +19538,10 @@
         <v>9</v>
       </c>
       <c r="D547" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E547" t="s">
         <v>1142</v>
-      </c>
-      <c r="E547" t="s">
-        <v>1233</v>
       </c>
       <c r="F547" t="s">
         <v>1234</v>
@@ -19584,10 +19584,10 @@
         <v>9</v>
       </c>
       <c r="D549" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E549" t="s">
         <v>1292</v>
-      </c>
-      <c r="E549" t="s">
-        <v>1288</v>
       </c>
       <c r="F549" t="s">
         <v>1289</v>
@@ -19607,10 +19607,10 @@
         <v>9</v>
       </c>
       <c r="D550" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E550" t="s">
         <v>1295</v>
-      </c>
-      <c r="E550" t="s">
-        <v>1288</v>
       </c>
       <c r="F550" t="s">
         <v>1289</v>
@@ -19699,10 +19699,10 @@
         <v>9</v>
       </c>
       <c r="D554" t="s">
-        <v>1287</v>
+        <v>1304</v>
       </c>
       <c r="E554" t="s">
-        <v>1304</v>
+        <v>1288</v>
       </c>
       <c r="F554" t="s">
         <v>1289</v>
@@ -19837,10 +19837,10 @@
         <v>9</v>
       </c>
       <c r="D560" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E560" t="s">
         <v>1319</v>
-      </c>
-      <c r="E560" t="s">
-        <v>1288</v>
       </c>
       <c r="F560" t="s">
         <v>1289</v>
@@ -19860,10 +19860,10 @@
         <v>9</v>
       </c>
       <c r="D561" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E561" t="s">
         <v>1319</v>
-      </c>
-      <c r="E561" t="s">
-        <v>1288</v>
       </c>
       <c r="F561" t="s">
         <v>1289</v>
@@ -19906,10 +19906,10 @@
         <v>9</v>
       </c>
       <c r="D563" t="s">
-        <v>1287</v>
+        <v>1326</v>
       </c>
       <c r="E563" t="s">
-        <v>1326</v>
+        <v>1288</v>
       </c>
       <c r="F563" t="s">
         <v>1289</v>
@@ -20136,10 +20136,10 @@
         <v>9</v>
       </c>
       <c r="D573" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E573" t="s">
         <v>1349</v>
-      </c>
-      <c r="E573" t="s">
-        <v>1233</v>
       </c>
       <c r="F573" t="s">
         <v>1350</v>
@@ -20159,10 +20159,10 @@
         <v>9</v>
       </c>
       <c r="D574" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E574" t="s">
         <v>1349</v>
-      </c>
-      <c r="E574" t="s">
-        <v>1353</v>
       </c>
       <c r="F574" t="s">
         <v>1350</v>
@@ -20182,10 +20182,10 @@
         <v>9</v>
       </c>
       <c r="D575" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E575" t="s">
         <v>1349</v>
-      </c>
-      <c r="E575" t="s">
-        <v>1353</v>
       </c>
       <c r="F575" t="s">
         <v>1350</v>
@@ -20205,10 +20205,10 @@
         <v>9</v>
       </c>
       <c r="D576" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E576" t="s">
         <v>1349</v>
-      </c>
-      <c r="E576" t="s">
-        <v>1353</v>
       </c>
       <c r="F576" t="s">
         <v>1350</v>
@@ -20228,10 +20228,10 @@
         <v>9</v>
       </c>
       <c r="D577" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E577" t="s">
         <v>1349</v>
-      </c>
-      <c r="E577" t="s">
-        <v>1288</v>
       </c>
       <c r="F577" t="s">
         <v>1350</v>
@@ -20251,10 +20251,10 @@
         <v>9</v>
       </c>
       <c r="D578" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E578" t="s">
         <v>1362</v>
-      </c>
-      <c r="E578" t="s">
-        <v>1353</v>
       </c>
       <c r="F578" t="s">
         <v>1350</v>
@@ -20297,10 +20297,10 @@
         <v>9</v>
       </c>
       <c r="D580" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E580" t="s">
         <v>1369</v>
-      </c>
-      <c r="E580" t="s">
-        <v>1353</v>
       </c>
       <c r="F580" t="s">
         <v>1350</v>
@@ -20320,10 +20320,10 @@
         <v>9</v>
       </c>
       <c r="D581" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E581" t="s">
         <v>1372</v>
-      </c>
-      <c r="E581" t="s">
-        <v>1353</v>
       </c>
       <c r="F581" t="s">
         <v>1350</v>
@@ -20343,10 +20343,10 @@
         <v>9</v>
       </c>
       <c r="D582" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E582" t="s">
         <v>1349</v>
-      </c>
-      <c r="E582" t="s">
-        <v>1353</v>
       </c>
       <c r="F582" t="s">
         <v>1350</v>
@@ -20412,10 +20412,10 @@
         <v>9</v>
       </c>
       <c r="D585" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E585" t="s">
         <v>1349</v>
-      </c>
-      <c r="E585" t="s">
-        <v>1353</v>
       </c>
       <c r="F585" t="s">
         <v>1350</v>
@@ -20458,10 +20458,10 @@
         <v>9</v>
       </c>
       <c r="D587" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E587" t="s">
         <v>1391</v>
-      </c>
-      <c r="E587" t="s">
-        <v>1353</v>
       </c>
       <c r="F587" t="s">
         <v>1350</v>
@@ -20481,10 +20481,10 @@
         <v>9</v>
       </c>
       <c r="D588" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E588" t="s">
         <v>1394</v>
-      </c>
-      <c r="E588" t="s">
-        <v>1353</v>
       </c>
       <c r="F588" t="s">
         <v>1350</v>
@@ -20504,10 +20504,10 @@
         <v>9</v>
       </c>
       <c r="D589" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E589" t="s">
         <v>1349</v>
-      </c>
-      <c r="E589" t="s">
-        <v>1353</v>
       </c>
       <c r="F589" t="s">
         <v>1350</v>
@@ -20527,10 +20527,10 @@
         <v>9</v>
       </c>
       <c r="D590" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E590" t="s">
         <v>1349</v>
-      </c>
-      <c r="E590" t="s">
-        <v>1353</v>
       </c>
       <c r="F590" t="s">
         <v>1350</v>
@@ -20550,10 +20550,10 @@
         <v>9</v>
       </c>
       <c r="D591" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E591" t="s">
         <v>1349</v>
-      </c>
-      <c r="E591" t="s">
-        <v>1353</v>
       </c>
       <c r="F591" t="s">
         <v>1350</v>
@@ -20573,10 +20573,10 @@
         <v>9</v>
       </c>
       <c r="D592" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E592" t="s">
         <v>1349</v>
-      </c>
-      <c r="E592" t="s">
-        <v>1403</v>
       </c>
       <c r="F592" t="s">
         <v>1350</v>
@@ -20596,10 +20596,10 @@
         <v>9</v>
       </c>
       <c r="D593" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E593" t="s">
         <v>1349</v>
-      </c>
-      <c r="E593" t="s">
-        <v>1353</v>
       </c>
       <c r="F593" t="s">
         <v>1350</v>
@@ -20619,10 +20619,10 @@
         <v>9</v>
       </c>
       <c r="D594" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E594" t="s">
         <v>1349</v>
-      </c>
-      <c r="E594" t="s">
-        <v>1353</v>
       </c>
       <c r="F594" t="s">
         <v>1350</v>
@@ -20642,10 +20642,10 @@
         <v>9</v>
       </c>
       <c r="D595" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E595" t="s">
         <v>1349</v>
-      </c>
-      <c r="E595" t="s">
-        <v>1353</v>
       </c>
       <c r="F595" t="s">
         <v>1350</v>
@@ -20665,10 +20665,10 @@
         <v>9</v>
       </c>
       <c r="D596" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E596" t="s">
         <v>1349</v>
-      </c>
-      <c r="E596" t="s">
-        <v>1353</v>
       </c>
       <c r="F596" t="s">
         <v>1350</v>
@@ -20872,10 +20872,10 @@
         <v>9</v>
       </c>
       <c r="D605" t="s">
+        <v>1414</v>
+      </c>
+      <c r="E605" t="s">
         <v>1441</v>
-      </c>
-      <c r="E605" t="s">
-        <v>1415</v>
       </c>
       <c r="F605" t="s">
         <v>1416</v>
@@ -20964,10 +20964,10 @@
         <v>9</v>
       </c>
       <c r="D609" t="s">
+        <v>1391</v>
+      </c>
+      <c r="E609" t="s">
         <v>1452</v>
-      </c>
-      <c r="E609" t="s">
-        <v>1391</v>
       </c>
       <c r="F609" t="s">
         <v>1416</v>
@@ -21010,10 +21010,10 @@
         <v>9</v>
       </c>
       <c r="D611" t="s">
-        <v>1419</v>
+        <v>1457</v>
       </c>
       <c r="E611" t="s">
-        <v>1457</v>
+        <v>1420</v>
       </c>
       <c r="F611" t="s">
         <v>1416</v>
@@ -21033,10 +21033,10 @@
         <v>9</v>
       </c>
       <c r="D612" t="s">
+        <v>1414</v>
+      </c>
+      <c r="E612" t="s">
         <v>1460</v>
-      </c>
-      <c r="E612" t="s">
-        <v>1415</v>
       </c>
       <c r="F612" t="s">
         <v>1416</v>
@@ -21079,10 +21079,10 @@
         <v>9</v>
       </c>
       <c r="D614" t="s">
+        <v>1414</v>
+      </c>
+      <c r="E614" t="s">
         <v>1465</v>
-      </c>
-      <c r="E614" t="s">
-        <v>1415</v>
       </c>
       <c r="F614" t="s">
         <v>1416</v>
@@ -21401,10 +21401,10 @@
         <v>9</v>
       </c>
       <c r="D628" t="s">
-        <v>1484</v>
+        <v>1499</v>
       </c>
       <c r="E628" t="s">
-        <v>1499</v>
+        <v>1485</v>
       </c>
       <c r="F628" t="s">
         <v>1486</v>
@@ -21424,10 +21424,10 @@
         <v>9</v>
       </c>
       <c r="D629" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E629" t="s">
         <v>1502</v>
-      </c>
-      <c r="E629" t="s">
-        <v>1485</v>
       </c>
       <c r="F629" t="s">
         <v>1486</v>
@@ -21493,10 +21493,10 @@
         <v>9</v>
       </c>
       <c r="D632" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E632" t="s">
         <v>1502</v>
-      </c>
-      <c r="E632" t="s">
-        <v>1509</v>
       </c>
       <c r="F632" t="s">
         <v>1486</v>
@@ -21585,10 +21585,10 @@
         <v>9</v>
       </c>
       <c r="D636" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E636" t="s">
         <v>1522</v>
-      </c>
-      <c r="E636" t="s">
-        <v>1485</v>
       </c>
       <c r="F636" t="s">
         <v>1486</v>
@@ -21723,10 +21723,10 @@
         <v>9</v>
       </c>
       <c r="D642" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E642" t="s">
         <v>1539</v>
-      </c>
-      <c r="E642" t="s">
-        <v>1485</v>
       </c>
       <c r="F642" t="s">
         <v>1486</v>
@@ -21746,10 +21746,10 @@
         <v>9</v>
       </c>
       <c r="D643" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E643" t="s">
         <v>1542</v>
-      </c>
-      <c r="E643" t="s">
-        <v>1485</v>
       </c>
       <c r="F643" t="s">
         <v>1486</v>
@@ -21815,10 +21815,10 @@
         <v>9</v>
       </c>
       <c r="D646" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E646" t="s">
         <v>1549</v>
-      </c>
-      <c r="E646" t="s">
-        <v>1485</v>
       </c>
       <c r="F646" t="s">
         <v>1486</v>
@@ -21930,10 +21930,10 @@
         <v>9</v>
       </c>
       <c r="D651" t="s">
-        <v>1556</v>
+        <v>1565</v>
       </c>
       <c r="E651" t="s">
-        <v>1565</v>
+        <v>1557</v>
       </c>
       <c r="F651" t="s">
         <v>1558</v>
@@ -21999,10 +21999,10 @@
         <v>9</v>
       </c>
       <c r="D654" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E654" t="s">
         <v>1542</v>
-      </c>
-      <c r="E654" t="s">
-        <v>1485</v>
       </c>
       <c r="F654" t="s">
         <v>1558</v>
@@ -22114,10 +22114,10 @@
         <v>9</v>
       </c>
       <c r="D659" t="s">
+        <v>1588</v>
+      </c>
+      <c r="E659" t="s">
         <v>1522</v>
-      </c>
-      <c r="E659" t="s">
-        <v>1588</v>
       </c>
       <c r="F659" t="s">
         <v>1558</v>
@@ -22183,10 +22183,10 @@
         <v>9</v>
       </c>
       <c r="D662" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="E662" t="s">
-        <v>1561</v>
+        <v>1569</v>
       </c>
       <c r="F662" t="s">
         <v>1558</v>
@@ -22229,10 +22229,10 @@
         <v>9</v>
       </c>
       <c r="D664" t="s">
+        <v>1603</v>
+      </c>
+      <c r="E664" t="s">
         <v>1542</v>
-      </c>
-      <c r="E664" t="s">
-        <v>1603</v>
       </c>
       <c r="F664" t="s">
         <v>1558</v>
@@ -22252,10 +22252,10 @@
         <v>9</v>
       </c>
       <c r="D665" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E665" t="s">
         <v>1606</v>
-      </c>
-      <c r="E665" t="s">
-        <v>1569</v>
       </c>
       <c r="F665" t="s">
         <v>1558</v>
@@ -22275,10 +22275,10 @@
         <v>9</v>
       </c>
       <c r="D666" t="s">
+        <v>1556</v>
+      </c>
+      <c r="E666" t="s">
         <v>1606</v>
-      </c>
-      <c r="E666" t="s">
-        <v>1557</v>
       </c>
       <c r="F666" t="s">
         <v>1558</v>
@@ -22344,10 +22344,10 @@
         <v>9</v>
       </c>
       <c r="D669" t="s">
+        <v>1588</v>
+      </c>
+      <c r="E669" t="s">
         <v>1542</v>
-      </c>
-      <c r="E669" t="s">
-        <v>1588</v>
       </c>
       <c r="F669" t="s">
         <v>1558</v>
@@ -22390,10 +22390,10 @@
         <v>9</v>
       </c>
       <c r="D671" t="s">
-        <v>1556</v>
+        <v>1621</v>
       </c>
       <c r="E671" t="s">
-        <v>1621</v>
+        <v>1557</v>
       </c>
       <c r="F671" t="s">
         <v>1558</v>
@@ -22459,10 +22459,10 @@
         <v>9</v>
       </c>
       <c r="D674" t="s">
+        <v>1591</v>
+      </c>
+      <c r="E674" t="s">
         <v>1542</v>
-      </c>
-      <c r="E674" t="s">
-        <v>1592</v>
       </c>
       <c r="F674" t="s">
         <v>1558</v>
@@ -22482,10 +22482,10 @@
         <v>9</v>
       </c>
       <c r="D675" t="s">
-        <v>1556</v>
+        <v>1565</v>
       </c>
       <c r="E675" t="s">
-        <v>1565</v>
+        <v>1557</v>
       </c>
       <c r="F675" t="s">
         <v>1558</v>
@@ -22505,10 +22505,10 @@
         <v>9</v>
       </c>
       <c r="D676" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E676" t="s">
         <v>1632</v>
-      </c>
-      <c r="E676" t="s">
-        <v>1569</v>
       </c>
       <c r="F676" t="s">
         <v>1558</v>
@@ -22804,10 +22804,10 @@
         <v>9</v>
       </c>
       <c r="D689" t="s">
-        <v>1650</v>
+        <v>1666</v>
       </c>
       <c r="E689" t="s">
-        <v>1666</v>
+        <v>1651</v>
       </c>
       <c r="F689" t="s">
         <v>1647</v>
@@ -22873,10 +22873,10 @@
         <v>9</v>
       </c>
       <c r="D692" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E692" t="s">
         <v>1675</v>
-      </c>
-      <c r="E692" t="s">
-        <v>1569</v>
       </c>
       <c r="F692" t="s">
         <v>1647</v>
@@ -23126,10 +23126,10 @@
         <v>9</v>
       </c>
       <c r="D703" t="s">
+        <v>1702</v>
+      </c>
+      <c r="E703" t="s">
         <v>1712</v>
-      </c>
-      <c r="E703" t="s">
-        <v>1703</v>
       </c>
       <c r="F703" t="s">
         <v>1647</v>
@@ -23172,10 +23172,10 @@
         <v>9</v>
       </c>
       <c r="D705" t="s">
+        <v>1696</v>
+      </c>
+      <c r="E705" t="s">
         <v>1717</v>
-      </c>
-      <c r="E705" t="s">
-        <v>1697</v>
       </c>
       <c r="F705" t="s">
         <v>1647</v>
@@ -23218,10 +23218,10 @@
         <v>9</v>
       </c>
       <c r="D707" t="s">
-        <v>1654</v>
+        <v>1696</v>
       </c>
       <c r="E707" t="s">
-        <v>1697</v>
+        <v>1655</v>
       </c>
       <c r="F707" t="s">
         <v>1647</v>
@@ -23241,10 +23241,10 @@
         <v>9</v>
       </c>
       <c r="D708" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E708" t="s">
         <v>1724</v>
-      </c>
-      <c r="E708" t="s">
-        <v>1651</v>
       </c>
       <c r="F708" t="s">
         <v>1647</v>
@@ -23310,10 +23310,10 @@
         <v>9</v>
       </c>
       <c r="D711" t="s">
-        <v>1654</v>
+        <v>1696</v>
       </c>
       <c r="E711" t="s">
-        <v>1697</v>
+        <v>1655</v>
       </c>
       <c r="F711" t="s">
         <v>1647</v>
@@ -23402,10 +23402,10 @@
         <v>9</v>
       </c>
       <c r="D715" t="s">
-        <v>1692</v>
+        <v>1696</v>
       </c>
       <c r="E715" t="s">
-        <v>1697</v>
+        <v>1693</v>
       </c>
       <c r="F715" t="s">
         <v>1647</v>
@@ -23494,10 +23494,10 @@
         <v>9</v>
       </c>
       <c r="D719" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E719" t="s">
         <v>1752</v>
-      </c>
-      <c r="E719" t="s">
-        <v>1748</v>
       </c>
       <c r="F719" t="s">
         <v>1749</v>
@@ -23517,10 +23517,10 @@
         <v>9</v>
       </c>
       <c r="D720" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E720" t="s">
         <v>1752</v>
-      </c>
-      <c r="E720" t="s">
-        <v>1748</v>
       </c>
       <c r="F720" t="s">
         <v>1749</v>
@@ -23540,10 +23540,10 @@
         <v>9</v>
       </c>
       <c r="D721" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E721" t="s">
         <v>1752</v>
-      </c>
-      <c r="E721" t="s">
-        <v>1748</v>
       </c>
       <c r="F721" t="s">
         <v>1749</v>
@@ -23563,10 +23563,10 @@
         <v>9</v>
       </c>
       <c r="D722" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E722" t="s">
         <v>1752</v>
-      </c>
-      <c r="E722" t="s">
-        <v>1748</v>
       </c>
       <c r="F722" t="s">
         <v>1749</v>
@@ -23586,10 +23586,10 @@
         <v>9</v>
       </c>
       <c r="D723" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E723" t="s">
         <v>1752</v>
-      </c>
-      <c r="E723" t="s">
-        <v>1748</v>
       </c>
       <c r="F723" t="s">
         <v>1749</v>
@@ -23609,10 +23609,10 @@
         <v>9</v>
       </c>
       <c r="D724" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E724" t="s">
         <v>1752</v>
-      </c>
-      <c r="E724" t="s">
-        <v>1748</v>
       </c>
       <c r="F724" t="s">
         <v>1749</v>
@@ -23678,10 +23678,10 @@
         <v>9</v>
       </c>
       <c r="D727" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E727" t="s">
         <v>1752</v>
-      </c>
-      <c r="E727" t="s">
-        <v>1748</v>
       </c>
       <c r="F727" t="s">
         <v>1749</v>
@@ -23701,10 +23701,10 @@
         <v>9</v>
       </c>
       <c r="D728" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E728" t="s">
         <v>1752</v>
-      </c>
-      <c r="E728" t="s">
-        <v>1748</v>
       </c>
       <c r="F728" t="s">
         <v>1749</v>
@@ -23747,10 +23747,10 @@
         <v>9</v>
       </c>
       <c r="D730" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E730" t="s">
         <v>1752</v>
-      </c>
-      <c r="E730" t="s">
-        <v>1748</v>
       </c>
       <c r="F730" t="s">
         <v>1749</v>
@@ -23816,10 +23816,10 @@
         <v>9</v>
       </c>
       <c r="D733" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E733" t="s">
         <v>1789</v>
-      </c>
-      <c r="E733" t="s">
-        <v>1748</v>
       </c>
       <c r="F733" t="s">
         <v>1749</v>
@@ -23862,10 +23862,10 @@
         <v>9</v>
       </c>
       <c r="D735" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E735" t="s">
         <v>1752</v>
-      </c>
-      <c r="E735" t="s">
-        <v>1748</v>
       </c>
       <c r="F735" t="s">
         <v>1749</v>
@@ -23885,10 +23885,10 @@
         <v>9</v>
       </c>
       <c r="D736" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E736" t="s">
         <v>1798</v>
-      </c>
-      <c r="E736" t="s">
-        <v>1748</v>
       </c>
       <c r="F736" t="s">
         <v>1749</v>
@@ -23908,10 +23908,10 @@
         <v>9</v>
       </c>
       <c r="D737" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E737" t="s">
         <v>1752</v>
-      </c>
-      <c r="E737" t="s">
-        <v>1748</v>
       </c>
       <c r="F737" t="s">
         <v>1749</v>
@@ -23931,10 +23931,10 @@
         <v>9</v>
       </c>
       <c r="D738" t="s">
+        <v>1654</v>
+      </c>
+      <c r="E738" t="s">
         <v>1803</v>
-      </c>
-      <c r="E738" t="s">
-        <v>1655</v>
       </c>
       <c r="F738" t="s">
         <v>1749</v>
@@ -23954,10 +23954,10 @@
         <v>9</v>
       </c>
       <c r="D739" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E739" t="s">
         <v>1752</v>
-      </c>
-      <c r="E739" t="s">
-        <v>1748</v>
       </c>
       <c r="F739" t="s">
         <v>1749</v>
@@ -23977,10 +23977,10 @@
         <v>9</v>
       </c>
       <c r="D740" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E740" t="s">
         <v>1752</v>
-      </c>
-      <c r="E740" t="s">
-        <v>1748</v>
       </c>
       <c r="F740" t="s">
         <v>1749</v>
@@ -24023,10 +24023,10 @@
         <v>9</v>
       </c>
       <c r="D742" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E742" t="s">
         <v>1814</v>
-      </c>
-      <c r="E742" t="s">
-        <v>1748</v>
       </c>
       <c r="F742" t="s">
         <v>1749</v>
@@ -24046,10 +24046,10 @@
         <v>9</v>
       </c>
       <c r="D743" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E743" t="s">
         <v>1752</v>
-      </c>
-      <c r="E743" t="s">
-        <v>1748</v>
       </c>
       <c r="F743" t="s">
         <v>1749</v>
@@ -24092,10 +24092,10 @@
         <v>9</v>
       </c>
       <c r="D745" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E745" t="s">
         <v>1821</v>
-      </c>
-      <c r="E745" t="s">
-        <v>1748</v>
       </c>
       <c r="F745" t="s">
         <v>1749</v>
@@ -24115,10 +24115,10 @@
         <v>9</v>
       </c>
       <c r="D746" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E746" t="s">
         <v>1752</v>
-      </c>
-      <c r="E746" t="s">
-        <v>1748</v>
       </c>
       <c r="F746" t="s">
         <v>1749</v>
@@ -24138,10 +24138,10 @@
         <v>9</v>
       </c>
       <c r="D747" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E747" t="s">
         <v>1752</v>
-      </c>
-      <c r="E747" t="s">
-        <v>1748</v>
       </c>
       <c r="F747" t="s">
         <v>1749</v>
@@ -24161,10 +24161,10 @@
         <v>9</v>
       </c>
       <c r="D748" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E748" t="s">
         <v>1752</v>
-      </c>
-      <c r="E748" t="s">
-        <v>1748</v>
       </c>
       <c r="F748" t="s">
         <v>1749</v>
@@ -24184,10 +24184,10 @@
         <v>9</v>
       </c>
       <c r="D749" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E749" t="s">
         <v>1752</v>
-      </c>
-      <c r="E749" t="s">
-        <v>1748</v>
       </c>
       <c r="F749" t="s">
         <v>1749</v>
@@ -24391,10 +24391,10 @@
         <v>9</v>
       </c>
       <c r="D758" t="s">
-        <v>1832</v>
+        <v>1837</v>
       </c>
       <c r="E758" t="s">
-        <v>1838</v>
+        <v>1833</v>
       </c>
       <c r="F758" t="s">
         <v>1834</v>
@@ -24414,10 +24414,10 @@
         <v>9</v>
       </c>
       <c r="D759" t="s">
+        <v>1841</v>
+      </c>
+      <c r="E759" t="s">
         <v>1798</v>
-      </c>
-      <c r="E759" t="s">
-        <v>1842</v>
       </c>
       <c r="F759" t="s">
         <v>1834</v>
@@ -24483,10 +24483,10 @@
         <v>9</v>
       </c>
       <c r="D762" t="s">
+        <v>1863</v>
+      </c>
+      <c r="E762" t="s">
         <v>1798</v>
-      </c>
-      <c r="E762" t="s">
-        <v>1863</v>
       </c>
       <c r="F762" t="s">
         <v>1834</v>
@@ -24552,10 +24552,10 @@
         <v>9</v>
       </c>
       <c r="D765" t="s">
-        <v>1841</v>
+        <v>1832</v>
       </c>
       <c r="E765" t="s">
-        <v>1833</v>
+        <v>1842</v>
       </c>
       <c r="F765" t="s">
         <v>1834</v>
@@ -24575,10 +24575,10 @@
         <v>9</v>
       </c>
       <c r="D766" t="s">
+        <v>1863</v>
+      </c>
+      <c r="E766" t="s">
         <v>1874</v>
-      </c>
-      <c r="E766" t="s">
-        <v>1863</v>
       </c>
       <c r="F766" t="s">
         <v>1834</v>
@@ -24828,10 +24828,10 @@
         <v>9</v>
       </c>
       <c r="D777" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E777" t="s">
         <v>1906</v>
-      </c>
-      <c r="E777" t="s">
-        <v>1902</v>
       </c>
       <c r="F777" t="s">
         <v>1903</v>
@@ -24897,10 +24897,10 @@
         <v>9</v>
       </c>
       <c r="D780" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E780" t="s">
         <v>1906</v>
-      </c>
-      <c r="E780" t="s">
-        <v>1902</v>
       </c>
       <c r="F780" t="s">
         <v>1903</v>
@@ -24920,10 +24920,10 @@
         <v>9</v>
       </c>
       <c r="D781" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E781" t="s">
         <v>1906</v>
-      </c>
-      <c r="E781" t="s">
-        <v>1902</v>
       </c>
       <c r="F781" t="s">
         <v>1903</v>
@@ -24943,10 +24943,10 @@
         <v>9</v>
       </c>
       <c r="D782" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E782" t="s">
         <v>1921</v>
-      </c>
-      <c r="E782" t="s">
-        <v>1902</v>
       </c>
       <c r="F782" t="s">
         <v>1903</v>
@@ -24966,10 +24966,10 @@
         <v>9</v>
       </c>
       <c r="D783" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E783" t="s">
         <v>1906</v>
-      </c>
-      <c r="E783" t="s">
-        <v>1902</v>
       </c>
       <c r="F783" t="s">
         <v>1903</v>
@@ -24989,10 +24989,10 @@
         <v>9</v>
       </c>
       <c r="D784" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E784" t="s">
         <v>1906</v>
-      </c>
-      <c r="E784" t="s">
-        <v>1902</v>
       </c>
       <c r="F784" t="s">
         <v>1903</v>
@@ -25012,10 +25012,10 @@
         <v>9</v>
       </c>
       <c r="D785" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E785" t="s">
         <v>1906</v>
-      </c>
-      <c r="E785" t="s">
-        <v>1902</v>
       </c>
       <c r="F785" t="s">
         <v>1903</v>
@@ -25035,10 +25035,10 @@
         <v>9</v>
       </c>
       <c r="D786" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E786" t="s">
         <v>1906</v>
-      </c>
-      <c r="E786" t="s">
-        <v>1902</v>
       </c>
       <c r="F786" t="s">
         <v>1903</v>
@@ -25058,10 +25058,10 @@
         <v>9</v>
       </c>
       <c r="D787" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E787" t="s">
         <v>1906</v>
-      </c>
-      <c r="E787" t="s">
-        <v>1902</v>
       </c>
       <c r="F787" t="s">
         <v>1903</v>
@@ -25081,10 +25081,10 @@
         <v>9</v>
       </c>
       <c r="D788" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E788" t="s">
         <v>1906</v>
-      </c>
-      <c r="E788" t="s">
-        <v>1902</v>
       </c>
       <c r="F788" t="s">
         <v>1903</v>
@@ -25104,10 +25104,10 @@
         <v>9</v>
       </c>
       <c r="D789" t="s">
-        <v>1901</v>
+        <v>1936</v>
       </c>
       <c r="E789" t="s">
-        <v>1936</v>
+        <v>1902</v>
       </c>
       <c r="F789" t="s">
         <v>1903</v>
@@ -25127,10 +25127,10 @@
         <v>9</v>
       </c>
       <c r="D790" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E790" t="s">
         <v>1906</v>
-      </c>
-      <c r="E790" t="s">
-        <v>1902</v>
       </c>
       <c r="F790" t="s">
         <v>1903</v>
@@ -25150,10 +25150,10 @@
         <v>9</v>
       </c>
       <c r="D791" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E791" t="s">
         <v>1921</v>
-      </c>
-      <c r="E791" t="s">
-        <v>1941</v>
       </c>
       <c r="F791" t="s">
         <v>1903</v>
@@ -25173,10 +25173,10 @@
         <v>9</v>
       </c>
       <c r="D792" t="s">
+        <v>1936</v>
+      </c>
+      <c r="E792" t="s">
         <v>1944</v>
-      </c>
-      <c r="E792" t="s">
-        <v>1936</v>
       </c>
       <c r="F792" t="s">
         <v>1903</v>
@@ -25196,10 +25196,10 @@
         <v>9</v>
       </c>
       <c r="D793" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E793" t="s">
         <v>1906</v>
-      </c>
-      <c r="E793" t="s">
-        <v>1902</v>
       </c>
       <c r="F793" t="s">
         <v>1903</v>
@@ -25219,10 +25219,10 @@
         <v>9</v>
       </c>
       <c r="D794" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E794" t="s">
         <v>1906</v>
-      </c>
-      <c r="E794" t="s">
-        <v>1949</v>
       </c>
       <c r="F794" t="s">
         <v>1903</v>
@@ -25242,10 +25242,10 @@
         <v>9</v>
       </c>
       <c r="D795" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E795" t="s">
         <v>1952</v>
-      </c>
-      <c r="E795" t="s">
-        <v>1902</v>
       </c>
       <c r="F795" t="s">
         <v>1903</v>
@@ -25265,10 +25265,10 @@
         <v>9</v>
       </c>
       <c r="D796" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E796" t="s">
         <v>1906</v>
-      </c>
-      <c r="E796" t="s">
-        <v>1902</v>
       </c>
       <c r="F796" t="s">
         <v>1903</v>
@@ -25334,10 +25334,10 @@
         <v>9</v>
       </c>
       <c r="D799" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E799" t="s">
         <v>1906</v>
-      </c>
-      <c r="E799" t="s">
-        <v>1902</v>
       </c>
       <c r="F799" t="s">
         <v>1903</v>
@@ -25357,10 +25357,10 @@
         <v>9</v>
       </c>
       <c r="D800" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E800" t="s">
         <v>1906</v>
-      </c>
-      <c r="E800" t="s">
-        <v>1902</v>
       </c>
       <c r="F800" t="s">
         <v>1903</v>
@@ -25380,10 +25380,10 @@
         <v>9</v>
       </c>
       <c r="D801" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E801" t="s">
         <v>1906</v>
-      </c>
-      <c r="E801" t="s">
-        <v>1902</v>
       </c>
       <c r="F801" t="s">
         <v>1903</v>
@@ -25403,10 +25403,10 @@
         <v>9</v>
       </c>
       <c r="D802" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E802" t="s">
         <v>1906</v>
-      </c>
-      <c r="E802" t="s">
-        <v>1902</v>
       </c>
       <c r="F802" t="s">
         <v>1903</v>
@@ -25426,10 +25426,10 @@
         <v>9</v>
       </c>
       <c r="D803" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E803" t="s">
         <v>1906</v>
-      </c>
-      <c r="E803" t="s">
-        <v>1902</v>
       </c>
       <c r="F803" t="s">
         <v>1903</v>
@@ -25449,10 +25449,10 @@
         <v>9</v>
       </c>
       <c r="D804" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E804" t="s">
         <v>1906</v>
-      </c>
-      <c r="E804" t="s">
-        <v>1902</v>
       </c>
       <c r="F804" t="s">
         <v>1903</v>
@@ -25472,10 +25472,10 @@
         <v>9</v>
       </c>
       <c r="D805" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E805" t="s">
         <v>1906</v>
-      </c>
-      <c r="E805" t="s">
-        <v>1902</v>
       </c>
       <c r="F805" t="s">
         <v>1903</v>
@@ -25495,10 +25495,10 @@
         <v>9</v>
       </c>
       <c r="D806" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E806" t="s">
         <v>1906</v>
-      </c>
-      <c r="E806" t="s">
-        <v>1902</v>
       </c>
       <c r="F806" t="s">
         <v>1903</v>
@@ -25518,10 +25518,10 @@
         <v>9</v>
       </c>
       <c r="D807" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E807" t="s">
         <v>1906</v>
-      </c>
-      <c r="E807" t="s">
-        <v>1902</v>
       </c>
       <c r="F807" t="s">
         <v>1903</v>
@@ -25679,10 +25679,10 @@
         <v>9</v>
       </c>
       <c r="D814" t="s">
-        <v>1992</v>
+        <v>1983</v>
       </c>
       <c r="E814" t="s">
-        <v>1984</v>
+        <v>1993</v>
       </c>
       <c r="F814" t="s">
         <v>1985</v>
@@ -25886,10 +25886,10 @@
         <v>9</v>
       </c>
       <c r="D823" t="s">
-        <v>2020</v>
+        <v>1983</v>
       </c>
       <c r="E823" t="s">
-        <v>1984</v>
+        <v>2021</v>
       </c>
       <c r="F823" t="s">
         <v>1985</v>
@@ -26001,10 +26001,10 @@
         <v>9</v>
       </c>
       <c r="D828" t="s">
-        <v>2020</v>
+        <v>1983</v>
       </c>
       <c r="E828" t="s">
-        <v>1984</v>
+        <v>2021</v>
       </c>
       <c r="F828" t="s">
         <v>1985</v>
@@ -26047,10 +26047,10 @@
         <v>9</v>
       </c>
       <c r="D830" t="s">
-        <v>1992</v>
+        <v>1983</v>
       </c>
       <c r="E830" t="s">
-        <v>1984</v>
+        <v>1993</v>
       </c>
       <c r="F830" t="s">
         <v>1985</v>
@@ -26277,10 +26277,10 @@
         <v>9</v>
       </c>
       <c r="D840" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E840" t="s">
         <v>2061</v>
-      </c>
-      <c r="E840" t="s">
-        <v>2057</v>
       </c>
       <c r="F840" t="s">
         <v>2058</v>
@@ -26300,10 +26300,10 @@
         <v>9</v>
       </c>
       <c r="D841" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E841" t="s">
         <v>2061</v>
-      </c>
-      <c r="E841" t="s">
-        <v>2057</v>
       </c>
       <c r="F841" t="s">
         <v>2058</v>
@@ -26323,10 +26323,10 @@
         <v>9</v>
       </c>
       <c r="D842" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E842" t="s">
         <v>2061</v>
-      </c>
-      <c r="E842" t="s">
-        <v>2057</v>
       </c>
       <c r="F842" t="s">
         <v>2058</v>
@@ -26346,10 +26346,10 @@
         <v>9</v>
       </c>
       <c r="D843" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E843" t="s">
         <v>2061</v>
-      </c>
-      <c r="E843" t="s">
-        <v>2057</v>
       </c>
       <c r="F843" t="s">
         <v>2058</v>
@@ -26369,10 +26369,10 @@
         <v>9</v>
       </c>
       <c r="D844" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E844" t="s">
         <v>2061</v>
-      </c>
-      <c r="E844" t="s">
-        <v>2057</v>
       </c>
       <c r="F844" t="s">
         <v>2058</v>
@@ -26392,10 +26392,10 @@
         <v>9</v>
       </c>
       <c r="D845" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E845" t="s">
         <v>2061</v>
-      </c>
-      <c r="E845" t="s">
-        <v>2057</v>
       </c>
       <c r="F845" t="s">
         <v>2058</v>
@@ -26415,10 +26415,10 @@
         <v>9</v>
       </c>
       <c r="D846" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E846" t="s">
         <v>2061</v>
-      </c>
-      <c r="E846" t="s">
-        <v>2057</v>
       </c>
       <c r="F846" t="s">
         <v>2058</v>
@@ -26438,10 +26438,10 @@
         <v>9</v>
       </c>
       <c r="D847" t="s">
+        <v>1992</v>
+      </c>
+      <c r="E847" t="s">
         <v>2076</v>
-      </c>
-      <c r="E847" t="s">
-        <v>1993</v>
       </c>
       <c r="F847" t="s">
         <v>2058</v>
@@ -26461,10 +26461,10 @@
         <v>9</v>
       </c>
       <c r="D848" t="s">
+        <v>1992</v>
+      </c>
+      <c r="E848" t="s">
         <v>2076</v>
-      </c>
-      <c r="E848" t="s">
-        <v>1993</v>
       </c>
       <c r="F848" t="s">
         <v>2058</v>
@@ -26484,10 +26484,10 @@
         <v>9</v>
       </c>
       <c r="D849" t="s">
+        <v>1992</v>
+      </c>
+      <c r="E849" t="s">
         <v>2076</v>
-      </c>
-      <c r="E849" t="s">
-        <v>1993</v>
       </c>
       <c r="F849" t="s">
         <v>2058</v>
@@ -26507,10 +26507,10 @@
         <v>9</v>
       </c>
       <c r="D850" t="s">
+        <v>2083</v>
+      </c>
+      <c r="E850" t="s">
         <v>2076</v>
-      </c>
-      <c r="E850" t="s">
-        <v>2083</v>
       </c>
       <c r="F850" t="s">
         <v>2058</v>
@@ -26530,10 +26530,10 @@
         <v>9</v>
       </c>
       <c r="D851" t="s">
+        <v>1992</v>
+      </c>
+      <c r="E851" t="s">
         <v>2076</v>
-      </c>
-      <c r="E851" t="s">
-        <v>1993</v>
       </c>
       <c r="F851" t="s">
         <v>2058</v>
@@ -26553,10 +26553,10 @@
         <v>9</v>
       </c>
       <c r="D852" t="s">
+        <v>1992</v>
+      </c>
+      <c r="E852" t="s">
         <v>2076</v>
-      </c>
-      <c r="E852" t="s">
-        <v>1993</v>
       </c>
       <c r="F852" t="s">
         <v>2058</v>
@@ -26576,10 +26576,10 @@
         <v>9</v>
       </c>
       <c r="D853" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E853" t="s">
         <v>2061</v>
-      </c>
-      <c r="E853" t="s">
-        <v>2057</v>
       </c>
       <c r="F853" t="s">
         <v>2058</v>
@@ -26599,10 +26599,10 @@
         <v>9</v>
       </c>
       <c r="D854" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E854" t="s">
         <v>2061</v>
-      </c>
-      <c r="E854" t="s">
-        <v>2057</v>
       </c>
       <c r="F854" t="s">
         <v>2058</v>
@@ -26622,10 +26622,10 @@
         <v>9</v>
       </c>
       <c r="D855" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E855" t="s">
         <v>2061</v>
-      </c>
-      <c r="E855" t="s">
-        <v>2057</v>
       </c>
       <c r="F855" t="s">
         <v>2058</v>
@@ -26645,10 +26645,10 @@
         <v>9</v>
       </c>
       <c r="D856" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E856" t="s">
         <v>2061</v>
-      </c>
-      <c r="E856" t="s">
-        <v>2057</v>
       </c>
       <c r="F856" t="s">
         <v>2058</v>
@@ -26668,10 +26668,10 @@
         <v>9</v>
       </c>
       <c r="D857" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E857" t="s">
         <v>2061</v>
-      </c>
-      <c r="E857" t="s">
-        <v>2057</v>
       </c>
       <c r="F857" t="s">
         <v>2058</v>
@@ -26691,10 +26691,10 @@
         <v>9</v>
       </c>
       <c r="D858" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E858" t="s">
         <v>2061</v>
-      </c>
-      <c r="E858" t="s">
-        <v>2057</v>
       </c>
       <c r="F858" t="s">
         <v>2058</v>
@@ -26714,10 +26714,10 @@
         <v>9</v>
       </c>
       <c r="D859" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E859" t="s">
         <v>2061</v>
-      </c>
-      <c r="E859" t="s">
-        <v>2057</v>
       </c>
       <c r="F859" t="s">
         <v>2058</v>
@@ -26737,10 +26737,10 @@
         <v>9</v>
       </c>
       <c r="D860" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E860" t="s">
         <v>2061</v>
-      </c>
-      <c r="E860" t="s">
-        <v>2057</v>
       </c>
       <c r="F860" t="s">
         <v>2058</v>
@@ -26760,10 +26760,10 @@
         <v>9</v>
       </c>
       <c r="D861" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E861" t="s">
         <v>2061</v>
-      </c>
-      <c r="E861" t="s">
-        <v>2057</v>
       </c>
       <c r="F861" t="s">
         <v>2058</v>
@@ -26783,10 +26783,10 @@
         <v>9</v>
       </c>
       <c r="D862" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E862" t="s">
         <v>2061</v>
-      </c>
-      <c r="E862" t="s">
-        <v>2057</v>
       </c>
       <c r="F862" t="s">
         <v>2058</v>
@@ -26806,10 +26806,10 @@
         <v>9</v>
       </c>
       <c r="D863" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E863" t="s">
         <v>2061</v>
-      </c>
-      <c r="E863" t="s">
-        <v>2057</v>
       </c>
       <c r="F863" t="s">
         <v>2058</v>
@@ -26829,10 +26829,10 @@
         <v>9</v>
       </c>
       <c r="D864" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E864" t="s">
         <v>2061</v>
-      </c>
-      <c r="E864" t="s">
-        <v>2057</v>
       </c>
       <c r="F864" t="s">
         <v>2058</v>
@@ -26852,10 +26852,10 @@
         <v>9</v>
       </c>
       <c r="D865" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E865" t="s">
         <v>2061</v>
-      </c>
-      <c r="E865" t="s">
-        <v>2057</v>
       </c>
       <c r="F865" t="s">
         <v>2058</v>
@@ -26875,10 +26875,10 @@
         <v>9</v>
       </c>
       <c r="D866" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E866" t="s">
         <v>2061</v>
-      </c>
-      <c r="E866" t="s">
-        <v>2057</v>
       </c>
       <c r="F866" t="s">
         <v>2058</v>
@@ -26921,10 +26921,10 @@
         <v>9</v>
       </c>
       <c r="D868" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E868" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F868" t="s">
         <v>2120</v>
@@ -26944,10 +26944,10 @@
         <v>9</v>
       </c>
       <c r="D869" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E869" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F869" t="s">
         <v>2120</v>
@@ -26967,10 +26967,10 @@
         <v>9</v>
       </c>
       <c r="D870" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E870" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F870" t="s">
         <v>2120</v>
@@ -26990,10 +26990,10 @@
         <v>9</v>
       </c>
       <c r="D871" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E871" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F871" t="s">
         <v>2120</v>
@@ -27013,10 +27013,10 @@
         <v>9</v>
       </c>
       <c r="D872" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E872" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F872" t="s">
         <v>2120</v>
@@ -27036,10 +27036,10 @@
         <v>9</v>
       </c>
       <c r="D873" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E873" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F873" t="s">
         <v>2120</v>
@@ -27059,10 +27059,10 @@
         <v>9</v>
       </c>
       <c r="D874" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E874" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F874" t="s">
         <v>2120</v>
@@ -27082,10 +27082,10 @@
         <v>9</v>
       </c>
       <c r="D875" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E875" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F875" t="s">
         <v>2120</v>
@@ -27105,10 +27105,10 @@
         <v>9</v>
       </c>
       <c r="D876" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E876" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F876" t="s">
         <v>2120</v>
@@ -27128,10 +27128,10 @@
         <v>9</v>
       </c>
       <c r="D877" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E877" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F877" t="s">
         <v>2120</v>
@@ -27151,10 +27151,10 @@
         <v>9</v>
       </c>
       <c r="D878" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E878" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F878" t="s">
         <v>2120</v>
@@ -27174,10 +27174,10 @@
         <v>9</v>
       </c>
       <c r="D879" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E879" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F879" t="s">
         <v>2120</v>
@@ -27197,10 +27197,10 @@
         <v>9</v>
       </c>
       <c r="D880" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E880" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F880" t="s">
         <v>2120</v>
@@ -27220,10 +27220,10 @@
         <v>9</v>
       </c>
       <c r="D881" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E881" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F881" t="s">
         <v>2120</v>
@@ -27243,10 +27243,10 @@
         <v>9</v>
       </c>
       <c r="D882" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E882" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F882" t="s">
         <v>2120</v>
@@ -27266,10 +27266,10 @@
         <v>9</v>
       </c>
       <c r="D883" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E883" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F883" t="s">
         <v>2120</v>
@@ -27289,10 +27289,10 @@
         <v>9</v>
       </c>
       <c r="D884" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E884" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F884" t="s">
         <v>2120</v>
@@ -27312,10 +27312,10 @@
         <v>9</v>
       </c>
       <c r="D885" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E885" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F885" t="s">
         <v>2120</v>
@@ -27335,10 +27335,10 @@
         <v>9</v>
       </c>
       <c r="D886" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E886" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F886" t="s">
         <v>2120</v>
@@ -27358,10 +27358,10 @@
         <v>9</v>
       </c>
       <c r="D887" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E887" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F887" t="s">
         <v>2120</v>
@@ -27381,10 +27381,10 @@
         <v>9</v>
       </c>
       <c r="D888" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E888" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F888" t="s">
         <v>2120</v>
@@ -27404,10 +27404,10 @@
         <v>9</v>
       </c>
       <c r="D889" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="E889" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="F889" t="s">
         <v>2120</v>
@@ -27542,10 +27542,10 @@
         <v>9</v>
       </c>
       <c r="D895" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E895" t="s">
         <v>2181</v>
-      </c>
-      <c r="E895" t="s">
-        <v>2169</v>
       </c>
       <c r="F895" t="s">
         <v>2170</v>
@@ -27749,10 +27749,10 @@
         <v>9</v>
       </c>
       <c r="D904" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E904" t="s">
         <v>2200</v>
-      </c>
-      <c r="E904" t="s">
-        <v>2169</v>
       </c>
       <c r="F904" t="s">
         <v>2201</v>
@@ -27772,10 +27772,10 @@
         <v>9</v>
       </c>
       <c r="D905" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E905" t="s">
         <v>2204</v>
-      </c>
-      <c r="E905" t="s">
-        <v>2169</v>
       </c>
       <c r="F905" t="s">
         <v>2201</v>
@@ -27795,10 +27795,10 @@
         <v>9</v>
       </c>
       <c r="D906" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E906" t="s">
         <v>2200</v>
-      </c>
-      <c r="E906" t="s">
-        <v>2169</v>
       </c>
       <c r="F906" t="s">
         <v>2201</v>

--- a/api/2/clv3/xlsx/en/HumanitarianPlan.xlsx
+++ b/api/2/clv3/xlsx/en/HumanitarianPlan.xlsx
@@ -28,12 +28,12 @@
     <t>codeforiati:plan-end-date</t>
   </si>
   <si>
+    <t>codeforiati:plan-year</t>
+  </si>
+  <si>
     <t>codeforiati:plan-start-date</t>
   </si>
   <si>
-    <t>codeforiati:plan-year</t>
-  </si>
-  <si>
     <t>codeforiati:plan-type</t>
   </si>
   <si>
@@ -49,12 +49,12 @@
     <t>2025-12-31</t>
   </si>
   <si>
+    <t>2025</t>
+  </si>
+  <si>
     <t>2025-01-01</t>
   </si>
   <si>
-    <t>2025</t>
-  </si>
-  <si>
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
@@ -358,12 +358,12 @@
     <t>2024-12-31</t>
   </si>
   <si>
+    <t>2024</t>
+  </si>
+  <si>
     <t>2024-01-01</t>
   </si>
   <si>
-    <t>2024</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -715,12 +715,12 @@
     <t>2023-12-31</t>
   </si>
   <si>
+    <t>2023</t>
+  </si>
+  <si>
     <t>2023-01-01</t>
   </si>
   <si>
-    <t>2023</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -1033,12 +1033,12 @@
     <t>2022-12-31</t>
   </si>
   <si>
+    <t>2022</t>
+  </si>
+  <si>
     <t>2022-01-01</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -1381,12 +1381,12 @@
     <t>2021-12-31</t>
   </si>
   <si>
+    <t>2021</t>
+  </si>
+  <si>
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -1738,12 +1738,12 @@
     <t>2020-12-31</t>
   </si>
   <si>
+    <t>2020</t>
+  </si>
+  <si>
     <t>2020-01-01</t>
   </si>
   <si>
-    <t>2020</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -2173,12 +2173,12 @@
     <t>2019-12-31</t>
   </si>
   <si>
+    <t>2019</t>
+  </si>
+  <si>
     <t>2019-01-01</t>
   </si>
   <si>
-    <t>2019</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -2410,12 +2410,12 @@
     <t>2018-12-31</t>
   </si>
   <si>
+    <t>2018</t>
+  </si>
+  <si>
     <t>2018-01-01</t>
   </si>
   <si>
-    <t>2018</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -2635,12 +2635,12 @@
     <t>2017-12-31</t>
   </si>
   <si>
+    <t>2017</t>
+  </si>
+  <si>
     <t>2017-01-01</t>
   </si>
   <si>
-    <t>2017</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -2923,12 +2923,12 @@
     <t>2016-12-31</t>
   </si>
   <si>
+    <t>2016</t>
+  </si>
+  <si>
     <t>2016-01-01</t>
   </si>
   <si>
-    <t>2016</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -3199,12 +3199,12 @@
     <t>2015-12-31</t>
   </si>
   <si>
+    <t>2015</t>
+  </si>
+  <si>
     <t>2015-01-01</t>
   </si>
   <si>
-    <t>2015</t>
-  </si>
-  <si>
     <t>Strategic response plan</t>
   </si>
   <si>
@@ -3430,12 +3430,12 @@
     <t>2014-12-31</t>
   </si>
   <si>
+    <t>2014</t>
+  </si>
+  <si>
     <t>2014-01-01</t>
   </si>
   <si>
-    <t>2014</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -3880,12 +3880,12 @@
     <t>2012-12-31</t>
   </si>
   <si>
+    <t>2012</t>
+  </si>
+  <si>
     <t>2012-01-01</t>
   </si>
   <si>
-    <t>2012</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -4063,12 +4063,12 @@
     <t>2011+ Kenya Emergency Humanitarian Response Plan</t>
   </si>
   <si>
+    <t>2011</t>
+  </si>
+  <si>
     <t>2011-01-01</t>
   </si>
   <si>
-    <t>2011</t>
-  </si>
-  <si>
     <t>CAFG11</t>
   </si>
   <si>
@@ -4261,12 +4261,12 @@
     <t>2010-12-31</t>
   </si>
   <si>
+    <t>2010</t>
+  </si>
+  <si>
     <t>2010-01-01</t>
   </si>
   <si>
-    <t>2010</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
@@ -4471,12 +4471,12 @@
     <t>2009-12-31</t>
   </si>
   <si>
+    <t>2009</t>
+  </si>
+  <si>
     <t>2009-01-01</t>
   </si>
   <si>
-    <t>2009</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
@@ -4687,12 +4687,12 @@
     <t>2008-06-30</t>
   </si>
   <si>
+    <t>2008</t>
+  </si>
+  <si>
     <t>2008-02-01</t>
   </si>
   <si>
-    <t>2008</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
@@ -4954,12 +4954,12 @@
     <t>2007-08-21</t>
   </si>
   <si>
+    <t>2007</t>
+  </si>
+  <si>
     <t>2007-02-22</t>
   </si>
   <si>
-    <t>2007</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
@@ -5260,12 +5260,12 @@
     <t>2006-12-31</t>
   </si>
   <si>
+    <t>2006</t>
+  </si>
+  <si>
     <t>2006-07-01</t>
   </si>
   <si>
-    <t>2006</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -5515,12 +5515,12 @@
     <t>2005-06-30</t>
   </si>
   <si>
+    <t>2005</t>
+  </si>
+  <si>
     <t>2005-04-01</t>
   </si>
   <si>
-    <t>2005</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
@@ -5722,12 +5722,12 @@
     <t>2004-12-31</t>
   </si>
   <si>
+    <t>2004</t>
+  </si>
+  <si>
     <t>2004-09-01</t>
   </si>
   <si>
-    <t>2004</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -5968,12 +5968,12 @@
     <t>2003-12-31</t>
   </si>
   <si>
+    <t>2003</t>
+  </si>
+  <si>
     <t>2003-01-01</t>
   </si>
   <si>
-    <t>2003</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -6187,12 +6187,12 @@
     <t>2002-12-31</t>
   </si>
   <si>
+    <t>2002</t>
+  </si>
+  <si>
     <t>2001-10-01</t>
   </si>
   <si>
-    <t>2002</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -6373,12 +6373,12 @@
     <t>2001-09-30</t>
   </si>
   <si>
+    <t>2001</t>
+  </si>
+  <si>
     <t>2001-01-01</t>
   </si>
   <si>
-    <t>2001</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -6523,12 +6523,12 @@
     <t>2000-12-31</t>
   </si>
   <si>
+    <t>2000</t>
+  </si>
+  <si>
     <t>2000-01-01</t>
   </si>
   <si>
-    <t>2000</t>
-  </si>
-  <si>
     <t>CBDI00</t>
   </si>
   <si>
@@ -6616,10 +6616,10 @@
     <t>East Timor 1999</t>
   </si>
   <si>
+    <t>1999</t>
+  </si>
+  <si>
     <t>1999-10-01</t>
-  </si>
-  <si>
-    <t>1999</t>
   </si>
   <si>
     <t>CRUS9900</t>
@@ -7420,10 +7420,10 @@
         <v>10</v>
       </c>
       <c r="E20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" t="s">
         <v>58</v>
-      </c>
-      <c r="F20" t="s">
-        <v>12</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -7742,10 +7742,10 @@
         <v>10</v>
       </c>
       <c r="E34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" t="s">
         <v>88</v>
-      </c>
-      <c r="F34" t="s">
-        <v>12</v>
       </c>
       <c r="G34" t="s">
         <v>34</v>
@@ -8064,10 +8064,10 @@
         <v>113</v>
       </c>
       <c r="E48" t="s">
+        <v>114</v>
+      </c>
+      <c r="F48" t="s">
         <v>120</v>
-      </c>
-      <c r="F48" t="s">
-        <v>115</v>
       </c>
       <c r="G48" t="s">
         <v>20</v>
@@ -8110,10 +8110,10 @@
         <v>113</v>
       </c>
       <c r="E50" t="s">
+        <v>114</v>
+      </c>
+      <c r="F50" t="s">
         <v>125</v>
-      </c>
-      <c r="F50" t="s">
-        <v>115</v>
       </c>
       <c r="G50" t="s">
         <v>20</v>
@@ -8271,10 +8271,10 @@
         <v>113</v>
       </c>
       <c r="E57" t="s">
+        <v>114</v>
+      </c>
+      <c r="F57" t="s">
         <v>140</v>
-      </c>
-      <c r="F57" t="s">
-        <v>115</v>
       </c>
       <c r="G57" t="s">
         <v>34</v>
@@ -8363,10 +8363,10 @@
         <v>113</v>
       </c>
       <c r="E61" t="s">
+        <v>114</v>
+      </c>
+      <c r="F61" t="s">
         <v>149</v>
-      </c>
-      <c r="F61" t="s">
-        <v>115</v>
       </c>
       <c r="G61" t="s">
         <v>20</v>
@@ -8386,10 +8386,10 @@
         <v>113</v>
       </c>
       <c r="E62" t="s">
+        <v>114</v>
+      </c>
+      <c r="F62" t="s">
         <v>149</v>
-      </c>
-      <c r="F62" t="s">
-        <v>115</v>
       </c>
       <c r="G62" t="s">
         <v>34</v>
@@ -8455,10 +8455,10 @@
         <v>113</v>
       </c>
       <c r="E65" t="s">
+        <v>114</v>
+      </c>
+      <c r="F65" t="s">
         <v>160</v>
-      </c>
-      <c r="F65" t="s">
-        <v>115</v>
       </c>
       <c r="G65" t="s">
         <v>34</v>
@@ -8501,10 +8501,10 @@
         <v>157</v>
       </c>
       <c r="E67" t="s">
+        <v>114</v>
+      </c>
+      <c r="F67" t="s">
         <v>165</v>
-      </c>
-      <c r="F67" t="s">
-        <v>115</v>
       </c>
       <c r="G67" t="s">
         <v>20</v>
@@ -8524,10 +8524,10 @@
         <v>113</v>
       </c>
       <c r="E68" t="s">
+        <v>114</v>
+      </c>
+      <c r="F68" t="s">
         <v>168</v>
-      </c>
-      <c r="F68" t="s">
-        <v>115</v>
       </c>
       <c r="G68" t="s">
         <v>34</v>
@@ -8593,10 +8593,10 @@
         <v>113</v>
       </c>
       <c r="E71" t="s">
+        <v>114</v>
+      </c>
+      <c r="F71" t="s">
         <v>175</v>
-      </c>
-      <c r="F71" t="s">
-        <v>115</v>
       </c>
       <c r="G71" t="s">
         <v>20</v>
@@ -8662,10 +8662,10 @@
         <v>113</v>
       </c>
       <c r="E74" t="s">
+        <v>114</v>
+      </c>
+      <c r="F74" t="s">
         <v>182</v>
-      </c>
-      <c r="F74" t="s">
-        <v>115</v>
       </c>
       <c r="G74" t="s">
         <v>20</v>
@@ -8800,10 +8800,10 @@
         <v>113</v>
       </c>
       <c r="E80" t="s">
+        <v>114</v>
+      </c>
+      <c r="F80" t="s">
         <v>140</v>
-      </c>
-      <c r="F80" t="s">
-        <v>115</v>
       </c>
       <c r="G80" t="s">
         <v>34</v>
@@ -9099,10 +9099,10 @@
         <v>113</v>
       </c>
       <c r="E93" t="s">
+        <v>114</v>
+      </c>
+      <c r="F93" t="s">
         <v>222</v>
-      </c>
-      <c r="F93" t="s">
-        <v>115</v>
       </c>
       <c r="G93" t="s">
         <v>20</v>
@@ -9145,10 +9145,10 @@
         <v>113</v>
       </c>
       <c r="E95" t="s">
+        <v>114</v>
+      </c>
+      <c r="F95" t="s">
         <v>227</v>
-      </c>
-      <c r="F95" t="s">
-        <v>115</v>
       </c>
       <c r="G95" t="s">
         <v>34</v>
@@ -9168,10 +9168,10 @@
         <v>113</v>
       </c>
       <c r="E96" t="s">
+        <v>114</v>
+      </c>
+      <c r="F96" t="s">
         <v>227</v>
-      </c>
-      <c r="F96" t="s">
-        <v>115</v>
       </c>
       <c r="G96" t="s">
         <v>34</v>
@@ -9375,10 +9375,10 @@
         <v>232</v>
       </c>
       <c r="E105" t="s">
+        <v>233</v>
+      </c>
+      <c r="F105" t="s">
         <v>251</v>
-      </c>
-      <c r="F105" t="s">
-        <v>234</v>
       </c>
       <c r="G105" t="s">
         <v>34</v>
@@ -9559,10 +9559,10 @@
         <v>232</v>
       </c>
       <c r="E113" t="s">
+        <v>233</v>
+      </c>
+      <c r="F113" t="s">
         <v>268</v>
-      </c>
-      <c r="F113" t="s">
-        <v>234</v>
       </c>
       <c r="G113" t="s">
         <v>34</v>
@@ -9628,10 +9628,10 @@
         <v>275</v>
       </c>
       <c r="E116" t="s">
+        <v>233</v>
+      </c>
+      <c r="F116" t="s">
         <v>276</v>
-      </c>
-      <c r="F116" t="s">
-        <v>234</v>
       </c>
       <c r="G116" t="s">
         <v>20</v>
@@ -9651,10 +9651,10 @@
         <v>279</v>
       </c>
       <c r="E117" t="s">
+        <v>233</v>
+      </c>
+      <c r="F117" t="s">
         <v>280</v>
-      </c>
-      <c r="F117" t="s">
-        <v>234</v>
       </c>
       <c r="G117" t="s">
         <v>20</v>
@@ -9996,10 +9996,10 @@
         <v>310</v>
       </c>
       <c r="E132" t="s">
+        <v>233</v>
+      </c>
+      <c r="F132" t="s">
         <v>311</v>
-      </c>
-      <c r="F132" t="s">
-        <v>234</v>
       </c>
       <c r="G132" t="s">
         <v>16</v>
@@ -10042,10 +10042,10 @@
         <v>275</v>
       </c>
       <c r="E134" t="s">
+        <v>233</v>
+      </c>
+      <c r="F134" t="s">
         <v>316</v>
-      </c>
-      <c r="F134" t="s">
-        <v>234</v>
       </c>
       <c r="G134" t="s">
         <v>34</v>
@@ -10088,10 +10088,10 @@
         <v>275</v>
       </c>
       <c r="E136" t="s">
+        <v>233</v>
+      </c>
+      <c r="F136" t="s">
         <v>321</v>
-      </c>
-      <c r="F136" t="s">
-        <v>234</v>
       </c>
       <c r="G136" t="s">
         <v>34</v>
@@ -10433,10 +10433,10 @@
         <v>355</v>
       </c>
       <c r="E151" t="s">
+        <v>339</v>
+      </c>
+      <c r="F151" t="s">
         <v>356</v>
-      </c>
-      <c r="F151" t="s">
-        <v>340</v>
       </c>
       <c r="G151" t="s">
         <v>20</v>
@@ -10548,10 +10548,10 @@
         <v>367</v>
       </c>
       <c r="E156" t="s">
+        <v>339</v>
+      </c>
+      <c r="F156" t="s">
         <v>368</v>
-      </c>
-      <c r="F156" t="s">
-        <v>340</v>
       </c>
       <c r="G156" t="s">
         <v>34</v>
@@ -10571,10 +10571,10 @@
         <v>338</v>
       </c>
       <c r="E157" t="s">
+        <v>339</v>
+      </c>
+      <c r="F157" t="s">
         <v>368</v>
-      </c>
-      <c r="F157" t="s">
-        <v>340</v>
       </c>
       <c r="G157" t="s">
         <v>34</v>
@@ -10755,10 +10755,10 @@
         <v>388</v>
       </c>
       <c r="E165" t="s">
+        <v>339</v>
+      </c>
+      <c r="F165" t="s">
         <v>389</v>
-      </c>
-      <c r="F165" t="s">
-        <v>340</v>
       </c>
       <c r="G165" t="s">
         <v>34</v>
@@ -10801,10 +10801,10 @@
         <v>394</v>
       </c>
       <c r="E167" t="s">
+        <v>339</v>
+      </c>
+      <c r="F167" t="s">
         <v>395</v>
-      </c>
-      <c r="F167" t="s">
-        <v>340</v>
       </c>
       <c r="G167" t="s">
         <v>34</v>
@@ -10939,10 +10939,10 @@
         <v>338</v>
       </c>
       <c r="E173" t="s">
+        <v>339</v>
+      </c>
+      <c r="F173" t="s">
         <v>408</v>
-      </c>
-      <c r="F173" t="s">
-        <v>340</v>
       </c>
       <c r="G173" t="s">
         <v>20</v>
@@ -10962,10 +10962,10 @@
         <v>410</v>
       </c>
       <c r="E174" t="s">
+        <v>339</v>
+      </c>
+      <c r="F174" t="s">
         <v>408</v>
-      </c>
-      <c r="F174" t="s">
-        <v>340</v>
       </c>
       <c r="G174" t="s">
         <v>20</v>
@@ -10985,10 +10985,10 @@
         <v>413</v>
       </c>
       <c r="E175" t="s">
+        <v>339</v>
+      </c>
+      <c r="F175" t="s">
         <v>414</v>
-      </c>
-      <c r="F175" t="s">
-        <v>340</v>
       </c>
       <c r="G175" t="s">
         <v>20</v>
@@ -11169,10 +11169,10 @@
         <v>338</v>
       </c>
       <c r="E183" t="s">
+        <v>339</v>
+      </c>
+      <c r="F183" t="s">
         <v>431</v>
-      </c>
-      <c r="F183" t="s">
-        <v>340</v>
       </c>
       <c r="G183" t="s">
         <v>20</v>
@@ -11284,10 +11284,10 @@
         <v>338</v>
       </c>
       <c r="E188" t="s">
+        <v>339</v>
+      </c>
+      <c r="F188" t="s">
         <v>442</v>
-      </c>
-      <c r="F188" t="s">
-        <v>340</v>
       </c>
       <c r="G188" t="s">
         <v>34</v>
@@ -11330,10 +11330,10 @@
         <v>447</v>
       </c>
       <c r="E190" t="s">
+        <v>339</v>
+      </c>
+      <c r="F190" t="s">
         <v>442</v>
-      </c>
-      <c r="F190" t="s">
-        <v>340</v>
       </c>
       <c r="G190" t="s">
         <v>16</v>
@@ -11422,10 +11422,10 @@
         <v>454</v>
       </c>
       <c r="E194" t="s">
+        <v>455</v>
+      </c>
+      <c r="F194" t="s">
         <v>459</v>
-      </c>
-      <c r="F194" t="s">
-        <v>456</v>
       </c>
       <c r="G194" t="s">
         <v>25</v>
@@ -11445,10 +11445,10 @@
         <v>454</v>
       </c>
       <c r="E195" t="s">
+        <v>455</v>
+      </c>
+      <c r="F195" t="s">
         <v>459</v>
-      </c>
-      <c r="F195" t="s">
-        <v>456</v>
       </c>
       <c r="G195" t="s">
         <v>16</v>
@@ -11468,10 +11468,10 @@
         <v>454</v>
       </c>
       <c r="E196" t="s">
+        <v>455</v>
+      </c>
+      <c r="F196" t="s">
         <v>459</v>
-      </c>
-      <c r="F196" t="s">
-        <v>456</v>
       </c>
       <c r="G196" t="s">
         <v>25</v>
@@ -11491,10 +11491,10 @@
         <v>454</v>
       </c>
       <c r="E197" t="s">
+        <v>455</v>
+      </c>
+      <c r="F197" t="s">
         <v>459</v>
-      </c>
-      <c r="F197" t="s">
-        <v>456</v>
       </c>
       <c r="G197" t="s">
         <v>25</v>
@@ -11514,10 +11514,10 @@
         <v>454</v>
       </c>
       <c r="E198" t="s">
+        <v>455</v>
+      </c>
+      <c r="F198" t="s">
         <v>459</v>
-      </c>
-      <c r="F198" t="s">
-        <v>456</v>
       </c>
       <c r="G198" t="s">
         <v>16</v>
@@ -11537,10 +11537,10 @@
         <v>454</v>
       </c>
       <c r="E199" t="s">
+        <v>455</v>
+      </c>
+      <c r="F199" t="s">
         <v>459</v>
-      </c>
-      <c r="F199" t="s">
-        <v>456</v>
       </c>
       <c r="G199" t="s">
         <v>25</v>
@@ -11560,10 +11560,10 @@
         <v>454</v>
       </c>
       <c r="E200" t="s">
+        <v>455</v>
+      </c>
+      <c r="F200" t="s">
         <v>459</v>
-      </c>
-      <c r="F200" t="s">
-        <v>456</v>
       </c>
       <c r="G200" t="s">
         <v>25</v>
@@ -11583,10 +11583,10 @@
         <v>454</v>
       </c>
       <c r="E201" t="s">
+        <v>455</v>
+      </c>
+      <c r="F201" t="s">
         <v>459</v>
-      </c>
-      <c r="F201" t="s">
-        <v>456</v>
       </c>
       <c r="G201" t="s">
         <v>25</v>
@@ -11606,10 +11606,10 @@
         <v>454</v>
       </c>
       <c r="E202" t="s">
+        <v>455</v>
+      </c>
+      <c r="F202" t="s">
         <v>459</v>
-      </c>
-      <c r="F202" t="s">
-        <v>456</v>
       </c>
       <c r="G202" t="s">
         <v>25</v>
@@ -11629,10 +11629,10 @@
         <v>454</v>
       </c>
       <c r="E203" t="s">
+        <v>455</v>
+      </c>
+      <c r="F203" t="s">
         <v>459</v>
-      </c>
-      <c r="F203" t="s">
-        <v>456</v>
       </c>
       <c r="G203" t="s">
         <v>25</v>
@@ -11652,10 +11652,10 @@
         <v>454</v>
       </c>
       <c r="E204" t="s">
+        <v>455</v>
+      </c>
+      <c r="F204" t="s">
         <v>459</v>
-      </c>
-      <c r="F204" t="s">
-        <v>456</v>
       </c>
       <c r="G204" t="s">
         <v>16</v>
@@ -11675,10 +11675,10 @@
         <v>454</v>
       </c>
       <c r="E205" t="s">
+        <v>455</v>
+      </c>
+      <c r="F205" t="s">
         <v>482</v>
-      </c>
-      <c r="F205" t="s">
-        <v>456</v>
       </c>
       <c r="G205" t="s">
         <v>25</v>
@@ -11698,10 +11698,10 @@
         <v>338</v>
       </c>
       <c r="E206" t="s">
+        <v>455</v>
+      </c>
+      <c r="F206" t="s">
         <v>482</v>
-      </c>
-      <c r="F206" t="s">
-        <v>456</v>
       </c>
       <c r="G206" t="s">
         <v>25</v>
@@ -11721,10 +11721,10 @@
         <v>487</v>
       </c>
       <c r="E207" t="s">
+        <v>455</v>
+      </c>
+      <c r="F207" t="s">
         <v>488</v>
-      </c>
-      <c r="F207" t="s">
-        <v>456</v>
       </c>
       <c r="G207" t="s">
         <v>34</v>
@@ -11744,10 +11744,10 @@
         <v>454</v>
       </c>
       <c r="E208" t="s">
+        <v>455</v>
+      </c>
+      <c r="F208" t="s">
         <v>459</v>
-      </c>
-      <c r="F208" t="s">
-        <v>456</v>
       </c>
       <c r="G208" t="s">
         <v>25</v>
@@ -11767,10 +11767,10 @@
         <v>454</v>
       </c>
       <c r="E209" t="s">
+        <v>455</v>
+      </c>
+      <c r="F209" t="s">
         <v>482</v>
-      </c>
-      <c r="F209" t="s">
-        <v>456</v>
       </c>
       <c r="G209" t="s">
         <v>25</v>
@@ -11790,10 +11790,10 @@
         <v>338</v>
       </c>
       <c r="E210" t="s">
+        <v>455</v>
+      </c>
+      <c r="F210" t="s">
         <v>482</v>
-      </c>
-      <c r="F210" t="s">
-        <v>456</v>
       </c>
       <c r="G210" t="s">
         <v>25</v>
@@ -11813,10 +11813,10 @@
         <v>497</v>
       </c>
       <c r="E211" t="s">
+        <v>455</v>
+      </c>
+      <c r="F211" t="s">
         <v>498</v>
-      </c>
-      <c r="F211" t="s">
-        <v>456</v>
       </c>
       <c r="G211" t="s">
         <v>34</v>
@@ -11836,10 +11836,10 @@
         <v>454</v>
       </c>
       <c r="E212" t="s">
+        <v>455</v>
+      </c>
+      <c r="F212" t="s">
         <v>459</v>
-      </c>
-      <c r="F212" t="s">
-        <v>456</v>
       </c>
       <c r="G212" t="s">
         <v>25</v>
@@ -11859,10 +11859,10 @@
         <v>503</v>
       </c>
       <c r="E213" t="s">
+        <v>455</v>
+      </c>
+      <c r="F213" t="s">
         <v>504</v>
-      </c>
-      <c r="F213" t="s">
-        <v>456</v>
       </c>
       <c r="G213" t="s">
         <v>34</v>
@@ -11882,10 +11882,10 @@
         <v>454</v>
       </c>
       <c r="E214" t="s">
+        <v>455</v>
+      </c>
+      <c r="F214" t="s">
         <v>482</v>
-      </c>
-      <c r="F214" t="s">
-        <v>456</v>
       </c>
       <c r="G214" t="s">
         <v>25</v>
@@ -11905,10 +11905,10 @@
         <v>338</v>
       </c>
       <c r="E215" t="s">
+        <v>455</v>
+      </c>
+      <c r="F215" t="s">
         <v>482</v>
-      </c>
-      <c r="F215" t="s">
-        <v>456</v>
       </c>
       <c r="G215" t="s">
         <v>25</v>
@@ -11928,10 +11928,10 @@
         <v>454</v>
       </c>
       <c r="E216" t="s">
+        <v>455</v>
+      </c>
+      <c r="F216" t="s">
         <v>459</v>
-      </c>
-      <c r="F216" t="s">
-        <v>456</v>
       </c>
       <c r="G216" t="s">
         <v>25</v>
@@ -11951,10 +11951,10 @@
         <v>454</v>
       </c>
       <c r="E217" t="s">
+        <v>455</v>
+      </c>
+      <c r="F217" t="s">
         <v>513</v>
-      </c>
-      <c r="F217" t="s">
-        <v>456</v>
       </c>
       <c r="G217" t="s">
         <v>34</v>
@@ -11974,10 +11974,10 @@
         <v>516</v>
       </c>
       <c r="E218" t="s">
+        <v>455</v>
+      </c>
+      <c r="F218" t="s">
         <v>517</v>
-      </c>
-      <c r="F218" t="s">
-        <v>456</v>
       </c>
       <c r="G218" t="s">
         <v>20</v>
@@ -11997,10 +11997,10 @@
         <v>454</v>
       </c>
       <c r="E219" t="s">
+        <v>455</v>
+      </c>
+      <c r="F219" t="s">
         <v>459</v>
-      </c>
-      <c r="F219" t="s">
-        <v>456</v>
       </c>
       <c r="G219" t="s">
         <v>25</v>
@@ -12020,10 +12020,10 @@
         <v>388</v>
       </c>
       <c r="E220" t="s">
+        <v>455</v>
+      </c>
+      <c r="F220" t="s">
         <v>459</v>
-      </c>
-      <c r="F220" t="s">
-        <v>456</v>
       </c>
       <c r="G220" t="s">
         <v>34</v>
@@ -12043,10 +12043,10 @@
         <v>454</v>
       </c>
       <c r="E221" t="s">
+        <v>455</v>
+      </c>
+      <c r="F221" t="s">
         <v>459</v>
-      </c>
-      <c r="F221" t="s">
-        <v>456</v>
       </c>
       <c r="G221" t="s">
         <v>34</v>
@@ -12066,10 +12066,10 @@
         <v>454</v>
       </c>
       <c r="E222" t="s">
+        <v>455</v>
+      </c>
+      <c r="F222" t="s">
         <v>459</v>
-      </c>
-      <c r="F222" t="s">
-        <v>456</v>
       </c>
       <c r="G222" t="s">
         <v>25</v>
@@ -12089,10 +12089,10 @@
         <v>454</v>
       </c>
       <c r="E223" t="s">
+        <v>455</v>
+      </c>
+      <c r="F223" t="s">
         <v>459</v>
-      </c>
-      <c r="F223" t="s">
-        <v>456</v>
       </c>
       <c r="G223" t="s">
         <v>25</v>
@@ -12112,10 +12112,10 @@
         <v>454</v>
       </c>
       <c r="E224" t="s">
+        <v>455</v>
+      </c>
+      <c r="F224" t="s">
         <v>459</v>
-      </c>
-      <c r="F224" t="s">
-        <v>456</v>
       </c>
       <c r="G224" t="s">
         <v>25</v>
@@ -12135,10 +12135,10 @@
         <v>454</v>
       </c>
       <c r="E225" t="s">
+        <v>455</v>
+      </c>
+      <c r="F225" t="s">
         <v>532</v>
-      </c>
-      <c r="F225" t="s">
-        <v>456</v>
       </c>
       <c r="G225" t="s">
         <v>20</v>
@@ -12158,10 +12158,10 @@
         <v>454</v>
       </c>
       <c r="E226" t="s">
+        <v>455</v>
+      </c>
+      <c r="F226" t="s">
         <v>535</v>
-      </c>
-      <c r="F226" t="s">
-        <v>456</v>
       </c>
       <c r="G226" t="s">
         <v>20</v>
@@ -12181,10 +12181,10 @@
         <v>454</v>
       </c>
       <c r="E227" t="s">
+        <v>455</v>
+      </c>
+      <c r="F227" t="s">
         <v>459</v>
-      </c>
-      <c r="F227" t="s">
-        <v>456</v>
       </c>
       <c r="G227" t="s">
         <v>25</v>
@@ -12204,10 +12204,10 @@
         <v>454</v>
       </c>
       <c r="E228" t="s">
+        <v>455</v>
+      </c>
+      <c r="F228" t="s">
         <v>459</v>
-      </c>
-      <c r="F228" t="s">
-        <v>456</v>
       </c>
       <c r="G228" t="s">
         <v>25</v>
@@ -12227,10 +12227,10 @@
         <v>454</v>
       </c>
       <c r="E229" t="s">
+        <v>455</v>
+      </c>
+      <c r="F229" t="s">
         <v>535</v>
-      </c>
-      <c r="F229" t="s">
-        <v>456</v>
       </c>
       <c r="G229" t="s">
         <v>34</v>
@@ -12250,10 +12250,10 @@
         <v>454</v>
       </c>
       <c r="E230" t="s">
+        <v>455</v>
+      </c>
+      <c r="F230" t="s">
         <v>535</v>
-      </c>
-      <c r="F230" t="s">
-        <v>456</v>
       </c>
       <c r="G230" t="s">
         <v>20</v>
@@ -12273,10 +12273,10 @@
         <v>454</v>
       </c>
       <c r="E231" t="s">
+        <v>455</v>
+      </c>
+      <c r="F231" t="s">
         <v>459</v>
-      </c>
-      <c r="F231" t="s">
-        <v>456</v>
       </c>
       <c r="G231" t="s">
         <v>25</v>
@@ -12296,10 +12296,10 @@
         <v>454</v>
       </c>
       <c r="E232" t="s">
+        <v>455</v>
+      </c>
+      <c r="F232" t="s">
         <v>459</v>
-      </c>
-      <c r="F232" t="s">
-        <v>456</v>
       </c>
       <c r="G232" t="s">
         <v>25</v>
@@ -12319,10 +12319,10 @@
         <v>454</v>
       </c>
       <c r="E233" t="s">
+        <v>455</v>
+      </c>
+      <c r="F233" t="s">
         <v>459</v>
-      </c>
-      <c r="F233" t="s">
-        <v>456</v>
       </c>
       <c r="G233" t="s">
         <v>16</v>
@@ -12342,10 +12342,10 @@
         <v>454</v>
       </c>
       <c r="E234" t="s">
+        <v>455</v>
+      </c>
+      <c r="F234" t="s">
         <v>459</v>
-      </c>
-      <c r="F234" t="s">
-        <v>456</v>
       </c>
       <c r="G234" t="s">
         <v>16</v>
@@ -12365,10 +12365,10 @@
         <v>454</v>
       </c>
       <c r="E235" t="s">
+        <v>455</v>
+      </c>
+      <c r="F235" t="s">
         <v>459</v>
-      </c>
-      <c r="F235" t="s">
-        <v>456</v>
       </c>
       <c r="G235" t="s">
         <v>25</v>
@@ -12388,10 +12388,10 @@
         <v>454</v>
       </c>
       <c r="E236" t="s">
+        <v>455</v>
+      </c>
+      <c r="F236" t="s">
         <v>459</v>
-      </c>
-      <c r="F236" t="s">
-        <v>456</v>
       </c>
       <c r="G236" t="s">
         <v>25</v>
@@ -12411,10 +12411,10 @@
         <v>454</v>
       </c>
       <c r="E237" t="s">
+        <v>455</v>
+      </c>
+      <c r="F237" t="s">
         <v>459</v>
-      </c>
-      <c r="F237" t="s">
-        <v>456</v>
       </c>
       <c r="G237" t="s">
         <v>16</v>
@@ -12434,10 +12434,10 @@
         <v>454</v>
       </c>
       <c r="E238" t="s">
+        <v>455</v>
+      </c>
+      <c r="F238" t="s">
         <v>459</v>
-      </c>
-      <c r="F238" t="s">
-        <v>456</v>
       </c>
       <c r="G238" t="s">
         <v>25</v>
@@ -12457,10 +12457,10 @@
         <v>454</v>
       </c>
       <c r="E239" t="s">
+        <v>455</v>
+      </c>
+      <c r="F239" t="s">
         <v>459</v>
-      </c>
-      <c r="F239" t="s">
-        <v>456</v>
       </c>
       <c r="G239" t="s">
         <v>25</v>
@@ -12480,10 +12480,10 @@
         <v>454</v>
       </c>
       <c r="E240" t="s">
+        <v>455</v>
+      </c>
+      <c r="F240" t="s">
         <v>459</v>
-      </c>
-      <c r="F240" t="s">
-        <v>456</v>
       </c>
       <c r="G240" t="s">
         <v>16</v>
@@ -12503,10 +12503,10 @@
         <v>454</v>
       </c>
       <c r="E241" t="s">
+        <v>455</v>
+      </c>
+      <c r="F241" t="s">
         <v>459</v>
-      </c>
-      <c r="F241" t="s">
-        <v>456</v>
       </c>
       <c r="G241" t="s">
         <v>25</v>
@@ -12526,10 +12526,10 @@
         <v>454</v>
       </c>
       <c r="E242" t="s">
+        <v>455</v>
+      </c>
+      <c r="F242" t="s">
         <v>459</v>
-      </c>
-      <c r="F242" t="s">
-        <v>456</v>
       </c>
       <c r="G242" t="s">
         <v>25</v>
@@ -12549,10 +12549,10 @@
         <v>454</v>
       </c>
       <c r="E243" t="s">
+        <v>455</v>
+      </c>
+      <c r="F243" t="s">
         <v>459</v>
-      </c>
-      <c r="F243" t="s">
-        <v>456</v>
       </c>
       <c r="G243" t="s">
         <v>25</v>
@@ -12572,10 +12572,10 @@
         <v>454</v>
       </c>
       <c r="E244" t="s">
+        <v>455</v>
+      </c>
+      <c r="F244" t="s">
         <v>459</v>
-      </c>
-      <c r="F244" t="s">
-        <v>456</v>
       </c>
       <c r="G244" t="s">
         <v>25</v>
@@ -12618,10 +12618,10 @@
         <v>573</v>
       </c>
       <c r="E246" t="s">
+        <v>574</v>
+      </c>
+      <c r="F246" t="s">
         <v>578</v>
-      </c>
-      <c r="F246" t="s">
-        <v>575</v>
       </c>
       <c r="G246" t="s">
         <v>20</v>
@@ -12664,10 +12664,10 @@
         <v>573</v>
       </c>
       <c r="E248" t="s">
+        <v>574</v>
+      </c>
+      <c r="F248" t="s">
         <v>578</v>
-      </c>
-      <c r="F248" t="s">
-        <v>575</v>
       </c>
       <c r="G248" t="s">
         <v>20</v>
@@ -12756,10 +12756,10 @@
         <v>573</v>
       </c>
       <c r="E252" t="s">
+        <v>574</v>
+      </c>
+      <c r="F252" t="s">
         <v>591</v>
-      </c>
-      <c r="F252" t="s">
-        <v>575</v>
       </c>
       <c r="G252" t="s">
         <v>20</v>
@@ -12802,10 +12802,10 @@
         <v>459</v>
       </c>
       <c r="E254" t="s">
+        <v>574</v>
+      </c>
+      <c r="F254" t="s">
         <v>596</v>
-      </c>
-      <c r="F254" t="s">
-        <v>575</v>
       </c>
       <c r="G254" t="s">
         <v>25</v>
@@ -12871,10 +12871,10 @@
         <v>573</v>
       </c>
       <c r="E257" t="s">
+        <v>574</v>
+      </c>
+      <c r="F257" t="s">
         <v>578</v>
-      </c>
-      <c r="F257" t="s">
-        <v>575</v>
       </c>
       <c r="G257" t="s">
         <v>20</v>
@@ -12894,10 +12894,10 @@
         <v>573</v>
       </c>
       <c r="E258" t="s">
+        <v>574</v>
+      </c>
+      <c r="F258" t="s">
         <v>578</v>
-      </c>
-      <c r="F258" t="s">
-        <v>575</v>
       </c>
       <c r="G258" t="s">
         <v>20</v>
@@ -12917,10 +12917,10 @@
         <v>573</v>
       </c>
       <c r="E259" t="s">
+        <v>574</v>
+      </c>
+      <c r="F259" t="s">
         <v>607</v>
-      </c>
-      <c r="F259" t="s">
-        <v>575</v>
       </c>
       <c r="G259" t="s">
         <v>25</v>
@@ -12986,10 +12986,10 @@
         <v>614</v>
       </c>
       <c r="E262" t="s">
+        <v>574</v>
+      </c>
+      <c r="F262" t="s">
         <v>615</v>
-      </c>
-      <c r="F262" t="s">
-        <v>575</v>
       </c>
       <c r="G262" t="s">
         <v>34</v>
@@ -13009,10 +13009,10 @@
         <v>573</v>
       </c>
       <c r="E263" t="s">
+        <v>574</v>
+      </c>
+      <c r="F263" t="s">
         <v>578</v>
-      </c>
-      <c r="F263" t="s">
-        <v>575</v>
       </c>
       <c r="G263" t="s">
         <v>20</v>
@@ -13032,10 +13032,10 @@
         <v>573</v>
       </c>
       <c r="E264" t="s">
+        <v>574</v>
+      </c>
+      <c r="F264" t="s">
         <v>578</v>
-      </c>
-      <c r="F264" t="s">
-        <v>575</v>
       </c>
       <c r="G264" t="s">
         <v>20</v>
@@ -13078,10 +13078,10 @@
         <v>573</v>
       </c>
       <c r="E266" t="s">
+        <v>574</v>
+      </c>
+      <c r="F266" t="s">
         <v>578</v>
-      </c>
-      <c r="F266" t="s">
-        <v>575</v>
       </c>
       <c r="G266" t="s">
         <v>20</v>
@@ -13124,10 +13124,10 @@
         <v>573</v>
       </c>
       <c r="E268" t="s">
+        <v>574</v>
+      </c>
+      <c r="F268" t="s">
         <v>578</v>
-      </c>
-      <c r="F268" t="s">
-        <v>575</v>
       </c>
       <c r="G268" t="s">
         <v>20</v>
@@ -13147,10 +13147,10 @@
         <v>573</v>
       </c>
       <c r="E269" t="s">
+        <v>574</v>
+      </c>
+      <c r="F269" t="s">
         <v>607</v>
-      </c>
-      <c r="F269" t="s">
-        <v>575</v>
       </c>
       <c r="G269" t="s">
         <v>20</v>
@@ -13170,10 +13170,10 @@
         <v>573</v>
       </c>
       <c r="E270" t="s">
+        <v>574</v>
+      </c>
+      <c r="F270" t="s">
         <v>578</v>
-      </c>
-      <c r="F270" t="s">
-        <v>575</v>
       </c>
       <c r="G270" t="s">
         <v>20</v>
@@ -13193,10 +13193,10 @@
         <v>573</v>
       </c>
       <c r="E271" t="s">
+        <v>574</v>
+      </c>
+      <c r="F271" t="s">
         <v>578</v>
-      </c>
-      <c r="F271" t="s">
-        <v>575</v>
       </c>
       <c r="G271" t="s">
         <v>20</v>
@@ -13239,10 +13239,10 @@
         <v>573</v>
       </c>
       <c r="E273" t="s">
+        <v>574</v>
+      </c>
+      <c r="F273" t="s">
         <v>578</v>
-      </c>
-      <c r="F273" t="s">
-        <v>575</v>
       </c>
       <c r="G273" t="s">
         <v>20</v>
@@ -13285,10 +13285,10 @@
         <v>573</v>
       </c>
       <c r="E275" t="s">
+        <v>574</v>
+      </c>
+      <c r="F275" t="s">
         <v>578</v>
-      </c>
-      <c r="F275" t="s">
-        <v>575</v>
       </c>
       <c r="G275" t="s">
         <v>20</v>
@@ -13308,10 +13308,10 @@
         <v>573</v>
       </c>
       <c r="E276" t="s">
+        <v>574</v>
+      </c>
+      <c r="F276" t="s">
         <v>644</v>
-      </c>
-      <c r="F276" t="s">
-        <v>575</v>
       </c>
       <c r="G276" t="s">
         <v>20</v>
@@ -13331,10 +13331,10 @@
         <v>647</v>
       </c>
       <c r="E277" t="s">
+        <v>574</v>
+      </c>
+      <c r="F277" t="s">
         <v>648</v>
-      </c>
-      <c r="F277" t="s">
-        <v>575</v>
       </c>
       <c r="G277" t="s">
         <v>34</v>
@@ -13354,10 +13354,10 @@
         <v>573</v>
       </c>
       <c r="E278" t="s">
+        <v>574</v>
+      </c>
+      <c r="F278" t="s">
         <v>578</v>
-      </c>
-      <c r="F278" t="s">
-        <v>575</v>
       </c>
       <c r="G278" t="s">
         <v>20</v>
@@ -13377,10 +13377,10 @@
         <v>653</v>
       </c>
       <c r="E279" t="s">
+        <v>574</v>
+      </c>
+      <c r="F279" t="s">
         <v>654</v>
-      </c>
-      <c r="F279" t="s">
-        <v>575</v>
       </c>
       <c r="G279" t="s">
         <v>34</v>
@@ -13400,10 +13400,10 @@
         <v>573</v>
       </c>
       <c r="E280" t="s">
+        <v>574</v>
+      </c>
+      <c r="F280" t="s">
         <v>578</v>
-      </c>
-      <c r="F280" t="s">
-        <v>575</v>
       </c>
       <c r="G280" t="s">
         <v>20</v>
@@ -13469,10 +13469,10 @@
         <v>573</v>
       </c>
       <c r="E283" t="s">
+        <v>574</v>
+      </c>
+      <c r="F283" t="s">
         <v>578</v>
-      </c>
-      <c r="F283" t="s">
-        <v>575</v>
       </c>
       <c r="G283" t="s">
         <v>20</v>
@@ -13584,10 +13584,10 @@
         <v>573</v>
       </c>
       <c r="E288" t="s">
+        <v>574</v>
+      </c>
+      <c r="F288" t="s">
         <v>644</v>
-      </c>
-      <c r="F288" t="s">
-        <v>575</v>
       </c>
       <c r="G288" t="s">
         <v>20</v>
@@ -13607,10 +13607,10 @@
         <v>573</v>
       </c>
       <c r="E289" t="s">
+        <v>574</v>
+      </c>
+      <c r="F289" t="s">
         <v>578</v>
-      </c>
-      <c r="F289" t="s">
-        <v>575</v>
       </c>
       <c r="G289" t="s">
         <v>20</v>
@@ -13676,10 +13676,10 @@
         <v>573</v>
       </c>
       <c r="E292" t="s">
+        <v>574</v>
+      </c>
+      <c r="F292" t="s">
         <v>644</v>
-      </c>
-      <c r="F292" t="s">
-        <v>575</v>
       </c>
       <c r="G292" t="s">
         <v>20</v>
@@ -13699,10 +13699,10 @@
         <v>573</v>
       </c>
       <c r="E293" t="s">
+        <v>574</v>
+      </c>
+      <c r="F293" t="s">
         <v>578</v>
-      </c>
-      <c r="F293" t="s">
-        <v>575</v>
       </c>
       <c r="G293" t="s">
         <v>20</v>
@@ -13860,10 +13860,10 @@
         <v>573</v>
       </c>
       <c r="E300" t="s">
+        <v>574</v>
+      </c>
+      <c r="F300" t="s">
         <v>578</v>
-      </c>
-      <c r="F300" t="s">
-        <v>575</v>
       </c>
       <c r="G300" t="s">
         <v>20</v>
@@ -13883,10 +13883,10 @@
         <v>573</v>
       </c>
       <c r="E301" t="s">
+        <v>574</v>
+      </c>
+      <c r="F301" t="s">
         <v>578</v>
-      </c>
-      <c r="F301" t="s">
-        <v>575</v>
       </c>
       <c r="G301" t="s">
         <v>20</v>
@@ -13906,10 +13906,10 @@
         <v>573</v>
       </c>
       <c r="E302" t="s">
+        <v>574</v>
+      </c>
+      <c r="F302" t="s">
         <v>578</v>
-      </c>
-      <c r="F302" t="s">
-        <v>575</v>
       </c>
       <c r="G302" t="s">
         <v>20</v>
@@ -13952,10 +13952,10 @@
         <v>573</v>
       </c>
       <c r="E304" t="s">
+        <v>574</v>
+      </c>
+      <c r="F304" t="s">
         <v>578</v>
-      </c>
-      <c r="F304" t="s">
-        <v>575</v>
       </c>
       <c r="G304" t="s">
         <v>20</v>
@@ -14021,10 +14021,10 @@
         <v>614</v>
       </c>
       <c r="E307" t="s">
+        <v>574</v>
+      </c>
+      <c r="F307" t="s">
         <v>711</v>
-      </c>
-      <c r="F307" t="s">
-        <v>575</v>
       </c>
       <c r="G307" t="s">
         <v>20</v>
@@ -14044,10 +14044,10 @@
         <v>573</v>
       </c>
       <c r="E308" t="s">
+        <v>574</v>
+      </c>
+      <c r="F308" t="s">
         <v>578</v>
-      </c>
-      <c r="F308" t="s">
-        <v>575</v>
       </c>
       <c r="G308" t="s">
         <v>20</v>
@@ -14389,10 +14389,10 @@
         <v>718</v>
       </c>
       <c r="E323" t="s">
+        <v>719</v>
+      </c>
+      <c r="F323" t="s">
         <v>747</v>
-      </c>
-      <c r="F323" t="s">
-        <v>720</v>
       </c>
       <c r="G323" t="s">
         <v>20</v>
@@ -14849,10 +14849,10 @@
         <v>790</v>
       </c>
       <c r="E343" t="s">
+        <v>719</v>
+      </c>
+      <c r="F343" t="s">
         <v>791</v>
-      </c>
-      <c r="F343" t="s">
-        <v>720</v>
       </c>
       <c r="G343" t="s">
         <v>34</v>
@@ -14872,10 +14872,10 @@
         <v>790</v>
       </c>
       <c r="E344" t="s">
+        <v>719</v>
+      </c>
+      <c r="F344" t="s">
         <v>794</v>
-      </c>
-      <c r="F344" t="s">
-        <v>720</v>
       </c>
       <c r="G344" t="s">
         <v>34</v>
@@ -14918,10 +14918,10 @@
         <v>797</v>
       </c>
       <c r="E346" t="s">
+        <v>798</v>
+      </c>
+      <c r="F346" t="s">
         <v>802</v>
-      </c>
-      <c r="F346" t="s">
-        <v>799</v>
       </c>
       <c r="G346" t="s">
         <v>20</v>
@@ -15148,10 +15148,10 @@
         <v>797</v>
       </c>
       <c r="E356" t="s">
+        <v>798</v>
+      </c>
+      <c r="F356" t="s">
         <v>823</v>
-      </c>
-      <c r="F356" t="s">
-        <v>799</v>
       </c>
       <c r="G356" t="s">
         <v>20</v>
@@ -15378,10 +15378,10 @@
         <v>797</v>
       </c>
       <c r="E366" t="s">
+        <v>798</v>
+      </c>
+      <c r="F366" t="s">
         <v>844</v>
-      </c>
-      <c r="F366" t="s">
-        <v>799</v>
       </c>
       <c r="G366" t="s">
         <v>20</v>
@@ -15401,10 +15401,10 @@
         <v>797</v>
       </c>
       <c r="E367" t="s">
+        <v>798</v>
+      </c>
+      <c r="F367" t="s">
         <v>802</v>
-      </c>
-      <c r="F367" t="s">
-        <v>799</v>
       </c>
       <c r="G367" t="s">
         <v>16</v>
@@ -15516,10 +15516,10 @@
         <v>858</v>
       </c>
       <c r="E372" t="s">
+        <v>798</v>
+      </c>
+      <c r="F372" t="s">
         <v>859</v>
-      </c>
-      <c r="F372" t="s">
-        <v>799</v>
       </c>
       <c r="G372" t="s">
         <v>25</v>
@@ -15562,10 +15562,10 @@
         <v>858</v>
       </c>
       <c r="E374" t="s">
+        <v>798</v>
+      </c>
+      <c r="F374" t="s">
         <v>859</v>
-      </c>
-      <c r="F374" t="s">
-        <v>799</v>
       </c>
       <c r="G374" t="s">
         <v>25</v>
@@ -15700,10 +15700,10 @@
         <v>872</v>
       </c>
       <c r="E380" t="s">
+        <v>873</v>
+      </c>
+      <c r="F380" t="s">
         <v>879</v>
-      </c>
-      <c r="F380" t="s">
-        <v>874</v>
       </c>
       <c r="G380" t="s">
         <v>16</v>
@@ -15838,10 +15838,10 @@
         <v>872</v>
       </c>
       <c r="E386" t="s">
+        <v>873</v>
+      </c>
+      <c r="F386" t="s">
         <v>892</v>
-      </c>
-      <c r="F386" t="s">
-        <v>874</v>
       </c>
       <c r="G386" t="s">
         <v>20</v>
@@ -15861,10 +15861,10 @@
         <v>872</v>
       </c>
       <c r="E387" t="s">
+        <v>873</v>
+      </c>
+      <c r="F387" t="s">
         <v>895</v>
-      </c>
-      <c r="F387" t="s">
-        <v>874</v>
       </c>
       <c r="G387" t="s">
         <v>25</v>
@@ -15907,10 +15907,10 @@
         <v>900</v>
       </c>
       <c r="E389" t="s">
+        <v>873</v>
+      </c>
+      <c r="F389" t="s">
         <v>901</v>
-      </c>
-      <c r="F389" t="s">
-        <v>874</v>
       </c>
       <c r="G389" t="s">
         <v>34</v>
@@ -15999,10 +15999,10 @@
         <v>872</v>
       </c>
       <c r="E393" t="s">
+        <v>873</v>
+      </c>
+      <c r="F393" t="s">
         <v>910</v>
-      </c>
-      <c r="F393" t="s">
-        <v>874</v>
       </c>
       <c r="G393" t="s">
         <v>20</v>
@@ -16045,10 +16045,10 @@
         <v>915</v>
       </c>
       <c r="E395" t="s">
+        <v>873</v>
+      </c>
+      <c r="F395" t="s">
         <v>916</v>
-      </c>
-      <c r="F395" t="s">
-        <v>874</v>
       </c>
       <c r="G395" t="s">
         <v>34</v>
@@ -16091,10 +16091,10 @@
         <v>921</v>
       </c>
       <c r="E397" t="s">
+        <v>873</v>
+      </c>
+      <c r="F397" t="s">
         <v>922</v>
-      </c>
-      <c r="F397" t="s">
-        <v>874</v>
       </c>
       <c r="G397" t="s">
         <v>34</v>
@@ -16160,10 +16160,10 @@
         <v>929</v>
       </c>
       <c r="E400" t="s">
+        <v>873</v>
+      </c>
+      <c r="F400" t="s">
         <v>930</v>
-      </c>
-      <c r="F400" t="s">
-        <v>874</v>
       </c>
       <c r="G400" t="s">
         <v>34</v>
@@ -16298,10 +16298,10 @@
         <v>943</v>
       </c>
       <c r="E406" t="s">
+        <v>873</v>
+      </c>
+      <c r="F406" t="s">
         <v>944</v>
-      </c>
-      <c r="F406" t="s">
-        <v>874</v>
       </c>
       <c r="G406" t="s">
         <v>34</v>
@@ -16321,10 +16321,10 @@
         <v>872</v>
       </c>
       <c r="E407" t="s">
+        <v>873</v>
+      </c>
+      <c r="F407" t="s">
         <v>947</v>
-      </c>
-      <c r="F407" t="s">
-        <v>874</v>
       </c>
       <c r="G407" t="s">
         <v>25</v>
@@ -16597,10 +16597,10 @@
         <v>968</v>
       </c>
       <c r="E419" t="s">
+        <v>969</v>
+      </c>
+      <c r="F419" t="s">
         <v>975</v>
-      </c>
-      <c r="F419" t="s">
-        <v>970</v>
       </c>
       <c r="G419" t="s">
         <v>34</v>
@@ -16643,10 +16643,10 @@
         <v>968</v>
       </c>
       <c r="E421" t="s">
+        <v>969</v>
+      </c>
+      <c r="F421" t="s">
         <v>980</v>
-      </c>
-      <c r="F421" t="s">
-        <v>970</v>
       </c>
       <c r="G421" t="s">
         <v>25</v>
@@ -16804,10 +16804,10 @@
         <v>995</v>
       </c>
       <c r="E428" t="s">
+        <v>969</v>
+      </c>
+      <c r="F428" t="s">
         <v>996</v>
-      </c>
-      <c r="F428" t="s">
-        <v>970</v>
       </c>
       <c r="G428" t="s">
         <v>34</v>
@@ -16827,10 +16827,10 @@
         <v>999</v>
       </c>
       <c r="E429" t="s">
+        <v>969</v>
+      </c>
+      <c r="F429" t="s">
         <v>1000</v>
-      </c>
-      <c r="F429" t="s">
-        <v>970</v>
       </c>
       <c r="G429" t="s">
         <v>34</v>
@@ -16919,10 +16919,10 @@
         <v>968</v>
       </c>
       <c r="E433" t="s">
+        <v>969</v>
+      </c>
+      <c r="F433" t="s">
         <v>1009</v>
-      </c>
-      <c r="F433" t="s">
-        <v>970</v>
       </c>
       <c r="G433" t="s">
         <v>34</v>
@@ -16988,10 +16988,10 @@
         <v>968</v>
       </c>
       <c r="E436" t="s">
+        <v>969</v>
+      </c>
+      <c r="F436" t="s">
         <v>1016</v>
-      </c>
-      <c r="F436" t="s">
-        <v>970</v>
       </c>
       <c r="G436" t="s">
         <v>34</v>
@@ -17011,10 +17011,10 @@
         <v>968</v>
       </c>
       <c r="E437" t="s">
+        <v>969</v>
+      </c>
+      <c r="F437" t="s">
         <v>1019</v>
-      </c>
-      <c r="F437" t="s">
-        <v>970</v>
       </c>
       <c r="G437" t="s">
         <v>25</v>
@@ -17080,10 +17080,10 @@
         <v>1026</v>
       </c>
       <c r="E440" t="s">
+        <v>969</v>
+      </c>
+      <c r="F440" t="s">
         <v>1027</v>
-      </c>
-      <c r="F440" t="s">
-        <v>970</v>
       </c>
       <c r="G440" t="s">
         <v>34</v>
@@ -17402,10 +17402,10 @@
         <v>1056</v>
       </c>
       <c r="E454" t="s">
+        <v>969</v>
+      </c>
+      <c r="F454" t="s">
         <v>1057</v>
-      </c>
-      <c r="F454" t="s">
-        <v>970</v>
       </c>
       <c r="G454" t="s">
         <v>25</v>
@@ -17632,10 +17632,10 @@
         <v>1082</v>
       </c>
       <c r="E464" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F464" t="s">
         <v>1083</v>
-      </c>
-      <c r="F464" t="s">
-        <v>1062</v>
       </c>
       <c r="G464" t="s">
         <v>34</v>
@@ -17655,10 +17655,10 @@
         <v>1060</v>
       </c>
       <c r="E465" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F465" t="s">
         <v>1086</v>
-      </c>
-      <c r="F465" t="s">
-        <v>1062</v>
       </c>
       <c r="G465" t="s">
         <v>34</v>
@@ -17678,10 +17678,10 @@
         <v>1082</v>
       </c>
       <c r="E466" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F466" t="s">
         <v>1089</v>
-      </c>
-      <c r="F466" t="s">
-        <v>1062</v>
       </c>
       <c r="G466" t="s">
         <v>34</v>
@@ -17701,10 +17701,10 @@
         <v>1092</v>
       </c>
       <c r="E467" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F467" t="s">
         <v>1093</v>
-      </c>
-      <c r="F467" t="s">
-        <v>1062</v>
       </c>
       <c r="G467" t="s">
         <v>34</v>
@@ -17747,10 +17747,10 @@
         <v>1098</v>
       </c>
       <c r="E469" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F469" t="s">
         <v>1099</v>
-      </c>
-      <c r="F469" t="s">
-        <v>1062</v>
       </c>
       <c r="G469" t="s">
         <v>34</v>
@@ -17839,10 +17839,10 @@
         <v>1082</v>
       </c>
       <c r="E473" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F473" t="s">
         <v>1108</v>
-      </c>
-      <c r="F473" t="s">
-        <v>1062</v>
       </c>
       <c r="G473" t="s">
         <v>34</v>
@@ -18184,10 +18184,10 @@
         <v>1137</v>
       </c>
       <c r="E488" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F488" t="s">
         <v>1142</v>
-      </c>
-      <c r="F488" t="s">
-        <v>1139</v>
       </c>
       <c r="G488" t="s">
         <v>1063</v>
@@ -18322,10 +18322,10 @@
         <v>1156</v>
       </c>
       <c r="E494" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F494" t="s">
         <v>1099</v>
-      </c>
-      <c r="F494" t="s">
-        <v>1139</v>
       </c>
       <c r="G494" t="s">
         <v>16</v>
@@ -18345,10 +18345,10 @@
         <v>1156</v>
       </c>
       <c r="E495" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F495" t="s">
         <v>1099</v>
-      </c>
-      <c r="F495" t="s">
-        <v>1139</v>
       </c>
       <c r="G495" t="s">
         <v>20</v>
@@ -18414,10 +18414,10 @@
         <v>1137</v>
       </c>
       <c r="E498" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F498" t="s">
         <v>1165</v>
-      </c>
-      <c r="F498" t="s">
-        <v>1139</v>
       </c>
       <c r="G498" t="s">
         <v>1063</v>
@@ -18506,10 +18506,10 @@
         <v>1137</v>
       </c>
       <c r="E502" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F502" t="s">
         <v>1174</v>
-      </c>
-      <c r="F502" t="s">
-        <v>1139</v>
       </c>
       <c r="G502" t="s">
         <v>25</v>
@@ -18621,10 +18621,10 @@
         <v>1185</v>
       </c>
       <c r="E507" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F507" t="s">
         <v>1186</v>
-      </c>
-      <c r="F507" t="s">
-        <v>1139</v>
       </c>
       <c r="G507" t="s">
         <v>34</v>
@@ -18644,10 +18644,10 @@
         <v>1189</v>
       </c>
       <c r="E508" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F508" t="s">
         <v>1190</v>
-      </c>
-      <c r="F508" t="s">
-        <v>1139</v>
       </c>
       <c r="G508" t="s">
         <v>1063</v>
@@ -18667,10 +18667,10 @@
         <v>1193</v>
       </c>
       <c r="E509" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F509" t="s">
         <v>1190</v>
-      </c>
-      <c r="F509" t="s">
-        <v>1139</v>
       </c>
       <c r="G509" t="s">
         <v>25</v>
@@ -18690,10 +18690,10 @@
         <v>1196</v>
       </c>
       <c r="E510" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F510" t="s">
         <v>1197</v>
-      </c>
-      <c r="F510" t="s">
-        <v>1139</v>
       </c>
       <c r="G510" t="s">
         <v>34</v>
@@ -18736,10 +18736,10 @@
         <v>1137</v>
       </c>
       <c r="E512" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F512" t="s">
         <v>1202</v>
-      </c>
-      <c r="F512" t="s">
-        <v>1139</v>
       </c>
       <c r="G512" t="s">
         <v>20</v>
@@ -18943,10 +18943,10 @@
         <v>1137</v>
       </c>
       <c r="E521" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F521" t="s">
         <v>1222</v>
-      </c>
-      <c r="F521" t="s">
-        <v>1139</v>
       </c>
       <c r="G521" t="s">
         <v>25</v>
@@ -18966,10 +18966,10 @@
         <v>1137</v>
       </c>
       <c r="E522" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F522" t="s">
         <v>1225</v>
-      </c>
-      <c r="F522" t="s">
-        <v>1139</v>
       </c>
       <c r="G522" t="s">
         <v>16</v>
@@ -18989,10 +18989,10 @@
         <v>1137</v>
       </c>
       <c r="E523" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F523" t="s">
         <v>1228</v>
-      </c>
-      <c r="F523" t="s">
-        <v>1139</v>
       </c>
       <c r="G523" t="s">
         <v>34</v>
@@ -19035,10 +19035,10 @@
         <v>1233</v>
       </c>
       <c r="E525" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F525" t="s">
         <v>1142</v>
-      </c>
-      <c r="F525" t="s">
-        <v>1234</v>
       </c>
       <c r="G525" t="s">
         <v>1235</v>
@@ -19058,10 +19058,10 @@
         <v>1233</v>
       </c>
       <c r="E526" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F526" t="s">
         <v>1142</v>
-      </c>
-      <c r="F526" t="s">
-        <v>1234</v>
       </c>
       <c r="G526" t="s">
         <v>1235</v>
@@ -19081,10 +19081,10 @@
         <v>1233</v>
       </c>
       <c r="E527" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F527" t="s">
         <v>1142</v>
-      </c>
-      <c r="F527" t="s">
-        <v>1234</v>
       </c>
       <c r="G527" t="s">
         <v>1235</v>
@@ -19104,10 +19104,10 @@
         <v>1233</v>
       </c>
       <c r="E528" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F528" t="s">
         <v>1142</v>
-      </c>
-      <c r="F528" t="s">
-        <v>1234</v>
       </c>
       <c r="G528" t="s">
         <v>1235</v>
@@ -19127,10 +19127,10 @@
         <v>1233</v>
       </c>
       <c r="E529" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F529" t="s">
         <v>1244</v>
-      </c>
-      <c r="F529" t="s">
-        <v>1234</v>
       </c>
       <c r="G529" t="s">
         <v>20</v>
@@ -19150,10 +19150,10 @@
         <v>1247</v>
       </c>
       <c r="E530" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F530" t="s">
         <v>1142</v>
-      </c>
-      <c r="F530" t="s">
-        <v>1234</v>
       </c>
       <c r="G530" t="s">
         <v>1235</v>
@@ -19173,10 +19173,10 @@
         <v>1233</v>
       </c>
       <c r="E531" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F531" t="s">
         <v>1142</v>
-      </c>
-      <c r="F531" t="s">
-        <v>1234</v>
       </c>
       <c r="G531" t="s">
         <v>1235</v>
@@ -19196,10 +19196,10 @@
         <v>1233</v>
       </c>
       <c r="E532" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F532" t="s">
         <v>1142</v>
-      </c>
-      <c r="F532" t="s">
-        <v>1234</v>
       </c>
       <c r="G532" t="s">
         <v>1235</v>
@@ -19219,10 +19219,10 @@
         <v>1233</v>
       </c>
       <c r="E533" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F533" t="s">
         <v>1142</v>
-      </c>
-      <c r="F533" t="s">
-        <v>1234</v>
       </c>
       <c r="G533" t="s">
         <v>1235</v>
@@ -19242,10 +19242,10 @@
         <v>1233</v>
       </c>
       <c r="E534" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F534" t="s">
         <v>1142</v>
-      </c>
-      <c r="F534" t="s">
-        <v>1234</v>
       </c>
       <c r="G534" t="s">
         <v>1235</v>
@@ -19265,10 +19265,10 @@
         <v>1233</v>
       </c>
       <c r="E535" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F535" t="s">
         <v>1142</v>
-      </c>
-      <c r="F535" t="s">
-        <v>1234</v>
       </c>
       <c r="G535" t="s">
         <v>1235</v>
@@ -19288,10 +19288,10 @@
         <v>1233</v>
       </c>
       <c r="E536" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F536" t="s">
         <v>1260</v>
-      </c>
-      <c r="F536" t="s">
-        <v>1234</v>
       </c>
       <c r="G536" t="s">
         <v>20</v>
@@ -19311,10 +19311,10 @@
         <v>1233</v>
       </c>
       <c r="E537" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F537" t="s">
         <v>1263</v>
-      </c>
-      <c r="F537" t="s">
-        <v>1234</v>
       </c>
       <c r="G537" t="s">
         <v>20</v>
@@ -19334,10 +19334,10 @@
         <v>1233</v>
       </c>
       <c r="E538" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F538" t="s">
         <v>1142</v>
-      </c>
-      <c r="F538" t="s">
-        <v>1234</v>
       </c>
       <c r="G538" t="s">
         <v>1235</v>
@@ -19357,10 +19357,10 @@
         <v>1233</v>
       </c>
       <c r="E539" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F539" t="s">
         <v>1142</v>
-      </c>
-      <c r="F539" t="s">
-        <v>1234</v>
       </c>
       <c r="G539" t="s">
         <v>1235</v>
@@ -19380,10 +19380,10 @@
         <v>1196</v>
       </c>
       <c r="E540" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F540" t="s">
         <v>1142</v>
-      </c>
-      <c r="F540" t="s">
-        <v>1234</v>
       </c>
       <c r="G540" t="s">
         <v>1235</v>
@@ -19403,10 +19403,10 @@
         <v>1233</v>
       </c>
       <c r="E541" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F541" t="s">
         <v>1142</v>
-      </c>
-      <c r="F541" t="s">
-        <v>1234</v>
       </c>
       <c r="G541" t="s">
         <v>1235</v>
@@ -19426,10 +19426,10 @@
         <v>1233</v>
       </c>
       <c r="E542" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F542" t="s">
         <v>1142</v>
-      </c>
-      <c r="F542" t="s">
-        <v>1234</v>
       </c>
       <c r="G542" t="s">
         <v>1235</v>
@@ -19449,10 +19449,10 @@
         <v>1233</v>
       </c>
       <c r="E543" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F543" t="s">
         <v>1142</v>
-      </c>
-      <c r="F543" t="s">
-        <v>1234</v>
       </c>
       <c r="G543" t="s">
         <v>1235</v>
@@ -19472,10 +19472,10 @@
         <v>1233</v>
       </c>
       <c r="E544" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F544" t="s">
         <v>1142</v>
-      </c>
-      <c r="F544" t="s">
-        <v>1234</v>
       </c>
       <c r="G544" t="s">
         <v>1235</v>
@@ -19495,10 +19495,10 @@
         <v>1280</v>
       </c>
       <c r="E545" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F545" t="s">
         <v>1142</v>
-      </c>
-      <c r="F545" t="s">
-        <v>1234</v>
       </c>
       <c r="G545" t="s">
         <v>16</v>
@@ -19518,10 +19518,10 @@
         <v>1233</v>
       </c>
       <c r="E546" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F546" t="s">
         <v>1142</v>
-      </c>
-      <c r="F546" t="s">
-        <v>1234</v>
       </c>
       <c r="G546" t="s">
         <v>1235</v>
@@ -19541,10 +19541,10 @@
         <v>1233</v>
       </c>
       <c r="E547" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F547" t="s">
         <v>1142</v>
-      </c>
-      <c r="F547" t="s">
-        <v>1234</v>
       </c>
       <c r="G547" t="s">
         <v>20</v>
@@ -19587,10 +19587,10 @@
         <v>1287</v>
       </c>
       <c r="E549" t="s">
+        <v>1288</v>
+      </c>
+      <c r="F549" t="s">
         <v>1292</v>
-      </c>
-      <c r="F549" t="s">
-        <v>1289</v>
       </c>
       <c r="G549" t="s">
         <v>1235</v>
@@ -19610,10 +19610,10 @@
         <v>1287</v>
       </c>
       <c r="E550" t="s">
+        <v>1288</v>
+      </c>
+      <c r="F550" t="s">
         <v>1295</v>
-      </c>
-      <c r="F550" t="s">
-        <v>1289</v>
       </c>
       <c r="G550" t="s">
         <v>1235</v>
@@ -19794,10 +19794,10 @@
         <v>1313</v>
       </c>
       <c r="E558" t="s">
+        <v>1288</v>
+      </c>
+      <c r="F558" t="s">
         <v>1314</v>
-      </c>
-      <c r="F558" t="s">
-        <v>1289</v>
       </c>
       <c r="G558" t="s">
         <v>34</v>
@@ -19840,10 +19840,10 @@
         <v>1287</v>
       </c>
       <c r="E560" t="s">
+        <v>1288</v>
+      </c>
+      <c r="F560" t="s">
         <v>1319</v>
-      </c>
-      <c r="F560" t="s">
-        <v>1289</v>
       </c>
       <c r="G560" t="s">
         <v>1235</v>
@@ -19863,10 +19863,10 @@
         <v>1287</v>
       </c>
       <c r="E561" t="s">
+        <v>1288</v>
+      </c>
+      <c r="F561" t="s">
         <v>1319</v>
-      </c>
-      <c r="F561" t="s">
-        <v>1289</v>
       </c>
       <c r="G561" t="s">
         <v>1235</v>
@@ -20047,10 +20047,10 @@
         <v>1339</v>
       </c>
       <c r="E569" t="s">
+        <v>1288</v>
+      </c>
+      <c r="F569" t="s">
         <v>1340</v>
-      </c>
-      <c r="F569" t="s">
-        <v>1289</v>
       </c>
       <c r="G569" t="s">
         <v>1235</v>
@@ -20254,10 +20254,10 @@
         <v>1353</v>
       </c>
       <c r="E578" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F578" t="s">
         <v>1362</v>
-      </c>
-      <c r="F578" t="s">
-        <v>1350</v>
       </c>
       <c r="G578" t="s">
         <v>1235</v>
@@ -20277,10 +20277,10 @@
         <v>1365</v>
       </c>
       <c r="E579" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F579" t="s">
         <v>1366</v>
-      </c>
-      <c r="F579" t="s">
-        <v>1350</v>
       </c>
       <c r="G579" t="s">
         <v>34</v>
@@ -20300,10 +20300,10 @@
         <v>1353</v>
       </c>
       <c r="E580" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F580" t="s">
         <v>1369</v>
-      </c>
-      <c r="F580" t="s">
-        <v>1350</v>
       </c>
       <c r="G580" t="s">
         <v>1235</v>
@@ -20323,10 +20323,10 @@
         <v>1353</v>
       </c>
       <c r="E581" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F581" t="s">
         <v>1372</v>
-      </c>
-      <c r="F581" t="s">
-        <v>1350</v>
       </c>
       <c r="G581" t="s">
         <v>20</v>
@@ -20369,10 +20369,10 @@
         <v>1377</v>
       </c>
       <c r="E583" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F583" t="s">
         <v>1378</v>
-      </c>
-      <c r="F583" t="s">
-        <v>1350</v>
       </c>
       <c r="G583" t="s">
         <v>34</v>
@@ -20392,10 +20392,10 @@
         <v>1381</v>
       </c>
       <c r="E584" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F584" t="s">
         <v>1382</v>
-      </c>
-      <c r="F584" t="s">
-        <v>1350</v>
       </c>
       <c r="G584" t="s">
         <v>34</v>
@@ -20438,10 +20438,10 @@
         <v>1387</v>
       </c>
       <c r="E586" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F586" t="s">
         <v>1388</v>
-      </c>
-      <c r="F586" t="s">
-        <v>1350</v>
       </c>
       <c r="G586" t="s">
         <v>34</v>
@@ -20461,10 +20461,10 @@
         <v>1353</v>
       </c>
       <c r="E587" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F587" t="s">
         <v>1391</v>
-      </c>
-      <c r="F587" t="s">
-        <v>1350</v>
       </c>
       <c r="G587" t="s">
         <v>16</v>
@@ -20484,10 +20484,10 @@
         <v>1353</v>
       </c>
       <c r="E588" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F588" t="s">
         <v>1394</v>
-      </c>
-      <c r="F588" t="s">
-        <v>1350</v>
       </c>
       <c r="G588" t="s">
         <v>1235</v>
@@ -20714,10 +20714,10 @@
         <v>1419</v>
       </c>
       <c r="E598" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F598" t="s">
         <v>1420</v>
-      </c>
-      <c r="F598" t="s">
-        <v>1416</v>
       </c>
       <c r="G598" t="s">
         <v>20</v>
@@ -20806,10 +20806,10 @@
         <v>1429</v>
       </c>
       <c r="E602" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F602" t="s">
         <v>1430</v>
-      </c>
-      <c r="F602" t="s">
-        <v>1416</v>
       </c>
       <c r="G602" t="s">
         <v>34</v>
@@ -20829,10 +20829,10 @@
         <v>1433</v>
       </c>
       <c r="E603" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F603" t="s">
         <v>1434</v>
-      </c>
-      <c r="F603" t="s">
-        <v>1416</v>
       </c>
       <c r="G603" t="s">
         <v>34</v>
@@ -20852,10 +20852,10 @@
         <v>1437</v>
       </c>
       <c r="E604" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F604" t="s">
         <v>1438</v>
-      </c>
-      <c r="F604" t="s">
-        <v>1416</v>
       </c>
       <c r="G604" t="s">
         <v>1235</v>
@@ -20875,10 +20875,10 @@
         <v>1414</v>
       </c>
       <c r="E605" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F605" t="s">
         <v>1441</v>
-      </c>
-      <c r="F605" t="s">
-        <v>1416</v>
       </c>
       <c r="G605" t="s">
         <v>34</v>
@@ -20944,10 +20944,10 @@
         <v>1448</v>
       </c>
       <c r="E608" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F608" t="s">
         <v>1449</v>
-      </c>
-      <c r="F608" t="s">
-        <v>1416</v>
       </c>
       <c r="G608" t="s">
         <v>34</v>
@@ -20967,10 +20967,10 @@
         <v>1391</v>
       </c>
       <c r="E609" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F609" t="s">
         <v>1452</v>
-      </c>
-      <c r="F609" t="s">
-        <v>1416</v>
       </c>
       <c r="G609" t="s">
         <v>1235</v>
@@ -21013,10 +21013,10 @@
         <v>1457</v>
       </c>
       <c r="E611" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F611" t="s">
         <v>1420</v>
-      </c>
-      <c r="F611" t="s">
-        <v>1416</v>
       </c>
       <c r="G611" t="s">
         <v>34</v>
@@ -21036,10 +21036,10 @@
         <v>1414</v>
       </c>
       <c r="E612" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F612" t="s">
         <v>1460</v>
-      </c>
-      <c r="F612" t="s">
-        <v>1416</v>
       </c>
       <c r="G612" t="s">
         <v>20</v>
@@ -21082,10 +21082,10 @@
         <v>1414</v>
       </c>
       <c r="E614" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F614" t="s">
         <v>1465</v>
-      </c>
-      <c r="F614" t="s">
-        <v>1416</v>
       </c>
       <c r="G614" t="s">
         <v>1235</v>
@@ -21312,10 +21312,10 @@
         <v>1489</v>
       </c>
       <c r="E624" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F624" t="s">
         <v>1490</v>
-      </c>
-      <c r="F624" t="s">
-        <v>1486</v>
       </c>
       <c r="G624" t="s">
         <v>34</v>
@@ -21427,10 +21427,10 @@
         <v>1484</v>
       </c>
       <c r="E629" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F629" t="s">
         <v>1502</v>
-      </c>
-      <c r="F629" t="s">
-        <v>1486</v>
       </c>
       <c r="G629" t="s">
         <v>34</v>
@@ -21496,10 +21496,10 @@
         <v>1509</v>
       </c>
       <c r="E632" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F632" t="s">
         <v>1502</v>
-      </c>
-      <c r="F632" t="s">
-        <v>1486</v>
       </c>
       <c r="G632" t="s">
         <v>34</v>
@@ -21519,10 +21519,10 @@
         <v>1512</v>
       </c>
       <c r="E633" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F633" t="s">
         <v>1513</v>
-      </c>
-      <c r="F633" t="s">
-        <v>1486</v>
       </c>
       <c r="G633" t="s">
         <v>34</v>
@@ -21542,10 +21542,10 @@
         <v>1516</v>
       </c>
       <c r="E634" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F634" t="s">
         <v>1517</v>
-      </c>
-      <c r="F634" t="s">
-        <v>1486</v>
       </c>
       <c r="G634" t="s">
         <v>34</v>
@@ -21588,10 +21588,10 @@
         <v>1484</v>
       </c>
       <c r="E636" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F636" t="s">
         <v>1522</v>
-      </c>
-      <c r="F636" t="s">
-        <v>1486</v>
       </c>
       <c r="G636" t="s">
         <v>1235</v>
@@ -21611,10 +21611,10 @@
         <v>1525</v>
       </c>
       <c r="E637" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F637" t="s">
         <v>1526</v>
-      </c>
-      <c r="F637" t="s">
-        <v>1486</v>
       </c>
       <c r="G637" t="s">
         <v>34</v>
@@ -21703,10 +21703,10 @@
         <v>1535</v>
       </c>
       <c r="E641" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F641" t="s">
         <v>1536</v>
-      </c>
-      <c r="F641" t="s">
-        <v>1486</v>
       </c>
       <c r="G641" t="s">
         <v>20</v>
@@ -21726,10 +21726,10 @@
         <v>1484</v>
       </c>
       <c r="E642" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F642" t="s">
         <v>1539</v>
-      </c>
-      <c r="F642" t="s">
-        <v>1486</v>
       </c>
       <c r="G642" t="s">
         <v>20</v>
@@ -21749,10 +21749,10 @@
         <v>1484</v>
       </c>
       <c r="E643" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F643" t="s">
         <v>1542</v>
-      </c>
-      <c r="F643" t="s">
-        <v>1486</v>
       </c>
       <c r="G643" t="s">
         <v>20</v>
@@ -21818,10 +21818,10 @@
         <v>1484</v>
       </c>
       <c r="E646" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F646" t="s">
         <v>1549</v>
-      </c>
-      <c r="F646" t="s">
-        <v>1486</v>
       </c>
       <c r="G646" t="s">
         <v>34</v>
@@ -21910,10 +21910,10 @@
         <v>1561</v>
       </c>
       <c r="E650" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F650" t="s">
         <v>1562</v>
-      </c>
-      <c r="F650" t="s">
-        <v>1558</v>
       </c>
       <c r="G650" t="s">
         <v>20</v>
@@ -21956,10 +21956,10 @@
         <v>1568</v>
       </c>
       <c r="E652" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F652" t="s">
         <v>1569</v>
-      </c>
-      <c r="F652" t="s">
-        <v>1558</v>
       </c>
       <c r="G652" t="s">
         <v>1235</v>
@@ -21979,10 +21979,10 @@
         <v>1568</v>
       </c>
       <c r="E653" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F653" t="s">
         <v>1569</v>
-      </c>
-      <c r="F653" t="s">
-        <v>1558</v>
       </c>
       <c r="G653" t="s">
         <v>1235</v>
@@ -22002,10 +22002,10 @@
         <v>1484</v>
       </c>
       <c r="E654" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F654" t="s">
         <v>1542</v>
-      </c>
-      <c r="F654" t="s">
-        <v>1558</v>
       </c>
       <c r="G654" t="s">
         <v>20</v>
@@ -22025,10 +22025,10 @@
         <v>1568</v>
       </c>
       <c r="E655" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F655" t="s">
         <v>1569</v>
-      </c>
-      <c r="F655" t="s">
-        <v>1558</v>
       </c>
       <c r="G655" t="s">
         <v>1235</v>
@@ -22048,10 +22048,10 @@
         <v>1568</v>
       </c>
       <c r="E656" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F656" t="s">
         <v>1569</v>
-      </c>
-      <c r="F656" t="s">
-        <v>1558</v>
       </c>
       <c r="G656" t="s">
         <v>1235</v>
@@ -22071,10 +22071,10 @@
         <v>1580</v>
       </c>
       <c r="E657" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F657" t="s">
         <v>1581</v>
-      </c>
-      <c r="F657" t="s">
-        <v>1558</v>
       </c>
       <c r="G657" t="s">
         <v>20</v>
@@ -22094,10 +22094,10 @@
         <v>1584</v>
       </c>
       <c r="E658" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F658" t="s">
         <v>1585</v>
-      </c>
-      <c r="F658" t="s">
-        <v>1558</v>
       </c>
       <c r="G658" t="s">
         <v>34</v>
@@ -22117,10 +22117,10 @@
         <v>1588</v>
       </c>
       <c r="E659" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F659" t="s">
         <v>1522</v>
-      </c>
-      <c r="F659" t="s">
-        <v>1558</v>
       </c>
       <c r="G659" t="s">
         <v>34</v>
@@ -22140,10 +22140,10 @@
         <v>1591</v>
       </c>
       <c r="E660" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F660" t="s">
         <v>1592</v>
-      </c>
-      <c r="F660" t="s">
-        <v>1558</v>
       </c>
       <c r="G660" t="s">
         <v>34</v>
@@ -22163,10 +22163,10 @@
         <v>1568</v>
       </c>
       <c r="E661" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F661" t="s">
         <v>1569</v>
-      </c>
-      <c r="F661" t="s">
-        <v>1558</v>
       </c>
       <c r="G661" t="s">
         <v>1235</v>
@@ -22186,10 +22186,10 @@
         <v>1562</v>
       </c>
       <c r="E662" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F662" t="s">
         <v>1569</v>
-      </c>
-      <c r="F662" t="s">
-        <v>1558</v>
       </c>
       <c r="G662" t="s">
         <v>34</v>
@@ -22209,10 +22209,10 @@
         <v>1599</v>
       </c>
       <c r="E663" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F663" t="s">
         <v>1600</v>
-      </c>
-      <c r="F663" t="s">
-        <v>1558</v>
       </c>
       <c r="G663" t="s">
         <v>34</v>
@@ -22232,10 +22232,10 @@
         <v>1603</v>
       </c>
       <c r="E664" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F664" t="s">
         <v>1542</v>
-      </c>
-      <c r="F664" t="s">
-        <v>1558</v>
       </c>
       <c r="G664" t="s">
         <v>20</v>
@@ -22255,10 +22255,10 @@
         <v>1568</v>
       </c>
       <c r="E665" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F665" t="s">
         <v>1606</v>
-      </c>
-      <c r="F665" t="s">
-        <v>1558</v>
       </c>
       <c r="G665" t="s">
         <v>1235</v>
@@ -22278,10 +22278,10 @@
         <v>1556</v>
       </c>
       <c r="E666" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F666" t="s">
         <v>1606</v>
-      </c>
-      <c r="F666" t="s">
-        <v>1558</v>
       </c>
       <c r="G666" t="s">
         <v>34</v>
@@ -22301,10 +22301,10 @@
         <v>1611</v>
       </c>
       <c r="E667" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F667" t="s">
         <v>1612</v>
-      </c>
-      <c r="F667" t="s">
-        <v>1558</v>
       </c>
       <c r="G667" t="s">
         <v>34</v>
@@ -22324,10 +22324,10 @@
         <v>1568</v>
       </c>
       <c r="E668" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F668" t="s">
         <v>1569</v>
-      </c>
-      <c r="F668" t="s">
-        <v>1558</v>
       </c>
       <c r="G668" t="s">
         <v>20</v>
@@ -22347,10 +22347,10 @@
         <v>1588</v>
       </c>
       <c r="E669" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F669" t="s">
         <v>1542</v>
-      </c>
-      <c r="F669" t="s">
-        <v>1558</v>
       </c>
       <c r="G669" t="s">
         <v>20</v>
@@ -22370,10 +22370,10 @@
         <v>1568</v>
       </c>
       <c r="E670" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F670" t="s">
         <v>1569</v>
-      </c>
-      <c r="F670" t="s">
-        <v>1558</v>
       </c>
       <c r="G670" t="s">
         <v>1235</v>
@@ -22416,10 +22416,10 @@
         <v>1568</v>
       </c>
       <c r="E672" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F672" t="s">
         <v>1569</v>
-      </c>
-      <c r="F672" t="s">
-        <v>1558</v>
       </c>
       <c r="G672" t="s">
         <v>20</v>
@@ -22439,10 +22439,10 @@
         <v>1568</v>
       </c>
       <c r="E673" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F673" t="s">
         <v>1569</v>
-      </c>
-      <c r="F673" t="s">
-        <v>1558</v>
       </c>
       <c r="G673" t="s">
         <v>1235</v>
@@ -22462,10 +22462,10 @@
         <v>1591</v>
       </c>
       <c r="E674" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F674" t="s">
         <v>1542</v>
-      </c>
-      <c r="F674" t="s">
-        <v>1558</v>
       </c>
       <c r="G674" t="s">
         <v>20</v>
@@ -22508,10 +22508,10 @@
         <v>1568</v>
       </c>
       <c r="E676" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F676" t="s">
         <v>1632</v>
-      </c>
-      <c r="F676" t="s">
-        <v>1558</v>
       </c>
       <c r="G676" t="s">
         <v>20</v>
@@ -22531,10 +22531,10 @@
         <v>1568</v>
       </c>
       <c r="E677" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F677" t="s">
         <v>1569</v>
-      </c>
-      <c r="F677" t="s">
-        <v>1558</v>
       </c>
       <c r="G677" t="s">
         <v>1235</v>
@@ -22554,10 +22554,10 @@
         <v>1568</v>
       </c>
       <c r="E678" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F678" t="s">
         <v>1569</v>
-      </c>
-      <c r="F678" t="s">
-        <v>1558</v>
       </c>
       <c r="G678" t="s">
         <v>1235</v>
@@ -22577,10 +22577,10 @@
         <v>1591</v>
       </c>
       <c r="E679" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F679" t="s">
         <v>1592</v>
-      </c>
-      <c r="F679" t="s">
-        <v>1558</v>
       </c>
       <c r="G679" t="s">
         <v>34</v>
@@ -22600,10 +22600,10 @@
         <v>1568</v>
       </c>
       <c r="E680" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F680" t="s">
         <v>1569</v>
-      </c>
-      <c r="F680" t="s">
-        <v>1558</v>
       </c>
       <c r="G680" t="s">
         <v>1235</v>
@@ -22623,10 +22623,10 @@
         <v>1568</v>
       </c>
       <c r="E681" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F681" t="s">
         <v>1569</v>
-      </c>
-      <c r="F681" t="s">
-        <v>1558</v>
       </c>
       <c r="G681" t="s">
         <v>1235</v>
@@ -22669,10 +22669,10 @@
         <v>1650</v>
       </c>
       <c r="E683" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F683" t="s">
         <v>1651</v>
-      </c>
-      <c r="F683" t="s">
-        <v>1647</v>
       </c>
       <c r="G683" t="s">
         <v>34</v>
@@ -22692,10 +22692,10 @@
         <v>1654</v>
       </c>
       <c r="E684" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F684" t="s">
         <v>1655</v>
-      </c>
-      <c r="F684" t="s">
-        <v>1647</v>
       </c>
       <c r="G684" t="s">
         <v>1235</v>
@@ -22715,10 +22715,10 @@
         <v>1654</v>
       </c>
       <c r="E685" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F685" t="s">
         <v>1655</v>
-      </c>
-      <c r="F685" t="s">
-        <v>1647</v>
       </c>
       <c r="G685" t="s">
         <v>1235</v>
@@ -22738,10 +22738,10 @@
         <v>1654</v>
       </c>
       <c r="E686" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F686" t="s">
         <v>1655</v>
-      </c>
-      <c r="F686" t="s">
-        <v>1647</v>
       </c>
       <c r="G686" t="s">
         <v>1235</v>
@@ -22761,10 +22761,10 @@
         <v>1654</v>
       </c>
       <c r="E687" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F687" t="s">
         <v>1655</v>
-      </c>
-      <c r="F687" t="s">
-        <v>1647</v>
       </c>
       <c r="G687" t="s">
         <v>1235</v>
@@ -22784,10 +22784,10 @@
         <v>1654</v>
       </c>
       <c r="E688" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F688" t="s">
         <v>1655</v>
-      </c>
-      <c r="F688" t="s">
-        <v>1647</v>
       </c>
       <c r="G688" t="s">
         <v>1235</v>
@@ -22807,10 +22807,10 @@
         <v>1666</v>
       </c>
       <c r="E689" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F689" t="s">
         <v>1651</v>
-      </c>
-      <c r="F689" t="s">
-        <v>1647</v>
       </c>
       <c r="G689" t="s">
         <v>34</v>
@@ -22830,10 +22830,10 @@
         <v>1669</v>
       </c>
       <c r="E690" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F690" t="s">
         <v>1670</v>
-      </c>
-      <c r="F690" t="s">
-        <v>1647</v>
       </c>
       <c r="G690" t="s">
         <v>34</v>
@@ -22853,10 +22853,10 @@
         <v>1654</v>
       </c>
       <c r="E691" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F691" t="s">
         <v>1655</v>
-      </c>
-      <c r="F691" t="s">
-        <v>1647</v>
       </c>
       <c r="G691" t="s">
         <v>16</v>
@@ -22876,10 +22876,10 @@
         <v>1568</v>
       </c>
       <c r="E692" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F692" t="s">
         <v>1675</v>
-      </c>
-      <c r="F692" t="s">
-        <v>1647</v>
       </c>
       <c r="G692" t="s">
         <v>20</v>
@@ -22899,10 +22899,10 @@
         <v>1678</v>
       </c>
       <c r="E693" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F693" t="s">
         <v>1679</v>
-      </c>
-      <c r="F693" t="s">
-        <v>1647</v>
       </c>
       <c r="G693" t="s">
         <v>34</v>
@@ -22922,10 +22922,10 @@
         <v>1682</v>
       </c>
       <c r="E694" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F694" t="s">
         <v>1683</v>
-      </c>
-      <c r="F694" t="s">
-        <v>1647</v>
       </c>
       <c r="G694" t="s">
         <v>20</v>
@@ -22945,10 +22945,10 @@
         <v>1686</v>
       </c>
       <c r="E695" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F695" t="s">
         <v>1687</v>
-      </c>
-      <c r="F695" t="s">
-        <v>1647</v>
       </c>
       <c r="G695" t="s">
         <v>34</v>
@@ -22968,10 +22968,10 @@
         <v>1654</v>
       </c>
       <c r="E696" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F696" t="s">
         <v>1655</v>
-      </c>
-      <c r="F696" t="s">
-        <v>1647</v>
       </c>
       <c r="G696" t="s">
         <v>1235</v>
@@ -22991,10 +22991,10 @@
         <v>1692</v>
       </c>
       <c r="E697" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F697" t="s">
         <v>1693</v>
-      </c>
-      <c r="F697" t="s">
-        <v>1647</v>
       </c>
       <c r="G697" t="s">
         <v>34</v>
@@ -23014,10 +23014,10 @@
         <v>1696</v>
       </c>
       <c r="E698" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F698" t="s">
         <v>1697</v>
-      </c>
-      <c r="F698" t="s">
-        <v>1647</v>
       </c>
       <c r="G698" t="s">
         <v>34</v>
@@ -23037,10 +23037,10 @@
         <v>1654</v>
       </c>
       <c r="E699" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F699" t="s">
         <v>1655</v>
-      </c>
-      <c r="F699" t="s">
-        <v>1647</v>
       </c>
       <c r="G699" t="s">
         <v>20</v>
@@ -23060,10 +23060,10 @@
         <v>1702</v>
       </c>
       <c r="E700" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F700" t="s">
         <v>1703</v>
-      </c>
-      <c r="F700" t="s">
-        <v>1647</v>
       </c>
       <c r="G700" t="s">
         <v>34</v>
@@ -23083,10 +23083,10 @@
         <v>1654</v>
       </c>
       <c r="E701" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F701" t="s">
         <v>1655</v>
-      </c>
-      <c r="F701" t="s">
-        <v>1647</v>
       </c>
       <c r="G701" t="s">
         <v>20</v>
@@ -23106,10 +23106,10 @@
         <v>1708</v>
       </c>
       <c r="E702" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F702" t="s">
         <v>1709</v>
-      </c>
-      <c r="F702" t="s">
-        <v>1647</v>
       </c>
       <c r="G702" t="s">
         <v>34</v>
@@ -23129,10 +23129,10 @@
         <v>1702</v>
       </c>
       <c r="E703" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F703" t="s">
         <v>1712</v>
-      </c>
-      <c r="F703" t="s">
-        <v>1647</v>
       </c>
       <c r="G703" t="s">
         <v>34</v>
@@ -23152,10 +23152,10 @@
         <v>1654</v>
       </c>
       <c r="E704" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F704" t="s">
         <v>1655</v>
-      </c>
-      <c r="F704" t="s">
-        <v>1647</v>
       </c>
       <c r="G704" t="s">
         <v>1235</v>
@@ -23175,10 +23175,10 @@
         <v>1696</v>
       </c>
       <c r="E705" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F705" t="s">
         <v>1717</v>
-      </c>
-      <c r="F705" t="s">
-        <v>1647</v>
       </c>
       <c r="G705" t="s">
         <v>20</v>
@@ -23198,10 +23198,10 @@
         <v>1654</v>
       </c>
       <c r="E706" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F706" t="s">
         <v>1655</v>
-      </c>
-      <c r="F706" t="s">
-        <v>1647</v>
       </c>
       <c r="G706" t="s">
         <v>1235</v>
@@ -23221,10 +23221,10 @@
         <v>1696</v>
       </c>
       <c r="E707" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F707" t="s">
         <v>1655</v>
-      </c>
-      <c r="F707" t="s">
-        <v>1647</v>
       </c>
       <c r="G707" t="s">
         <v>20</v>
@@ -23244,10 +23244,10 @@
         <v>1650</v>
       </c>
       <c r="E708" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F708" t="s">
         <v>1724</v>
-      </c>
-      <c r="F708" t="s">
-        <v>1647</v>
       </c>
       <c r="G708" t="s">
         <v>34</v>
@@ -23267,10 +23267,10 @@
         <v>1654</v>
       </c>
       <c r="E709" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F709" t="s">
         <v>1655</v>
-      </c>
-      <c r="F709" t="s">
-        <v>1647</v>
       </c>
       <c r="G709" t="s">
         <v>1235</v>
@@ -23290,10 +23290,10 @@
         <v>1729</v>
       </c>
       <c r="E710" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F710" t="s">
         <v>1730</v>
-      </c>
-      <c r="F710" t="s">
-        <v>1647</v>
       </c>
       <c r="G710" t="s">
         <v>34</v>
@@ -23313,10 +23313,10 @@
         <v>1696</v>
       </c>
       <c r="E711" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F711" t="s">
         <v>1655</v>
-      </c>
-      <c r="F711" t="s">
-        <v>1647</v>
       </c>
       <c r="G711" t="s">
         <v>1235</v>
@@ -23336,10 +23336,10 @@
         <v>1654</v>
       </c>
       <c r="E712" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F712" t="s">
         <v>1655</v>
-      </c>
-      <c r="F712" t="s">
-        <v>1647</v>
       </c>
       <c r="G712" t="s">
         <v>1235</v>
@@ -23359,10 +23359,10 @@
         <v>1669</v>
       </c>
       <c r="E713" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F713" t="s">
         <v>1670</v>
-      </c>
-      <c r="F713" t="s">
-        <v>1647</v>
       </c>
       <c r="G713" t="s">
         <v>34</v>
@@ -23382,10 +23382,10 @@
         <v>1654</v>
       </c>
       <c r="E714" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F714" t="s">
         <v>1655</v>
-      </c>
-      <c r="F714" t="s">
-        <v>1647</v>
       </c>
       <c r="G714" t="s">
         <v>1235</v>
@@ -23405,10 +23405,10 @@
         <v>1696</v>
       </c>
       <c r="E715" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F715" t="s">
         <v>1693</v>
-      </c>
-      <c r="F715" t="s">
-        <v>1647</v>
       </c>
       <c r="G715" t="s">
         <v>34</v>
@@ -23428,10 +23428,10 @@
         <v>1654</v>
       </c>
       <c r="E716" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F716" t="s">
         <v>1655</v>
-      </c>
-      <c r="F716" t="s">
-        <v>1647</v>
       </c>
       <c r="G716" t="s">
         <v>1235</v>
@@ -23451,10 +23451,10 @@
         <v>1654</v>
       </c>
       <c r="E717" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F717" t="s">
         <v>1655</v>
-      </c>
-      <c r="F717" t="s">
-        <v>1647</v>
       </c>
       <c r="G717" t="s">
         <v>1235</v>
@@ -23497,10 +23497,10 @@
         <v>1747</v>
       </c>
       <c r="E719" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F719" t="s">
         <v>1752</v>
-      </c>
-      <c r="F719" t="s">
-        <v>1749</v>
       </c>
       <c r="G719" t="s">
         <v>1235</v>
@@ -23520,10 +23520,10 @@
         <v>1747</v>
       </c>
       <c r="E720" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F720" t="s">
         <v>1752</v>
-      </c>
-      <c r="F720" t="s">
-        <v>1749</v>
       </c>
       <c r="G720" t="s">
         <v>1235</v>
@@ -23543,10 +23543,10 @@
         <v>1747</v>
       </c>
       <c r="E721" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F721" t="s">
         <v>1752</v>
-      </c>
-      <c r="F721" t="s">
-        <v>1749</v>
       </c>
       <c r="G721" t="s">
         <v>1235</v>
@@ -23566,10 +23566,10 @@
         <v>1747</v>
       </c>
       <c r="E722" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F722" t="s">
         <v>1752</v>
-      </c>
-      <c r="F722" t="s">
-        <v>1749</v>
       </c>
       <c r="G722" t="s">
         <v>1235</v>
@@ -23589,10 +23589,10 @@
         <v>1747</v>
       </c>
       <c r="E723" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F723" t="s">
         <v>1752</v>
-      </c>
-      <c r="F723" t="s">
-        <v>1749</v>
       </c>
       <c r="G723" t="s">
         <v>1235</v>
@@ -23612,10 +23612,10 @@
         <v>1747</v>
       </c>
       <c r="E724" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F724" t="s">
         <v>1752</v>
-      </c>
-      <c r="F724" t="s">
-        <v>1749</v>
       </c>
       <c r="G724" t="s">
         <v>20</v>
@@ -23635,10 +23635,10 @@
         <v>1765</v>
       </c>
       <c r="E725" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F725" t="s">
         <v>1766</v>
-      </c>
-      <c r="F725" t="s">
-        <v>1749</v>
       </c>
       <c r="G725" t="s">
         <v>20</v>
@@ -23658,10 +23658,10 @@
         <v>1769</v>
       </c>
       <c r="E726" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F726" t="s">
         <v>1770</v>
-      </c>
-      <c r="F726" t="s">
-        <v>1749</v>
       </c>
       <c r="G726" t="s">
         <v>20</v>
@@ -23681,10 +23681,10 @@
         <v>1747</v>
       </c>
       <c r="E727" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F727" t="s">
         <v>1752</v>
-      </c>
-      <c r="F727" t="s">
-        <v>1749</v>
       </c>
       <c r="G727" t="s">
         <v>1235</v>
@@ -23704,10 +23704,10 @@
         <v>1747</v>
       </c>
       <c r="E728" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F728" t="s">
         <v>1752</v>
-      </c>
-      <c r="F728" t="s">
-        <v>1749</v>
       </c>
       <c r="G728" t="s">
         <v>1235</v>
@@ -23727,10 +23727,10 @@
         <v>1777</v>
       </c>
       <c r="E729" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F729" t="s">
         <v>1778</v>
-      </c>
-      <c r="F729" t="s">
-        <v>1749</v>
       </c>
       <c r="G729" t="s">
         <v>34</v>
@@ -23750,10 +23750,10 @@
         <v>1747</v>
       </c>
       <c r="E730" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F730" t="s">
         <v>1752</v>
-      </c>
-      <c r="F730" t="s">
-        <v>1749</v>
       </c>
       <c r="G730" t="s">
         <v>16</v>
@@ -23773,10 +23773,10 @@
         <v>1777</v>
       </c>
       <c r="E731" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F731" t="s">
         <v>1778</v>
-      </c>
-      <c r="F731" t="s">
-        <v>1749</v>
       </c>
       <c r="G731" t="s">
         <v>34</v>
@@ -23796,10 +23796,10 @@
         <v>1785</v>
       </c>
       <c r="E732" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F732" t="s">
         <v>1786</v>
-      </c>
-      <c r="F732" t="s">
-        <v>1749</v>
       </c>
       <c r="G732" t="s">
         <v>34</v>
@@ -23819,10 +23819,10 @@
         <v>1747</v>
       </c>
       <c r="E733" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F733" t="s">
         <v>1789</v>
-      </c>
-      <c r="F733" t="s">
-        <v>1749</v>
       </c>
       <c r="G733" t="s">
         <v>34</v>
@@ -23842,10 +23842,10 @@
         <v>1792</v>
       </c>
       <c r="E734" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F734" t="s">
         <v>1793</v>
-      </c>
-      <c r="F734" t="s">
-        <v>1749</v>
       </c>
       <c r="G734" t="s">
         <v>34</v>
@@ -23865,10 +23865,10 @@
         <v>1747</v>
       </c>
       <c r="E735" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F735" t="s">
         <v>1752</v>
-      </c>
-      <c r="F735" t="s">
-        <v>1749</v>
       </c>
       <c r="G735" t="s">
         <v>1235</v>
@@ -23888,10 +23888,10 @@
         <v>1747</v>
       </c>
       <c r="E736" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F736" t="s">
         <v>1798</v>
-      </c>
-      <c r="F736" t="s">
-        <v>1749</v>
       </c>
       <c r="G736" t="s">
         <v>1235</v>
@@ -23911,10 +23911,10 @@
         <v>1747</v>
       </c>
       <c r="E737" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F737" t="s">
         <v>1752</v>
-      </c>
-      <c r="F737" t="s">
-        <v>1749</v>
       </c>
       <c r="G737" t="s">
         <v>20</v>
@@ -23934,10 +23934,10 @@
         <v>1654</v>
       </c>
       <c r="E738" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F738" t="s">
         <v>1803</v>
-      </c>
-      <c r="F738" t="s">
-        <v>1749</v>
       </c>
       <c r="G738" t="s">
         <v>20</v>
@@ -23957,10 +23957,10 @@
         <v>1747</v>
       </c>
       <c r="E739" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F739" t="s">
         <v>1752</v>
-      </c>
-      <c r="F739" t="s">
-        <v>1749</v>
       </c>
       <c r="G739" t="s">
         <v>1235</v>
@@ -23980,10 +23980,10 @@
         <v>1747</v>
       </c>
       <c r="E740" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F740" t="s">
         <v>1752</v>
-      </c>
-      <c r="F740" t="s">
-        <v>1749</v>
       </c>
       <c r="G740" t="s">
         <v>1235</v>
@@ -24003,10 +24003,10 @@
         <v>1810</v>
       </c>
       <c r="E741" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F741" t="s">
         <v>1811</v>
-      </c>
-      <c r="F741" t="s">
-        <v>1749</v>
       </c>
       <c r="G741" t="s">
         <v>34</v>
@@ -24026,10 +24026,10 @@
         <v>1747</v>
       </c>
       <c r="E742" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F742" t="s">
         <v>1814</v>
-      </c>
-      <c r="F742" t="s">
-        <v>1749</v>
       </c>
       <c r="G742" t="s">
         <v>20</v>
@@ -24049,10 +24049,10 @@
         <v>1747</v>
       </c>
       <c r="E743" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F743" t="s">
         <v>1752</v>
-      </c>
-      <c r="F743" t="s">
-        <v>1749</v>
       </c>
       <c r="G743" t="s">
         <v>1235</v>
@@ -24095,10 +24095,10 @@
         <v>1747</v>
       </c>
       <c r="E745" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F745" t="s">
         <v>1821</v>
-      </c>
-      <c r="F745" t="s">
-        <v>1749</v>
       </c>
       <c r="G745" t="s">
         <v>34</v>
@@ -24118,10 +24118,10 @@
         <v>1747</v>
       </c>
       <c r="E746" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F746" t="s">
         <v>1752</v>
-      </c>
-      <c r="F746" t="s">
-        <v>1749</v>
       </c>
       <c r="G746" t="s">
         <v>1235</v>
@@ -24141,10 +24141,10 @@
         <v>1747</v>
       </c>
       <c r="E747" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F747" t="s">
         <v>1752</v>
-      </c>
-      <c r="F747" t="s">
-        <v>1749</v>
       </c>
       <c r="G747" t="s">
         <v>1235</v>
@@ -24164,10 +24164,10 @@
         <v>1747</v>
       </c>
       <c r="E748" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F748" t="s">
         <v>1752</v>
-      </c>
-      <c r="F748" t="s">
-        <v>1749</v>
       </c>
       <c r="G748" t="s">
         <v>1235</v>
@@ -24187,10 +24187,10 @@
         <v>1747</v>
       </c>
       <c r="E749" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F749" t="s">
         <v>1752</v>
-      </c>
-      <c r="F749" t="s">
-        <v>1749</v>
       </c>
       <c r="G749" t="s">
         <v>1235</v>
@@ -24233,10 +24233,10 @@
         <v>1837</v>
       </c>
       <c r="E751" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F751" t="s">
         <v>1838</v>
-      </c>
-      <c r="F751" t="s">
-        <v>1834</v>
       </c>
       <c r="G751" t="s">
         <v>34</v>
@@ -24256,10 +24256,10 @@
         <v>1841</v>
       </c>
       <c r="E752" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F752" t="s">
         <v>1842</v>
-      </c>
-      <c r="F752" t="s">
-        <v>1834</v>
       </c>
       <c r="G752" t="s">
         <v>1235</v>
@@ -24279,10 +24279,10 @@
         <v>1841</v>
       </c>
       <c r="E753" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F753" t="s">
         <v>1842</v>
-      </c>
-      <c r="F753" t="s">
-        <v>1834</v>
       </c>
       <c r="G753" t="s">
         <v>1235</v>
@@ -24302,10 +24302,10 @@
         <v>1841</v>
       </c>
       <c r="E754" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F754" t="s">
         <v>1842</v>
-      </c>
-      <c r="F754" t="s">
-        <v>1834</v>
       </c>
       <c r="G754" t="s">
         <v>1235</v>
@@ -24325,10 +24325,10 @@
         <v>1841</v>
       </c>
       <c r="E755" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F755" t="s">
         <v>1842</v>
-      </c>
-      <c r="F755" t="s">
-        <v>1834</v>
       </c>
       <c r="G755" t="s">
         <v>1235</v>
@@ -24348,10 +24348,10 @@
         <v>1841</v>
       </c>
       <c r="E756" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F756" t="s">
         <v>1842</v>
-      </c>
-      <c r="F756" t="s">
-        <v>1834</v>
       </c>
       <c r="G756" t="s">
         <v>1235</v>
@@ -24371,10 +24371,10 @@
         <v>1841</v>
       </c>
       <c r="E757" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F757" t="s">
         <v>1842</v>
-      </c>
-      <c r="F757" t="s">
-        <v>1834</v>
       </c>
       <c r="G757" t="s">
         <v>1235</v>
@@ -24417,10 +24417,10 @@
         <v>1841</v>
       </c>
       <c r="E759" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F759" t="s">
         <v>1798</v>
-      </c>
-      <c r="F759" t="s">
-        <v>1834</v>
       </c>
       <c r="G759" t="s">
         <v>20</v>
@@ -24440,10 +24440,10 @@
         <v>1841</v>
       </c>
       <c r="E760" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F760" t="s">
         <v>1842</v>
-      </c>
-      <c r="F760" t="s">
-        <v>1834</v>
       </c>
       <c r="G760" t="s">
         <v>1235</v>
@@ -24463,10 +24463,10 @@
         <v>1841</v>
       </c>
       <c r="E761" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F761" t="s">
         <v>1842</v>
-      </c>
-      <c r="F761" t="s">
-        <v>1834</v>
       </c>
       <c r="G761" t="s">
         <v>1235</v>
@@ -24486,10 +24486,10 @@
         <v>1863</v>
       </c>
       <c r="E762" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F762" t="s">
         <v>1798</v>
-      </c>
-      <c r="F762" t="s">
-        <v>1834</v>
       </c>
       <c r="G762" t="s">
         <v>34</v>
@@ -24509,10 +24509,10 @@
         <v>1841</v>
       </c>
       <c r="E763" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F763" t="s">
         <v>1842</v>
-      </c>
-      <c r="F763" t="s">
-        <v>1834</v>
       </c>
       <c r="G763" t="s">
         <v>1235</v>
@@ -24532,10 +24532,10 @@
         <v>1868</v>
       </c>
       <c r="E764" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F764" t="s">
         <v>1869</v>
-      </c>
-      <c r="F764" t="s">
-        <v>1834</v>
       </c>
       <c r="G764" t="s">
         <v>34</v>
@@ -24555,10 +24555,10 @@
         <v>1832</v>
       </c>
       <c r="E765" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F765" t="s">
         <v>1842</v>
-      </c>
-      <c r="F765" t="s">
-        <v>1834</v>
       </c>
       <c r="G765" t="s">
         <v>34</v>
@@ -24578,10 +24578,10 @@
         <v>1863</v>
       </c>
       <c r="E766" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F766" t="s">
         <v>1874</v>
-      </c>
-      <c r="F766" t="s">
-        <v>1834</v>
       </c>
       <c r="G766" t="s">
         <v>34</v>
@@ -24601,10 +24601,10 @@
         <v>1877</v>
       </c>
       <c r="E767" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F767" t="s">
         <v>1878</v>
-      </c>
-      <c r="F767" t="s">
-        <v>1834</v>
       </c>
       <c r="G767" t="s">
         <v>34</v>
@@ -24624,10 +24624,10 @@
         <v>1841</v>
       </c>
       <c r="E768" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F768" t="s">
         <v>1842</v>
-      </c>
-      <c r="F768" t="s">
-        <v>1834</v>
       </c>
       <c r="G768" t="s">
         <v>1235</v>
@@ -24647,10 +24647,10 @@
         <v>1841</v>
       </c>
       <c r="E769" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F769" t="s">
         <v>1842</v>
-      </c>
-      <c r="F769" t="s">
-        <v>1834</v>
       </c>
       <c r="G769" t="s">
         <v>1235</v>
@@ -24670,10 +24670,10 @@
         <v>1885</v>
       </c>
       <c r="E770" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F770" t="s">
         <v>1886</v>
-      </c>
-      <c r="F770" t="s">
-        <v>1834</v>
       </c>
       <c r="G770" t="s">
         <v>34</v>
@@ -24693,10 +24693,10 @@
         <v>1841</v>
       </c>
       <c r="E771" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F771" t="s">
         <v>1842</v>
-      </c>
-      <c r="F771" t="s">
-        <v>1834</v>
       </c>
       <c r="G771" t="s">
         <v>1235</v>
@@ -24716,10 +24716,10 @@
         <v>1841</v>
       </c>
       <c r="E772" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F772" t="s">
         <v>1842</v>
-      </c>
-      <c r="F772" t="s">
-        <v>1834</v>
       </c>
       <c r="G772" t="s">
         <v>1235</v>
@@ -24739,10 +24739,10 @@
         <v>1841</v>
       </c>
       <c r="E773" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F773" t="s">
         <v>1842</v>
-      </c>
-      <c r="F773" t="s">
-        <v>1834</v>
       </c>
       <c r="G773" t="s">
         <v>1235</v>
@@ -24762,10 +24762,10 @@
         <v>1895</v>
       </c>
       <c r="E774" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F774" t="s">
         <v>1896</v>
-      </c>
-      <c r="F774" t="s">
-        <v>1834</v>
       </c>
       <c r="G774" t="s">
         <v>34</v>
@@ -24785,10 +24785,10 @@
         <v>1841</v>
       </c>
       <c r="E775" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F775" t="s">
         <v>1842</v>
-      </c>
-      <c r="F775" t="s">
-        <v>1834</v>
       </c>
       <c r="G775" t="s">
         <v>1235</v>
@@ -24831,10 +24831,10 @@
         <v>1901</v>
       </c>
       <c r="E777" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F777" t="s">
         <v>1906</v>
-      </c>
-      <c r="F777" t="s">
-        <v>1903</v>
       </c>
       <c r="G777" t="s">
         <v>1235</v>
@@ -24854,10 +24854,10 @@
         <v>1909</v>
       </c>
       <c r="E778" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F778" t="s">
         <v>1910</v>
-      </c>
-      <c r="F778" t="s">
-        <v>1903</v>
       </c>
       <c r="G778" t="s">
         <v>34</v>
@@ -24877,10 +24877,10 @@
         <v>1913</v>
       </c>
       <c r="E779" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F779" t="s">
         <v>1914</v>
-      </c>
-      <c r="F779" t="s">
-        <v>1903</v>
       </c>
       <c r="G779" t="s">
         <v>34</v>
@@ -24900,10 +24900,10 @@
         <v>1901</v>
       </c>
       <c r="E780" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F780" t="s">
         <v>1906</v>
-      </c>
-      <c r="F780" t="s">
-        <v>1903</v>
       </c>
       <c r="G780" t="s">
         <v>1235</v>
@@ -24923,10 +24923,10 @@
         <v>1901</v>
       </c>
       <c r="E781" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F781" t="s">
         <v>1906</v>
-      </c>
-      <c r="F781" t="s">
-        <v>1903</v>
       </c>
       <c r="G781" t="s">
         <v>1235</v>
@@ -24946,10 +24946,10 @@
         <v>1901</v>
       </c>
       <c r="E782" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F782" t="s">
         <v>1921</v>
-      </c>
-      <c r="F782" t="s">
-        <v>1903</v>
       </c>
       <c r="G782" t="s">
         <v>1235</v>
@@ -24969,10 +24969,10 @@
         <v>1901</v>
       </c>
       <c r="E783" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F783" t="s">
         <v>1906</v>
-      </c>
-      <c r="F783" t="s">
-        <v>1903</v>
       </c>
       <c r="G783" t="s">
         <v>1235</v>
@@ -24992,10 +24992,10 @@
         <v>1901</v>
       </c>
       <c r="E784" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F784" t="s">
         <v>1906</v>
-      </c>
-      <c r="F784" t="s">
-        <v>1903</v>
       </c>
       <c r="G784" t="s">
         <v>1235</v>
@@ -25015,10 +25015,10 @@
         <v>1901</v>
       </c>
       <c r="E785" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F785" t="s">
         <v>1906</v>
-      </c>
-      <c r="F785" t="s">
-        <v>1903</v>
       </c>
       <c r="G785" t="s">
         <v>1235</v>
@@ -25038,10 +25038,10 @@
         <v>1901</v>
       </c>
       <c r="E786" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F786" t="s">
         <v>1906</v>
-      </c>
-      <c r="F786" t="s">
-        <v>1903</v>
       </c>
       <c r="G786" t="s">
         <v>1235</v>
@@ -25061,10 +25061,10 @@
         <v>1901</v>
       </c>
       <c r="E787" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F787" t="s">
         <v>1906</v>
-      </c>
-      <c r="F787" t="s">
-        <v>1903</v>
       </c>
       <c r="G787" t="s">
         <v>1235</v>
@@ -25084,10 +25084,10 @@
         <v>1901</v>
       </c>
       <c r="E788" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F788" t="s">
         <v>1906</v>
-      </c>
-      <c r="F788" t="s">
-        <v>1903</v>
       </c>
       <c r="G788" t="s">
         <v>1235</v>
@@ -25130,10 +25130,10 @@
         <v>1901</v>
       </c>
       <c r="E790" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F790" t="s">
         <v>1906</v>
-      </c>
-      <c r="F790" t="s">
-        <v>1903</v>
       </c>
       <c r="G790" t="s">
         <v>1235</v>
@@ -25153,10 +25153,10 @@
         <v>1941</v>
       </c>
       <c r="E791" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F791" t="s">
         <v>1921</v>
-      </c>
-      <c r="F791" t="s">
-        <v>1903</v>
       </c>
       <c r="G791" t="s">
         <v>34</v>
@@ -25176,10 +25176,10 @@
         <v>1936</v>
       </c>
       <c r="E792" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F792" t="s">
         <v>1944</v>
-      </c>
-      <c r="F792" t="s">
-        <v>1903</v>
       </c>
       <c r="G792" t="s">
         <v>34</v>
@@ -25199,10 +25199,10 @@
         <v>1901</v>
       </c>
       <c r="E793" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F793" t="s">
         <v>1906</v>
-      </c>
-      <c r="F793" t="s">
-        <v>1903</v>
       </c>
       <c r="G793" t="s">
         <v>1235</v>
@@ -25222,10 +25222,10 @@
         <v>1949</v>
       </c>
       <c r="E794" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F794" t="s">
         <v>1906</v>
-      </c>
-      <c r="F794" t="s">
-        <v>1903</v>
       </c>
       <c r="G794" t="s">
         <v>34</v>
@@ -25245,10 +25245,10 @@
         <v>1901</v>
       </c>
       <c r="E795" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F795" t="s">
         <v>1952</v>
-      </c>
-      <c r="F795" t="s">
-        <v>1903</v>
       </c>
       <c r="G795" t="s">
         <v>34</v>
@@ -25268,10 +25268,10 @@
         <v>1901</v>
       </c>
       <c r="E796" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F796" t="s">
         <v>1906</v>
-      </c>
-      <c r="F796" t="s">
-        <v>1903</v>
       </c>
       <c r="G796" t="s">
         <v>1235</v>
@@ -25291,10 +25291,10 @@
         <v>1957</v>
       </c>
       <c r="E797" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F797" t="s">
         <v>1958</v>
-      </c>
-      <c r="F797" t="s">
-        <v>1903</v>
       </c>
       <c r="G797" t="s">
         <v>34</v>
@@ -25314,10 +25314,10 @@
         <v>1961</v>
       </c>
       <c r="E798" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F798" t="s">
         <v>1962</v>
-      </c>
-      <c r="F798" t="s">
-        <v>1903</v>
       </c>
       <c r="G798" t="s">
         <v>34</v>
@@ -25337,10 +25337,10 @@
         <v>1901</v>
       </c>
       <c r="E799" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F799" t="s">
         <v>1906</v>
-      </c>
-      <c r="F799" t="s">
-        <v>1903</v>
       </c>
       <c r="G799" t="s">
         <v>1235</v>
@@ -25360,10 +25360,10 @@
         <v>1901</v>
       </c>
       <c r="E800" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F800" t="s">
         <v>1906</v>
-      </c>
-      <c r="F800" t="s">
-        <v>1903</v>
       </c>
       <c r="G800" t="s">
         <v>1235</v>
@@ -25383,10 +25383,10 @@
         <v>1901</v>
       </c>
       <c r="E801" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F801" t="s">
         <v>1906</v>
-      </c>
-      <c r="F801" t="s">
-        <v>1903</v>
       </c>
       <c r="G801" t="s">
         <v>1235</v>
@@ -25406,10 +25406,10 @@
         <v>1901</v>
       </c>
       <c r="E802" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F802" t="s">
         <v>1906</v>
-      </c>
-      <c r="F802" t="s">
-        <v>1903</v>
       </c>
       <c r="G802" t="s">
         <v>1235</v>
@@ -25429,10 +25429,10 @@
         <v>1901</v>
       </c>
       <c r="E803" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F803" t="s">
         <v>1906</v>
-      </c>
-      <c r="F803" t="s">
-        <v>1903</v>
       </c>
       <c r="G803" t="s">
         <v>1235</v>
@@ -25452,10 +25452,10 @@
         <v>1901</v>
       </c>
       <c r="E804" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F804" t="s">
         <v>1906</v>
-      </c>
-      <c r="F804" t="s">
-        <v>1903</v>
       </c>
       <c r="G804" t="s">
         <v>1235</v>
@@ -25475,10 +25475,10 @@
         <v>1901</v>
       </c>
       <c r="E805" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F805" t="s">
         <v>1906</v>
-      </c>
-      <c r="F805" t="s">
-        <v>1903</v>
       </c>
       <c r="G805" t="s">
         <v>1235</v>
@@ -25498,10 +25498,10 @@
         <v>1901</v>
       </c>
       <c r="E806" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F806" t="s">
         <v>1906</v>
-      </c>
-      <c r="F806" t="s">
-        <v>1903</v>
       </c>
       <c r="G806" t="s">
         <v>1235</v>
@@ -25521,10 +25521,10 @@
         <v>1901</v>
       </c>
       <c r="E807" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F807" t="s">
         <v>1906</v>
-      </c>
-      <c r="F807" t="s">
-        <v>1903</v>
       </c>
       <c r="G807" t="s">
         <v>1235</v>
@@ -25613,10 +25613,10 @@
         <v>1992</v>
       </c>
       <c r="E811" t="s">
+        <v>1984</v>
+      </c>
+      <c r="F811" t="s">
         <v>1993</v>
-      </c>
-      <c r="F811" t="s">
-        <v>1985</v>
       </c>
       <c r="G811" t="s">
         <v>34</v>
@@ -25682,10 +25682,10 @@
         <v>1983</v>
       </c>
       <c r="E814" t="s">
+        <v>1984</v>
+      </c>
+      <c r="F814" t="s">
         <v>1993</v>
-      </c>
-      <c r="F814" t="s">
-        <v>1985</v>
       </c>
       <c r="G814" t="s">
         <v>1235</v>
@@ -25705,10 +25705,10 @@
         <v>2002</v>
       </c>
       <c r="E815" t="s">
+        <v>1984</v>
+      </c>
+      <c r="F815" t="s">
         <v>2003</v>
-      </c>
-      <c r="F815" t="s">
-        <v>1985</v>
       </c>
       <c r="G815" t="s">
         <v>34</v>
@@ -25843,10 +25843,10 @@
         <v>2016</v>
       </c>
       <c r="E821" t="s">
+        <v>1984</v>
+      </c>
+      <c r="F821" t="s">
         <v>2017</v>
-      </c>
-      <c r="F821" t="s">
-        <v>1985</v>
       </c>
       <c r="G821" t="s">
         <v>20</v>
@@ -25866,10 +25866,10 @@
         <v>2020</v>
       </c>
       <c r="E822" t="s">
+        <v>1984</v>
+      </c>
+      <c r="F822" t="s">
         <v>2021</v>
-      </c>
-      <c r="F822" t="s">
-        <v>1985</v>
       </c>
       <c r="G822" t="s">
         <v>1235</v>
@@ -25889,10 +25889,10 @@
         <v>1983</v>
       </c>
       <c r="E823" t="s">
+        <v>1984</v>
+      </c>
+      <c r="F823" t="s">
         <v>2021</v>
-      </c>
-      <c r="F823" t="s">
-        <v>1985</v>
       </c>
       <c r="G823" t="s">
         <v>1235</v>
@@ -25912,10 +25912,10 @@
         <v>2020</v>
       </c>
       <c r="E824" t="s">
+        <v>1984</v>
+      </c>
+      <c r="F824" t="s">
         <v>2021</v>
-      </c>
-      <c r="F824" t="s">
-        <v>1985</v>
       </c>
       <c r="G824" t="s">
         <v>1235</v>
@@ -25935,10 +25935,10 @@
         <v>2020</v>
       </c>
       <c r="E825" t="s">
+        <v>1984</v>
+      </c>
+      <c r="F825" t="s">
         <v>2021</v>
-      </c>
-      <c r="F825" t="s">
-        <v>1985</v>
       </c>
       <c r="G825" t="s">
         <v>1235</v>
@@ -25958,10 +25958,10 @@
         <v>2020</v>
       </c>
       <c r="E826" t="s">
+        <v>1984</v>
+      </c>
+      <c r="F826" t="s">
         <v>2021</v>
-      </c>
-      <c r="F826" t="s">
-        <v>1985</v>
       </c>
       <c r="G826" t="s">
         <v>1235</v>
@@ -25981,10 +25981,10 @@
         <v>2020</v>
       </c>
       <c r="E827" t="s">
+        <v>1984</v>
+      </c>
+      <c r="F827" t="s">
         <v>2021</v>
-      </c>
-      <c r="F827" t="s">
-        <v>1985</v>
       </c>
       <c r="G827" t="s">
         <v>1235</v>
@@ -26004,10 +26004,10 @@
         <v>1983</v>
       </c>
       <c r="E828" t="s">
+        <v>1984</v>
+      </c>
+      <c r="F828" t="s">
         <v>2021</v>
-      </c>
-      <c r="F828" t="s">
-        <v>1985</v>
       </c>
       <c r="G828" t="s">
         <v>1235</v>
@@ -26050,10 +26050,10 @@
         <v>1983</v>
       </c>
       <c r="E830" t="s">
+        <v>1984</v>
+      </c>
+      <c r="F830" t="s">
         <v>1993</v>
-      </c>
-      <c r="F830" t="s">
-        <v>1985</v>
       </c>
       <c r="G830" t="s">
         <v>1235</v>
@@ -26280,10 +26280,10 @@
         <v>2056</v>
       </c>
       <c r="E840" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F840" t="s">
         <v>2061</v>
-      </c>
-      <c r="F840" t="s">
-        <v>2058</v>
       </c>
       <c r="G840" t="s">
         <v>1235</v>
@@ -26303,10 +26303,10 @@
         <v>2056</v>
       </c>
       <c r="E841" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F841" t="s">
         <v>2061</v>
-      </c>
-      <c r="F841" t="s">
-        <v>2058</v>
       </c>
       <c r="G841" t="s">
         <v>1235</v>
@@ -26326,10 +26326,10 @@
         <v>2056</v>
       </c>
       <c r="E842" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F842" t="s">
         <v>2061</v>
-      </c>
-      <c r="F842" t="s">
-        <v>2058</v>
       </c>
       <c r="G842" t="s">
         <v>1235</v>
@@ -26349,10 +26349,10 @@
         <v>2056</v>
       </c>
       <c r="E843" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F843" t="s">
         <v>2061</v>
-      </c>
-      <c r="F843" t="s">
-        <v>2058</v>
       </c>
       <c r="G843" t="s">
         <v>1235</v>
@@ -26372,10 +26372,10 @@
         <v>2056</v>
       </c>
       <c r="E844" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F844" t="s">
         <v>2061</v>
-      </c>
-      <c r="F844" t="s">
-        <v>2058</v>
       </c>
       <c r="G844" t="s">
         <v>1235</v>
@@ -26395,10 +26395,10 @@
         <v>2056</v>
       </c>
       <c r="E845" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F845" t="s">
         <v>2061</v>
-      </c>
-      <c r="F845" t="s">
-        <v>2058</v>
       </c>
       <c r="G845" t="s">
         <v>1235</v>
@@ -26418,10 +26418,10 @@
         <v>2056</v>
       </c>
       <c r="E846" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F846" t="s">
         <v>2061</v>
-      </c>
-      <c r="F846" t="s">
-        <v>2058</v>
       </c>
       <c r="G846" t="s">
         <v>1235</v>
@@ -26441,10 +26441,10 @@
         <v>1992</v>
       </c>
       <c r="E847" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F847" t="s">
         <v>2076</v>
-      </c>
-      <c r="F847" t="s">
-        <v>2058</v>
       </c>
       <c r="G847" t="s">
         <v>1235</v>
@@ -26464,10 +26464,10 @@
         <v>1992</v>
       </c>
       <c r="E848" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F848" t="s">
         <v>2076</v>
-      </c>
-      <c r="F848" t="s">
-        <v>2058</v>
       </c>
       <c r="G848" t="s">
         <v>1235</v>
@@ -26487,10 +26487,10 @@
         <v>1992</v>
       </c>
       <c r="E849" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F849" t="s">
         <v>2076</v>
-      </c>
-      <c r="F849" t="s">
-        <v>2058</v>
       </c>
       <c r="G849" t="s">
         <v>1235</v>
@@ -26510,10 +26510,10 @@
         <v>2083</v>
       </c>
       <c r="E850" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F850" t="s">
         <v>2076</v>
-      </c>
-      <c r="F850" t="s">
-        <v>2058</v>
       </c>
       <c r="G850" t="s">
         <v>1235</v>
@@ -26533,10 +26533,10 @@
         <v>1992</v>
       </c>
       <c r="E851" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F851" t="s">
         <v>2076</v>
-      </c>
-      <c r="F851" t="s">
-        <v>2058</v>
       </c>
       <c r="G851" t="s">
         <v>1235</v>
@@ -26556,10 +26556,10 @@
         <v>1992</v>
       </c>
       <c r="E852" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F852" t="s">
         <v>2076</v>
-      </c>
-      <c r="F852" t="s">
-        <v>2058</v>
       </c>
       <c r="G852" t="s">
         <v>1235</v>
@@ -26579,10 +26579,10 @@
         <v>2056</v>
       </c>
       <c r="E853" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F853" t="s">
         <v>2061</v>
-      </c>
-      <c r="F853" t="s">
-        <v>2058</v>
       </c>
       <c r="G853" t="s">
         <v>1235</v>
@@ -26602,10 +26602,10 @@
         <v>2056</v>
       </c>
       <c r="E854" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F854" t="s">
         <v>2061</v>
-      </c>
-      <c r="F854" t="s">
-        <v>2058</v>
       </c>
       <c r="G854" t="s">
         <v>20</v>
@@ -26625,10 +26625,10 @@
         <v>2056</v>
       </c>
       <c r="E855" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F855" t="s">
         <v>2061</v>
-      </c>
-      <c r="F855" t="s">
-        <v>2058</v>
       </c>
       <c r="G855" t="s">
         <v>20</v>
@@ -26648,10 +26648,10 @@
         <v>2056</v>
       </c>
       <c r="E856" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F856" t="s">
         <v>2061</v>
-      </c>
-      <c r="F856" t="s">
-        <v>2058</v>
       </c>
       <c r="G856" t="s">
         <v>20</v>
@@ -26671,10 +26671,10 @@
         <v>2056</v>
       </c>
       <c r="E857" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F857" t="s">
         <v>2061</v>
-      </c>
-      <c r="F857" t="s">
-        <v>2058</v>
       </c>
       <c r="G857" t="s">
         <v>1235</v>
@@ -26694,10 +26694,10 @@
         <v>2056</v>
       </c>
       <c r="E858" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F858" t="s">
         <v>2061</v>
-      </c>
-      <c r="F858" t="s">
-        <v>2058</v>
       </c>
       <c r="G858" t="s">
         <v>1235</v>
@@ -26717,10 +26717,10 @@
         <v>2056</v>
       </c>
       <c r="E859" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F859" t="s">
         <v>2061</v>
-      </c>
-      <c r="F859" t="s">
-        <v>2058</v>
       </c>
       <c r="G859" t="s">
         <v>20</v>
@@ -26740,10 +26740,10 @@
         <v>2056</v>
       </c>
       <c r="E860" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F860" t="s">
         <v>2061</v>
-      </c>
-      <c r="F860" t="s">
-        <v>2058</v>
       </c>
       <c r="G860" t="s">
         <v>1235</v>
@@ -26763,10 +26763,10 @@
         <v>2056</v>
       </c>
       <c r="E861" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F861" t="s">
         <v>2061</v>
-      </c>
-      <c r="F861" t="s">
-        <v>2058</v>
       </c>
       <c r="G861" t="s">
         <v>1235</v>
@@ -26786,10 +26786,10 @@
         <v>2056</v>
       </c>
       <c r="E862" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F862" t="s">
         <v>2061</v>
-      </c>
-      <c r="F862" t="s">
-        <v>2058</v>
       </c>
       <c r="G862" t="s">
         <v>1235</v>
@@ -26809,10 +26809,10 @@
         <v>2056</v>
       </c>
       <c r="E863" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F863" t="s">
         <v>2061</v>
-      </c>
-      <c r="F863" t="s">
-        <v>2058</v>
       </c>
       <c r="G863" t="s">
         <v>1235</v>
@@ -26832,10 +26832,10 @@
         <v>2056</v>
       </c>
       <c r="E864" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F864" t="s">
         <v>2061</v>
-      </c>
-      <c r="F864" t="s">
-        <v>2058</v>
       </c>
       <c r="G864" t="s">
         <v>1235</v>
@@ -26855,10 +26855,10 @@
         <v>2056</v>
       </c>
       <c r="E865" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F865" t="s">
         <v>2061</v>
-      </c>
-      <c r="F865" t="s">
-        <v>2058</v>
       </c>
       <c r="G865" t="s">
         <v>1235</v>
@@ -26878,10 +26878,10 @@
         <v>2056</v>
       </c>
       <c r="E866" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F866" t="s">
         <v>2061</v>
-      </c>
-      <c r="F866" t="s">
-        <v>2058</v>
       </c>
       <c r="G866" t="s">
         <v>1235</v>
@@ -27545,10 +27545,10 @@
         <v>2168</v>
       </c>
       <c r="E895" t="s">
+        <v>2169</v>
+      </c>
+      <c r="F895" t="s">
         <v>2181</v>
-      </c>
-      <c r="F895" t="s">
-        <v>2170</v>
       </c>
       <c r="G895" t="s">
         <v>1235</v>
@@ -27775,10 +27775,10 @@
         <v>2168</v>
       </c>
       <c r="E905" t="s">
+        <v>2200</v>
+      </c>
+      <c r="F905" t="s">
         <v>2204</v>
-      </c>
-      <c r="F905" t="s">
-        <v>2201</v>
       </c>
       <c r="G905" t="s">
         <v>1235</v>

--- a/api/2/clv3/xlsx/en/HumanitarianPlan.xlsx
+++ b/api/2/clv3/xlsx/en/HumanitarianPlan.xlsx
@@ -25,15 +25,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:plan-start-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-end-date</t>
   </si>
   <si>
     <t>codeforiati:plan-year</t>
   </si>
   <si>
-    <t>codeforiati:plan-start-date</t>
-  </si>
-  <si>
     <t>codeforiati:plan-type</t>
   </si>
   <si>
@@ -46,15 +46,15 @@
     <t>active</t>
   </si>
   <si>
+    <t>2025-01-01</t>
+  </si>
+  <si>
     <t>2025-12-31</t>
   </si>
   <si>
     <t>2025</t>
   </si>
   <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
@@ -355,15 +355,15 @@
     <t>Afghanistan Humanitarian Needs and Response Plan 2024</t>
   </si>
   <si>
+    <t>2024-01-01</t>
+  </si>
+  <si>
     <t>2024-12-31</t>
   </si>
   <si>
     <t>2024</t>
   </si>
   <si>
-    <t>2024-01-01</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -712,15 +712,15 @@
     <t>Afghanistan Humanitarian Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-01-01</t>
+  </si>
+  <si>
     <t>2023-12-31</t>
   </si>
   <si>
     <t>2023</t>
   </si>
   <si>
-    <t>2023-01-01</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -841,24 +841,24 @@
     <t>Mongolia Dzud Early Action and Response Plan 2023</t>
   </si>
   <si>
+    <t>2022-12-01</t>
+  </si>
+  <si>
     <t>2023-05-31</t>
   </si>
   <si>
-    <t>2022-12-01</t>
-  </si>
-  <si>
     <t>OMOZ23</t>
   </si>
   <si>
     <t>Mozambique Cyclone Freddy, Floods and Cholera Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-03-01</t>
+  </si>
+  <si>
     <t>2023-09-30</t>
   </si>
   <si>
-    <t>2023-03-01</t>
-  </si>
-  <si>
     <t>HMOZ23</t>
   </si>
   <si>
@@ -946,12 +946,12 @@
     <t>Sudan Emergency: Regional Refugee Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-05-01</t>
+  </si>
+  <si>
     <t>2023-10-31</t>
   </si>
   <si>
-    <t>2023-05-01</t>
-  </si>
-  <si>
     <t>HSDN23</t>
   </si>
   <si>
@@ -1030,15 +1030,15 @@
     <t>Afghanistan Humanitarian Response Plan 2022</t>
   </si>
   <si>
+    <t>2022-01-01</t>
+  </si>
+  <si>
     <t>2022-12-31</t>
   </si>
   <si>
     <t>2022</t>
   </si>
   <si>
-    <t>2022-01-01</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -1081,12 +1081,12 @@
     <t>Cuba Hurricane Ian Response - Plan of Action 2022</t>
   </si>
   <si>
+    <t>2022-10-20</t>
+  </si>
+  <si>
     <t>2023-03-31</t>
   </si>
   <si>
-    <t>2022-10-20</t>
-  </si>
-  <si>
     <t>RDRCRRP22</t>
   </si>
   <si>
@@ -1117,12 +1117,12 @@
     <t>Haïti Choléra+ Appel Éclair 2022</t>
   </si>
   <si>
+    <t>2022-10-16</t>
+  </si>
+  <si>
     <t>2023-04-15</t>
   </si>
   <si>
-    <t>2022-10-16</t>
-  </si>
-  <si>
     <t>FHTI22</t>
   </si>
   <si>
@@ -1180,12 +1180,12 @@
     <t>Malawi Flash Appeal 2022</t>
   </si>
   <si>
+    <t>2022-02-26</t>
+  </si>
+  <si>
     <t>2022-05-31</t>
   </si>
   <si>
-    <t>2022-02-26</t>
-  </si>
-  <si>
     <t>HMLI22</t>
   </si>
   <si>
@@ -1198,12 +1198,12 @@
     <t>Mozambique Gombe Emergency Response Plan 2022</t>
   </si>
   <si>
+    <t>2022-04-01</t>
+  </si>
+  <si>
     <t>2022-09-30</t>
   </si>
   <si>
-    <t>2022-04-01</t>
-  </si>
-  <si>
     <t>HMOZ22</t>
   </si>
   <si>
@@ -1255,12 +1255,12 @@
     <t>Philippines Super Typhoon Rai (Odette) Humanitarian Needs and Priorities 2022</t>
   </si>
   <si>
+    <t>2021-12-24</t>
+  </si>
+  <si>
     <t>2022-06-30</t>
   </si>
   <si>
-    <t>2021-12-24</t>
-  </si>
-  <si>
     <t>RREG22</t>
   </si>
   <si>
@@ -1378,15 +1378,15 @@
     <t>Afghanistan Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
     <t>2021-12-31</t>
   </si>
   <si>
     <t>2021</t>
   </si>
   <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -1477,12 +1477,12 @@
     <t>Escalation of Hostilities in the OPT Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-05-27</t>
+  </si>
+  <si>
     <t>2021-08-27</t>
   </si>
   <si>
-    <t>2021-05-27</t>
-  </si>
-  <si>
     <t>HETH21</t>
   </si>
   <si>
@@ -1507,12 +1507,12 @@
     <t>Haiti Earthquake Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-08-16</t>
+  </si>
+  <si>
     <t>2022-02-15</t>
   </si>
   <si>
-    <t>2021-08-16</t>
-  </si>
-  <si>
     <t>HHTI21</t>
   </si>
   <si>
@@ -1525,12 +1525,12 @@
     <t>Honduras Tropical Storm Eta Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2020-11-15</t>
+  </si>
+  <si>
     <t>2021-06-30</t>
   </si>
   <si>
-    <t>2020-11-15</t>
-  </si>
-  <si>
     <t>HHND21</t>
   </si>
   <si>
@@ -1564,12 +1564,12 @@
     <t>Lebanon Emergency Response Plan 2021</t>
   </si>
   <si>
+    <t>2021-08-03</t>
+  </si>
+  <si>
     <t>2022-07-31</t>
   </si>
   <si>
-    <t>2021-08-03</t>
-  </si>
-  <si>
     <t>HLBY21</t>
   </si>
   <si>
@@ -1735,15 +1735,15 @@
     <t>Afghanistan Humanitarian Response Plan 2020</t>
   </si>
   <si>
+    <t>2020-01-01</t>
+  </si>
+  <si>
     <t>2020-12-31</t>
   </si>
   <si>
     <t>2020</t>
   </si>
   <si>
-    <t>2020-01-01</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -1858,12 +1858,12 @@
     <t>Djibouti Flash Appeal 2020</t>
   </si>
   <si>
+    <t>2019-12-17</t>
+  </si>
+  <si>
     <t>2020-03-31</t>
   </si>
   <si>
-    <t>2019-12-17</t>
-  </si>
-  <si>
     <t>ODJI20</t>
   </si>
   <si>
@@ -1957,12 +1957,12 @@
     <t>Lebanon Flash Appeal 2020</t>
   </si>
   <si>
+    <t>2020-08-05</t>
+  </si>
+  <si>
     <t>2020-11-13</t>
   </si>
   <si>
-    <t>2020-08-05</t>
-  </si>
-  <si>
     <t>OLBN20</t>
   </si>
   <si>
@@ -1975,12 +1975,12 @@
     <t>Lesotho Flash Appeal 2019-2020</t>
   </si>
   <si>
+    <t>2019-11-01</t>
+  </si>
+  <si>
     <t>2020-04-30</t>
   </si>
   <si>
-    <t>2019-11-01</t>
-  </si>
-  <si>
     <t>OLBR20</t>
   </si>
   <si>
@@ -2170,15 +2170,15 @@
     <t>Afghanistan Humanitarian Response Plan 2019</t>
   </si>
   <si>
+    <t>2019-01-01</t>
+  </si>
+  <si>
     <t>2019-12-31</t>
   </si>
   <si>
     <t>2019</t>
   </si>
   <si>
-    <t>2019-01-01</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -2386,12 +2386,12 @@
     <t>Zimbabwe Flash Appeal 2019</t>
   </si>
   <si>
+    <t>2019-02-01</t>
+  </si>
+  <si>
     <t>2020-04-29</t>
   </si>
   <si>
-    <t>2019-02-01</t>
-  </si>
-  <si>
     <t>FZWE1820</t>
   </si>
   <si>
@@ -2407,15 +2407,15 @@
     <t>Afghanistan Humanitarian Response Plan 2018</t>
   </si>
   <si>
+    <t>2018-01-01</t>
+  </si>
+  <si>
     <t>2018-12-31</t>
   </si>
   <si>
     <t>2018</t>
   </si>
   <si>
-    <t>2018-01-01</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -2590,12 +2590,12 @@
     <t>Syrian Arab Republic Humanitarian Response Plan 2018</t>
   </si>
   <si>
+    <t>2018-11-30</t>
+  </si>
+  <si>
     <t>2018-12-30</t>
   </si>
   <si>
-    <t>2018-11-30</t>
-  </si>
-  <si>
     <t>RSYR18</t>
   </si>
   <si>
@@ -2632,15 +2632,15 @@
     <t>2017 Europe Situation - Regional Refugee and Migrant Response</t>
   </si>
   <si>
+    <t>2017-01-01</t>
+  </si>
+  <si>
     <t>2017-12-31</t>
   </si>
   <si>
     <t>2017</t>
   </si>
   <si>
-    <t>2017-01-01</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -2716,12 +2716,12 @@
     <t>Dominica Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-09-28</t>
+  </si>
+  <si>
     <t>2017-12-29</t>
   </si>
   <si>
-    <t>2017-09-28</t>
-  </si>
-  <si>
     <t>OPRK17</t>
   </si>
   <si>
@@ -2761,12 +2761,12 @@
     <t>Kenya Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
     <t>2017-11-30</t>
   </si>
   <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
     <t>HLBY17</t>
   </si>
   <si>
@@ -2779,12 +2779,12 @@
     <t>Madagascar Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-03-20</t>
+  </si>
+  <si>
     <t>2017-06-20</t>
   </si>
   <si>
-    <t>2017-03-20</t>
-  </si>
-  <si>
     <t>HMLI17</t>
   </si>
   <si>
@@ -2803,12 +2803,12 @@
     <t>Mozambique Cyclone Dineo Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-02-28</t>
+  </si>
+  <si>
     <t>2017-05-31</t>
   </si>
   <si>
-    <t>2017-02-28</t>
-  </si>
-  <si>
     <t>HMMR17</t>
   </si>
   <si>
@@ -2845,12 +2845,12 @@
     <t>Peru Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-04-01</t>
+  </si>
+  <si>
     <t>2017-10-31</t>
   </si>
   <si>
-    <t>2017-04-01</t>
-  </si>
-  <si>
     <t>HCOG17</t>
   </si>
   <si>
@@ -2920,15 +2920,15 @@
     <t>2016 Europe Situation -Regional Refugee and Migrant Response</t>
   </si>
   <si>
+    <t>2016-01-01</t>
+  </si>
+  <si>
     <t>2016-12-31</t>
   </si>
   <si>
     <t>2016</t>
   </si>
   <si>
-    <t>2016-01-01</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -3001,24 +3001,24 @@
     <t>Ecuador Earthquake Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-04-16</t>
+  </si>
+  <si>
     <t>2016-10-31</t>
   </si>
   <si>
-    <t>2016-04-16</t>
-  </si>
-  <si>
     <t>FFJI16</t>
   </si>
   <si>
     <t>Fiji Tropical Cyclone Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-02-20</t>
+  </si>
+  <si>
     <t>2016-05-30</t>
   </si>
   <si>
-    <t>2016-02-20</t>
-  </si>
-  <si>
     <t>HGMB16</t>
   </si>
   <si>
@@ -3094,12 +3094,12 @@
     <t>Mosul Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-07-20</t>
+  </si>
+  <si>
     <t>2016-10-01</t>
   </si>
   <si>
-    <t>2016-07-20</t>
-  </si>
-  <si>
     <t>HMMR16</t>
   </si>
   <si>
@@ -3184,27 +3184,27 @@
     <t>Zimbabwe Humanitarian Response Plan 2016</t>
   </si>
   <si>
+    <t>2016-04-01</t>
+  </si>
+  <si>
     <t>2017-03-31</t>
   </si>
   <si>
-    <t>2016-04-01</t>
-  </si>
-  <si>
     <t>HAFG15</t>
   </si>
   <si>
     <t>Afghanistan Strategic Response Plan 2015</t>
   </si>
   <si>
+    <t>2015-01-01</t>
+  </si>
+  <si>
     <t>2015-12-31</t>
   </si>
   <si>
     <t>2015</t>
   </si>
   <si>
-    <t>2015-01-01</t>
-  </si>
-  <si>
     <t>Strategic response plan</t>
   </si>
   <si>
@@ -3262,12 +3262,12 @@
     <t>Guatemala Plan de Respuesta Sequia 2015</t>
   </si>
   <si>
+    <t>2014-11-03</t>
+  </si>
+  <si>
     <t>2015-09-30</t>
   </si>
   <si>
-    <t>2014-11-03</t>
-  </si>
-  <si>
     <t>FHTI15</t>
   </si>
   <si>
@@ -3292,12 +3292,12 @@
     <t>Vanuatu Emergency Response Plan for Tropical Cyclone PAM 2015</t>
   </si>
   <si>
+    <t>2015-03-24</t>
+  </si>
+  <si>
     <t>2015-10-31</t>
   </si>
   <si>
-    <t>2015-03-24</t>
-  </si>
-  <si>
     <t>HIRQ15</t>
   </si>
   <si>
@@ -3310,12 +3310,12 @@
     <t>Libya Humanitarian Appeal 2014- 2015</t>
   </si>
   <si>
+    <t>2014-10-01</t>
+  </si>
+  <si>
     <t>2015-05-31</t>
   </si>
   <si>
-    <t>2014-10-01</t>
-  </si>
-  <si>
     <t>HMLI15</t>
   </si>
   <si>
@@ -3427,15 +3427,15 @@
     <t>Afghanistan Strategic Response Plan 2014</t>
   </si>
   <si>
+    <t>2014-01-01</t>
+  </si>
+  <si>
     <t>2014-12-31</t>
   </si>
   <si>
     <t>2014</t>
   </si>
   <si>
-    <t>2014-01-01</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -3571,24 +3571,24 @@
     <t>Philippines Bohol Earthquake Flash Appeal 2014</t>
   </si>
   <si>
+    <t>2013-10-22</t>
+  </si>
+  <si>
     <t>2014-04-22</t>
   </si>
   <si>
-    <t>2013-10-22</t>
-  </si>
-  <si>
     <t>SPHL1314</t>
   </si>
   <si>
     <t>Philippines Typhoon Haiyan Strategic Response Plan 2014</t>
   </si>
   <si>
+    <t>2013-11-08</t>
+  </si>
+  <si>
     <t>2014-11-07</t>
   </si>
   <si>
-    <t>2013-11-08</t>
-  </si>
-  <si>
     <t>HPHL1314</t>
   </si>
   <si>
@@ -3604,12 +3604,12 @@
     <t>Philippines Zamboanga Crisis Flash Appeal 2014</t>
   </si>
   <si>
+    <t>2013-10-01</t>
+  </si>
+  <si>
     <t>2014-08-31</t>
   </si>
   <si>
-    <t>2013-10-01</t>
-  </si>
-  <si>
     <t>SCOD14</t>
   </si>
   <si>
@@ -3877,15 +3877,15 @@
     <t>2012+ Kenya Emergency Humanitarian Response Plan</t>
   </si>
   <si>
+    <t>2012-01-01</t>
+  </si>
+  <si>
     <t>2012-12-31</t>
   </si>
   <si>
     <t>2012</t>
   </si>
   <si>
-    <t>2012-01-01</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -3955,12 +3955,12 @@
     <t>Lesotho Food Insecurity (September 2012 - March 2013)</t>
   </si>
   <si>
+    <t>2012-09-18</t>
+  </si>
+  <si>
     <t>2013-03-25</t>
   </si>
   <si>
-    <t>2012-09-18</t>
-  </si>
-  <si>
     <t>CLBR12</t>
   </si>
   <si>
@@ -4033,12 +4033,12 @@
     <t>Syria Humanitarian Assistance Response Plan (SHARP) 2012</t>
   </si>
   <si>
+    <t>2012-06-05</t>
+  </si>
+  <si>
     <t>2012-12-05</t>
   </si>
   <si>
-    <t>2012-06-05</t>
-  </si>
-  <si>
     <t>CYEM12</t>
   </si>
   <si>
@@ -4063,12 +4063,12 @@
     <t>2011+ Kenya Emergency Humanitarian Response Plan</t>
   </si>
   <si>
+    <t>2011-01-01</t>
+  </si>
+  <si>
     <t>2011</t>
   </si>
   <si>
-    <t>2011-01-01</t>
-  </si>
-  <si>
     <t>CAFG11</t>
   </si>
   <si>
@@ -4111,12 +4111,12 @@
     <t>El Salvador Flash Appeal (October 2011 - April 2012)</t>
   </si>
   <si>
+    <t>2011-10-25</t>
+  </si>
+  <si>
     <t>2012-04-25</t>
   </si>
   <si>
-    <t>2011-10-25</t>
-  </si>
-  <si>
     <t>CHTI1011</t>
   </si>
   <si>
@@ -4147,24 +4147,24 @@
     <t>Namibia Flash Appeal (April - October 2011)</t>
   </si>
   <si>
+    <t>2011-04-11</t>
+  </si>
+  <si>
     <t>2011-10-11</t>
   </si>
   <si>
-    <t>2011-04-11</t>
-  </si>
-  <si>
     <t>FNIC1112</t>
   </si>
   <si>
     <t>Nicaragua Flash Appeal (October 2011 - April 2012)</t>
   </si>
   <si>
+    <t>2011-10-27</t>
+  </si>
+  <si>
     <t>2012-04-26</t>
   </si>
   <si>
-    <t>2011-10-27</t>
-  </si>
-  <si>
     <t>CNER11</t>
   </si>
   <si>
@@ -4177,12 +4177,12 @@
     <t>Pakistan Rapid Response Plan Floods 2011 (September - March 2012)</t>
   </si>
   <si>
+    <t>2011-09-15</t>
+  </si>
+  <si>
     <t>2012-06-30</t>
   </si>
   <si>
-    <t>2011-09-15</t>
-  </si>
-  <si>
     <t>FXLBYREG11</t>
   </si>
   <si>
@@ -4258,27 +4258,27 @@
     <t>Afghanistan Humanitarian Action Plan 2010</t>
   </si>
   <si>
+    <t>2010-01-01</t>
+  </si>
+  <si>
     <t>2010-12-31</t>
   </si>
   <si>
     <t>2010</t>
   </si>
   <si>
-    <t>2010-01-01</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
     <t>Burkina Faso Emergency Humanitarian Action Plan 2010</t>
   </si>
   <si>
+    <t>2010-08-01</t>
+  </si>
+  <si>
     <t>2011-01-31</t>
   </si>
   <si>
-    <t>2010-08-01</t>
-  </si>
-  <si>
     <t>CCAF10</t>
   </si>
   <si>
@@ -4303,36 +4303,36 @@
     <t>El Salvador Flash Appeal (Revised) (November 2009 - May 2010)</t>
   </si>
   <si>
+    <t>2009-11-01</t>
+  </si>
+  <si>
     <t>2010-05-31</t>
   </si>
   <si>
-    <t>2009-11-01</t>
-  </si>
-  <si>
     <t>FGTM10</t>
   </si>
   <si>
     <t>Guatemala Flash Appeal (Revised) (June - December 2010)</t>
   </si>
   <si>
+    <t>2010-06-10</t>
+  </si>
+  <si>
     <t>2010-12-09</t>
   </si>
   <si>
-    <t>2010-06-10</t>
-  </si>
-  <si>
     <t>CGTM10</t>
   </si>
   <si>
     <t>Guatemala Food Insecurity and Acute Malnutrition Appeal 2010</t>
   </si>
   <si>
+    <t>2010-02-12</t>
+  </si>
+  <si>
     <t>2010-08-11</t>
   </si>
   <si>
-    <t>2010-02-12</t>
-  </si>
-  <si>
     <t>FHTI10</t>
   </si>
   <si>
@@ -4360,12 +4360,12 @@
     <t>Kyrgyzstan Flash Appeal (Revised) (June 2010 - June 2011)</t>
   </si>
   <si>
+    <t>2010-06-01</t>
+  </si>
+  <si>
     <t>2011-06-30</t>
   </si>
   <si>
-    <t>2010-06-01</t>
-  </si>
-  <si>
     <t>CMNG1011</t>
   </si>
   <si>
@@ -4468,27 +4468,27 @@
     <t>Afghanistan Humanitarian Action Plan 2009</t>
   </si>
   <si>
+    <t>2009-01-01</t>
+  </si>
+  <si>
     <t>2009-12-31</t>
   </si>
   <si>
     <t>2009</t>
   </si>
   <si>
-    <t>2009-01-01</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
     <t>Burkina Faso Flash Appeal (September 2009 - February 2010)</t>
   </si>
   <si>
+    <t>2009-09-10</t>
+  </si>
+  <si>
     <t>2010-03-09</t>
   </si>
   <si>
-    <t>2009-09-10</t>
-  </si>
-  <si>
     <t>CCAF09</t>
   </si>
   <si>
@@ -4552,24 +4552,24 @@
     <t>Madagascar Flash Appeal (Revised) (April - October 2009)</t>
   </si>
   <si>
+    <t>2009-04-01</t>
+  </si>
+  <si>
     <t>2009-10-31</t>
   </si>
   <si>
-    <t>2009-04-01</t>
-  </si>
-  <si>
     <t>FNAM09</t>
   </si>
   <si>
     <t>Namibia Flash Appeal (Revised) (March - November 2009)</t>
   </si>
   <si>
+    <t>2009-03-20</t>
+  </si>
+  <si>
     <t>2009-09-30</t>
   </si>
   <si>
-    <t>2009-03-20</t>
-  </si>
-  <si>
     <t>ONPL09</t>
   </si>
   <si>
@@ -4591,12 +4591,12 @@
     <t>Philippines Flash Appeal (Revised) (October 2009 - March 2010)</t>
   </si>
   <si>
+    <t>2009-10-03</t>
+  </si>
+  <si>
     <t>2010-03-31</t>
   </si>
   <si>
-    <t>2009-10-03</t>
-  </si>
-  <si>
     <t>CSOM09</t>
   </si>
   <si>
@@ -4621,12 +4621,12 @@
     <t>Syria Drought Response Plan (Revised) (July 2009 - June 2010)</t>
   </si>
   <si>
+    <t>2009-07-15</t>
+  </si>
+  <si>
     <t>2010-06-14</t>
   </si>
   <si>
-    <t>2009-07-15</t>
-  </si>
-  <si>
     <t>OTJK09</t>
   </si>
   <si>
@@ -4684,27 +4684,27 @@
     <t>Afghanistan Joint Appeal 2008: Humanitarian Consequences of Rise in Food Prices (February - June 2008)</t>
   </si>
   <si>
+    <t>2008-02-01</t>
+  </si>
+  <si>
     <t>2008-06-30</t>
   </si>
   <si>
     <t>2008</t>
   </si>
   <si>
-    <t>2008-02-01</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
     <t>Afghanistan Joint Emergency Appeal 2008: High Food Price and Drought Crisis (July 2008 - June 2009)</t>
   </si>
   <si>
+    <t>2008-07-01</t>
+  </si>
+  <si>
     <t>2009-06-30</t>
   </si>
   <si>
-    <t>2008-07-01</t>
-  </si>
-  <si>
     <t>FBOL08</t>
   </si>
   <si>
@@ -4720,12 +4720,12 @@
     <t>Central African Republic 2008</t>
   </si>
   <si>
+    <t>2008-01-01</t>
+  </si>
+  <si>
     <t>2008-12-31</t>
   </si>
   <si>
-    <t>2008-01-01</t>
-  </si>
-  <si>
     <t>CTCD08</t>
   </si>
   <si>
@@ -4756,24 +4756,24 @@
     <t>Djibouti Joint Appeal 2008: Response Plan for Drought, Food and Nutrition Crisis</t>
   </si>
   <si>
+    <t>2008-08-01</t>
+  </si>
+  <si>
     <t>2009-02-28</t>
   </si>
   <si>
-    <t>2008-08-01</t>
-  </si>
-  <si>
     <t>FGEO0809</t>
   </si>
   <si>
     <t>Georgia Crisis Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2008-08-09</t>
+  </si>
+  <si>
     <t>2009-02-09</t>
   </si>
   <si>
-    <t>2008-08-09</t>
-  </si>
-  <si>
     <t>FHTI0809</t>
   </si>
   <si>
@@ -4789,12 +4789,12 @@
     <t>Honduras Flash Appeal (Updated) (November - April) 2008</t>
   </si>
   <si>
+    <t>2008-11-01</t>
+  </si>
+  <si>
     <t>2009-04-30</t>
   </si>
   <si>
-    <t>2008-11-01</t>
-  </si>
-  <si>
     <t>CIRQ08</t>
   </si>
   <si>
@@ -4813,12 +4813,12 @@
     <t>Kyrgyzstan Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2008-12-01</t>
+  </si>
+  <si>
     <t>2009-05-31</t>
   </si>
   <si>
-    <t>2008-12-01</t>
-  </si>
-  <si>
     <t>OLAO0809</t>
   </si>
   <si>
@@ -4849,12 +4849,12 @@
     <t>Myanmar Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2008-05-01</t>
+  </si>
+  <si>
     <t>2008-11-30</t>
   </si>
   <si>
-    <t>2008-05-01</t>
-  </si>
-  <si>
     <t>ONPL08</t>
   </si>
   <si>
@@ -4951,39 +4951,39 @@
     <t>Bolivia Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-02-22</t>
+  </si>
+  <si>
     <t>2007-08-21</t>
   </si>
   <si>
     <t>2007</t>
   </si>
   <si>
-    <t>2007-02-22</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
     <t>Burkina Faso Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-11-01</t>
+  </si>
+  <si>
     <t>2008-01-31</t>
   </si>
   <si>
-    <t>2007-11-01</t>
-  </si>
-  <si>
     <t>CBDI07</t>
   </si>
   <si>
     <t>Burundi 2007</t>
   </si>
   <si>
+    <t>2007-01-01</t>
+  </si>
+  <si>
     <t>2007-12-31</t>
   </si>
   <si>
-    <t>2007-01-01</t>
-  </si>
-  <si>
     <t>CCAF07</t>
   </si>
   <si>
@@ -5023,12 +5023,12 @@
     <t>Ghana Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-09-01</t>
+  </si>
+  <si>
     <t>2008-03-31</t>
   </si>
   <si>
-    <t>2007-09-01</t>
-  </si>
-  <si>
     <t>CXGLR07</t>
   </si>
   <si>
@@ -5050,36 +5050,36 @@
     <t>Korea DPR Flash Appeal: Floods Emergency 2007</t>
   </si>
   <si>
+    <t>2007-08-28</t>
+  </si>
+  <si>
     <t>2007-11-30</t>
   </si>
   <si>
-    <t>2007-08-28</t>
-  </si>
-  <si>
     <t>OLBN07</t>
   </si>
   <si>
     <t>Lebanon Crisis Appeal 2007</t>
   </si>
   <si>
+    <t>2007-06-04</t>
+  </si>
+  <si>
     <t>2007-09-03</t>
   </si>
   <si>
-    <t>2007-06-04</t>
-  </si>
-  <si>
     <t>FLSO0708</t>
   </si>
   <si>
     <t>Lesotho Drought Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-07-28</t>
+  </si>
+  <si>
     <t>2008-01-28</t>
   </si>
   <si>
-    <t>2007-07-28</t>
-  </si>
-  <si>
     <t>CLBR07</t>
   </si>
   <si>
@@ -5092,24 +5092,24 @@
     <t>Madagascar Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-03-15</t>
+  </si>
+  <si>
     <t>2007-09-15</t>
   </si>
   <si>
-    <t>2007-03-15</t>
-  </si>
-  <si>
     <t>FMOZ07</t>
   </si>
   <si>
     <t>Mozambique Floods and Cyclone Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-03-01</t>
+  </si>
+  <si>
     <t>2007-06-30</t>
   </si>
   <si>
-    <t>2007-03-01</t>
-  </si>
-  <si>
     <t>ONPL07</t>
   </si>
   <si>
@@ -5122,12 +5122,12 @@
     <t>Nicaragua Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-09-07</t>
+  </si>
+  <si>
     <t>2008-02-28</t>
   </si>
   <si>
-    <t>2007-09-07</t>
-  </si>
-  <si>
     <t>ORUS07</t>
   </si>
   <si>
@@ -5140,12 +5140,12 @@
     <t>Pakistan Cyclone and Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-07-15</t>
+  </si>
+  <si>
     <t>2007-10-31</t>
   </si>
   <si>
-    <t>2007-07-15</t>
-  </si>
-  <si>
     <t>FPER0708</t>
   </si>
   <si>
@@ -5203,12 +5203,12 @@
     <t>Swaziland Drought Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-07-20</t>
+  </si>
+  <si>
     <t>2008-01-20</t>
   </si>
   <si>
-    <t>2007-07-20</t>
-  </si>
-  <si>
     <t>CTLS07</t>
   </si>
   <si>
@@ -5257,15 +5257,15 @@
     <t>Afghanistan Drought Joint Appeal 2006</t>
   </si>
   <si>
+    <t>2006-07-01</t>
+  </si>
+  <si>
     <t>2006-12-31</t>
   </si>
   <si>
     <t>2006</t>
   </si>
   <si>
-    <t>2006-07-01</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -5311,24 +5311,24 @@
     <t>Ethiopia Floods Joint Appeal 2006</t>
   </si>
   <si>
+    <t>2006-08-25</t>
+  </si>
+  <si>
     <t>2006-11-25</t>
   </si>
   <si>
-    <t>2006-08-25</t>
-  </si>
-  <si>
     <t>OETH0607</t>
   </si>
   <si>
     <t>Ethiopia: 2006 Govt-UN Joint Emergency Flood Appeal for Somali Region</t>
   </si>
   <si>
+    <t>2006-11-23</t>
+  </si>
+  <si>
     <t>2007-01-22</t>
   </si>
   <si>
-    <t>2006-11-23</t>
-  </si>
-  <si>
     <t>CXGLR06</t>
   </si>
   <si>
@@ -5347,12 +5347,12 @@
     <t>Guinea-Bissau 2006</t>
   </si>
   <si>
+    <t>2006-05-01</t>
+  </si>
+  <si>
     <t>2006-11-30</t>
   </si>
   <si>
-    <t>2006-05-01</t>
-  </si>
-  <si>
     <t>CXHAF06</t>
   </si>
   <si>
@@ -5371,12 +5371,12 @@
     <t>Kenya 2006</t>
   </si>
   <si>
+    <t>2006-10-16</t>
+  </si>
+  <si>
     <t>2007-04-15</t>
   </si>
   <si>
-    <t>2006-10-16</t>
-  </si>
-  <si>
     <t>FKEN06</t>
   </si>
   <si>
@@ -5392,12 +5392,12 @@
     <t>Lebanon Crisis 2006</t>
   </si>
   <si>
+    <t>2006-07-24</t>
+  </si>
+  <si>
     <t>2006-10-23</t>
   </si>
   <si>
-    <t>2006-07-24</t>
-  </si>
-  <si>
     <t>CLBR06</t>
   </si>
   <si>
@@ -5446,12 +5446,12 @@
     <t>Somalia: 2006 Flood Response Plan</t>
   </si>
   <si>
+    <t>2006-12-05</t>
+  </si>
+  <si>
     <t>2007-03-05</t>
   </si>
   <si>
-    <t>2006-12-05</t>
-  </si>
-  <si>
     <t>OLKA06</t>
   </si>
   <si>
@@ -5512,39 +5512,39 @@
     <t>Angola Marburg VHF 2005</t>
   </si>
   <si>
+    <t>2005-04-01</t>
+  </si>
+  <si>
     <t>2005-06-30</t>
   </si>
   <si>
     <t>2005</t>
   </si>
   <si>
-    <t>2005-04-01</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
     <t>Benin 2005</t>
   </si>
   <si>
+    <t>2005-05-01</t>
+  </si>
+  <si>
     <t>2005-10-31</t>
   </si>
   <si>
-    <t>2005-05-01</t>
-  </si>
-  <si>
     <t>CBDI05</t>
   </si>
   <si>
     <t>Burundi 2005</t>
   </si>
   <si>
+    <t>2005-01-01</t>
+  </si>
+  <si>
     <t>2005-12-31</t>
   </si>
   <si>
-    <t>2005-01-01</t>
-  </si>
-  <si>
     <t>CCAF05</t>
   </si>
   <si>
@@ -5620,12 +5620,12 @@
     <t>Guyana 2005</t>
   </si>
   <si>
+    <t>2005-02-01</t>
+  </si>
+  <si>
     <t>2005-08-01</t>
   </si>
   <si>
-    <t>2005-02-01</t>
-  </si>
-  <si>
     <t>FXINDTSU05</t>
   </si>
   <si>
@@ -5647,12 +5647,12 @@
     <t>Niger 2005</t>
   </si>
   <si>
+    <t>2005-06-01</t>
+  </si>
+  <si>
     <t>2005-09-30</t>
   </si>
   <si>
-    <t>2005-06-01</t>
-  </si>
-  <si>
     <t>CCOG05</t>
   </si>
   <si>
@@ -5671,12 +5671,12 @@
     <t>South Asia Earthquake 2005</t>
   </si>
   <si>
+    <t>2005-10-11</t>
+  </si>
+  <si>
     <t>2006-04-10</t>
   </si>
   <si>
-    <t>2005-10-11</t>
-  </si>
-  <si>
     <t>CSDN05</t>
   </si>
   <si>
@@ -5701,12 +5701,12 @@
     <t>West and Central Africa Region Cholera 2005</t>
   </si>
   <si>
+    <t>2005-11-01</t>
+  </si>
+  <si>
     <t>2006-05-31</t>
   </si>
   <si>
-    <t>2005-11-01</t>
-  </si>
-  <si>
     <t>CPSE05</t>
   </si>
   <si>
@@ -5719,15 +5719,15 @@
     <t>Afghanistan UN-Government Drought Appeal 2004</t>
   </si>
   <si>
+    <t>2004-09-01</t>
+  </si>
+  <si>
     <t>2004-12-31</t>
   </si>
   <si>
     <t>2004</t>
   </si>
   <si>
-    <t>2004-09-01</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -5743,24 +5743,24 @@
     <t>Bangladesh 2004</t>
   </si>
   <si>
+    <t>2004-08-01</t>
+  </si>
+  <si>
     <t>2005-01-31</t>
   </si>
   <si>
-    <t>2004-08-01</t>
-  </si>
-  <si>
     <t>FBOL0405</t>
   </si>
   <si>
     <t>Bolivia 2004</t>
   </si>
   <si>
+    <t>2004-11-01</t>
+  </si>
+  <si>
     <t>2005-05-31</t>
   </si>
   <si>
-    <t>2004-11-01</t>
-  </si>
-  <si>
     <t>CBDI04</t>
   </si>
   <si>
@@ -5887,24 +5887,24 @@
     <t>Madagascar 2004</t>
   </si>
   <si>
+    <t>2004-03-19</t>
+  </si>
+  <si>
     <t>2004-06-19</t>
   </si>
   <si>
-    <t>2004-03-19</t>
-  </si>
-  <si>
     <t>FPHL0405</t>
   </si>
   <si>
     <t>Philippines 2004</t>
   </si>
   <si>
+    <t>2004-12-15</t>
+  </si>
+  <si>
     <t>2005-03-15</t>
   </si>
   <si>
-    <t>2004-12-15</t>
-  </si>
-  <si>
     <t>CSLE04</t>
   </si>
   <si>
@@ -5965,15 +5965,15 @@
     <t>Afghanistan TAPA 2003</t>
   </si>
   <si>
+    <t>2003-01-01</t>
+  </si>
+  <si>
     <t>2003-12-31</t>
   </si>
   <si>
     <t>2003</t>
   </si>
   <si>
-    <t>2003-01-01</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -5992,12 +5992,12 @@
     <t>Central African Republic 2003</t>
   </si>
   <si>
+    <t>2003-04-01</t>
+  </si>
+  <si>
     <t>2003-06-30</t>
   </si>
   <si>
-    <t>2003-04-01</t>
-  </si>
-  <si>
     <t>CRUS03</t>
   </si>
   <si>
@@ -6022,12 +6022,12 @@
     <t>Côte d'Ivoire and the West Africa Sub-Region 2002-2003</t>
   </si>
   <si>
+    <t>2002-11-01</t>
+  </si>
+  <si>
     <t>2003-01-31</t>
   </si>
   <si>
-    <t>2002-11-01</t>
-  </si>
-  <si>
     <t>CPRK03</t>
   </si>
   <si>
@@ -6064,24 +6064,24 @@
     <t>Haiti (PIR) 2003</t>
   </si>
   <si>
+    <t>2003-03-01</t>
+  </si>
+  <si>
     <t>2003-08-31</t>
   </si>
   <si>
-    <t>2003-03-01</t>
-  </si>
-  <si>
     <t>CLSO0304</t>
   </si>
   <si>
     <t>Humanitarian Crisis in Southern Africa - LESOTHO (July 2003 - June 2004)</t>
   </si>
   <si>
+    <t>2003-07-01</t>
+  </si>
+  <si>
     <t>2004-06-30</t>
   </si>
   <si>
-    <t>2003-07-01</t>
-  </si>
-  <si>
     <t>CMWI03</t>
   </si>
   <si>
@@ -6184,15 +6184,15 @@
     <t>Afghanistan 2002 (ITAP for the Afghan People)</t>
   </si>
   <si>
+    <t>2001-10-01</t>
+  </si>
+  <si>
     <t>2002-12-31</t>
   </si>
   <si>
     <t>2002</t>
   </si>
   <si>
-    <t>2001-10-01</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -6370,15 +6370,15 @@
     <t>Afghanistan 2001</t>
   </si>
   <si>
+    <t>2001-01-01</t>
+  </si>
+  <si>
     <t>2001-09-30</t>
   </si>
   <si>
     <t>2001</t>
   </si>
   <si>
-    <t>2001-01-01</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -6520,15 +6520,15 @@
     <t>Angola 2000</t>
   </si>
   <si>
+    <t>2000-01-01</t>
+  </si>
+  <si>
     <t>2000-12-31</t>
   </si>
   <si>
     <t>2000</t>
   </si>
   <si>
-    <t>2000-01-01</t>
-  </si>
-  <si>
     <t>CBDI00</t>
   </si>
   <si>
@@ -6616,10 +6616,10 @@
     <t>East Timor 1999</t>
   </si>
   <si>
+    <t>1999-10-01</t>
+  </si>
+  <si>
     <t>1999</t>
-  </si>
-  <si>
-    <t>1999-10-01</t>
   </si>
   <si>
     <t>CRUS9900</t>
@@ -7049,10 +7049,10 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
         <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
@@ -7279,10 +7279,10 @@
         <v>9</v>
       </c>
       <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
         <v>19</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
@@ -7302,10 +7302,10 @@
         <v>9</v>
       </c>
       <c r="D15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" t="s">
         <v>45</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
@@ -7348,10 +7348,10 @@
         <v>9</v>
       </c>
       <c r="D17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" t="s">
         <v>50</v>
-      </c>
-      <c r="E17" t="s">
-        <v>11</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
@@ -7394,10 +7394,10 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" t="s">
         <v>55</v>
-      </c>
-      <c r="E19" t="s">
-        <v>11</v>
       </c>
       <c r="F19" t="s">
         <v>12</v>
@@ -7417,13 +7417,13 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="E20" t="s">
         <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -7509,10 +7509,10 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" t="s">
         <v>67</v>
-      </c>
-      <c r="E24" t="s">
-        <v>11</v>
       </c>
       <c r="F24" t="s">
         <v>12</v>
@@ -7739,13 +7739,13 @@
         <v>9</v>
       </c>
       <c r="D34" t="s">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="E34" t="s">
         <v>11</v>
       </c>
       <c r="F34" t="s">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="G34" t="s">
         <v>34</v>
@@ -7923,10 +7923,10 @@
         <v>9</v>
       </c>
       <c r="D42" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" t="s">
         <v>55</v>
-      </c>
-      <c r="E42" t="s">
-        <v>11</v>
       </c>
       <c r="F42" t="s">
         <v>12</v>
@@ -7969,10 +7969,10 @@
         <v>9</v>
       </c>
       <c r="D44" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" t="s">
         <v>55</v>
-      </c>
-      <c r="E44" t="s">
-        <v>11</v>
       </c>
       <c r="F44" t="s">
         <v>12</v>
@@ -7992,10 +7992,10 @@
         <v>9</v>
       </c>
       <c r="D45" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" t="s">
         <v>45</v>
-      </c>
-      <c r="E45" t="s">
-        <v>11</v>
       </c>
       <c r="F45" t="s">
         <v>12</v>
@@ -8061,13 +8061,13 @@
         <v>9</v>
       </c>
       <c r="D48" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E48" t="s">
         <v>114</v>
       </c>
       <c r="F48" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G48" t="s">
         <v>20</v>
@@ -8107,13 +8107,13 @@
         <v>9</v>
       </c>
       <c r="D50" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E50" t="s">
         <v>114</v>
       </c>
       <c r="F50" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G50" t="s">
         <v>20</v>
@@ -8268,13 +8268,13 @@
         <v>9</v>
       </c>
       <c r="D57" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="E57" t="s">
         <v>114</v>
       </c>
       <c r="F57" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="G57" t="s">
         <v>34</v>
@@ -8360,13 +8360,13 @@
         <v>9</v>
       </c>
       <c r="D61" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="E61" t="s">
         <v>114</v>
       </c>
       <c r="F61" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="G61" t="s">
         <v>20</v>
@@ -8383,13 +8383,13 @@
         <v>9</v>
       </c>
       <c r="D62" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="E62" t="s">
         <v>114</v>
       </c>
       <c r="F62" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="G62" t="s">
         <v>34</v>
@@ -8406,10 +8406,10 @@
         <v>9</v>
       </c>
       <c r="D63" t="s">
+        <v>113</v>
+      </c>
+      <c r="E63" t="s">
         <v>154</v>
-      </c>
-      <c r="E63" t="s">
-        <v>114</v>
       </c>
       <c r="F63" t="s">
         <v>115</v>
@@ -8429,10 +8429,10 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
+        <v>113</v>
+      </c>
+      <c r="E64" t="s">
         <v>157</v>
-      </c>
-      <c r="E64" t="s">
-        <v>114</v>
       </c>
       <c r="F64" t="s">
         <v>115</v>
@@ -8452,13 +8452,13 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>113</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
         <v>114</v>
       </c>
       <c r="F65" t="s">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="G65" t="s">
         <v>34</v>
@@ -8498,13 +8498,13 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
+        <v>165</v>
+      </c>
+      <c r="E67" t="s">
         <v>157</v>
       </c>
-      <c r="E67" t="s">
-        <v>114</v>
-      </c>
       <c r="F67" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="G67" t="s">
         <v>20</v>
@@ -8521,13 +8521,13 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="E68" t="s">
         <v>114</v>
       </c>
       <c r="F68" t="s">
-        <v>168</v>
+        <v>115</v>
       </c>
       <c r="G68" t="s">
         <v>34</v>
@@ -8590,13 +8590,13 @@
         <v>9</v>
       </c>
       <c r="D71" t="s">
-        <v>113</v>
+        <v>175</v>
       </c>
       <c r="E71" t="s">
         <v>114</v>
       </c>
       <c r="F71" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
       <c r="G71" t="s">
         <v>20</v>
@@ -8659,13 +8659,13 @@
         <v>9</v>
       </c>
       <c r="D74" t="s">
-        <v>113</v>
+        <v>182</v>
       </c>
       <c r="E74" t="s">
         <v>114</v>
       </c>
       <c r="F74" t="s">
-        <v>182</v>
+        <v>115</v>
       </c>
       <c r="G74" t="s">
         <v>20</v>
@@ -8797,13 +8797,13 @@
         <v>9</v>
       </c>
       <c r="D80" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="E80" t="s">
         <v>114</v>
       </c>
       <c r="F80" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="G80" t="s">
         <v>34</v>
@@ -9096,13 +9096,13 @@
         <v>9</v>
       </c>
       <c r="D93" t="s">
-        <v>113</v>
+        <v>222</v>
       </c>
       <c r="E93" t="s">
         <v>114</v>
       </c>
       <c r="F93" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="G93" t="s">
         <v>20</v>
@@ -9142,13 +9142,13 @@
         <v>9</v>
       </c>
       <c r="D95" t="s">
-        <v>113</v>
+        <v>227</v>
       </c>
       <c r="E95" t="s">
         <v>114</v>
       </c>
       <c r="F95" t="s">
-        <v>227</v>
+        <v>115</v>
       </c>
       <c r="G95" t="s">
         <v>34</v>
@@ -9165,13 +9165,13 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>113</v>
+        <v>227</v>
       </c>
       <c r="E96" t="s">
         <v>114</v>
       </c>
       <c r="F96" t="s">
-        <v>227</v>
+        <v>115</v>
       </c>
       <c r="G96" t="s">
         <v>34</v>
@@ -9372,13 +9372,13 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="E105" t="s">
         <v>233</v>
       </c>
       <c r="F105" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="G105" t="s">
         <v>34</v>
@@ -9556,13 +9556,13 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="E113" t="s">
         <v>233</v>
       </c>
       <c r="F113" t="s">
-        <v>268</v>
+        <v>234</v>
       </c>
       <c r="G113" t="s">
         <v>34</v>
@@ -9628,10 +9628,10 @@
         <v>275</v>
       </c>
       <c r="E116" t="s">
-        <v>233</v>
+        <v>276</v>
       </c>
       <c r="F116" t="s">
-        <v>276</v>
+        <v>234</v>
       </c>
       <c r="G116" t="s">
         <v>20</v>
@@ -9651,10 +9651,10 @@
         <v>279</v>
       </c>
       <c r="E117" t="s">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="F117" t="s">
-        <v>280</v>
+        <v>234</v>
       </c>
       <c r="G117" t="s">
         <v>20</v>
@@ -9763,10 +9763,10 @@
         <v>9</v>
       </c>
       <c r="D122" t="s">
-        <v>279</v>
+        <v>232</v>
       </c>
       <c r="E122" t="s">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="F122" t="s">
         <v>234</v>
@@ -9786,10 +9786,10 @@
         <v>9</v>
       </c>
       <c r="D123" t="s">
-        <v>275</v>
+        <v>232</v>
       </c>
       <c r="E123" t="s">
-        <v>233</v>
+        <v>276</v>
       </c>
       <c r="F123" t="s">
         <v>234</v>
@@ -9996,10 +9996,10 @@
         <v>310</v>
       </c>
       <c r="E132" t="s">
-        <v>233</v>
+        <v>311</v>
       </c>
       <c r="F132" t="s">
-        <v>311</v>
+        <v>234</v>
       </c>
       <c r="G132" t="s">
         <v>16</v>
@@ -10039,13 +10039,13 @@
         <v>9</v>
       </c>
       <c r="D134" t="s">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="E134" t="s">
-        <v>233</v>
+        <v>276</v>
       </c>
       <c r="F134" t="s">
-        <v>316</v>
+        <v>234</v>
       </c>
       <c r="G134" t="s">
         <v>34</v>
@@ -10085,13 +10085,13 @@
         <v>9</v>
       </c>
       <c r="D136" t="s">
-        <v>275</v>
+        <v>321</v>
       </c>
       <c r="E136" t="s">
-        <v>233</v>
+        <v>276</v>
       </c>
       <c r="F136" t="s">
-        <v>321</v>
+        <v>234</v>
       </c>
       <c r="G136" t="s">
         <v>34</v>
@@ -10433,10 +10433,10 @@
         <v>355</v>
       </c>
       <c r="E151" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="F151" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="G151" t="s">
         <v>20</v>
@@ -10548,10 +10548,10 @@
         <v>367</v>
       </c>
       <c r="E156" t="s">
-        <v>339</v>
+        <v>368</v>
       </c>
       <c r="F156" t="s">
-        <v>368</v>
+        <v>340</v>
       </c>
       <c r="G156" t="s">
         <v>34</v>
@@ -10568,13 +10568,13 @@
         <v>185</v>
       </c>
       <c r="D157" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="E157" t="s">
         <v>339</v>
       </c>
       <c r="F157" t="s">
-        <v>368</v>
+        <v>340</v>
       </c>
       <c r="G157" t="s">
         <v>34</v>
@@ -10660,10 +10660,10 @@
         <v>9</v>
       </c>
       <c r="D161" t="s">
+        <v>338</v>
+      </c>
+      <c r="E161" t="s">
         <v>379</v>
-      </c>
-      <c r="E161" t="s">
-        <v>339</v>
       </c>
       <c r="F161" t="s">
         <v>340</v>
@@ -10755,10 +10755,10 @@
         <v>388</v>
       </c>
       <c r="E165" t="s">
-        <v>339</v>
+        <v>389</v>
       </c>
       <c r="F165" t="s">
-        <v>389</v>
+        <v>340</v>
       </c>
       <c r="G165" t="s">
         <v>34</v>
@@ -10801,10 +10801,10 @@
         <v>394</v>
       </c>
       <c r="E167" t="s">
-        <v>339</v>
+        <v>395</v>
       </c>
       <c r="F167" t="s">
-        <v>395</v>
+        <v>340</v>
       </c>
       <c r="G167" t="s">
         <v>34</v>
@@ -10936,13 +10936,13 @@
         <v>9</v>
       </c>
       <c r="D173" t="s">
-        <v>338</v>
+        <v>408</v>
       </c>
       <c r="E173" t="s">
         <v>339</v>
       </c>
       <c r="F173" t="s">
-        <v>408</v>
+        <v>340</v>
       </c>
       <c r="G173" t="s">
         <v>20</v>
@@ -10959,13 +10959,13 @@
         <v>185</v>
       </c>
       <c r="D174" t="s">
+        <v>408</v>
+      </c>
+      <c r="E174" t="s">
         <v>410</v>
       </c>
-      <c r="E174" t="s">
-        <v>339</v>
-      </c>
       <c r="F174" t="s">
-        <v>408</v>
+        <v>340</v>
       </c>
       <c r="G174" t="s">
         <v>20</v>
@@ -10985,10 +10985,10 @@
         <v>413</v>
       </c>
       <c r="E175" t="s">
-        <v>339</v>
+        <v>414</v>
       </c>
       <c r="F175" t="s">
-        <v>414</v>
+        <v>340</v>
       </c>
       <c r="G175" t="s">
         <v>20</v>
@@ -11166,13 +11166,13 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>338</v>
+        <v>431</v>
       </c>
       <c r="E183" t="s">
         <v>339</v>
       </c>
       <c r="F183" t="s">
-        <v>431</v>
+        <v>340</v>
       </c>
       <c r="G183" t="s">
         <v>20</v>
@@ -11281,13 +11281,13 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>338</v>
+        <v>442</v>
       </c>
       <c r="E188" t="s">
         <v>339</v>
       </c>
       <c r="F188" t="s">
-        <v>442</v>
+        <v>340</v>
       </c>
       <c r="G188" t="s">
         <v>34</v>
@@ -11327,13 +11327,13 @@
         <v>9</v>
       </c>
       <c r="D190" t="s">
+        <v>442</v>
+      </c>
+      <c r="E190" t="s">
         <v>447</v>
       </c>
-      <c r="E190" t="s">
-        <v>339</v>
-      </c>
       <c r="F190" t="s">
-        <v>442</v>
+        <v>340</v>
       </c>
       <c r="G190" t="s">
         <v>16</v>
@@ -11419,13 +11419,13 @@
         <v>9</v>
       </c>
       <c r="D194" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E194" t="s">
         <v>455</v>
       </c>
       <c r="F194" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G194" t="s">
         <v>25</v>
@@ -11442,13 +11442,13 @@
         <v>9</v>
       </c>
       <c r="D195" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E195" t="s">
         <v>455</v>
       </c>
       <c r="F195" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G195" t="s">
         <v>16</v>
@@ -11465,13 +11465,13 @@
         <v>9</v>
       </c>
       <c r="D196" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E196" t="s">
         <v>455</v>
       </c>
       <c r="F196" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G196" t="s">
         <v>25</v>
@@ -11488,13 +11488,13 @@
         <v>9</v>
       </c>
       <c r="D197" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E197" t="s">
         <v>455</v>
       </c>
       <c r="F197" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G197" t="s">
         <v>25</v>
@@ -11511,13 +11511,13 @@
         <v>9</v>
       </c>
       <c r="D198" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E198" t="s">
         <v>455</v>
       </c>
       <c r="F198" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G198" t="s">
         <v>16</v>
@@ -11534,13 +11534,13 @@
         <v>9</v>
       </c>
       <c r="D199" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E199" t="s">
         <v>455</v>
       </c>
       <c r="F199" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G199" t="s">
         <v>25</v>
@@ -11557,13 +11557,13 @@
         <v>9</v>
       </c>
       <c r="D200" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E200" t="s">
         <v>455</v>
       </c>
       <c r="F200" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G200" t="s">
         <v>25</v>
@@ -11580,13 +11580,13 @@
         <v>9</v>
       </c>
       <c r="D201" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E201" t="s">
         <v>455</v>
       </c>
       <c r="F201" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G201" t="s">
         <v>25</v>
@@ -11603,13 +11603,13 @@
         <v>9</v>
       </c>
       <c r="D202" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E202" t="s">
         <v>455</v>
       </c>
       <c r="F202" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G202" t="s">
         <v>25</v>
@@ -11626,13 +11626,13 @@
         <v>9</v>
       </c>
       <c r="D203" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E203" t="s">
         <v>455</v>
       </c>
       <c r="F203" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G203" t="s">
         <v>25</v>
@@ -11649,13 +11649,13 @@
         <v>9</v>
       </c>
       <c r="D204" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E204" t="s">
         <v>455</v>
       </c>
       <c r="F204" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G204" t="s">
         <v>16</v>
@@ -11672,13 +11672,13 @@
         <v>9</v>
       </c>
       <c r="D205" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="E205" t="s">
         <v>455</v>
       </c>
       <c r="F205" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G205" t="s">
         <v>25</v>
@@ -11695,13 +11695,13 @@
         <v>185</v>
       </c>
       <c r="D206" t="s">
-        <v>338</v>
+        <v>482</v>
       </c>
       <c r="E206" t="s">
-        <v>455</v>
+        <v>339</v>
       </c>
       <c r="F206" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G206" t="s">
         <v>25</v>
@@ -11721,10 +11721,10 @@
         <v>487</v>
       </c>
       <c r="E207" t="s">
-        <v>455</v>
+        <v>488</v>
       </c>
       <c r="F207" t="s">
-        <v>488</v>
+        <v>456</v>
       </c>
       <c r="G207" t="s">
         <v>34</v>
@@ -11741,13 +11741,13 @@
         <v>9</v>
       </c>
       <c r="D208" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E208" t="s">
         <v>455</v>
       </c>
       <c r="F208" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G208" t="s">
         <v>25</v>
@@ -11764,13 +11764,13 @@
         <v>9</v>
       </c>
       <c r="D209" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="E209" t="s">
         <v>455</v>
       </c>
       <c r="F209" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G209" t="s">
         <v>25</v>
@@ -11787,13 +11787,13 @@
         <v>185</v>
       </c>
       <c r="D210" t="s">
-        <v>338</v>
+        <v>482</v>
       </c>
       <c r="E210" t="s">
-        <v>455</v>
+        <v>339</v>
       </c>
       <c r="F210" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G210" t="s">
         <v>25</v>
@@ -11813,10 +11813,10 @@
         <v>497</v>
       </c>
       <c r="E211" t="s">
-        <v>455</v>
+        <v>498</v>
       </c>
       <c r="F211" t="s">
-        <v>498</v>
+        <v>456</v>
       </c>
       <c r="G211" t="s">
         <v>34</v>
@@ -11833,13 +11833,13 @@
         <v>9</v>
       </c>
       <c r="D212" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E212" t="s">
         <v>455</v>
       </c>
       <c r="F212" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G212" t="s">
         <v>25</v>
@@ -11859,10 +11859,10 @@
         <v>503</v>
       </c>
       <c r="E213" t="s">
-        <v>455</v>
+        <v>504</v>
       </c>
       <c r="F213" t="s">
-        <v>504</v>
+        <v>456</v>
       </c>
       <c r="G213" t="s">
         <v>34</v>
@@ -11879,13 +11879,13 @@
         <v>9</v>
       </c>
       <c r="D214" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="E214" t="s">
         <v>455</v>
       </c>
       <c r="F214" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G214" t="s">
         <v>25</v>
@@ -11902,13 +11902,13 @@
         <v>185</v>
       </c>
       <c r="D215" t="s">
-        <v>338</v>
+        <v>482</v>
       </c>
       <c r="E215" t="s">
-        <v>455</v>
+        <v>339</v>
       </c>
       <c r="F215" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G215" t="s">
         <v>25</v>
@@ -11925,13 +11925,13 @@
         <v>9</v>
       </c>
       <c r="D216" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E216" t="s">
         <v>455</v>
       </c>
       <c r="F216" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G216" t="s">
         <v>25</v>
@@ -11948,13 +11948,13 @@
         <v>9</v>
       </c>
       <c r="D217" t="s">
-        <v>454</v>
+        <v>513</v>
       </c>
       <c r="E217" t="s">
         <v>455</v>
       </c>
       <c r="F217" t="s">
-        <v>513</v>
+        <v>456</v>
       </c>
       <c r="G217" t="s">
         <v>34</v>
@@ -11974,10 +11974,10 @@
         <v>516</v>
       </c>
       <c r="E218" t="s">
-        <v>455</v>
+        <v>517</v>
       </c>
       <c r="F218" t="s">
-        <v>517</v>
+        <v>456</v>
       </c>
       <c r="G218" t="s">
         <v>20</v>
@@ -11994,13 +11994,13 @@
         <v>9</v>
       </c>
       <c r="D219" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E219" t="s">
         <v>455</v>
       </c>
       <c r="F219" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G219" t="s">
         <v>25</v>
@@ -12017,13 +12017,13 @@
         <v>185</v>
       </c>
       <c r="D220" t="s">
-        <v>388</v>
+        <v>459</v>
       </c>
       <c r="E220" t="s">
-        <v>455</v>
+        <v>389</v>
       </c>
       <c r="F220" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G220" t="s">
         <v>34</v>
@@ -12040,13 +12040,13 @@
         <v>9</v>
       </c>
       <c r="D221" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E221" t="s">
         <v>455</v>
       </c>
       <c r="F221" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G221" t="s">
         <v>34</v>
@@ -12063,13 +12063,13 @@
         <v>9</v>
       </c>
       <c r="D222" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E222" t="s">
         <v>455</v>
       </c>
       <c r="F222" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G222" t="s">
         <v>25</v>
@@ -12086,13 +12086,13 @@
         <v>9</v>
       </c>
       <c r="D223" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E223" t="s">
         <v>455</v>
       </c>
       <c r="F223" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G223" t="s">
         <v>25</v>
@@ -12109,13 +12109,13 @@
         <v>9</v>
       </c>
       <c r="D224" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E224" t="s">
         <v>455</v>
       </c>
       <c r="F224" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G224" t="s">
         <v>25</v>
@@ -12132,13 +12132,13 @@
         <v>9</v>
       </c>
       <c r="D225" t="s">
-        <v>454</v>
+        <v>532</v>
       </c>
       <c r="E225" t="s">
         <v>455</v>
       </c>
       <c r="F225" t="s">
-        <v>532</v>
+        <v>456</v>
       </c>
       <c r="G225" t="s">
         <v>20</v>
@@ -12155,13 +12155,13 @@
         <v>9</v>
       </c>
       <c r="D226" t="s">
-        <v>454</v>
+        <v>535</v>
       </c>
       <c r="E226" t="s">
         <v>455</v>
       </c>
       <c r="F226" t="s">
-        <v>535</v>
+        <v>456</v>
       </c>
       <c r="G226" t="s">
         <v>20</v>
@@ -12178,13 +12178,13 @@
         <v>9</v>
       </c>
       <c r="D227" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E227" t="s">
         <v>455</v>
       </c>
       <c r="F227" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G227" t="s">
         <v>25</v>
@@ -12201,13 +12201,13 @@
         <v>9</v>
       </c>
       <c r="D228" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E228" t="s">
         <v>455</v>
       </c>
       <c r="F228" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G228" t="s">
         <v>25</v>
@@ -12224,13 +12224,13 @@
         <v>9</v>
       </c>
       <c r="D229" t="s">
-        <v>454</v>
+        <v>535</v>
       </c>
       <c r="E229" t="s">
         <v>455</v>
       </c>
       <c r="F229" t="s">
-        <v>535</v>
+        <v>456</v>
       </c>
       <c r="G229" t="s">
         <v>34</v>
@@ -12247,13 +12247,13 @@
         <v>185</v>
       </c>
       <c r="D230" t="s">
-        <v>454</v>
+        <v>535</v>
       </c>
       <c r="E230" t="s">
         <v>455</v>
       </c>
       <c r="F230" t="s">
-        <v>535</v>
+        <v>456</v>
       </c>
       <c r="G230" t="s">
         <v>20</v>
@@ -12270,13 +12270,13 @@
         <v>9</v>
       </c>
       <c r="D231" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E231" t="s">
         <v>455</v>
       </c>
       <c r="F231" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G231" t="s">
         <v>25</v>
@@ -12293,13 +12293,13 @@
         <v>9</v>
       </c>
       <c r="D232" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E232" t="s">
         <v>455</v>
       </c>
       <c r="F232" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G232" t="s">
         <v>25</v>
@@ -12316,13 +12316,13 @@
         <v>9</v>
       </c>
       <c r="D233" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E233" t="s">
         <v>455</v>
       </c>
       <c r="F233" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G233" t="s">
         <v>16</v>
@@ -12339,13 +12339,13 @@
         <v>9</v>
       </c>
       <c r="D234" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E234" t="s">
         <v>455</v>
       </c>
       <c r="F234" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G234" t="s">
         <v>16</v>
@@ -12362,13 +12362,13 @@
         <v>9</v>
       </c>
       <c r="D235" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E235" t="s">
         <v>455</v>
       </c>
       <c r="F235" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G235" t="s">
         <v>25</v>
@@ -12385,13 +12385,13 @@
         <v>9</v>
       </c>
       <c r="D236" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E236" t="s">
         <v>455</v>
       </c>
       <c r="F236" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G236" t="s">
         <v>25</v>
@@ -12408,13 +12408,13 @@
         <v>9</v>
       </c>
       <c r="D237" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E237" t="s">
         <v>455</v>
       </c>
       <c r="F237" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G237" t="s">
         <v>16</v>
@@ -12431,13 +12431,13 @@
         <v>9</v>
       </c>
       <c r="D238" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E238" t="s">
         <v>455</v>
       </c>
       <c r="F238" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G238" t="s">
         <v>25</v>
@@ -12454,13 +12454,13 @@
         <v>9</v>
       </c>
       <c r="D239" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E239" t="s">
         <v>455</v>
       </c>
       <c r="F239" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G239" t="s">
         <v>25</v>
@@ -12477,13 +12477,13 @@
         <v>9</v>
       </c>
       <c r="D240" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E240" t="s">
         <v>455</v>
       </c>
       <c r="F240" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G240" t="s">
         <v>16</v>
@@ -12500,13 +12500,13 @@
         <v>9</v>
       </c>
       <c r="D241" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E241" t="s">
         <v>455</v>
       </c>
       <c r="F241" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G241" t="s">
         <v>25</v>
@@ -12523,13 +12523,13 @@
         <v>9</v>
       </c>
       <c r="D242" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E242" t="s">
         <v>455</v>
       </c>
       <c r="F242" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G242" t="s">
         <v>25</v>
@@ -12546,13 +12546,13 @@
         <v>9</v>
       </c>
       <c r="D243" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E243" t="s">
         <v>455</v>
       </c>
       <c r="F243" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G243" t="s">
         <v>25</v>
@@ -12569,13 +12569,13 @@
         <v>9</v>
       </c>
       <c r="D244" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E244" t="s">
         <v>455</v>
       </c>
       <c r="F244" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G244" t="s">
         <v>25</v>
@@ -12615,13 +12615,13 @@
         <v>9</v>
       </c>
       <c r="D246" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E246" t="s">
         <v>574</v>
       </c>
       <c r="F246" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G246" t="s">
         <v>20</v>
@@ -12661,13 +12661,13 @@
         <v>9</v>
       </c>
       <c r="D248" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E248" t="s">
         <v>574</v>
       </c>
       <c r="F248" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G248" t="s">
         <v>20</v>
@@ -12753,13 +12753,13 @@
         <v>9</v>
       </c>
       <c r="D252" t="s">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="E252" t="s">
         <v>574</v>
       </c>
       <c r="F252" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="G252" t="s">
         <v>20</v>
@@ -12799,13 +12799,13 @@
         <v>9</v>
       </c>
       <c r="D254" t="s">
+        <v>596</v>
+      </c>
+      <c r="E254" t="s">
         <v>459</v>
       </c>
-      <c r="E254" t="s">
-        <v>574</v>
-      </c>
       <c r="F254" t="s">
-        <v>596</v>
+        <v>575</v>
       </c>
       <c r="G254" t="s">
         <v>25</v>
@@ -12868,13 +12868,13 @@
         <v>9</v>
       </c>
       <c r="D257" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E257" t="s">
         <v>574</v>
       </c>
       <c r="F257" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G257" t="s">
         <v>20</v>
@@ -12891,13 +12891,13 @@
         <v>9</v>
       </c>
       <c r="D258" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E258" t="s">
         <v>574</v>
       </c>
       <c r="F258" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G258" t="s">
         <v>20</v>
@@ -12914,13 +12914,13 @@
         <v>185</v>
       </c>
       <c r="D259" t="s">
-        <v>573</v>
+        <v>607</v>
       </c>
       <c r="E259" t="s">
         <v>574</v>
       </c>
       <c r="F259" t="s">
-        <v>607</v>
+        <v>575</v>
       </c>
       <c r="G259" t="s">
         <v>25</v>
@@ -12986,10 +12986,10 @@
         <v>614</v>
       </c>
       <c r="E262" t="s">
-        <v>574</v>
+        <v>615</v>
       </c>
       <c r="F262" t="s">
-        <v>615</v>
+        <v>575</v>
       </c>
       <c r="G262" t="s">
         <v>34</v>
@@ -13006,13 +13006,13 @@
         <v>9</v>
       </c>
       <c r="D263" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E263" t="s">
         <v>574</v>
       </c>
       <c r="F263" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G263" t="s">
         <v>20</v>
@@ -13029,13 +13029,13 @@
         <v>185</v>
       </c>
       <c r="D264" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E264" t="s">
         <v>574</v>
       </c>
       <c r="F264" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G264" t="s">
         <v>20</v>
@@ -13075,13 +13075,13 @@
         <v>9</v>
       </c>
       <c r="D266" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E266" t="s">
         <v>574</v>
       </c>
       <c r="F266" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G266" t="s">
         <v>20</v>
@@ -13121,13 +13121,13 @@
         <v>9</v>
       </c>
       <c r="D268" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E268" t="s">
         <v>574</v>
       </c>
       <c r="F268" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G268" t="s">
         <v>20</v>
@@ -13144,13 +13144,13 @@
         <v>9</v>
       </c>
       <c r="D269" t="s">
-        <v>573</v>
+        <v>607</v>
       </c>
       <c r="E269" t="s">
         <v>574</v>
       </c>
       <c r="F269" t="s">
-        <v>607</v>
+        <v>575</v>
       </c>
       <c r="G269" t="s">
         <v>20</v>
@@ -13167,13 +13167,13 @@
         <v>185</v>
       </c>
       <c r="D270" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E270" t="s">
         <v>574</v>
       </c>
       <c r="F270" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G270" t="s">
         <v>20</v>
@@ -13190,13 +13190,13 @@
         <v>9</v>
       </c>
       <c r="D271" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E271" t="s">
         <v>574</v>
       </c>
       <c r="F271" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G271" t="s">
         <v>20</v>
@@ -13236,13 +13236,13 @@
         <v>9</v>
       </c>
       <c r="D273" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E273" t="s">
         <v>574</v>
       </c>
       <c r="F273" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G273" t="s">
         <v>20</v>
@@ -13282,13 +13282,13 @@
         <v>9</v>
       </c>
       <c r="D275" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E275" t="s">
         <v>574</v>
       </c>
       <c r="F275" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G275" t="s">
         <v>20</v>
@@ -13305,13 +13305,13 @@
         <v>9</v>
       </c>
       <c r="D276" t="s">
-        <v>573</v>
+        <v>644</v>
       </c>
       <c r="E276" t="s">
         <v>574</v>
       </c>
       <c r="F276" t="s">
-        <v>644</v>
+        <v>575</v>
       </c>
       <c r="G276" t="s">
         <v>20</v>
@@ -13331,10 +13331,10 @@
         <v>647</v>
       </c>
       <c r="E277" t="s">
-        <v>574</v>
+        <v>648</v>
       </c>
       <c r="F277" t="s">
-        <v>648</v>
+        <v>575</v>
       </c>
       <c r="G277" t="s">
         <v>34</v>
@@ -13351,13 +13351,13 @@
         <v>9</v>
       </c>
       <c r="D278" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E278" t="s">
         <v>574</v>
       </c>
       <c r="F278" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G278" t="s">
         <v>20</v>
@@ -13377,10 +13377,10 @@
         <v>653</v>
       </c>
       <c r="E279" t="s">
-        <v>574</v>
+        <v>654</v>
       </c>
       <c r="F279" t="s">
-        <v>654</v>
+        <v>575</v>
       </c>
       <c r="G279" t="s">
         <v>34</v>
@@ -13397,13 +13397,13 @@
         <v>9</v>
       </c>
       <c r="D280" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E280" t="s">
         <v>574</v>
       </c>
       <c r="F280" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G280" t="s">
         <v>20</v>
@@ -13466,13 +13466,13 @@
         <v>9</v>
       </c>
       <c r="D283" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E283" t="s">
         <v>574</v>
       </c>
       <c r="F283" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G283" t="s">
         <v>20</v>
@@ -13581,13 +13581,13 @@
         <v>9</v>
       </c>
       <c r="D288" t="s">
-        <v>573</v>
+        <v>644</v>
       </c>
       <c r="E288" t="s">
         <v>574</v>
       </c>
       <c r="F288" t="s">
-        <v>644</v>
+        <v>575</v>
       </c>
       <c r="G288" t="s">
         <v>20</v>
@@ -13604,13 +13604,13 @@
         <v>9</v>
       </c>
       <c r="D289" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E289" t="s">
         <v>574</v>
       </c>
       <c r="F289" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G289" t="s">
         <v>20</v>
@@ -13673,13 +13673,13 @@
         <v>9</v>
       </c>
       <c r="D292" t="s">
-        <v>573</v>
+        <v>644</v>
       </c>
       <c r="E292" t="s">
         <v>574</v>
       </c>
       <c r="F292" t="s">
-        <v>644</v>
+        <v>575</v>
       </c>
       <c r="G292" t="s">
         <v>20</v>
@@ -13696,13 +13696,13 @@
         <v>9</v>
       </c>
       <c r="D293" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E293" t="s">
         <v>574</v>
       </c>
       <c r="F293" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G293" t="s">
         <v>20</v>
@@ -13857,13 +13857,13 @@
         <v>9</v>
       </c>
       <c r="D300" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E300" t="s">
         <v>574</v>
       </c>
       <c r="F300" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G300" t="s">
         <v>20</v>
@@ -13880,13 +13880,13 @@
         <v>9</v>
       </c>
       <c r="D301" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E301" t="s">
         <v>574</v>
       </c>
       <c r="F301" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G301" t="s">
         <v>20</v>
@@ -13903,13 +13903,13 @@
         <v>9</v>
       </c>
       <c r="D302" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E302" t="s">
         <v>574</v>
       </c>
       <c r="F302" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G302" t="s">
         <v>20</v>
@@ -13949,13 +13949,13 @@
         <v>9</v>
       </c>
       <c r="D304" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E304" t="s">
         <v>574</v>
       </c>
       <c r="F304" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G304" t="s">
         <v>20</v>
@@ -14018,13 +14018,13 @@
         <v>9</v>
       </c>
       <c r="D307" t="s">
-        <v>614</v>
+        <v>711</v>
       </c>
       <c r="E307" t="s">
-        <v>574</v>
+        <v>615</v>
       </c>
       <c r="F307" t="s">
-        <v>711</v>
+        <v>575</v>
       </c>
       <c r="G307" t="s">
         <v>20</v>
@@ -14041,13 +14041,13 @@
         <v>9</v>
       </c>
       <c r="D308" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E308" t="s">
         <v>574</v>
       </c>
       <c r="F308" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G308" t="s">
         <v>20</v>
@@ -14386,13 +14386,13 @@
         <v>9</v>
       </c>
       <c r="D323" t="s">
-        <v>718</v>
+        <v>747</v>
       </c>
       <c r="E323" t="s">
         <v>719</v>
       </c>
       <c r="F323" t="s">
-        <v>747</v>
+        <v>720</v>
       </c>
       <c r="G323" t="s">
         <v>20</v>
@@ -14432,10 +14432,10 @@
         <v>9</v>
       </c>
       <c r="D325" t="s">
+        <v>718</v>
+      </c>
+      <c r="E325" t="s">
         <v>752</v>
-      </c>
-      <c r="E325" t="s">
-        <v>719</v>
       </c>
       <c r="F325" t="s">
         <v>720</v>
@@ -14570,10 +14570,10 @@
         <v>9</v>
       </c>
       <c r="D331" t="s">
+        <v>718</v>
+      </c>
+      <c r="E331" t="s">
         <v>765</v>
-      </c>
-      <c r="E331" t="s">
-        <v>719</v>
       </c>
       <c r="F331" t="s">
         <v>720</v>
@@ -14849,10 +14849,10 @@
         <v>790</v>
       </c>
       <c r="E343" t="s">
-        <v>719</v>
+        <v>791</v>
       </c>
       <c r="F343" t="s">
-        <v>791</v>
+        <v>720</v>
       </c>
       <c r="G343" t="s">
         <v>34</v>
@@ -14869,13 +14869,13 @@
         <v>185</v>
       </c>
       <c r="D344" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="E344" t="s">
-        <v>719</v>
+        <v>791</v>
       </c>
       <c r="F344" t="s">
-        <v>794</v>
+        <v>720</v>
       </c>
       <c r="G344" t="s">
         <v>34</v>
@@ -14915,13 +14915,13 @@
         <v>185</v>
       </c>
       <c r="D346" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="E346" t="s">
         <v>798</v>
       </c>
       <c r="F346" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="G346" t="s">
         <v>20</v>
@@ -15145,13 +15145,13 @@
         <v>9</v>
       </c>
       <c r="D356" t="s">
-        <v>797</v>
+        <v>823</v>
       </c>
       <c r="E356" t="s">
         <v>798</v>
       </c>
       <c r="F356" t="s">
-        <v>823</v>
+        <v>799</v>
       </c>
       <c r="G356" t="s">
         <v>20</v>
@@ -15375,13 +15375,13 @@
         <v>9</v>
       </c>
       <c r="D366" t="s">
-        <v>797</v>
+        <v>844</v>
       </c>
       <c r="E366" t="s">
         <v>798</v>
       </c>
       <c r="F366" t="s">
-        <v>844</v>
+        <v>799</v>
       </c>
       <c r="G366" t="s">
         <v>20</v>
@@ -15398,13 +15398,13 @@
         <v>9</v>
       </c>
       <c r="D367" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="E367" t="s">
         <v>798</v>
       </c>
       <c r="F367" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="G367" t="s">
         <v>16</v>
@@ -15490,10 +15490,10 @@
         <v>9</v>
       </c>
       <c r="D371" t="s">
+        <v>797</v>
+      </c>
+      <c r="E371" t="s">
         <v>855</v>
-      </c>
-      <c r="E371" t="s">
-        <v>798</v>
       </c>
       <c r="F371" t="s">
         <v>799</v>
@@ -15516,10 +15516,10 @@
         <v>858</v>
       </c>
       <c r="E372" t="s">
-        <v>798</v>
+        <v>859</v>
       </c>
       <c r="F372" t="s">
-        <v>859</v>
+        <v>799</v>
       </c>
       <c r="G372" t="s">
         <v>25</v>
@@ -15562,10 +15562,10 @@
         <v>858</v>
       </c>
       <c r="E374" t="s">
-        <v>798</v>
+        <v>859</v>
       </c>
       <c r="F374" t="s">
-        <v>859</v>
+        <v>799</v>
       </c>
       <c r="G374" t="s">
         <v>25</v>
@@ -15697,13 +15697,13 @@
         <v>9</v>
       </c>
       <c r="D380" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="E380" t="s">
         <v>873</v>
       </c>
       <c r="F380" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="G380" t="s">
         <v>16</v>
@@ -15835,13 +15835,13 @@
         <v>9</v>
       </c>
       <c r="D386" t="s">
-        <v>872</v>
+        <v>892</v>
       </c>
       <c r="E386" t="s">
         <v>873</v>
       </c>
       <c r="F386" t="s">
-        <v>892</v>
+        <v>874</v>
       </c>
       <c r="G386" t="s">
         <v>20</v>
@@ -15858,13 +15858,13 @@
         <v>9</v>
       </c>
       <c r="D387" t="s">
-        <v>872</v>
+        <v>895</v>
       </c>
       <c r="E387" t="s">
         <v>873</v>
       </c>
       <c r="F387" t="s">
-        <v>895</v>
+        <v>874</v>
       </c>
       <c r="G387" t="s">
         <v>25</v>
@@ -15907,10 +15907,10 @@
         <v>900</v>
       </c>
       <c r="E389" t="s">
-        <v>873</v>
+        <v>901</v>
       </c>
       <c r="F389" t="s">
-        <v>901</v>
+        <v>874</v>
       </c>
       <c r="G389" t="s">
         <v>34</v>
@@ -15996,13 +15996,13 @@
         <v>9</v>
       </c>
       <c r="D393" t="s">
-        <v>872</v>
+        <v>910</v>
       </c>
       <c r="E393" t="s">
         <v>873</v>
       </c>
       <c r="F393" t="s">
-        <v>910</v>
+        <v>874</v>
       </c>
       <c r="G393" t="s">
         <v>20</v>
@@ -16045,10 +16045,10 @@
         <v>915</v>
       </c>
       <c r="E395" t="s">
-        <v>873</v>
+        <v>916</v>
       </c>
       <c r="F395" t="s">
-        <v>916</v>
+        <v>874</v>
       </c>
       <c r="G395" t="s">
         <v>34</v>
@@ -16091,10 +16091,10 @@
         <v>921</v>
       </c>
       <c r="E397" t="s">
-        <v>873</v>
+        <v>922</v>
       </c>
       <c r="F397" t="s">
-        <v>922</v>
+        <v>874</v>
       </c>
       <c r="G397" t="s">
         <v>34</v>
@@ -16160,10 +16160,10 @@
         <v>929</v>
       </c>
       <c r="E400" t="s">
-        <v>873</v>
+        <v>930</v>
       </c>
       <c r="F400" t="s">
-        <v>930</v>
+        <v>874</v>
       </c>
       <c r="G400" t="s">
         <v>34</v>
@@ -16298,10 +16298,10 @@
         <v>943</v>
       </c>
       <c r="E406" t="s">
-        <v>873</v>
+        <v>944</v>
       </c>
       <c r="F406" t="s">
-        <v>944</v>
+        <v>874</v>
       </c>
       <c r="G406" t="s">
         <v>34</v>
@@ -16318,13 +16318,13 @@
         <v>9</v>
       </c>
       <c r="D407" t="s">
-        <v>872</v>
+        <v>947</v>
       </c>
       <c r="E407" t="s">
         <v>873</v>
       </c>
       <c r="F407" t="s">
-        <v>947</v>
+        <v>874</v>
       </c>
       <c r="G407" t="s">
         <v>25</v>
@@ -16594,13 +16594,13 @@
         <v>9</v>
       </c>
       <c r="D419" t="s">
-        <v>968</v>
+        <v>975</v>
       </c>
       <c r="E419" t="s">
         <v>969</v>
       </c>
       <c r="F419" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="G419" t="s">
         <v>34</v>
@@ -16640,13 +16640,13 @@
         <v>9</v>
       </c>
       <c r="D421" t="s">
-        <v>968</v>
+        <v>980</v>
       </c>
       <c r="E421" t="s">
         <v>969</v>
       </c>
       <c r="F421" t="s">
-        <v>980</v>
+        <v>970</v>
       </c>
       <c r="G421" t="s">
         <v>25</v>
@@ -16804,10 +16804,10 @@
         <v>995</v>
       </c>
       <c r="E428" t="s">
-        <v>969</v>
+        <v>996</v>
       </c>
       <c r="F428" t="s">
-        <v>996</v>
+        <v>970</v>
       </c>
       <c r="G428" t="s">
         <v>34</v>
@@ -16827,10 +16827,10 @@
         <v>999</v>
       </c>
       <c r="E429" t="s">
-        <v>969</v>
+        <v>1000</v>
       </c>
       <c r="F429" t="s">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="G429" t="s">
         <v>34</v>
@@ -16916,13 +16916,13 @@
         <v>9</v>
       </c>
       <c r="D433" t="s">
-        <v>968</v>
+        <v>1009</v>
       </c>
       <c r="E433" t="s">
         <v>969</v>
       </c>
       <c r="F433" t="s">
-        <v>1009</v>
+        <v>970</v>
       </c>
       <c r="G433" t="s">
         <v>34</v>
@@ -16985,13 +16985,13 @@
         <v>9</v>
       </c>
       <c r="D436" t="s">
-        <v>968</v>
+        <v>1016</v>
       </c>
       <c r="E436" t="s">
         <v>969</v>
       </c>
       <c r="F436" t="s">
-        <v>1016</v>
+        <v>970</v>
       </c>
       <c r="G436" t="s">
         <v>34</v>
@@ -17008,13 +17008,13 @@
         <v>9</v>
       </c>
       <c r="D437" t="s">
-        <v>968</v>
+        <v>1019</v>
       </c>
       <c r="E437" t="s">
         <v>969</v>
       </c>
       <c r="F437" t="s">
-        <v>1019</v>
+        <v>970</v>
       </c>
       <c r="G437" t="s">
         <v>25</v>
@@ -17080,10 +17080,10 @@
         <v>1026</v>
       </c>
       <c r="E440" t="s">
-        <v>969</v>
+        <v>1027</v>
       </c>
       <c r="F440" t="s">
-        <v>1027</v>
+        <v>970</v>
       </c>
       <c r="G440" t="s">
         <v>34</v>
@@ -17402,10 +17402,10 @@
         <v>1056</v>
       </c>
       <c r="E454" t="s">
-        <v>969</v>
+        <v>1057</v>
       </c>
       <c r="F454" t="s">
-        <v>1057</v>
+        <v>970</v>
       </c>
       <c r="G454" t="s">
         <v>25</v>
@@ -17632,10 +17632,10 @@
         <v>1082</v>
       </c>
       <c r="E464" t="s">
-        <v>1061</v>
+        <v>1083</v>
       </c>
       <c r="F464" t="s">
-        <v>1083</v>
+        <v>1062</v>
       </c>
       <c r="G464" t="s">
         <v>34</v>
@@ -17652,13 +17652,13 @@
         <v>9</v>
       </c>
       <c r="D465" t="s">
-        <v>1060</v>
+        <v>1086</v>
       </c>
       <c r="E465" t="s">
         <v>1061</v>
       </c>
       <c r="F465" t="s">
-        <v>1086</v>
+        <v>1062</v>
       </c>
       <c r="G465" t="s">
         <v>34</v>
@@ -17675,13 +17675,13 @@
         <v>9</v>
       </c>
       <c r="D466" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="E466" t="s">
-        <v>1061</v>
+        <v>1083</v>
       </c>
       <c r="F466" t="s">
-        <v>1089</v>
+        <v>1062</v>
       </c>
       <c r="G466" t="s">
         <v>34</v>
@@ -17701,10 +17701,10 @@
         <v>1092</v>
       </c>
       <c r="E467" t="s">
-        <v>1061</v>
+        <v>1093</v>
       </c>
       <c r="F467" t="s">
-        <v>1093</v>
+        <v>1062</v>
       </c>
       <c r="G467" t="s">
         <v>34</v>
@@ -17747,10 +17747,10 @@
         <v>1098</v>
       </c>
       <c r="E469" t="s">
-        <v>1061</v>
+        <v>1099</v>
       </c>
       <c r="F469" t="s">
-        <v>1099</v>
+        <v>1062</v>
       </c>
       <c r="G469" t="s">
         <v>34</v>
@@ -17836,13 +17836,13 @@
         <v>9</v>
       </c>
       <c r="D473" t="s">
-        <v>1082</v>
+        <v>1108</v>
       </c>
       <c r="E473" t="s">
-        <v>1061</v>
+        <v>1083</v>
       </c>
       <c r="F473" t="s">
-        <v>1108</v>
+        <v>1062</v>
       </c>
       <c r="G473" t="s">
         <v>34</v>
@@ -18181,13 +18181,13 @@
         <v>9</v>
       </c>
       <c r="D488" t="s">
-        <v>1137</v>
+        <v>1142</v>
       </c>
       <c r="E488" t="s">
         <v>1138</v>
       </c>
       <c r="F488" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="G488" t="s">
         <v>1063</v>
@@ -18273,10 +18273,10 @@
         <v>185</v>
       </c>
       <c r="D492" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E492" t="s">
         <v>1151</v>
-      </c>
-      <c r="E492" t="s">
-        <v>1138</v>
       </c>
       <c r="F492" t="s">
         <v>1139</v>
@@ -18319,13 +18319,13 @@
         <v>9</v>
       </c>
       <c r="D494" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E494" t="s">
         <v>1156</v>
       </c>
-      <c r="E494" t="s">
-        <v>1138</v>
-      </c>
       <c r="F494" t="s">
-        <v>1099</v>
+        <v>1139</v>
       </c>
       <c r="G494" t="s">
         <v>16</v>
@@ -18342,13 +18342,13 @@
         <v>185</v>
       </c>
       <c r="D495" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E495" t="s">
         <v>1156</v>
       </c>
-      <c r="E495" t="s">
-        <v>1138</v>
-      </c>
       <c r="F495" t="s">
-        <v>1099</v>
+        <v>1139</v>
       </c>
       <c r="G495" t="s">
         <v>20</v>
@@ -18411,13 +18411,13 @@
         <v>9</v>
       </c>
       <c r="D498" t="s">
-        <v>1137</v>
+        <v>1165</v>
       </c>
       <c r="E498" t="s">
         <v>1138</v>
       </c>
       <c r="F498" t="s">
-        <v>1165</v>
+        <v>1139</v>
       </c>
       <c r="G498" t="s">
         <v>1063</v>
@@ -18503,13 +18503,13 @@
         <v>185</v>
       </c>
       <c r="D502" t="s">
-        <v>1137</v>
+        <v>1174</v>
       </c>
       <c r="E502" t="s">
         <v>1138</v>
       </c>
       <c r="F502" t="s">
-        <v>1174</v>
+        <v>1139</v>
       </c>
       <c r="G502" t="s">
         <v>25</v>
@@ -18621,10 +18621,10 @@
         <v>1185</v>
       </c>
       <c r="E507" t="s">
-        <v>1138</v>
+        <v>1186</v>
       </c>
       <c r="F507" t="s">
-        <v>1186</v>
+        <v>1139</v>
       </c>
       <c r="G507" t="s">
         <v>34</v>
@@ -18644,10 +18644,10 @@
         <v>1189</v>
       </c>
       <c r="E508" t="s">
-        <v>1138</v>
+        <v>1190</v>
       </c>
       <c r="F508" t="s">
-        <v>1190</v>
+        <v>1139</v>
       </c>
       <c r="G508" t="s">
         <v>1063</v>
@@ -18664,13 +18664,13 @@
         <v>185</v>
       </c>
       <c r="D509" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E509" t="s">
         <v>1193</v>
       </c>
-      <c r="E509" t="s">
-        <v>1138</v>
-      </c>
       <c r="F509" t="s">
-        <v>1190</v>
+        <v>1139</v>
       </c>
       <c r="G509" t="s">
         <v>25</v>
@@ -18690,10 +18690,10 @@
         <v>1196</v>
       </c>
       <c r="E510" t="s">
-        <v>1138</v>
+        <v>1197</v>
       </c>
       <c r="F510" t="s">
-        <v>1197</v>
+        <v>1139</v>
       </c>
       <c r="G510" t="s">
         <v>34</v>
@@ -18733,13 +18733,13 @@
         <v>9</v>
       </c>
       <c r="D512" t="s">
-        <v>1137</v>
+        <v>1202</v>
       </c>
       <c r="E512" t="s">
         <v>1138</v>
       </c>
       <c r="F512" t="s">
-        <v>1202</v>
+        <v>1139</v>
       </c>
       <c r="G512" t="s">
         <v>20</v>
@@ -18756,10 +18756,10 @@
         <v>185</v>
       </c>
       <c r="D513" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E513" t="s">
         <v>1205</v>
-      </c>
-      <c r="E513" t="s">
-        <v>1138</v>
       </c>
       <c r="F513" t="s">
         <v>1139</v>
@@ -18940,13 +18940,13 @@
         <v>185</v>
       </c>
       <c r="D521" t="s">
-        <v>1137</v>
+        <v>1222</v>
       </c>
       <c r="E521" t="s">
         <v>1138</v>
       </c>
       <c r="F521" t="s">
-        <v>1222</v>
+        <v>1139</v>
       </c>
       <c r="G521" t="s">
         <v>25</v>
@@ -18963,13 +18963,13 @@
         <v>185</v>
       </c>
       <c r="D522" t="s">
-        <v>1137</v>
+        <v>1225</v>
       </c>
       <c r="E522" t="s">
         <v>1138</v>
       </c>
       <c r="F522" t="s">
-        <v>1225</v>
+        <v>1139</v>
       </c>
       <c r="G522" t="s">
         <v>16</v>
@@ -18986,13 +18986,13 @@
         <v>9</v>
       </c>
       <c r="D523" t="s">
-        <v>1137</v>
+        <v>1228</v>
       </c>
       <c r="E523" t="s">
         <v>1138</v>
       </c>
       <c r="F523" t="s">
-        <v>1228</v>
+        <v>1139</v>
       </c>
       <c r="G523" t="s">
         <v>34</v>
@@ -19032,13 +19032,13 @@
         <v>9</v>
       </c>
       <c r="D525" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E525" t="s">
         <v>1233</v>
       </c>
-      <c r="E525" t="s">
+      <c r="F525" t="s">
         <v>1234</v>
-      </c>
-      <c r="F525" t="s">
-        <v>1142</v>
       </c>
       <c r="G525" t="s">
         <v>1235</v>
@@ -19055,13 +19055,13 @@
         <v>9</v>
       </c>
       <c r="D526" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E526" t="s">
         <v>1233</v>
       </c>
-      <c r="E526" t="s">
+      <c r="F526" t="s">
         <v>1234</v>
-      </c>
-      <c r="F526" t="s">
-        <v>1142</v>
       </c>
       <c r="G526" t="s">
         <v>1235</v>
@@ -19078,13 +19078,13 @@
         <v>9</v>
       </c>
       <c r="D527" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E527" t="s">
         <v>1233</v>
       </c>
-      <c r="E527" t="s">
+      <c r="F527" t="s">
         <v>1234</v>
-      </c>
-      <c r="F527" t="s">
-        <v>1142</v>
       </c>
       <c r="G527" t="s">
         <v>1235</v>
@@ -19101,13 +19101,13 @@
         <v>9</v>
       </c>
       <c r="D528" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E528" t="s">
         <v>1233</v>
       </c>
-      <c r="E528" t="s">
+      <c r="F528" t="s">
         <v>1234</v>
-      </c>
-      <c r="F528" t="s">
-        <v>1142</v>
       </c>
       <c r="G528" t="s">
         <v>1235</v>
@@ -19124,13 +19124,13 @@
         <v>9</v>
       </c>
       <c r="D529" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E529" t="s">
         <v>1233</v>
       </c>
-      <c r="E529" t="s">
+      <c r="F529" t="s">
         <v>1234</v>
-      </c>
-      <c r="F529" t="s">
-        <v>1244</v>
       </c>
       <c r="G529" t="s">
         <v>20</v>
@@ -19147,13 +19147,13 @@
         <v>9</v>
       </c>
       <c r="D530" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E530" t="s">
         <v>1247</v>
       </c>
-      <c r="E530" t="s">
+      <c r="F530" t="s">
         <v>1234</v>
-      </c>
-      <c r="F530" t="s">
-        <v>1142</v>
       </c>
       <c r="G530" t="s">
         <v>1235</v>
@@ -19170,13 +19170,13 @@
         <v>9</v>
       </c>
       <c r="D531" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E531" t="s">
         <v>1233</v>
       </c>
-      <c r="E531" t="s">
+      <c r="F531" t="s">
         <v>1234</v>
-      </c>
-      <c r="F531" t="s">
-        <v>1142</v>
       </c>
       <c r="G531" t="s">
         <v>1235</v>
@@ -19193,13 +19193,13 @@
         <v>9</v>
       </c>
       <c r="D532" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E532" t="s">
         <v>1233</v>
       </c>
-      <c r="E532" t="s">
+      <c r="F532" t="s">
         <v>1234</v>
-      </c>
-      <c r="F532" t="s">
-        <v>1142</v>
       </c>
       <c r="G532" t="s">
         <v>1235</v>
@@ -19216,13 +19216,13 @@
         <v>9</v>
       </c>
       <c r="D533" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E533" t="s">
         <v>1233</v>
       </c>
-      <c r="E533" t="s">
+      <c r="F533" t="s">
         <v>1234</v>
-      </c>
-      <c r="F533" t="s">
-        <v>1142</v>
       </c>
       <c r="G533" t="s">
         <v>1235</v>
@@ -19239,13 +19239,13 @@
         <v>9</v>
       </c>
       <c r="D534" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E534" t="s">
         <v>1233</v>
       </c>
-      <c r="E534" t="s">
+      <c r="F534" t="s">
         <v>1234</v>
-      </c>
-      <c r="F534" t="s">
-        <v>1142</v>
       </c>
       <c r="G534" t="s">
         <v>1235</v>
@@ -19262,13 +19262,13 @@
         <v>9</v>
       </c>
       <c r="D535" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E535" t="s">
         <v>1233</v>
       </c>
-      <c r="E535" t="s">
+      <c r="F535" t="s">
         <v>1234</v>
-      </c>
-      <c r="F535" t="s">
-        <v>1142</v>
       </c>
       <c r="G535" t="s">
         <v>1235</v>
@@ -19285,13 +19285,13 @@
         <v>9</v>
       </c>
       <c r="D536" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E536" t="s">
         <v>1233</v>
       </c>
-      <c r="E536" t="s">
+      <c r="F536" t="s">
         <v>1234</v>
-      </c>
-      <c r="F536" t="s">
-        <v>1260</v>
       </c>
       <c r="G536" t="s">
         <v>20</v>
@@ -19308,13 +19308,13 @@
         <v>9</v>
       </c>
       <c r="D537" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E537" t="s">
         <v>1233</v>
       </c>
-      <c r="E537" t="s">
+      <c r="F537" t="s">
         <v>1234</v>
-      </c>
-      <c r="F537" t="s">
-        <v>1263</v>
       </c>
       <c r="G537" t="s">
         <v>20</v>
@@ -19331,13 +19331,13 @@
         <v>9</v>
       </c>
       <c r="D538" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E538" t="s">
         <v>1233</v>
       </c>
-      <c r="E538" t="s">
+      <c r="F538" t="s">
         <v>1234</v>
-      </c>
-      <c r="F538" t="s">
-        <v>1142</v>
       </c>
       <c r="G538" t="s">
         <v>1235</v>
@@ -19354,13 +19354,13 @@
         <v>9</v>
       </c>
       <c r="D539" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E539" t="s">
         <v>1233</v>
       </c>
-      <c r="E539" t="s">
+      <c r="F539" t="s">
         <v>1234</v>
-      </c>
-      <c r="F539" t="s">
-        <v>1142</v>
       </c>
       <c r="G539" t="s">
         <v>1235</v>
@@ -19377,13 +19377,13 @@
         <v>9</v>
       </c>
       <c r="D540" t="s">
-        <v>1196</v>
+        <v>1142</v>
       </c>
       <c r="E540" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F540" t="s">
         <v>1234</v>
-      </c>
-      <c r="F540" t="s">
-        <v>1142</v>
       </c>
       <c r="G540" t="s">
         <v>1235</v>
@@ -19400,13 +19400,13 @@
         <v>9</v>
       </c>
       <c r="D541" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E541" t="s">
         <v>1233</v>
       </c>
-      <c r="E541" t="s">
+      <c r="F541" t="s">
         <v>1234</v>
-      </c>
-      <c r="F541" t="s">
-        <v>1142</v>
       </c>
       <c r="G541" t="s">
         <v>1235</v>
@@ -19423,13 +19423,13 @@
         <v>9</v>
       </c>
       <c r="D542" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E542" t="s">
         <v>1233</v>
       </c>
-      <c r="E542" t="s">
+      <c r="F542" t="s">
         <v>1234</v>
-      </c>
-      <c r="F542" t="s">
-        <v>1142</v>
       </c>
       <c r="G542" t="s">
         <v>1235</v>
@@ -19446,13 +19446,13 @@
         <v>9</v>
       </c>
       <c r="D543" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E543" t="s">
         <v>1233</v>
       </c>
-      <c r="E543" t="s">
+      <c r="F543" t="s">
         <v>1234</v>
-      </c>
-      <c r="F543" t="s">
-        <v>1142</v>
       </c>
       <c r="G543" t="s">
         <v>1235</v>
@@ -19469,13 +19469,13 @@
         <v>9</v>
       </c>
       <c r="D544" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E544" t="s">
         <v>1233</v>
       </c>
-      <c r="E544" t="s">
+      <c r="F544" t="s">
         <v>1234</v>
-      </c>
-      <c r="F544" t="s">
-        <v>1142</v>
       </c>
       <c r="G544" t="s">
         <v>1235</v>
@@ -19492,13 +19492,13 @@
         <v>9</v>
       </c>
       <c r="D545" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E545" t="s">
         <v>1280</v>
       </c>
-      <c r="E545" t="s">
+      <c r="F545" t="s">
         <v>1234</v>
-      </c>
-      <c r="F545" t="s">
-        <v>1142</v>
       </c>
       <c r="G545" t="s">
         <v>16</v>
@@ -19515,13 +19515,13 @@
         <v>9</v>
       </c>
       <c r="D546" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E546" t="s">
         <v>1233</v>
       </c>
-      <c r="E546" t="s">
+      <c r="F546" t="s">
         <v>1234</v>
-      </c>
-      <c r="F546" t="s">
-        <v>1142</v>
       </c>
       <c r="G546" t="s">
         <v>1235</v>
@@ -19538,13 +19538,13 @@
         <v>9</v>
       </c>
       <c r="D547" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E547" t="s">
         <v>1233</v>
       </c>
-      <c r="E547" t="s">
+      <c r="F547" t="s">
         <v>1234</v>
-      </c>
-      <c r="F547" t="s">
-        <v>1142</v>
       </c>
       <c r="G547" t="s">
         <v>20</v>
@@ -19584,13 +19584,13 @@
         <v>9</v>
       </c>
       <c r="D549" t="s">
-        <v>1287</v>
+        <v>1292</v>
       </c>
       <c r="E549" t="s">
         <v>1288</v>
       </c>
       <c r="F549" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="G549" t="s">
         <v>1235</v>
@@ -19607,13 +19607,13 @@
         <v>9</v>
       </c>
       <c r="D550" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
       <c r="E550" t="s">
         <v>1288</v>
       </c>
       <c r="F550" t="s">
-        <v>1295</v>
+        <v>1289</v>
       </c>
       <c r="G550" t="s">
         <v>1235</v>
@@ -19699,10 +19699,10 @@
         <v>9</v>
       </c>
       <c r="D554" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E554" t="s">
         <v>1304</v>
-      </c>
-      <c r="E554" t="s">
-        <v>1288</v>
       </c>
       <c r="F554" t="s">
         <v>1289</v>
@@ -19794,10 +19794,10 @@
         <v>1313</v>
       </c>
       <c r="E558" t="s">
-        <v>1288</v>
+        <v>1314</v>
       </c>
       <c r="F558" t="s">
-        <v>1314</v>
+        <v>1289</v>
       </c>
       <c r="G558" t="s">
         <v>34</v>
@@ -19837,13 +19837,13 @@
         <v>9</v>
       </c>
       <c r="D560" t="s">
-        <v>1287</v>
+        <v>1319</v>
       </c>
       <c r="E560" t="s">
         <v>1288</v>
       </c>
       <c r="F560" t="s">
-        <v>1319</v>
+        <v>1289</v>
       </c>
       <c r="G560" t="s">
         <v>1235</v>
@@ -19860,13 +19860,13 @@
         <v>9</v>
       </c>
       <c r="D561" t="s">
-        <v>1287</v>
+        <v>1319</v>
       </c>
       <c r="E561" t="s">
         <v>1288</v>
       </c>
       <c r="F561" t="s">
-        <v>1319</v>
+        <v>1289</v>
       </c>
       <c r="G561" t="s">
         <v>1235</v>
@@ -19906,10 +19906,10 @@
         <v>9</v>
       </c>
       <c r="D563" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E563" t="s">
         <v>1326</v>
-      </c>
-      <c r="E563" t="s">
-        <v>1288</v>
       </c>
       <c r="F563" t="s">
         <v>1289</v>
@@ -20047,10 +20047,10 @@
         <v>1339</v>
       </c>
       <c r="E569" t="s">
-        <v>1288</v>
+        <v>1340</v>
       </c>
       <c r="F569" t="s">
-        <v>1340</v>
+        <v>1289</v>
       </c>
       <c r="G569" t="s">
         <v>1235</v>
@@ -20136,10 +20136,10 @@
         <v>9</v>
       </c>
       <c r="D573" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E573" t="s">
         <v>1233</v>
-      </c>
-      <c r="E573" t="s">
-        <v>1349</v>
       </c>
       <c r="F573" t="s">
         <v>1350</v>
@@ -20159,10 +20159,10 @@
         <v>9</v>
       </c>
       <c r="D574" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E574" t="s">
         <v>1353</v>
-      </c>
-      <c r="E574" t="s">
-        <v>1349</v>
       </c>
       <c r="F574" t="s">
         <v>1350</v>
@@ -20182,10 +20182,10 @@
         <v>9</v>
       </c>
       <c r="D575" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E575" t="s">
         <v>1353</v>
-      </c>
-      <c r="E575" t="s">
-        <v>1349</v>
       </c>
       <c r="F575" t="s">
         <v>1350</v>
@@ -20205,10 +20205,10 @@
         <v>9</v>
       </c>
       <c r="D576" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E576" t="s">
         <v>1353</v>
-      </c>
-      <c r="E576" t="s">
-        <v>1349</v>
       </c>
       <c r="F576" t="s">
         <v>1350</v>
@@ -20228,10 +20228,10 @@
         <v>9</v>
       </c>
       <c r="D577" t="s">
-        <v>1287</v>
+        <v>1349</v>
       </c>
       <c r="E577" t="s">
-        <v>1349</v>
+        <v>1288</v>
       </c>
       <c r="F577" t="s">
         <v>1350</v>
@@ -20251,13 +20251,13 @@
         <v>9</v>
       </c>
       <c r="D578" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E578" t="s">
         <v>1353</v>
       </c>
-      <c r="E578" t="s">
-        <v>1349</v>
-      </c>
       <c r="F578" t="s">
-        <v>1362</v>
+        <v>1350</v>
       </c>
       <c r="G578" t="s">
         <v>1235</v>
@@ -20277,10 +20277,10 @@
         <v>1365</v>
       </c>
       <c r="E579" t="s">
-        <v>1349</v>
+        <v>1366</v>
       </c>
       <c r="F579" t="s">
-        <v>1366</v>
+        <v>1350</v>
       </c>
       <c r="G579" t="s">
         <v>34</v>
@@ -20297,13 +20297,13 @@
         <v>9</v>
       </c>
       <c r="D580" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E580" t="s">
         <v>1353</v>
       </c>
-      <c r="E580" t="s">
-        <v>1349</v>
-      </c>
       <c r="F580" t="s">
-        <v>1369</v>
+        <v>1350</v>
       </c>
       <c r="G580" t="s">
         <v>1235</v>
@@ -20320,13 +20320,13 @@
         <v>9</v>
       </c>
       <c r="D581" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E581" t="s">
         <v>1353</v>
       </c>
-      <c r="E581" t="s">
-        <v>1349</v>
-      </c>
       <c r="F581" t="s">
-        <v>1372</v>
+        <v>1350</v>
       </c>
       <c r="G581" t="s">
         <v>20</v>
@@ -20343,10 +20343,10 @@
         <v>9</v>
       </c>
       <c r="D582" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E582" t="s">
         <v>1353</v>
-      </c>
-      <c r="E582" t="s">
-        <v>1349</v>
       </c>
       <c r="F582" t="s">
         <v>1350</v>
@@ -20369,10 +20369,10 @@
         <v>1377</v>
       </c>
       <c r="E583" t="s">
-        <v>1349</v>
+        <v>1378</v>
       </c>
       <c r="F583" t="s">
-        <v>1378</v>
+        <v>1350</v>
       </c>
       <c r="G583" t="s">
         <v>34</v>
@@ -20392,10 +20392,10 @@
         <v>1381</v>
       </c>
       <c r="E584" t="s">
-        <v>1349</v>
+        <v>1382</v>
       </c>
       <c r="F584" t="s">
-        <v>1382</v>
+        <v>1350</v>
       </c>
       <c r="G584" t="s">
         <v>34</v>
@@ -20412,10 +20412,10 @@
         <v>9</v>
       </c>
       <c r="D585" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E585" t="s">
         <v>1353</v>
-      </c>
-      <c r="E585" t="s">
-        <v>1349</v>
       </c>
       <c r="F585" t="s">
         <v>1350</v>
@@ -20438,10 +20438,10 @@
         <v>1387</v>
       </c>
       <c r="E586" t="s">
-        <v>1349</v>
+        <v>1388</v>
       </c>
       <c r="F586" t="s">
-        <v>1388</v>
+        <v>1350</v>
       </c>
       <c r="G586" t="s">
         <v>34</v>
@@ -20458,13 +20458,13 @@
         <v>9</v>
       </c>
       <c r="D587" t="s">
+        <v>1391</v>
+      </c>
+      <c r="E587" t="s">
         <v>1353</v>
       </c>
-      <c r="E587" t="s">
-        <v>1349</v>
-      </c>
       <c r="F587" t="s">
-        <v>1391</v>
+        <v>1350</v>
       </c>
       <c r="G587" t="s">
         <v>16</v>
@@ -20481,13 +20481,13 @@
         <v>9</v>
       </c>
       <c r="D588" t="s">
+        <v>1394</v>
+      </c>
+      <c r="E588" t="s">
         <v>1353</v>
       </c>
-      <c r="E588" t="s">
-        <v>1349</v>
-      </c>
       <c r="F588" t="s">
-        <v>1394</v>
+        <v>1350</v>
       </c>
       <c r="G588" t="s">
         <v>1235</v>
@@ -20504,10 +20504,10 @@
         <v>9</v>
       </c>
       <c r="D589" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E589" t="s">
         <v>1353</v>
-      </c>
-      <c r="E589" t="s">
-        <v>1349</v>
       </c>
       <c r="F589" t="s">
         <v>1350</v>
@@ -20527,10 +20527,10 @@
         <v>9</v>
       </c>
       <c r="D590" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E590" t="s">
         <v>1353</v>
-      </c>
-      <c r="E590" t="s">
-        <v>1349</v>
       </c>
       <c r="F590" t="s">
         <v>1350</v>
@@ -20550,10 +20550,10 @@
         <v>9</v>
       </c>
       <c r="D591" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E591" t="s">
         <v>1353</v>
-      </c>
-      <c r="E591" t="s">
-        <v>1349</v>
       </c>
       <c r="F591" t="s">
         <v>1350</v>
@@ -20573,10 +20573,10 @@
         <v>9</v>
       </c>
       <c r="D592" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E592" t="s">
         <v>1403</v>
-      </c>
-      <c r="E592" t="s">
-        <v>1349</v>
       </c>
       <c r="F592" t="s">
         <v>1350</v>
@@ -20596,10 +20596,10 @@
         <v>9</v>
       </c>
       <c r="D593" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E593" t="s">
         <v>1353</v>
-      </c>
-      <c r="E593" t="s">
-        <v>1349</v>
       </c>
       <c r="F593" t="s">
         <v>1350</v>
@@ -20619,10 +20619,10 @@
         <v>9</v>
       </c>
       <c r="D594" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E594" t="s">
         <v>1353</v>
-      </c>
-      <c r="E594" t="s">
-        <v>1349</v>
       </c>
       <c r="F594" t="s">
         <v>1350</v>
@@ -20642,10 +20642,10 @@
         <v>9</v>
       </c>
       <c r="D595" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E595" t="s">
         <v>1353</v>
-      </c>
-      <c r="E595" t="s">
-        <v>1349</v>
       </c>
       <c r="F595" t="s">
         <v>1350</v>
@@ -20665,10 +20665,10 @@
         <v>9</v>
       </c>
       <c r="D596" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E596" t="s">
         <v>1353</v>
-      </c>
-      <c r="E596" t="s">
-        <v>1349</v>
       </c>
       <c r="F596" t="s">
         <v>1350</v>
@@ -20714,10 +20714,10 @@
         <v>1419</v>
       </c>
       <c r="E598" t="s">
-        <v>1415</v>
+        <v>1420</v>
       </c>
       <c r="F598" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="G598" t="s">
         <v>20</v>
@@ -20806,10 +20806,10 @@
         <v>1429</v>
       </c>
       <c r="E602" t="s">
-        <v>1415</v>
+        <v>1430</v>
       </c>
       <c r="F602" t="s">
-        <v>1430</v>
+        <v>1416</v>
       </c>
       <c r="G602" t="s">
         <v>34</v>
@@ -20829,10 +20829,10 @@
         <v>1433</v>
       </c>
       <c r="E603" t="s">
-        <v>1415</v>
+        <v>1434</v>
       </c>
       <c r="F603" t="s">
-        <v>1434</v>
+        <v>1416</v>
       </c>
       <c r="G603" t="s">
         <v>34</v>
@@ -20852,10 +20852,10 @@
         <v>1437</v>
       </c>
       <c r="E604" t="s">
-        <v>1415</v>
+        <v>1438</v>
       </c>
       <c r="F604" t="s">
-        <v>1438</v>
+        <v>1416</v>
       </c>
       <c r="G604" t="s">
         <v>1235</v>
@@ -20872,13 +20872,13 @@
         <v>9</v>
       </c>
       <c r="D605" t="s">
-        <v>1414</v>
+        <v>1441</v>
       </c>
       <c r="E605" t="s">
         <v>1415</v>
       </c>
       <c r="F605" t="s">
-        <v>1441</v>
+        <v>1416</v>
       </c>
       <c r="G605" t="s">
         <v>34</v>
@@ -20944,10 +20944,10 @@
         <v>1448</v>
       </c>
       <c r="E608" t="s">
-        <v>1415</v>
+        <v>1449</v>
       </c>
       <c r="F608" t="s">
-        <v>1449</v>
+        <v>1416</v>
       </c>
       <c r="G608" t="s">
         <v>34</v>
@@ -20964,13 +20964,13 @@
         <v>9</v>
       </c>
       <c r="D609" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E609" t="s">
         <v>1391</v>
       </c>
-      <c r="E609" t="s">
-        <v>1415</v>
-      </c>
       <c r="F609" t="s">
-        <v>1452</v>
+        <v>1416</v>
       </c>
       <c r="G609" t="s">
         <v>1235</v>
@@ -21010,13 +21010,13 @@
         <v>9</v>
       </c>
       <c r="D611" t="s">
+        <v>1419</v>
+      </c>
+      <c r="E611" t="s">
         <v>1457</v>
       </c>
-      <c r="E611" t="s">
-        <v>1415</v>
-      </c>
       <c r="F611" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="G611" t="s">
         <v>34</v>
@@ -21033,13 +21033,13 @@
         <v>9</v>
       </c>
       <c r="D612" t="s">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="E612" t="s">
         <v>1415</v>
       </c>
       <c r="F612" t="s">
-        <v>1460</v>
+        <v>1416</v>
       </c>
       <c r="G612" t="s">
         <v>20</v>
@@ -21079,13 +21079,13 @@
         <v>9</v>
       </c>
       <c r="D614" t="s">
-        <v>1414</v>
+        <v>1465</v>
       </c>
       <c r="E614" t="s">
         <v>1415</v>
       </c>
       <c r="F614" t="s">
-        <v>1465</v>
+        <v>1416</v>
       </c>
       <c r="G614" t="s">
         <v>1235</v>
@@ -21312,10 +21312,10 @@
         <v>1489</v>
       </c>
       <c r="E624" t="s">
-        <v>1485</v>
+        <v>1490</v>
       </c>
       <c r="F624" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
       <c r="G624" t="s">
         <v>34</v>
@@ -21401,10 +21401,10 @@
         <v>9</v>
       </c>
       <c r="D628" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E628" t="s">
         <v>1499</v>
-      </c>
-      <c r="E628" t="s">
-        <v>1485</v>
       </c>
       <c r="F628" t="s">
         <v>1486</v>
@@ -21424,13 +21424,13 @@
         <v>9</v>
       </c>
       <c r="D629" t="s">
-        <v>1484</v>
+        <v>1502</v>
       </c>
       <c r="E629" t="s">
         <v>1485</v>
       </c>
       <c r="F629" t="s">
-        <v>1502</v>
+        <v>1486</v>
       </c>
       <c r="G629" t="s">
         <v>34</v>
@@ -21493,13 +21493,13 @@
         <v>9</v>
       </c>
       <c r="D632" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E632" t="s">
         <v>1509</v>
       </c>
-      <c r="E632" t="s">
-        <v>1485</v>
-      </c>
       <c r="F632" t="s">
-        <v>1502</v>
+        <v>1486</v>
       </c>
       <c r="G632" t="s">
         <v>34</v>
@@ -21519,10 +21519,10 @@
         <v>1512</v>
       </c>
       <c r="E633" t="s">
-        <v>1485</v>
+        <v>1513</v>
       </c>
       <c r="F633" t="s">
-        <v>1513</v>
+        <v>1486</v>
       </c>
       <c r="G633" t="s">
         <v>34</v>
@@ -21542,10 +21542,10 @@
         <v>1516</v>
       </c>
       <c r="E634" t="s">
-        <v>1485</v>
+        <v>1517</v>
       </c>
       <c r="F634" t="s">
-        <v>1517</v>
+        <v>1486</v>
       </c>
       <c r="G634" t="s">
         <v>34</v>
@@ -21585,13 +21585,13 @@
         <v>9</v>
       </c>
       <c r="D636" t="s">
-        <v>1484</v>
+        <v>1522</v>
       </c>
       <c r="E636" t="s">
         <v>1485</v>
       </c>
       <c r="F636" t="s">
-        <v>1522</v>
+        <v>1486</v>
       </c>
       <c r="G636" t="s">
         <v>1235</v>
@@ -21611,10 +21611,10 @@
         <v>1525</v>
       </c>
       <c r="E637" t="s">
-        <v>1485</v>
+        <v>1526</v>
       </c>
       <c r="F637" t="s">
-        <v>1526</v>
+        <v>1486</v>
       </c>
       <c r="G637" t="s">
         <v>34</v>
@@ -21703,10 +21703,10 @@
         <v>1535</v>
       </c>
       <c r="E641" t="s">
-        <v>1485</v>
+        <v>1536</v>
       </c>
       <c r="F641" t="s">
-        <v>1536</v>
+        <v>1486</v>
       </c>
       <c r="G641" t="s">
         <v>20</v>
@@ -21723,13 +21723,13 @@
         <v>9</v>
       </c>
       <c r="D642" t="s">
-        <v>1484</v>
+        <v>1539</v>
       </c>
       <c r="E642" t="s">
         <v>1485</v>
       </c>
       <c r="F642" t="s">
-        <v>1539</v>
+        <v>1486</v>
       </c>
       <c r="G642" t="s">
         <v>20</v>
@@ -21746,13 +21746,13 @@
         <v>9</v>
       </c>
       <c r="D643" t="s">
-        <v>1484</v>
+        <v>1542</v>
       </c>
       <c r="E643" t="s">
         <v>1485</v>
       </c>
       <c r="F643" t="s">
-        <v>1542</v>
+        <v>1486</v>
       </c>
       <c r="G643" t="s">
         <v>20</v>
@@ -21815,13 +21815,13 @@
         <v>9</v>
       </c>
       <c r="D646" t="s">
-        <v>1484</v>
+        <v>1549</v>
       </c>
       <c r="E646" t="s">
         <v>1485</v>
       </c>
       <c r="F646" t="s">
-        <v>1549</v>
+        <v>1486</v>
       </c>
       <c r="G646" t="s">
         <v>34</v>
@@ -21910,10 +21910,10 @@
         <v>1561</v>
       </c>
       <c r="E650" t="s">
-        <v>1557</v>
+        <v>1562</v>
       </c>
       <c r="F650" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="G650" t="s">
         <v>20</v>
@@ -21930,10 +21930,10 @@
         <v>9</v>
       </c>
       <c r="D651" t="s">
+        <v>1556</v>
+      </c>
+      <c r="E651" t="s">
         <v>1565</v>
-      </c>
-      <c r="E651" t="s">
-        <v>1557</v>
       </c>
       <c r="F651" t="s">
         <v>1558</v>
@@ -21956,10 +21956,10 @@
         <v>1568</v>
       </c>
       <c r="E652" t="s">
-        <v>1557</v>
+        <v>1569</v>
       </c>
       <c r="F652" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G652" t="s">
         <v>1235</v>
@@ -21979,10 +21979,10 @@
         <v>1568</v>
       </c>
       <c r="E653" t="s">
-        <v>1557</v>
+        <v>1569</v>
       </c>
       <c r="F653" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G653" t="s">
         <v>1235</v>
@@ -21999,13 +21999,13 @@
         <v>9</v>
       </c>
       <c r="D654" t="s">
-        <v>1484</v>
+        <v>1542</v>
       </c>
       <c r="E654" t="s">
-        <v>1557</v>
+        <v>1485</v>
       </c>
       <c r="F654" t="s">
-        <v>1542</v>
+        <v>1558</v>
       </c>
       <c r="G654" t="s">
         <v>20</v>
@@ -22025,10 +22025,10 @@
         <v>1568</v>
       </c>
       <c r="E655" t="s">
-        <v>1557</v>
+        <v>1569</v>
       </c>
       <c r="F655" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G655" t="s">
         <v>1235</v>
@@ -22048,10 +22048,10 @@
         <v>1568</v>
       </c>
       <c r="E656" t="s">
-        <v>1557</v>
+        <v>1569</v>
       </c>
       <c r="F656" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G656" t="s">
         <v>1235</v>
@@ -22071,10 +22071,10 @@
         <v>1580</v>
       </c>
       <c r="E657" t="s">
-        <v>1557</v>
+        <v>1581</v>
       </c>
       <c r="F657" t="s">
-        <v>1581</v>
+        <v>1558</v>
       </c>
       <c r="G657" t="s">
         <v>20</v>
@@ -22094,10 +22094,10 @@
         <v>1584</v>
       </c>
       <c r="E658" t="s">
-        <v>1557</v>
+        <v>1585</v>
       </c>
       <c r="F658" t="s">
-        <v>1585</v>
+        <v>1558</v>
       </c>
       <c r="G658" t="s">
         <v>34</v>
@@ -22114,13 +22114,13 @@
         <v>9</v>
       </c>
       <c r="D659" t="s">
+        <v>1522</v>
+      </c>
+      <c r="E659" t="s">
         <v>1588</v>
       </c>
-      <c r="E659" t="s">
-        <v>1557</v>
-      </c>
       <c r="F659" t="s">
-        <v>1522</v>
+        <v>1558</v>
       </c>
       <c r="G659" t="s">
         <v>34</v>
@@ -22140,10 +22140,10 @@
         <v>1591</v>
       </c>
       <c r="E660" t="s">
-        <v>1557</v>
+        <v>1592</v>
       </c>
       <c r="F660" t="s">
-        <v>1592</v>
+        <v>1558</v>
       </c>
       <c r="G660" t="s">
         <v>34</v>
@@ -22163,10 +22163,10 @@
         <v>1568</v>
       </c>
       <c r="E661" t="s">
-        <v>1557</v>
+        <v>1569</v>
       </c>
       <c r="F661" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G661" t="s">
         <v>1235</v>
@@ -22183,13 +22183,13 @@
         <v>9</v>
       </c>
       <c r="D662" t="s">
-        <v>1562</v>
+        <v>1568</v>
       </c>
       <c r="E662" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="F662" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G662" t="s">
         <v>34</v>
@@ -22209,10 +22209,10 @@
         <v>1599</v>
       </c>
       <c r="E663" t="s">
-        <v>1557</v>
+        <v>1600</v>
       </c>
       <c r="F663" t="s">
-        <v>1600</v>
+        <v>1558</v>
       </c>
       <c r="G663" t="s">
         <v>34</v>
@@ -22229,13 +22229,13 @@
         <v>9</v>
       </c>
       <c r="D664" t="s">
+        <v>1542</v>
+      </c>
+      <c r="E664" t="s">
         <v>1603</v>
       </c>
-      <c r="E664" t="s">
-        <v>1557</v>
-      </c>
       <c r="F664" t="s">
-        <v>1542</v>
+        <v>1558</v>
       </c>
       <c r="G664" t="s">
         <v>20</v>
@@ -22252,13 +22252,13 @@
         <v>9</v>
       </c>
       <c r="D665" t="s">
-        <v>1568</v>
+        <v>1606</v>
       </c>
       <c r="E665" t="s">
-        <v>1557</v>
+        <v>1569</v>
       </c>
       <c r="F665" t="s">
-        <v>1606</v>
+        <v>1558</v>
       </c>
       <c r="G665" t="s">
         <v>1235</v>
@@ -22275,13 +22275,13 @@
         <v>9</v>
       </c>
       <c r="D666" t="s">
-        <v>1556</v>
+        <v>1606</v>
       </c>
       <c r="E666" t="s">
         <v>1557</v>
       </c>
       <c r="F666" t="s">
-        <v>1606</v>
+        <v>1558</v>
       </c>
       <c r="G666" t="s">
         <v>34</v>
@@ -22301,10 +22301,10 @@
         <v>1611</v>
       </c>
       <c r="E667" t="s">
-        <v>1557</v>
+        <v>1612</v>
       </c>
       <c r="F667" t="s">
-        <v>1612</v>
+        <v>1558</v>
       </c>
       <c r="G667" t="s">
         <v>34</v>
@@ -22324,10 +22324,10 @@
         <v>1568</v>
       </c>
       <c r="E668" t="s">
-        <v>1557</v>
+        <v>1569</v>
       </c>
       <c r="F668" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G668" t="s">
         <v>20</v>
@@ -22344,13 +22344,13 @@
         <v>9</v>
       </c>
       <c r="D669" t="s">
+        <v>1542</v>
+      </c>
+      <c r="E669" t="s">
         <v>1588</v>
       </c>
-      <c r="E669" t="s">
-        <v>1557</v>
-      </c>
       <c r="F669" t="s">
-        <v>1542</v>
+        <v>1558</v>
       </c>
       <c r="G669" t="s">
         <v>20</v>
@@ -22370,10 +22370,10 @@
         <v>1568</v>
       </c>
       <c r="E670" t="s">
-        <v>1557</v>
+        <v>1569</v>
       </c>
       <c r="F670" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G670" t="s">
         <v>1235</v>
@@ -22390,10 +22390,10 @@
         <v>9</v>
       </c>
       <c r="D671" t="s">
+        <v>1556</v>
+      </c>
+      <c r="E671" t="s">
         <v>1621</v>
-      </c>
-      <c r="E671" t="s">
-        <v>1557</v>
       </c>
       <c r="F671" t="s">
         <v>1558</v>
@@ -22416,10 +22416,10 @@
         <v>1568</v>
       </c>
       <c r="E672" t="s">
-        <v>1557</v>
+        <v>1569</v>
       </c>
       <c r="F672" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G672" t="s">
         <v>20</v>
@@ -22439,10 +22439,10 @@
         <v>1568</v>
       </c>
       <c r="E673" t="s">
-        <v>1557</v>
+        <v>1569</v>
       </c>
       <c r="F673" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G673" t="s">
         <v>1235</v>
@@ -22459,13 +22459,13 @@
         <v>9</v>
       </c>
       <c r="D674" t="s">
-        <v>1591</v>
+        <v>1542</v>
       </c>
       <c r="E674" t="s">
-        <v>1557</v>
+        <v>1592</v>
       </c>
       <c r="F674" t="s">
-        <v>1542</v>
+        <v>1558</v>
       </c>
       <c r="G674" t="s">
         <v>20</v>
@@ -22482,10 +22482,10 @@
         <v>9</v>
       </c>
       <c r="D675" t="s">
+        <v>1556</v>
+      </c>
+      <c r="E675" t="s">
         <v>1565</v>
-      </c>
-      <c r="E675" t="s">
-        <v>1557</v>
       </c>
       <c r="F675" t="s">
         <v>1558</v>
@@ -22505,13 +22505,13 @@
         <v>9</v>
       </c>
       <c r="D676" t="s">
-        <v>1568</v>
+        <v>1632</v>
       </c>
       <c r="E676" t="s">
-        <v>1557</v>
+        <v>1569</v>
       </c>
       <c r="F676" t="s">
-        <v>1632</v>
+        <v>1558</v>
       </c>
       <c r="G676" t="s">
         <v>20</v>
@@ -22531,10 +22531,10 @@
         <v>1568</v>
       </c>
       <c r="E677" t="s">
-        <v>1557</v>
+        <v>1569</v>
       </c>
       <c r="F677" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G677" t="s">
         <v>1235</v>
@@ -22554,10 +22554,10 @@
         <v>1568</v>
       </c>
       <c r="E678" t="s">
-        <v>1557</v>
+        <v>1569</v>
       </c>
       <c r="F678" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G678" t="s">
         <v>1235</v>
@@ -22577,10 +22577,10 @@
         <v>1591</v>
       </c>
       <c r="E679" t="s">
-        <v>1557</v>
+        <v>1592</v>
       </c>
       <c r="F679" t="s">
-        <v>1592</v>
+        <v>1558</v>
       </c>
       <c r="G679" t="s">
         <v>34</v>
@@ -22600,10 +22600,10 @@
         <v>1568</v>
       </c>
       <c r="E680" t="s">
-        <v>1557</v>
+        <v>1569</v>
       </c>
       <c r="F680" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G680" t="s">
         <v>1235</v>
@@ -22623,10 +22623,10 @@
         <v>1568</v>
       </c>
       <c r="E681" t="s">
-        <v>1557</v>
+        <v>1569</v>
       </c>
       <c r="F681" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="G681" t="s">
         <v>1235</v>
@@ -22669,10 +22669,10 @@
         <v>1650</v>
       </c>
       <c r="E683" t="s">
-        <v>1646</v>
+        <v>1651</v>
       </c>
       <c r="F683" t="s">
-        <v>1651</v>
+        <v>1647</v>
       </c>
       <c r="G683" t="s">
         <v>34</v>
@@ -22692,10 +22692,10 @@
         <v>1654</v>
       </c>
       <c r="E684" t="s">
-        <v>1646</v>
+        <v>1655</v>
       </c>
       <c r="F684" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G684" t="s">
         <v>1235</v>
@@ -22715,10 +22715,10 @@
         <v>1654</v>
       </c>
       <c r="E685" t="s">
-        <v>1646</v>
+        <v>1655</v>
       </c>
       <c r="F685" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G685" t="s">
         <v>1235</v>
@@ -22738,10 +22738,10 @@
         <v>1654</v>
       </c>
       <c r="E686" t="s">
-        <v>1646</v>
+        <v>1655</v>
       </c>
       <c r="F686" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G686" t="s">
         <v>1235</v>
@@ -22761,10 +22761,10 @@
         <v>1654</v>
       </c>
       <c r="E687" t="s">
-        <v>1646</v>
+        <v>1655</v>
       </c>
       <c r="F687" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G687" t="s">
         <v>1235</v>
@@ -22784,10 +22784,10 @@
         <v>1654</v>
       </c>
       <c r="E688" t="s">
-        <v>1646</v>
+        <v>1655</v>
       </c>
       <c r="F688" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G688" t="s">
         <v>1235</v>
@@ -22804,13 +22804,13 @@
         <v>9</v>
       </c>
       <c r="D689" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E689" t="s">
         <v>1666</v>
       </c>
-      <c r="E689" t="s">
-        <v>1646</v>
-      </c>
       <c r="F689" t="s">
-        <v>1651</v>
+        <v>1647</v>
       </c>
       <c r="G689" t="s">
         <v>34</v>
@@ -22830,10 +22830,10 @@
         <v>1669</v>
       </c>
       <c r="E690" t="s">
-        <v>1646</v>
+        <v>1670</v>
       </c>
       <c r="F690" t="s">
-        <v>1670</v>
+        <v>1647</v>
       </c>
       <c r="G690" t="s">
         <v>34</v>
@@ -22853,10 +22853,10 @@
         <v>1654</v>
       </c>
       <c r="E691" t="s">
-        <v>1646</v>
+        <v>1655</v>
       </c>
       <c r="F691" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G691" t="s">
         <v>16</v>
@@ -22873,13 +22873,13 @@
         <v>9</v>
       </c>
       <c r="D692" t="s">
-        <v>1568</v>
+        <v>1675</v>
       </c>
       <c r="E692" t="s">
-        <v>1646</v>
+        <v>1569</v>
       </c>
       <c r="F692" t="s">
-        <v>1675</v>
+        <v>1647</v>
       </c>
       <c r="G692" t="s">
         <v>20</v>
@@ -22899,10 +22899,10 @@
         <v>1678</v>
       </c>
       <c r="E693" t="s">
-        <v>1646</v>
+        <v>1679</v>
       </c>
       <c r="F693" t="s">
-        <v>1679</v>
+        <v>1647</v>
       </c>
       <c r="G693" t="s">
         <v>34</v>
@@ -22922,10 +22922,10 @@
         <v>1682</v>
       </c>
       <c r="E694" t="s">
-        <v>1646</v>
+        <v>1683</v>
       </c>
       <c r="F694" t="s">
-        <v>1683</v>
+        <v>1647</v>
       </c>
       <c r="G694" t="s">
         <v>20</v>
@@ -22945,10 +22945,10 @@
         <v>1686</v>
       </c>
       <c r="E695" t="s">
-        <v>1646</v>
+        <v>1687</v>
       </c>
       <c r="F695" t="s">
-        <v>1687</v>
+        <v>1647</v>
       </c>
       <c r="G695" t="s">
         <v>34</v>
@@ -22968,10 +22968,10 @@
         <v>1654</v>
       </c>
       <c r="E696" t="s">
-        <v>1646</v>
+        <v>1655</v>
       </c>
       <c r="F696" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G696" t="s">
         <v>1235</v>
@@ -22991,10 +22991,10 @@
         <v>1692</v>
       </c>
       <c r="E697" t="s">
-        <v>1646</v>
+        <v>1693</v>
       </c>
       <c r="F697" t="s">
-        <v>1693</v>
+        <v>1647</v>
       </c>
       <c r="G697" t="s">
         <v>34</v>
@@ -23014,10 +23014,10 @@
         <v>1696</v>
       </c>
       <c r="E698" t="s">
-        <v>1646</v>
+        <v>1697</v>
       </c>
       <c r="F698" t="s">
-        <v>1697</v>
+        <v>1647</v>
       </c>
       <c r="G698" t="s">
         <v>34</v>
@@ -23037,10 +23037,10 @@
         <v>1654</v>
       </c>
       <c r="E699" t="s">
-        <v>1646</v>
+        <v>1655</v>
       </c>
       <c r="F699" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G699" t="s">
         <v>20</v>
@@ -23060,10 +23060,10 @@
         <v>1702</v>
       </c>
       <c r="E700" t="s">
-        <v>1646</v>
+        <v>1703</v>
       </c>
       <c r="F700" t="s">
-        <v>1703</v>
+        <v>1647</v>
       </c>
       <c r="G700" t="s">
         <v>34</v>
@@ -23083,10 +23083,10 @@
         <v>1654</v>
       </c>
       <c r="E701" t="s">
-        <v>1646</v>
+        <v>1655</v>
       </c>
       <c r="F701" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G701" t="s">
         <v>20</v>
@@ -23106,10 +23106,10 @@
         <v>1708</v>
       </c>
       <c r="E702" t="s">
-        <v>1646</v>
+        <v>1709</v>
       </c>
       <c r="F702" t="s">
-        <v>1709</v>
+        <v>1647</v>
       </c>
       <c r="G702" t="s">
         <v>34</v>
@@ -23126,13 +23126,13 @@
         <v>9</v>
       </c>
       <c r="D703" t="s">
-        <v>1702</v>
+        <v>1712</v>
       </c>
       <c r="E703" t="s">
-        <v>1646</v>
+        <v>1703</v>
       </c>
       <c r="F703" t="s">
-        <v>1712</v>
+        <v>1647</v>
       </c>
       <c r="G703" t="s">
         <v>34</v>
@@ -23152,10 +23152,10 @@
         <v>1654</v>
       </c>
       <c r="E704" t="s">
-        <v>1646</v>
+        <v>1655</v>
       </c>
       <c r="F704" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G704" t="s">
         <v>1235</v>
@@ -23172,13 +23172,13 @@
         <v>9</v>
       </c>
       <c r="D705" t="s">
-        <v>1696</v>
+        <v>1717</v>
       </c>
       <c r="E705" t="s">
-        <v>1646</v>
+        <v>1697</v>
       </c>
       <c r="F705" t="s">
-        <v>1717</v>
+        <v>1647</v>
       </c>
       <c r="G705" t="s">
         <v>20</v>
@@ -23198,10 +23198,10 @@
         <v>1654</v>
       </c>
       <c r="E706" t="s">
-        <v>1646</v>
+        <v>1655</v>
       </c>
       <c r="F706" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G706" t="s">
         <v>1235</v>
@@ -23218,13 +23218,13 @@
         <v>9</v>
       </c>
       <c r="D707" t="s">
-        <v>1696</v>
+        <v>1654</v>
       </c>
       <c r="E707" t="s">
-        <v>1646</v>
+        <v>1697</v>
       </c>
       <c r="F707" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G707" t="s">
         <v>20</v>
@@ -23241,13 +23241,13 @@
         <v>9</v>
       </c>
       <c r="D708" t="s">
-        <v>1650</v>
+        <v>1724</v>
       </c>
       <c r="E708" t="s">
-        <v>1646</v>
+        <v>1651</v>
       </c>
       <c r="F708" t="s">
-        <v>1724</v>
+        <v>1647</v>
       </c>
       <c r="G708" t="s">
         <v>34</v>
@@ -23267,10 +23267,10 @@
         <v>1654</v>
       </c>
       <c r="E709" t="s">
-        <v>1646</v>
+        <v>1655</v>
       </c>
       <c r="F709" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G709" t="s">
         <v>1235</v>
@@ -23290,10 +23290,10 @@
         <v>1729</v>
       </c>
       <c r="E710" t="s">
-        <v>1646</v>
+        <v>1730</v>
       </c>
       <c r="F710" t="s">
-        <v>1730</v>
+        <v>1647</v>
       </c>
       <c r="G710" t="s">
         <v>34</v>
@@ -23310,13 +23310,13 @@
         <v>9</v>
       </c>
       <c r="D711" t="s">
-        <v>1696</v>
+        <v>1654</v>
       </c>
       <c r="E711" t="s">
-        <v>1646</v>
+        <v>1697</v>
       </c>
       <c r="F711" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G711" t="s">
         <v>1235</v>
@@ -23336,10 +23336,10 @@
         <v>1654</v>
       </c>
       <c r="E712" t="s">
-        <v>1646</v>
+        <v>1655</v>
       </c>
       <c r="F712" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G712" t="s">
         <v>1235</v>
@@ -23359,10 +23359,10 @@
         <v>1669</v>
       </c>
       <c r="E713" t="s">
-        <v>1646</v>
+        <v>1670</v>
       </c>
       <c r="F713" t="s">
-        <v>1670</v>
+        <v>1647</v>
       </c>
       <c r="G713" t="s">
         <v>34</v>
@@ -23382,10 +23382,10 @@
         <v>1654</v>
       </c>
       <c r="E714" t="s">
-        <v>1646</v>
+        <v>1655</v>
       </c>
       <c r="F714" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G714" t="s">
         <v>1235</v>
@@ -23402,13 +23402,13 @@
         <v>9</v>
       </c>
       <c r="D715" t="s">
-        <v>1696</v>
+        <v>1692</v>
       </c>
       <c r="E715" t="s">
-        <v>1646</v>
+        <v>1697</v>
       </c>
       <c r="F715" t="s">
-        <v>1693</v>
+        <v>1647</v>
       </c>
       <c r="G715" t="s">
         <v>34</v>
@@ -23428,10 +23428,10 @@
         <v>1654</v>
       </c>
       <c r="E716" t="s">
-        <v>1646</v>
+        <v>1655</v>
       </c>
       <c r="F716" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G716" t="s">
         <v>1235</v>
@@ -23451,10 +23451,10 @@
         <v>1654</v>
       </c>
       <c r="E717" t="s">
-        <v>1646</v>
+        <v>1655</v>
       </c>
       <c r="F717" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G717" t="s">
         <v>1235</v>
@@ -23494,13 +23494,13 @@
         <v>9</v>
       </c>
       <c r="D719" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E719" t="s">
         <v>1748</v>
       </c>
       <c r="F719" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G719" t="s">
         <v>1235</v>
@@ -23517,13 +23517,13 @@
         <v>9</v>
       </c>
       <c r="D720" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E720" t="s">
         <v>1748</v>
       </c>
       <c r="F720" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G720" t="s">
         <v>1235</v>
@@ -23540,13 +23540,13 @@
         <v>9</v>
       </c>
       <c r="D721" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E721" t="s">
         <v>1748</v>
       </c>
       <c r="F721" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G721" t="s">
         <v>1235</v>
@@ -23563,13 +23563,13 @@
         <v>9</v>
       </c>
       <c r="D722" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E722" t="s">
         <v>1748</v>
       </c>
       <c r="F722" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G722" t="s">
         <v>1235</v>
@@ -23586,13 +23586,13 @@
         <v>9</v>
       </c>
       <c r="D723" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E723" t="s">
         <v>1748</v>
       </c>
       <c r="F723" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G723" t="s">
         <v>1235</v>
@@ -23609,13 +23609,13 @@
         <v>9</v>
       </c>
       <c r="D724" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E724" t="s">
         <v>1748</v>
       </c>
       <c r="F724" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G724" t="s">
         <v>20</v>
@@ -23635,10 +23635,10 @@
         <v>1765</v>
       </c>
       <c r="E725" t="s">
-        <v>1748</v>
+        <v>1766</v>
       </c>
       <c r="F725" t="s">
-        <v>1766</v>
+        <v>1749</v>
       </c>
       <c r="G725" t="s">
         <v>20</v>
@@ -23658,10 +23658,10 @@
         <v>1769</v>
       </c>
       <c r="E726" t="s">
-        <v>1748</v>
+        <v>1770</v>
       </c>
       <c r="F726" t="s">
-        <v>1770</v>
+        <v>1749</v>
       </c>
       <c r="G726" t="s">
         <v>20</v>
@@ -23678,13 +23678,13 @@
         <v>9</v>
       </c>
       <c r="D727" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E727" t="s">
         <v>1748</v>
       </c>
       <c r="F727" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G727" t="s">
         <v>1235</v>
@@ -23701,13 +23701,13 @@
         <v>9</v>
       </c>
       <c r="D728" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E728" t="s">
         <v>1748</v>
       </c>
       <c r="F728" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G728" t="s">
         <v>1235</v>
@@ -23727,10 +23727,10 @@
         <v>1777</v>
       </c>
       <c r="E729" t="s">
-        <v>1748</v>
+        <v>1778</v>
       </c>
       <c r="F729" t="s">
-        <v>1778</v>
+        <v>1749</v>
       </c>
       <c r="G729" t="s">
         <v>34</v>
@@ -23747,13 +23747,13 @@
         <v>9</v>
       </c>
       <c r="D730" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E730" t="s">
         <v>1748</v>
       </c>
       <c r="F730" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G730" t="s">
         <v>16</v>
@@ -23773,10 +23773,10 @@
         <v>1777</v>
       </c>
       <c r="E731" t="s">
-        <v>1748</v>
+        <v>1778</v>
       </c>
       <c r="F731" t="s">
-        <v>1778</v>
+        <v>1749</v>
       </c>
       <c r="G731" t="s">
         <v>34</v>
@@ -23796,10 +23796,10 @@
         <v>1785</v>
       </c>
       <c r="E732" t="s">
-        <v>1748</v>
+        <v>1786</v>
       </c>
       <c r="F732" t="s">
-        <v>1786</v>
+        <v>1749</v>
       </c>
       <c r="G732" t="s">
         <v>34</v>
@@ -23816,13 +23816,13 @@
         <v>9</v>
       </c>
       <c r="D733" t="s">
-        <v>1747</v>
+        <v>1789</v>
       </c>
       <c r="E733" t="s">
         <v>1748</v>
       </c>
       <c r="F733" t="s">
-        <v>1789</v>
+        <v>1749</v>
       </c>
       <c r="G733" t="s">
         <v>34</v>
@@ -23842,10 +23842,10 @@
         <v>1792</v>
       </c>
       <c r="E734" t="s">
-        <v>1748</v>
+        <v>1793</v>
       </c>
       <c r="F734" t="s">
-        <v>1793</v>
+        <v>1749</v>
       </c>
       <c r="G734" t="s">
         <v>34</v>
@@ -23862,13 +23862,13 @@
         <v>9</v>
       </c>
       <c r="D735" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E735" t="s">
         <v>1748</v>
       </c>
       <c r="F735" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G735" t="s">
         <v>1235</v>
@@ -23885,13 +23885,13 @@
         <v>9</v>
       </c>
       <c r="D736" t="s">
-        <v>1747</v>
+        <v>1798</v>
       </c>
       <c r="E736" t="s">
         <v>1748</v>
       </c>
       <c r="F736" t="s">
-        <v>1798</v>
+        <v>1749</v>
       </c>
       <c r="G736" t="s">
         <v>1235</v>
@@ -23908,13 +23908,13 @@
         <v>9</v>
       </c>
       <c r="D737" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E737" t="s">
         <v>1748</v>
       </c>
       <c r="F737" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G737" t="s">
         <v>20</v>
@@ -23931,13 +23931,13 @@
         <v>9</v>
       </c>
       <c r="D738" t="s">
-        <v>1654</v>
+        <v>1803</v>
       </c>
       <c r="E738" t="s">
-        <v>1748</v>
+        <v>1655</v>
       </c>
       <c r="F738" t="s">
-        <v>1803</v>
+        <v>1749</v>
       </c>
       <c r="G738" t="s">
         <v>20</v>
@@ -23954,13 +23954,13 @@
         <v>9</v>
       </c>
       <c r="D739" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E739" t="s">
         <v>1748</v>
       </c>
       <c r="F739" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G739" t="s">
         <v>1235</v>
@@ -23977,13 +23977,13 @@
         <v>9</v>
       </c>
       <c r="D740" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E740" t="s">
         <v>1748</v>
       </c>
       <c r="F740" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G740" t="s">
         <v>1235</v>
@@ -24003,10 +24003,10 @@
         <v>1810</v>
       </c>
       <c r="E741" t="s">
-        <v>1748</v>
+        <v>1811</v>
       </c>
       <c r="F741" t="s">
-        <v>1811</v>
+        <v>1749</v>
       </c>
       <c r="G741" t="s">
         <v>34</v>
@@ -24023,13 +24023,13 @@
         <v>9</v>
       </c>
       <c r="D742" t="s">
-        <v>1747</v>
+        <v>1814</v>
       </c>
       <c r="E742" t="s">
         <v>1748</v>
       </c>
       <c r="F742" t="s">
-        <v>1814</v>
+        <v>1749</v>
       </c>
       <c r="G742" t="s">
         <v>20</v>
@@ -24046,13 +24046,13 @@
         <v>9</v>
       </c>
       <c r="D743" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E743" t="s">
         <v>1748</v>
       </c>
       <c r="F743" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G743" t="s">
         <v>1235</v>
@@ -24092,13 +24092,13 @@
         <v>9</v>
       </c>
       <c r="D745" t="s">
-        <v>1747</v>
+        <v>1821</v>
       </c>
       <c r="E745" t="s">
         <v>1748</v>
       </c>
       <c r="F745" t="s">
-        <v>1821</v>
+        <v>1749</v>
       </c>
       <c r="G745" t="s">
         <v>34</v>
@@ -24115,13 +24115,13 @@
         <v>9</v>
       </c>
       <c r="D746" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E746" t="s">
         <v>1748</v>
       </c>
       <c r="F746" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G746" t="s">
         <v>1235</v>
@@ -24138,13 +24138,13 @@
         <v>9</v>
       </c>
       <c r="D747" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E747" t="s">
         <v>1748</v>
       </c>
       <c r="F747" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G747" t="s">
         <v>1235</v>
@@ -24161,13 +24161,13 @@
         <v>9</v>
       </c>
       <c r="D748" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E748" t="s">
         <v>1748</v>
       </c>
       <c r="F748" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G748" t="s">
         <v>1235</v>
@@ -24184,13 +24184,13 @@
         <v>9</v>
       </c>
       <c r="D749" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="E749" t="s">
         <v>1748</v>
       </c>
       <c r="F749" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="G749" t="s">
         <v>1235</v>
@@ -24233,10 +24233,10 @@
         <v>1837</v>
       </c>
       <c r="E751" t="s">
-        <v>1833</v>
+        <v>1838</v>
       </c>
       <c r="F751" t="s">
-        <v>1838</v>
+        <v>1834</v>
       </c>
       <c r="G751" t="s">
         <v>34</v>
@@ -24256,10 +24256,10 @@
         <v>1841</v>
       </c>
       <c r="E752" t="s">
-        <v>1833</v>
+        <v>1842</v>
       </c>
       <c r="F752" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G752" t="s">
         <v>1235</v>
@@ -24279,10 +24279,10 @@
         <v>1841</v>
       </c>
       <c r="E753" t="s">
-        <v>1833</v>
+        <v>1842</v>
       </c>
       <c r="F753" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G753" t="s">
         <v>1235</v>
@@ -24302,10 +24302,10 @@
         <v>1841</v>
       </c>
       <c r="E754" t="s">
-        <v>1833</v>
+        <v>1842</v>
       </c>
       <c r="F754" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G754" t="s">
         <v>1235</v>
@@ -24325,10 +24325,10 @@
         <v>1841</v>
       </c>
       <c r="E755" t="s">
-        <v>1833</v>
+        <v>1842</v>
       </c>
       <c r="F755" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G755" t="s">
         <v>1235</v>
@@ -24348,10 +24348,10 @@
         <v>1841</v>
       </c>
       <c r="E756" t="s">
-        <v>1833</v>
+        <v>1842</v>
       </c>
       <c r="F756" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G756" t="s">
         <v>1235</v>
@@ -24371,10 +24371,10 @@
         <v>1841</v>
       </c>
       <c r="E757" t="s">
-        <v>1833</v>
+        <v>1842</v>
       </c>
       <c r="F757" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G757" t="s">
         <v>1235</v>
@@ -24391,10 +24391,10 @@
         <v>9</v>
       </c>
       <c r="D758" t="s">
-        <v>1837</v>
+        <v>1832</v>
       </c>
       <c r="E758" t="s">
-        <v>1833</v>
+        <v>1838</v>
       </c>
       <c r="F758" t="s">
         <v>1834</v>
@@ -24414,13 +24414,13 @@
         <v>9</v>
       </c>
       <c r="D759" t="s">
-        <v>1841</v>
+        <v>1798</v>
       </c>
       <c r="E759" t="s">
-        <v>1833</v>
+        <v>1842</v>
       </c>
       <c r="F759" t="s">
-        <v>1798</v>
+        <v>1834</v>
       </c>
       <c r="G759" t="s">
         <v>20</v>
@@ -24440,10 +24440,10 @@
         <v>1841</v>
       </c>
       <c r="E760" t="s">
-        <v>1833</v>
+        <v>1842</v>
       </c>
       <c r="F760" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G760" t="s">
         <v>1235</v>
@@ -24463,10 +24463,10 @@
         <v>1841</v>
       </c>
       <c r="E761" t="s">
-        <v>1833</v>
+        <v>1842</v>
       </c>
       <c r="F761" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G761" t="s">
         <v>1235</v>
@@ -24483,13 +24483,13 @@
         <v>9</v>
       </c>
       <c r="D762" t="s">
+        <v>1798</v>
+      </c>
+      <c r="E762" t="s">
         <v>1863</v>
       </c>
-      <c r="E762" t="s">
-        <v>1833</v>
-      </c>
       <c r="F762" t="s">
-        <v>1798</v>
+        <v>1834</v>
       </c>
       <c r="G762" t="s">
         <v>34</v>
@@ -24509,10 +24509,10 @@
         <v>1841</v>
       </c>
       <c r="E763" t="s">
-        <v>1833</v>
+        <v>1842</v>
       </c>
       <c r="F763" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G763" t="s">
         <v>1235</v>
@@ -24532,10 +24532,10 @@
         <v>1868</v>
       </c>
       <c r="E764" t="s">
-        <v>1833</v>
+        <v>1869</v>
       </c>
       <c r="F764" t="s">
-        <v>1869</v>
+        <v>1834</v>
       </c>
       <c r="G764" t="s">
         <v>34</v>
@@ -24552,13 +24552,13 @@
         <v>9</v>
       </c>
       <c r="D765" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="E765" t="s">
         <v>1833</v>
       </c>
       <c r="F765" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G765" t="s">
         <v>34</v>
@@ -24575,13 +24575,13 @@
         <v>9</v>
       </c>
       <c r="D766" t="s">
+        <v>1874</v>
+      </c>
+      <c r="E766" t="s">
         <v>1863</v>
       </c>
-      <c r="E766" t="s">
-        <v>1833</v>
-      </c>
       <c r="F766" t="s">
-        <v>1874</v>
+        <v>1834</v>
       </c>
       <c r="G766" t="s">
         <v>34</v>
@@ -24601,10 +24601,10 @@
         <v>1877</v>
       </c>
       <c r="E767" t="s">
-        <v>1833</v>
+        <v>1878</v>
       </c>
       <c r="F767" t="s">
-        <v>1878</v>
+        <v>1834</v>
       </c>
       <c r="G767" t="s">
         <v>34</v>
@@ -24624,10 +24624,10 @@
         <v>1841</v>
       </c>
       <c r="E768" t="s">
-        <v>1833</v>
+        <v>1842</v>
       </c>
       <c r="F768" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G768" t="s">
         <v>1235</v>
@@ -24647,10 +24647,10 @@
         <v>1841</v>
       </c>
       <c r="E769" t="s">
-        <v>1833</v>
+        <v>1842</v>
       </c>
       <c r="F769" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G769" t="s">
         <v>1235</v>
@@ -24670,10 +24670,10 @@
         <v>1885</v>
       </c>
       <c r="E770" t="s">
-        <v>1833</v>
+        <v>1886</v>
       </c>
       <c r="F770" t="s">
-        <v>1886</v>
+        <v>1834</v>
       </c>
       <c r="G770" t="s">
         <v>34</v>
@@ -24693,10 +24693,10 @@
         <v>1841</v>
       </c>
       <c r="E771" t="s">
-        <v>1833</v>
+        <v>1842</v>
       </c>
       <c r="F771" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G771" t="s">
         <v>1235</v>
@@ -24716,10 +24716,10 @@
         <v>1841</v>
       </c>
       <c r="E772" t="s">
-        <v>1833</v>
+        <v>1842</v>
       </c>
       <c r="F772" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G772" t="s">
         <v>1235</v>
@@ -24739,10 +24739,10 @@
         <v>1841</v>
       </c>
       <c r="E773" t="s">
-        <v>1833</v>
+        <v>1842</v>
       </c>
       <c r="F773" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G773" t="s">
         <v>1235</v>
@@ -24762,10 +24762,10 @@
         <v>1895</v>
       </c>
       <c r="E774" t="s">
-        <v>1833</v>
+        <v>1896</v>
       </c>
       <c r="F774" t="s">
-        <v>1896</v>
+        <v>1834</v>
       </c>
       <c r="G774" t="s">
         <v>34</v>
@@ -24785,10 +24785,10 @@
         <v>1841</v>
       </c>
       <c r="E775" t="s">
-        <v>1833</v>
+        <v>1842</v>
       </c>
       <c r="F775" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="G775" t="s">
         <v>1235</v>
@@ -24828,13 +24828,13 @@
         <v>9</v>
       </c>
       <c r="D777" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E777" t="s">
         <v>1902</v>
       </c>
       <c r="F777" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G777" t="s">
         <v>1235</v>
@@ -24854,10 +24854,10 @@
         <v>1909</v>
       </c>
       <c r="E778" t="s">
-        <v>1902</v>
+        <v>1910</v>
       </c>
       <c r="F778" t="s">
-        <v>1910</v>
+        <v>1903</v>
       </c>
       <c r="G778" t="s">
         <v>34</v>
@@ -24877,10 +24877,10 @@
         <v>1913</v>
       </c>
       <c r="E779" t="s">
-        <v>1902</v>
+        <v>1914</v>
       </c>
       <c r="F779" t="s">
-        <v>1914</v>
+        <v>1903</v>
       </c>
       <c r="G779" t="s">
         <v>34</v>
@@ -24897,13 +24897,13 @@
         <v>9</v>
       </c>
       <c r="D780" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E780" t="s">
         <v>1902</v>
       </c>
       <c r="F780" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G780" t="s">
         <v>1235</v>
@@ -24920,13 +24920,13 @@
         <v>9</v>
       </c>
       <c r="D781" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E781" t="s">
         <v>1902</v>
       </c>
       <c r="F781" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G781" t="s">
         <v>1235</v>
@@ -24943,13 +24943,13 @@
         <v>9</v>
       </c>
       <c r="D782" t="s">
-        <v>1901</v>
+        <v>1921</v>
       </c>
       <c r="E782" t="s">
         <v>1902</v>
       </c>
       <c r="F782" t="s">
-        <v>1921</v>
+        <v>1903</v>
       </c>
       <c r="G782" t="s">
         <v>1235</v>
@@ -24966,13 +24966,13 @@
         <v>9</v>
       </c>
       <c r="D783" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E783" t="s">
         <v>1902</v>
       </c>
       <c r="F783" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G783" t="s">
         <v>1235</v>
@@ -24989,13 +24989,13 @@
         <v>9</v>
       </c>
       <c r="D784" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E784" t="s">
         <v>1902</v>
       </c>
       <c r="F784" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G784" t="s">
         <v>1235</v>
@@ -25012,13 +25012,13 @@
         <v>9</v>
       </c>
       <c r="D785" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E785" t="s">
         <v>1902</v>
       </c>
       <c r="F785" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G785" t="s">
         <v>1235</v>
@@ -25035,13 +25035,13 @@
         <v>9</v>
       </c>
       <c r="D786" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E786" t="s">
         <v>1902</v>
       </c>
       <c r="F786" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G786" t="s">
         <v>1235</v>
@@ -25058,13 +25058,13 @@
         <v>9</v>
       </c>
       <c r="D787" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E787" t="s">
         <v>1902</v>
       </c>
       <c r="F787" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G787" t="s">
         <v>1235</v>
@@ -25081,13 +25081,13 @@
         <v>9</v>
       </c>
       <c r="D788" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E788" t="s">
         <v>1902</v>
       </c>
       <c r="F788" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G788" t="s">
         <v>1235</v>
@@ -25104,10 +25104,10 @@
         <v>9</v>
       </c>
       <c r="D789" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E789" t="s">
         <v>1936</v>
-      </c>
-      <c r="E789" t="s">
-        <v>1902</v>
       </c>
       <c r="F789" t="s">
         <v>1903</v>
@@ -25127,13 +25127,13 @@
         <v>9</v>
       </c>
       <c r="D790" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E790" t="s">
         <v>1902</v>
       </c>
       <c r="F790" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G790" t="s">
         <v>1235</v>
@@ -25150,13 +25150,13 @@
         <v>9</v>
       </c>
       <c r="D791" t="s">
+        <v>1921</v>
+      </c>
+      <c r="E791" t="s">
         <v>1941</v>
       </c>
-      <c r="E791" t="s">
-        <v>1902</v>
-      </c>
       <c r="F791" t="s">
-        <v>1921</v>
+        <v>1903</v>
       </c>
       <c r="G791" t="s">
         <v>34</v>
@@ -25173,13 +25173,13 @@
         <v>9</v>
       </c>
       <c r="D792" t="s">
+        <v>1944</v>
+      </c>
+      <c r="E792" t="s">
         <v>1936</v>
       </c>
-      <c r="E792" t="s">
-        <v>1902</v>
-      </c>
       <c r="F792" t="s">
-        <v>1944</v>
+        <v>1903</v>
       </c>
       <c r="G792" t="s">
         <v>34</v>
@@ -25196,13 +25196,13 @@
         <v>9</v>
       </c>
       <c r="D793" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E793" t="s">
         <v>1902</v>
       </c>
       <c r="F793" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G793" t="s">
         <v>1235</v>
@@ -25219,13 +25219,13 @@
         <v>9</v>
       </c>
       <c r="D794" t="s">
+        <v>1906</v>
+      </c>
+      <c r="E794" t="s">
         <v>1949</v>
       </c>
-      <c r="E794" t="s">
-        <v>1902</v>
-      </c>
       <c r="F794" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G794" t="s">
         <v>34</v>
@@ -25242,13 +25242,13 @@
         <v>9</v>
       </c>
       <c r="D795" t="s">
-        <v>1901</v>
+        <v>1952</v>
       </c>
       <c r="E795" t="s">
         <v>1902</v>
       </c>
       <c r="F795" t="s">
-        <v>1952</v>
+        <v>1903</v>
       </c>
       <c r="G795" t="s">
         <v>34</v>
@@ -25265,13 +25265,13 @@
         <v>9</v>
       </c>
       <c r="D796" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E796" t="s">
         <v>1902</v>
       </c>
       <c r="F796" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G796" t="s">
         <v>1235</v>
@@ -25291,10 +25291,10 @@
         <v>1957</v>
       </c>
       <c r="E797" t="s">
-        <v>1902</v>
+        <v>1958</v>
       </c>
       <c r="F797" t="s">
-        <v>1958</v>
+        <v>1903</v>
       </c>
       <c r="G797" t="s">
         <v>34</v>
@@ -25314,10 +25314,10 @@
         <v>1961</v>
       </c>
       <c r="E798" t="s">
-        <v>1902</v>
+        <v>1962</v>
       </c>
       <c r="F798" t="s">
-        <v>1962</v>
+        <v>1903</v>
       </c>
       <c r="G798" t="s">
         <v>34</v>
@@ -25334,13 +25334,13 @@
         <v>9</v>
       </c>
       <c r="D799" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E799" t="s">
         <v>1902</v>
       </c>
       <c r="F799" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G799" t="s">
         <v>1235</v>
@@ -25357,13 +25357,13 @@
         <v>9</v>
       </c>
       <c r="D800" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E800" t="s">
         <v>1902</v>
       </c>
       <c r="F800" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G800" t="s">
         <v>1235</v>
@@ -25380,13 +25380,13 @@
         <v>9</v>
       </c>
       <c r="D801" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E801" t="s">
         <v>1902</v>
       </c>
       <c r="F801" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G801" t="s">
         <v>1235</v>
@@ -25403,13 +25403,13 @@
         <v>9</v>
       </c>
       <c r="D802" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E802" t="s">
         <v>1902</v>
       </c>
       <c r="F802" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G802" t="s">
         <v>1235</v>
@@ -25426,13 +25426,13 @@
         <v>9</v>
       </c>
       <c r="D803" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E803" t="s">
         <v>1902</v>
       </c>
       <c r="F803" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G803" t="s">
         <v>1235</v>
@@ -25449,13 +25449,13 @@
         <v>9</v>
       </c>
       <c r="D804" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E804" t="s">
         <v>1902</v>
       </c>
       <c r="F804" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G804" t="s">
         <v>1235</v>
@@ -25472,13 +25472,13 @@
         <v>9</v>
       </c>
       <c r="D805" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E805" t="s">
         <v>1902</v>
       </c>
       <c r="F805" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G805" t="s">
         <v>1235</v>
@@ -25495,13 +25495,13 @@
         <v>9</v>
       </c>
       <c r="D806" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E806" t="s">
         <v>1902</v>
       </c>
       <c r="F806" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G806" t="s">
         <v>1235</v>
@@ -25518,13 +25518,13 @@
         <v>9</v>
       </c>
       <c r="D807" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="E807" t="s">
         <v>1902</v>
       </c>
       <c r="F807" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G807" t="s">
         <v>1235</v>
@@ -25613,10 +25613,10 @@
         <v>1992</v>
       </c>
       <c r="E811" t="s">
-        <v>1984</v>
+        <v>1993</v>
       </c>
       <c r="F811" t="s">
-        <v>1993</v>
+        <v>1985</v>
       </c>
       <c r="G811" t="s">
         <v>34</v>
@@ -25679,13 +25679,13 @@
         <v>9</v>
       </c>
       <c r="D814" t="s">
-        <v>1983</v>
+        <v>1992</v>
       </c>
       <c r="E814" t="s">
         <v>1984</v>
       </c>
       <c r="F814" t="s">
-        <v>1993</v>
+        <v>1985</v>
       </c>
       <c r="G814" t="s">
         <v>1235</v>
@@ -25705,10 +25705,10 @@
         <v>2002</v>
       </c>
       <c r="E815" t="s">
-        <v>1984</v>
+        <v>2003</v>
       </c>
       <c r="F815" t="s">
-        <v>2003</v>
+        <v>1985</v>
       </c>
       <c r="G815" t="s">
         <v>34</v>
@@ -25843,10 +25843,10 @@
         <v>2016</v>
       </c>
       <c r="E821" t="s">
-        <v>1984</v>
+        <v>2017</v>
       </c>
       <c r="F821" t="s">
-        <v>2017</v>
+        <v>1985</v>
       </c>
       <c r="G821" t="s">
         <v>20</v>
@@ -25866,10 +25866,10 @@
         <v>2020</v>
       </c>
       <c r="E822" t="s">
-        <v>1984</v>
+        <v>2021</v>
       </c>
       <c r="F822" t="s">
-        <v>2021</v>
+        <v>1985</v>
       </c>
       <c r="G822" t="s">
         <v>1235</v>
@@ -25886,13 +25886,13 @@
         <v>9</v>
       </c>
       <c r="D823" t="s">
-        <v>1983</v>
+        <v>2020</v>
       </c>
       <c r="E823" t="s">
         <v>1984</v>
       </c>
       <c r="F823" t="s">
-        <v>2021</v>
+        <v>1985</v>
       </c>
       <c r="G823" t="s">
         <v>1235</v>
@@ -25912,10 +25912,10 @@
         <v>2020</v>
       </c>
       <c r="E824" t="s">
-        <v>1984</v>
+        <v>2021</v>
       </c>
       <c r="F824" t="s">
-        <v>2021</v>
+        <v>1985</v>
       </c>
       <c r="G824" t="s">
         <v>1235</v>
@@ -25935,10 +25935,10 @@
         <v>2020</v>
       </c>
       <c r="E825" t="s">
-        <v>1984</v>
+        <v>2021</v>
       </c>
       <c r="F825" t="s">
-        <v>2021</v>
+        <v>1985</v>
       </c>
       <c r="G825" t="s">
         <v>1235</v>
@@ -25958,10 +25958,10 @@
         <v>2020</v>
       </c>
       <c r="E826" t="s">
-        <v>1984</v>
+        <v>2021</v>
       </c>
       <c r="F826" t="s">
-        <v>2021</v>
+        <v>1985</v>
       </c>
       <c r="G826" t="s">
         <v>1235</v>
@@ -25981,10 +25981,10 @@
         <v>2020</v>
       </c>
       <c r="E827" t="s">
-        <v>1984</v>
+        <v>2021</v>
       </c>
       <c r="F827" t="s">
-        <v>2021</v>
+        <v>1985</v>
       </c>
       <c r="G827" t="s">
         <v>1235</v>
@@ -26001,13 +26001,13 @@
         <v>9</v>
       </c>
       <c r="D828" t="s">
-        <v>1983</v>
+        <v>2020</v>
       </c>
       <c r="E828" t="s">
         <v>1984</v>
       </c>
       <c r="F828" t="s">
-        <v>2021</v>
+        <v>1985</v>
       </c>
       <c r="G828" t="s">
         <v>1235</v>
@@ -26047,13 +26047,13 @@
         <v>9</v>
       </c>
       <c r="D830" t="s">
-        <v>1983</v>
+        <v>1992</v>
       </c>
       <c r="E830" t="s">
         <v>1984</v>
       </c>
       <c r="F830" t="s">
-        <v>1993</v>
+        <v>1985</v>
       </c>
       <c r="G830" t="s">
         <v>1235</v>
@@ -26277,13 +26277,13 @@
         <v>9</v>
       </c>
       <c r="D840" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E840" t="s">
         <v>2057</v>
       </c>
       <c r="F840" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G840" t="s">
         <v>1235</v>
@@ -26300,13 +26300,13 @@
         <v>9</v>
       </c>
       <c r="D841" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E841" t="s">
         <v>2057</v>
       </c>
       <c r="F841" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G841" t="s">
         <v>1235</v>
@@ -26323,13 +26323,13 @@
         <v>9</v>
       </c>
       <c r="D842" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E842" t="s">
         <v>2057</v>
       </c>
       <c r="F842" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G842" t="s">
         <v>1235</v>
@@ -26346,13 +26346,13 @@
         <v>9</v>
       </c>
       <c r="D843" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E843" t="s">
         <v>2057</v>
       </c>
       <c r="F843" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G843" t="s">
         <v>1235</v>
@@ -26369,13 +26369,13 @@
         <v>9</v>
       </c>
       <c r="D844" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E844" t="s">
         <v>2057</v>
       </c>
       <c r="F844" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G844" t="s">
         <v>1235</v>
@@ -26392,13 +26392,13 @@
         <v>9</v>
       </c>
       <c r="D845" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E845" t="s">
         <v>2057</v>
       </c>
       <c r="F845" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G845" t="s">
         <v>1235</v>
@@ -26415,13 +26415,13 @@
         <v>9</v>
       </c>
       <c r="D846" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E846" t="s">
         <v>2057</v>
       </c>
       <c r="F846" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G846" t="s">
         <v>1235</v>
@@ -26438,13 +26438,13 @@
         <v>9</v>
       </c>
       <c r="D847" t="s">
-        <v>1992</v>
+        <v>2076</v>
       </c>
       <c r="E847" t="s">
-        <v>2057</v>
+        <v>1993</v>
       </c>
       <c r="F847" t="s">
-        <v>2076</v>
+        <v>2058</v>
       </c>
       <c r="G847" t="s">
         <v>1235</v>
@@ -26461,13 +26461,13 @@
         <v>9</v>
       </c>
       <c r="D848" t="s">
-        <v>1992</v>
+        <v>2076</v>
       </c>
       <c r="E848" t="s">
-        <v>2057</v>
+        <v>1993</v>
       </c>
       <c r="F848" t="s">
-        <v>2076</v>
+        <v>2058</v>
       </c>
       <c r="G848" t="s">
         <v>1235</v>
@@ -26484,13 +26484,13 @@
         <v>9</v>
       </c>
       <c r="D849" t="s">
-        <v>1992</v>
+        <v>2076</v>
       </c>
       <c r="E849" t="s">
-        <v>2057</v>
+        <v>1993</v>
       </c>
       <c r="F849" t="s">
-        <v>2076</v>
+        <v>2058</v>
       </c>
       <c r="G849" t="s">
         <v>1235</v>
@@ -26507,13 +26507,13 @@
         <v>9</v>
       </c>
       <c r="D850" t="s">
+        <v>2076</v>
+      </c>
+      <c r="E850" t="s">
         <v>2083</v>
       </c>
-      <c r="E850" t="s">
-        <v>2057</v>
-      </c>
       <c r="F850" t="s">
-        <v>2076</v>
+        <v>2058</v>
       </c>
       <c r="G850" t="s">
         <v>1235</v>
@@ -26530,13 +26530,13 @@
         <v>9</v>
       </c>
       <c r="D851" t="s">
-        <v>1992</v>
+        <v>2076</v>
       </c>
       <c r="E851" t="s">
-        <v>2057</v>
+        <v>1993</v>
       </c>
       <c r="F851" t="s">
-        <v>2076</v>
+        <v>2058</v>
       </c>
       <c r="G851" t="s">
         <v>1235</v>
@@ -26553,13 +26553,13 @@
         <v>9</v>
       </c>
       <c r="D852" t="s">
-        <v>1992</v>
+        <v>2076</v>
       </c>
       <c r="E852" t="s">
-        <v>2057</v>
+        <v>1993</v>
       </c>
       <c r="F852" t="s">
-        <v>2076</v>
+        <v>2058</v>
       </c>
       <c r="G852" t="s">
         <v>1235</v>
@@ -26576,13 +26576,13 @@
         <v>9</v>
       </c>
       <c r="D853" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E853" t="s">
         <v>2057</v>
       </c>
       <c r="F853" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G853" t="s">
         <v>1235</v>
@@ -26599,13 +26599,13 @@
         <v>9</v>
       </c>
       <c r="D854" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E854" t="s">
         <v>2057</v>
       </c>
       <c r="F854" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G854" t="s">
         <v>20</v>
@@ -26622,13 +26622,13 @@
         <v>9</v>
       </c>
       <c r="D855" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E855" t="s">
         <v>2057</v>
       </c>
       <c r="F855" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G855" t="s">
         <v>20</v>
@@ -26645,13 +26645,13 @@
         <v>9</v>
       </c>
       <c r="D856" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E856" t="s">
         <v>2057</v>
       </c>
       <c r="F856" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G856" t="s">
         <v>20</v>
@@ -26668,13 +26668,13 @@
         <v>9</v>
       </c>
       <c r="D857" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E857" t="s">
         <v>2057</v>
       </c>
       <c r="F857" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G857" t="s">
         <v>1235</v>
@@ -26691,13 +26691,13 @@
         <v>9</v>
       </c>
       <c r="D858" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E858" t="s">
         <v>2057</v>
       </c>
       <c r="F858" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G858" t="s">
         <v>1235</v>
@@ -26714,13 +26714,13 @@
         <v>9</v>
       </c>
       <c r="D859" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E859" t="s">
         <v>2057</v>
       </c>
       <c r="F859" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G859" t="s">
         <v>20</v>
@@ -26737,13 +26737,13 @@
         <v>9</v>
       </c>
       <c r="D860" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E860" t="s">
         <v>2057</v>
       </c>
       <c r="F860" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G860" t="s">
         <v>1235</v>
@@ -26760,13 +26760,13 @@
         <v>9</v>
       </c>
       <c r="D861" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E861" t="s">
         <v>2057</v>
       </c>
       <c r="F861" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G861" t="s">
         <v>1235</v>
@@ -26783,13 +26783,13 @@
         <v>9</v>
       </c>
       <c r="D862" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E862" t="s">
         <v>2057</v>
       </c>
       <c r="F862" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G862" t="s">
         <v>1235</v>
@@ -26806,13 +26806,13 @@
         <v>9</v>
       </c>
       <c r="D863" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E863" t="s">
         <v>2057</v>
       </c>
       <c r="F863" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G863" t="s">
         <v>1235</v>
@@ -26829,13 +26829,13 @@
         <v>9</v>
       </c>
       <c r="D864" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E864" t="s">
         <v>2057</v>
       </c>
       <c r="F864" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G864" t="s">
         <v>1235</v>
@@ -26852,13 +26852,13 @@
         <v>9</v>
       </c>
       <c r="D865" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E865" t="s">
         <v>2057</v>
       </c>
       <c r="F865" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G865" t="s">
         <v>1235</v>
@@ -26875,13 +26875,13 @@
         <v>9</v>
       </c>
       <c r="D866" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="E866" t="s">
         <v>2057</v>
       </c>
       <c r="F866" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="G866" t="s">
         <v>1235</v>
@@ -26921,10 +26921,10 @@
         <v>9</v>
       </c>
       <c r="D868" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E868" t="s">
         <v>2123</v>
-      </c>
-      <c r="E868" t="s">
-        <v>2119</v>
       </c>
       <c r="F868" t="s">
         <v>2120</v>
@@ -26944,10 +26944,10 @@
         <v>9</v>
       </c>
       <c r="D869" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E869" t="s">
         <v>2123</v>
-      </c>
-      <c r="E869" t="s">
-        <v>2119</v>
       </c>
       <c r="F869" t="s">
         <v>2120</v>
@@ -26967,10 +26967,10 @@
         <v>9</v>
       </c>
       <c r="D870" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E870" t="s">
         <v>2123</v>
-      </c>
-      <c r="E870" t="s">
-        <v>2119</v>
       </c>
       <c r="F870" t="s">
         <v>2120</v>
@@ -26990,10 +26990,10 @@
         <v>9</v>
       </c>
       <c r="D871" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E871" t="s">
         <v>2123</v>
-      </c>
-      <c r="E871" t="s">
-        <v>2119</v>
       </c>
       <c r="F871" t="s">
         <v>2120</v>
@@ -27013,10 +27013,10 @@
         <v>9</v>
       </c>
       <c r="D872" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E872" t="s">
         <v>2123</v>
-      </c>
-      <c r="E872" t="s">
-        <v>2119</v>
       </c>
       <c r="F872" t="s">
         <v>2120</v>
@@ -27036,10 +27036,10 @@
         <v>9</v>
       </c>
       <c r="D873" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E873" t="s">
         <v>2123</v>
-      </c>
-      <c r="E873" t="s">
-        <v>2119</v>
       </c>
       <c r="F873" t="s">
         <v>2120</v>
@@ -27059,10 +27059,10 @@
         <v>9</v>
       </c>
       <c r="D874" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E874" t="s">
         <v>2123</v>
-      </c>
-      <c r="E874" t="s">
-        <v>2119</v>
       </c>
       <c r="F874" t="s">
         <v>2120</v>
@@ -27082,10 +27082,10 @@
         <v>9</v>
       </c>
       <c r="D875" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E875" t="s">
         <v>2123</v>
-      </c>
-      <c r="E875" t="s">
-        <v>2119</v>
       </c>
       <c r="F875" t="s">
         <v>2120</v>
@@ -27105,10 +27105,10 @@
         <v>9</v>
       </c>
       <c r="D876" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E876" t="s">
         <v>2123</v>
-      </c>
-      <c r="E876" t="s">
-        <v>2119</v>
       </c>
       <c r="F876" t="s">
         <v>2120</v>
@@ -27128,10 +27128,10 @@
         <v>9</v>
       </c>
       <c r="D877" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E877" t="s">
         <v>2123</v>
-      </c>
-      <c r="E877" t="s">
-        <v>2119</v>
       </c>
       <c r="F877" t="s">
         <v>2120</v>
@@ -27151,10 +27151,10 @@
         <v>9</v>
       </c>
       <c r="D878" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E878" t="s">
         <v>2123</v>
-      </c>
-      <c r="E878" t="s">
-        <v>2119</v>
       </c>
       <c r="F878" t="s">
         <v>2120</v>
@@ -27174,10 +27174,10 @@
         <v>9</v>
       </c>
       <c r="D879" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E879" t="s">
         <v>2123</v>
-      </c>
-      <c r="E879" t="s">
-        <v>2119</v>
       </c>
       <c r="F879" t="s">
         <v>2120</v>
@@ -27197,10 +27197,10 @@
         <v>9</v>
       </c>
       <c r="D880" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E880" t="s">
         <v>2123</v>
-      </c>
-      <c r="E880" t="s">
-        <v>2119</v>
       </c>
       <c r="F880" t="s">
         <v>2120</v>
@@ -27220,10 +27220,10 @@
         <v>9</v>
       </c>
       <c r="D881" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E881" t="s">
         <v>2123</v>
-      </c>
-      <c r="E881" t="s">
-        <v>2119</v>
       </c>
       <c r="F881" t="s">
         <v>2120</v>
@@ -27243,10 +27243,10 @@
         <v>9</v>
       </c>
       <c r="D882" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E882" t="s">
         <v>2123</v>
-      </c>
-      <c r="E882" t="s">
-        <v>2119</v>
       </c>
       <c r="F882" t="s">
         <v>2120</v>
@@ -27266,10 +27266,10 @@
         <v>9</v>
       </c>
       <c r="D883" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E883" t="s">
         <v>2123</v>
-      </c>
-      <c r="E883" t="s">
-        <v>2119</v>
       </c>
       <c r="F883" t="s">
         <v>2120</v>
@@ -27289,10 +27289,10 @@
         <v>9</v>
       </c>
       <c r="D884" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E884" t="s">
         <v>2123</v>
-      </c>
-      <c r="E884" t="s">
-        <v>2119</v>
       </c>
       <c r="F884" t="s">
         <v>2120</v>
@@ -27312,10 +27312,10 @@
         <v>9</v>
       </c>
       <c r="D885" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E885" t="s">
         <v>2123</v>
-      </c>
-      <c r="E885" t="s">
-        <v>2119</v>
       </c>
       <c r="F885" t="s">
         <v>2120</v>
@@ -27335,10 +27335,10 @@
         <v>9</v>
       </c>
       <c r="D886" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E886" t="s">
         <v>2123</v>
-      </c>
-      <c r="E886" t="s">
-        <v>2119</v>
       </c>
       <c r="F886" t="s">
         <v>2120</v>
@@ -27358,10 +27358,10 @@
         <v>9</v>
       </c>
       <c r="D887" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E887" t="s">
         <v>2123</v>
-      </c>
-      <c r="E887" t="s">
-        <v>2119</v>
       </c>
       <c r="F887" t="s">
         <v>2120</v>
@@ -27381,10 +27381,10 @@
         <v>9</v>
       </c>
       <c r="D888" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E888" t="s">
         <v>2123</v>
-      </c>
-      <c r="E888" t="s">
-        <v>2119</v>
       </c>
       <c r="F888" t="s">
         <v>2120</v>
@@ -27404,10 +27404,10 @@
         <v>9</v>
       </c>
       <c r="D889" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E889" t="s">
         <v>2123</v>
-      </c>
-      <c r="E889" t="s">
-        <v>2119</v>
       </c>
       <c r="F889" t="s">
         <v>2120</v>
@@ -27542,13 +27542,13 @@
         <v>9</v>
       </c>
       <c r="D895" t="s">
-        <v>2168</v>
+        <v>2181</v>
       </c>
       <c r="E895" t="s">
         <v>2169</v>
       </c>
       <c r="F895" t="s">
-        <v>2181</v>
+        <v>2170</v>
       </c>
       <c r="G895" t="s">
         <v>1235</v>
@@ -27749,10 +27749,10 @@
         <v>9</v>
       </c>
       <c r="D904" t="s">
-        <v>2168</v>
+        <v>2200</v>
       </c>
       <c r="E904" t="s">
-        <v>2200</v>
+        <v>2169</v>
       </c>
       <c r="F904" t="s">
         <v>2201</v>
@@ -27772,13 +27772,13 @@
         <v>9</v>
       </c>
       <c r="D905" t="s">
-        <v>2168</v>
+        <v>2204</v>
       </c>
       <c r="E905" t="s">
-        <v>2200</v>
+        <v>2169</v>
       </c>
       <c r="F905" t="s">
-        <v>2204</v>
+        <v>2201</v>
       </c>
       <c r="G905" t="s">
         <v>1235</v>
@@ -27795,10 +27795,10 @@
         <v>9</v>
       </c>
       <c r="D906" t="s">
-        <v>2168</v>
+        <v>2200</v>
       </c>
       <c r="E906" t="s">
-        <v>2200</v>
+        <v>2169</v>
       </c>
       <c r="F906" t="s">
         <v>2201</v>

--- a/api/2/clv3/xlsx/en/HumanitarianPlan.xlsx
+++ b/api/2/clv3/xlsx/en/HumanitarianPlan.xlsx
@@ -25,12 +25,12 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:plan-year</t>
+  </si>
+  <si>
     <t>codeforiati:plan-start-date</t>
   </si>
   <si>
-    <t>codeforiati:plan-year</t>
-  </si>
-  <si>
     <t>codeforiati:plan-type</t>
   </si>
   <si>
@@ -46,12 +46,12 @@
     <t>active</t>
   </si>
   <si>
+    <t>2025</t>
+  </si>
+  <si>
     <t>2025-01-01</t>
   </si>
   <si>
-    <t>2025</t>
-  </si>
-  <si>
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
@@ -364,12 +364,12 @@
     <t>Afghanistan Humanitarian Needs and Response Plan 2024</t>
   </si>
   <si>
+    <t>2024</t>
+  </si>
+  <si>
     <t>2024-01-01</t>
   </si>
   <si>
-    <t>2024</t>
-  </si>
-  <si>
     <t>2024-12-31</t>
   </si>
   <si>
@@ -721,12 +721,12 @@
     <t>Afghanistan Humanitarian Response Plan 2023</t>
   </si>
   <si>
+    <t>2023</t>
+  </si>
+  <si>
     <t>2023-01-01</t>
   </si>
   <si>
-    <t>2023</t>
-  </si>
-  <si>
     <t>2023-12-31</t>
   </si>
   <si>
@@ -1039,12 +1039,12 @@
     <t>Afghanistan Humanitarian Response Plan 2022</t>
   </si>
   <si>
+    <t>2022</t>
+  </si>
+  <si>
     <t>2022-01-01</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
     <t>2022-12-31</t>
   </si>
   <si>
@@ -1387,12 +1387,12 @@
     <t>Afghanistan Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021</t>
+  </si>
+  <si>
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021</t>
-  </si>
-  <si>
     <t>2021-12-31</t>
   </si>
   <si>
@@ -1744,12 +1744,12 @@
     <t>Afghanistan Humanitarian Response Plan 2020</t>
   </si>
   <si>
+    <t>2020</t>
+  </si>
+  <si>
     <t>2020-01-01</t>
   </si>
   <si>
-    <t>2020</t>
-  </si>
-  <si>
     <t>2020-12-31</t>
   </si>
   <si>
@@ -2179,12 +2179,12 @@
     <t>Afghanistan Humanitarian Response Plan 2019</t>
   </si>
   <si>
+    <t>2019</t>
+  </si>
+  <si>
     <t>2019-01-01</t>
   </si>
   <si>
-    <t>2019</t>
-  </si>
-  <si>
     <t>2019-12-31</t>
   </si>
   <si>
@@ -2416,12 +2416,12 @@
     <t>Afghanistan Humanitarian Response Plan 2018</t>
   </si>
   <si>
+    <t>2018</t>
+  </si>
+  <si>
     <t>2018-01-01</t>
   </si>
   <si>
-    <t>2018</t>
-  </si>
-  <si>
     <t>2018-12-31</t>
   </si>
   <si>
@@ -2641,12 +2641,12 @@
     <t>Regional Refugee and Migrant Response Plan for Europe 2017</t>
   </si>
   <si>
+    <t>2017</t>
+  </si>
+  <si>
     <t>2017-01-01</t>
   </si>
   <si>
-    <t>2017</t>
-  </si>
-  <si>
     <t>2017-12-31</t>
   </si>
   <si>
@@ -2932,12 +2932,12 @@
     <t>Regional Refugee and Migrant Response Plan for Europe 2016</t>
   </si>
   <si>
+    <t>2016</t>
+  </si>
+  <si>
     <t>2016-01-01</t>
   </si>
   <si>
-    <t>2016</t>
-  </si>
-  <si>
     <t>2016-12-31</t>
   </si>
   <si>
@@ -3214,12 +3214,12 @@
     <t>Afghanistan Strategic Response Plan 2015</t>
   </si>
   <si>
+    <t>2015</t>
+  </si>
+  <si>
     <t>2015-01-01</t>
   </si>
   <si>
-    <t>2015</t>
-  </si>
-  <si>
     <t>Strategic response plan</t>
   </si>
   <si>
@@ -3448,12 +3448,12 @@
     <t>Afghanistan Strategic Response Plan 2014</t>
   </si>
   <si>
+    <t>2014</t>
+  </si>
+  <si>
     <t>2014-01-01</t>
   </si>
   <si>
-    <t>2014</t>
-  </si>
-  <si>
     <t>2014-12-31</t>
   </si>
   <si>
@@ -3901,12 +3901,12 @@
     <t>2012+ Kenya Emergency Humanitarian Response Plan</t>
   </si>
   <si>
+    <t>2012</t>
+  </si>
+  <si>
     <t>2012-01-01</t>
   </si>
   <si>
-    <t>2012</t>
-  </si>
-  <si>
     <t>2012-12-31</t>
   </si>
   <si>
@@ -4087,12 +4087,12 @@
     <t>2011+ Kenya Emergency Humanitarian Response Plan</t>
   </si>
   <si>
+    <t>2011</t>
+  </si>
+  <si>
     <t>2011-01-01</t>
   </si>
   <si>
-    <t>2011</t>
-  </si>
-  <si>
     <t>CAFG11</t>
   </si>
   <si>
@@ -4282,12 +4282,12 @@
     <t>Afghanistan Humanitarian Action Plan 2010</t>
   </si>
   <si>
+    <t>2010</t>
+  </si>
+  <si>
     <t>2010-01-01</t>
   </si>
   <si>
-    <t>2010</t>
-  </si>
-  <si>
     <t>2010-12-31</t>
   </si>
   <si>
@@ -4504,12 +4504,12 @@
     <t>Afghanistan Humanitarian Action Plan 2009</t>
   </si>
   <si>
+    <t>2009</t>
+  </si>
+  <si>
     <t>2009-01-01</t>
   </si>
   <si>
-    <t>2009</t>
-  </si>
-  <si>
     <t>2009-12-31</t>
   </si>
   <si>
@@ -4726,12 +4726,12 @@
     <t>Afghanistan Joint Appeal 2008: Humanitarian Consequences of Rise in Food Prices (February - June 2008)</t>
   </si>
   <si>
+    <t>2008</t>
+  </si>
+  <si>
     <t>2008-02-01</t>
   </si>
   <si>
-    <t>2008</t>
-  </si>
-  <si>
     <t>2008-06-30</t>
   </si>
   <si>
@@ -4999,12 +4999,12 @@
     <t>Bolivia Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007</t>
+  </si>
+  <si>
     <t>2007-02-22</t>
   </si>
   <si>
-    <t>2007</t>
-  </si>
-  <si>
     <t>2007-08-21</t>
   </si>
   <si>
@@ -5311,12 +5311,12 @@
     <t>Afghanistan Drought Joint Appeal 2006</t>
   </si>
   <si>
+    <t>2006</t>
+  </si>
+  <si>
     <t>2006-07-01</t>
   </si>
   <si>
-    <t>2006</t>
-  </si>
-  <si>
     <t>2006-12-31</t>
   </si>
   <si>
@@ -5569,12 +5569,12 @@
     <t>Angola Marburg VHF 2005</t>
   </si>
   <si>
+    <t>2005</t>
+  </si>
+  <si>
     <t>2005-04-01</t>
   </si>
   <si>
-    <t>2005</t>
-  </si>
-  <si>
     <t>2005-06-30</t>
   </si>
   <si>
@@ -5785,12 +5785,12 @@
     <t>Afghanistan UN-Government Drought Appeal 2004</t>
   </si>
   <si>
+    <t>2004</t>
+  </si>
+  <si>
     <t>2004-09-01</t>
   </si>
   <si>
-    <t>2004</t>
-  </si>
-  <si>
     <t>2004-12-31</t>
   </si>
   <si>
@@ -6034,12 +6034,12 @@
     <t>Afghanistan TAPA 2003</t>
   </si>
   <si>
+    <t>2003</t>
+  </si>
+  <si>
     <t>2003-01-01</t>
   </si>
   <si>
-    <t>2003</t>
-  </si>
-  <si>
     <t>2003-12-31</t>
   </si>
   <si>
@@ -6271,12 +6271,12 @@
     <t>Afghanistan 2002 (ITAP for the Afghan People)</t>
   </si>
   <si>
+    <t>2002</t>
+  </si>
+  <si>
     <t>2001-10-01</t>
   </si>
   <si>
-    <t>2002</t>
-  </si>
-  <si>
     <t>2002-12-31</t>
   </si>
   <si>
@@ -6463,12 +6463,12 @@
     <t>Afghanistan 2001</t>
   </si>
   <si>
+    <t>2001</t>
+  </si>
+  <si>
     <t>2001-01-01</t>
   </si>
   <si>
-    <t>2001</t>
-  </si>
-  <si>
     <t>2001-09-30</t>
   </si>
   <si>
@@ -6616,10 +6616,10 @@
     <t>Angola 2000</t>
   </si>
   <si>
+    <t>2000</t>
+  </si>
+  <si>
     <t>2000-01-01</t>
-  </si>
-  <si>
-    <t>2000</t>
   </si>
   <si>
     <t>2000-12-31</t>
@@ -7516,10 +7516,10 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
         <v>58</v>
-      </c>
-      <c r="E20" t="s">
-        <v>11</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
@@ -7838,10 +7838,10 @@
         <v>9</v>
       </c>
       <c r="D34" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" t="s">
         <v>88</v>
-      </c>
-      <c r="E34" t="s">
-        <v>11</v>
       </c>
       <c r="F34" t="s">
         <v>34</v>
@@ -8045,10 +8045,10 @@
         <v>9</v>
       </c>
       <c r="D43" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" t="s">
         <v>107</v>
-      </c>
-      <c r="E43" t="s">
-        <v>11</v>
       </c>
       <c r="F43" t="s">
         <v>19</v>
@@ -8183,10 +8183,10 @@
         <v>9</v>
       </c>
       <c r="D49" t="s">
+        <v>116</v>
+      </c>
+      <c r="E49" t="s">
         <v>123</v>
-      </c>
-      <c r="E49" t="s">
-        <v>117</v>
       </c>
       <c r="F49" t="s">
         <v>19</v>
@@ -8229,10 +8229,10 @@
         <v>9</v>
       </c>
       <c r="D51" t="s">
+        <v>116</v>
+      </c>
+      <c r="E51" t="s">
         <v>128</v>
-      </c>
-      <c r="E51" t="s">
-        <v>117</v>
       </c>
       <c r="F51" t="s">
         <v>19</v>
@@ -8390,10 +8390,10 @@
         <v>9</v>
       </c>
       <c r="D58" t="s">
+        <v>116</v>
+      </c>
+      <c r="E58" t="s">
         <v>143</v>
-      </c>
-      <c r="E58" t="s">
-        <v>117</v>
       </c>
       <c r="F58" t="s">
         <v>34</v>
@@ -8482,10 +8482,10 @@
         <v>9</v>
       </c>
       <c r="D62" t="s">
+        <v>116</v>
+      </c>
+      <c r="E62" t="s">
         <v>152</v>
-      </c>
-      <c r="E62" t="s">
-        <v>117</v>
       </c>
       <c r="F62" t="s">
         <v>19</v>
@@ -8505,10 +8505,10 @@
         <v>9</v>
       </c>
       <c r="D63" t="s">
+        <v>116</v>
+      </c>
+      <c r="E63" t="s">
         <v>152</v>
-      </c>
-      <c r="E63" t="s">
-        <v>117</v>
       </c>
       <c r="F63" t="s">
         <v>34</v>
@@ -8574,10 +8574,10 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
+        <v>116</v>
+      </c>
+      <c r="E66" t="s">
         <v>163</v>
-      </c>
-      <c r="E66" t="s">
-        <v>117</v>
       </c>
       <c r="F66" t="s">
         <v>34</v>
@@ -8620,10 +8620,10 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
+        <v>116</v>
+      </c>
+      <c r="E68" t="s">
         <v>168</v>
-      </c>
-      <c r="E68" t="s">
-        <v>117</v>
       </c>
       <c r="F68" t="s">
         <v>19</v>
@@ -8643,10 +8643,10 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
+        <v>116</v>
+      </c>
+      <c r="E69" t="s">
         <v>171</v>
-      </c>
-      <c r="E69" t="s">
-        <v>117</v>
       </c>
       <c r="F69" t="s">
         <v>34</v>
@@ -8712,10 +8712,10 @@
         <v>9</v>
       </c>
       <c r="D72" t="s">
+        <v>116</v>
+      </c>
+      <c r="E72" t="s">
         <v>178</v>
-      </c>
-      <c r="E72" t="s">
-        <v>117</v>
       </c>
       <c r="F72" t="s">
         <v>19</v>
@@ -8781,10 +8781,10 @@
         <v>9</v>
       </c>
       <c r="D75" t="s">
+        <v>116</v>
+      </c>
+      <c r="E75" t="s">
         <v>185</v>
-      </c>
-      <c r="E75" t="s">
-        <v>117</v>
       </c>
       <c r="F75" t="s">
         <v>19</v>
@@ -8919,10 +8919,10 @@
         <v>9</v>
       </c>
       <c r="D81" t="s">
+        <v>116</v>
+      </c>
+      <c r="E81" t="s">
         <v>143</v>
-      </c>
-      <c r="E81" t="s">
-        <v>117</v>
       </c>
       <c r="F81" t="s">
         <v>34</v>
@@ -9218,10 +9218,10 @@
         <v>9</v>
       </c>
       <c r="D94" t="s">
+        <v>116</v>
+      </c>
+      <c r="E94" t="s">
         <v>225</v>
-      </c>
-      <c r="E94" t="s">
-        <v>117</v>
       </c>
       <c r="F94" t="s">
         <v>19</v>
@@ -9264,10 +9264,10 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
+        <v>116</v>
+      </c>
+      <c r="E96" t="s">
         <v>230</v>
-      </c>
-      <c r="E96" t="s">
-        <v>117</v>
       </c>
       <c r="F96" t="s">
         <v>34</v>
@@ -9287,10 +9287,10 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
+        <v>116</v>
+      </c>
+      <c r="E97" t="s">
         <v>230</v>
-      </c>
-      <c r="E97" t="s">
-        <v>117</v>
       </c>
       <c r="F97" t="s">
         <v>34</v>
@@ -9494,10 +9494,10 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
+        <v>235</v>
+      </c>
+      <c r="E106" t="s">
         <v>254</v>
-      </c>
-      <c r="E106" t="s">
-        <v>236</v>
       </c>
       <c r="F106" t="s">
         <v>34</v>
@@ -9678,10 +9678,10 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
+        <v>235</v>
+      </c>
+      <c r="E114" t="s">
         <v>271</v>
-      </c>
-      <c r="E114" t="s">
-        <v>236</v>
       </c>
       <c r="F114" t="s">
         <v>34</v>
@@ -9747,10 +9747,10 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
+        <v>235</v>
+      </c>
+      <c r="E117" t="s">
         <v>278</v>
-      </c>
-      <c r="E117" t="s">
-        <v>236</v>
       </c>
       <c r="F117" t="s">
         <v>19</v>
@@ -9770,10 +9770,10 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
+        <v>235</v>
+      </c>
+      <c r="E118" t="s">
         <v>282</v>
-      </c>
-      <c r="E118" t="s">
-        <v>236</v>
       </c>
       <c r="F118" t="s">
         <v>19</v>
@@ -10115,10 +10115,10 @@
         <v>9</v>
       </c>
       <c r="D133" t="s">
+        <v>235</v>
+      </c>
+      <c r="E133" t="s">
         <v>313</v>
-      </c>
-      <c r="E133" t="s">
-        <v>236</v>
       </c>
       <c r="F133" t="s">
         <v>16</v>
@@ -10161,10 +10161,10 @@
         <v>9</v>
       </c>
       <c r="D135" t="s">
+        <v>235</v>
+      </c>
+      <c r="E135" t="s">
         <v>319</v>
-      </c>
-      <c r="E135" t="s">
-        <v>236</v>
       </c>
       <c r="F135" t="s">
         <v>34</v>
@@ -10207,10 +10207,10 @@
         <v>9</v>
       </c>
       <c r="D137" t="s">
+        <v>235</v>
+      </c>
+      <c r="E137" t="s">
         <v>324</v>
-      </c>
-      <c r="E137" t="s">
-        <v>236</v>
       </c>
       <c r="F137" t="s">
         <v>34</v>
@@ -10552,10 +10552,10 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
+        <v>341</v>
+      </c>
+      <c r="E152" t="s">
         <v>358</v>
-      </c>
-      <c r="E152" t="s">
-        <v>342</v>
       </c>
       <c r="F152" t="s">
         <v>19</v>
@@ -10667,10 +10667,10 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
+        <v>341</v>
+      </c>
+      <c r="E157" t="s">
         <v>370</v>
-      </c>
-      <c r="E157" t="s">
-        <v>342</v>
       </c>
       <c r="F157" t="s">
         <v>34</v>
@@ -10690,10 +10690,10 @@
         <v>188</v>
       </c>
       <c r="D158" t="s">
+        <v>341</v>
+      </c>
+      <c r="E158" t="s">
         <v>370</v>
-      </c>
-      <c r="E158" t="s">
-        <v>342</v>
       </c>
       <c r="F158" t="s">
         <v>34</v>
@@ -10874,10 +10874,10 @@
         <v>9</v>
       </c>
       <c r="D166" t="s">
+        <v>341</v>
+      </c>
+      <c r="E166" t="s">
         <v>391</v>
-      </c>
-      <c r="E166" t="s">
-        <v>342</v>
       </c>
       <c r="F166" t="s">
         <v>34</v>
@@ -10920,10 +10920,10 @@
         <v>9</v>
       </c>
       <c r="D168" t="s">
+        <v>341</v>
+      </c>
+      <c r="E168" t="s">
         <v>397</v>
-      </c>
-      <c r="E168" t="s">
-        <v>342</v>
       </c>
       <c r="F168" t="s">
         <v>34</v>
@@ -11058,10 +11058,10 @@
         <v>9</v>
       </c>
       <c r="D174" t="s">
+        <v>341</v>
+      </c>
+      <c r="E174" t="s">
         <v>411</v>
-      </c>
-      <c r="E174" t="s">
-        <v>342</v>
       </c>
       <c r="F174" t="s">
         <v>19</v>
@@ -11081,10 +11081,10 @@
         <v>188</v>
       </c>
       <c r="D175" t="s">
+        <v>341</v>
+      </c>
+      <c r="E175" t="s">
         <v>411</v>
-      </c>
-      <c r="E175" t="s">
-        <v>342</v>
       </c>
       <c r="F175" t="s">
         <v>19</v>
@@ -11104,10 +11104,10 @@
         <v>9</v>
       </c>
       <c r="D176" t="s">
+        <v>341</v>
+      </c>
+      <c r="E176" t="s">
         <v>416</v>
-      </c>
-      <c r="E176" t="s">
-        <v>342</v>
       </c>
       <c r="F176" t="s">
         <v>19</v>
@@ -11288,10 +11288,10 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
+        <v>341</v>
+      </c>
+      <c r="E184" t="s">
         <v>434</v>
-      </c>
-      <c r="E184" t="s">
-        <v>342</v>
       </c>
       <c r="F184" t="s">
         <v>19</v>
@@ -11403,10 +11403,10 @@
         <v>9</v>
       </c>
       <c r="D189" t="s">
+        <v>341</v>
+      </c>
+      <c r="E189" t="s">
         <v>445</v>
-      </c>
-      <c r="E189" t="s">
-        <v>342</v>
       </c>
       <c r="F189" t="s">
         <v>34</v>
@@ -11449,10 +11449,10 @@
         <v>9</v>
       </c>
       <c r="D191" t="s">
+        <v>341</v>
+      </c>
+      <c r="E191" t="s">
         <v>445</v>
-      </c>
-      <c r="E191" t="s">
-        <v>342</v>
       </c>
       <c r="F191" t="s">
         <v>16</v>
@@ -11541,10 +11541,10 @@
         <v>9</v>
       </c>
       <c r="D195" t="s">
+        <v>457</v>
+      </c>
+      <c r="E195" t="s">
         <v>462</v>
-      </c>
-      <c r="E195" t="s">
-        <v>458</v>
       </c>
       <c r="F195" t="s">
         <v>25</v>
@@ -11564,10 +11564,10 @@
         <v>9</v>
       </c>
       <c r="D196" t="s">
+        <v>457</v>
+      </c>
+      <c r="E196" t="s">
         <v>462</v>
-      </c>
-      <c r="E196" t="s">
-        <v>458</v>
       </c>
       <c r="F196" t="s">
         <v>16</v>
@@ -11587,10 +11587,10 @@
         <v>9</v>
       </c>
       <c r="D197" t="s">
+        <v>457</v>
+      </c>
+      <c r="E197" t="s">
         <v>462</v>
-      </c>
-      <c r="E197" t="s">
-        <v>458</v>
       </c>
       <c r="F197" t="s">
         <v>25</v>
@@ -11610,10 +11610,10 @@
         <v>9</v>
       </c>
       <c r="D198" t="s">
+        <v>457</v>
+      </c>
+      <c r="E198" t="s">
         <v>462</v>
-      </c>
-      <c r="E198" t="s">
-        <v>458</v>
       </c>
       <c r="F198" t="s">
         <v>25</v>
@@ -11633,10 +11633,10 @@
         <v>9</v>
       </c>
       <c r="D199" t="s">
+        <v>457</v>
+      </c>
+      <c r="E199" t="s">
         <v>462</v>
-      </c>
-      <c r="E199" t="s">
-        <v>458</v>
       </c>
       <c r="F199" t="s">
         <v>16</v>
@@ -11656,10 +11656,10 @@
         <v>9</v>
       </c>
       <c r="D200" t="s">
+        <v>457</v>
+      </c>
+      <c r="E200" t="s">
         <v>462</v>
-      </c>
-      <c r="E200" t="s">
-        <v>458</v>
       </c>
       <c r="F200" t="s">
         <v>25</v>
@@ -11679,10 +11679,10 @@
         <v>9</v>
       </c>
       <c r="D201" t="s">
+        <v>457</v>
+      </c>
+      <c r="E201" t="s">
         <v>462</v>
-      </c>
-      <c r="E201" t="s">
-        <v>458</v>
       </c>
       <c r="F201" t="s">
         <v>25</v>
@@ -11702,10 +11702,10 @@
         <v>9</v>
       </c>
       <c r="D202" t="s">
+        <v>457</v>
+      </c>
+      <c r="E202" t="s">
         <v>462</v>
-      </c>
-      <c r="E202" t="s">
-        <v>458</v>
       </c>
       <c r="F202" t="s">
         <v>25</v>
@@ -11725,10 +11725,10 @@
         <v>9</v>
       </c>
       <c r="D203" t="s">
+        <v>457</v>
+      </c>
+      <c r="E203" t="s">
         <v>462</v>
-      </c>
-      <c r="E203" t="s">
-        <v>458</v>
       </c>
       <c r="F203" t="s">
         <v>25</v>
@@ -11748,10 +11748,10 @@
         <v>9</v>
       </c>
       <c r="D204" t="s">
+        <v>457</v>
+      </c>
+      <c r="E204" t="s">
         <v>462</v>
-      </c>
-      <c r="E204" t="s">
-        <v>458</v>
       </c>
       <c r="F204" t="s">
         <v>25</v>
@@ -11771,10 +11771,10 @@
         <v>9</v>
       </c>
       <c r="D205" t="s">
+        <v>457</v>
+      </c>
+      <c r="E205" t="s">
         <v>462</v>
-      </c>
-      <c r="E205" t="s">
-        <v>458</v>
       </c>
       <c r="F205" t="s">
         <v>16</v>
@@ -11794,10 +11794,10 @@
         <v>9</v>
       </c>
       <c r="D206" t="s">
+        <v>457</v>
+      </c>
+      <c r="E206" t="s">
         <v>485</v>
-      </c>
-      <c r="E206" t="s">
-        <v>458</v>
       </c>
       <c r="F206" t="s">
         <v>25</v>
@@ -11817,10 +11817,10 @@
         <v>188</v>
       </c>
       <c r="D207" t="s">
+        <v>457</v>
+      </c>
+      <c r="E207" t="s">
         <v>485</v>
-      </c>
-      <c r="E207" t="s">
-        <v>458</v>
       </c>
       <c r="F207" t="s">
         <v>25</v>
@@ -11840,10 +11840,10 @@
         <v>9</v>
       </c>
       <c r="D208" t="s">
+        <v>457</v>
+      </c>
+      <c r="E208" t="s">
         <v>490</v>
-      </c>
-      <c r="E208" t="s">
-        <v>458</v>
       </c>
       <c r="F208" t="s">
         <v>34</v>
@@ -11863,10 +11863,10 @@
         <v>9</v>
       </c>
       <c r="D209" t="s">
+        <v>457</v>
+      </c>
+      <c r="E209" t="s">
         <v>462</v>
-      </c>
-      <c r="E209" t="s">
-        <v>458</v>
       </c>
       <c r="F209" t="s">
         <v>25</v>
@@ -11886,10 +11886,10 @@
         <v>9</v>
       </c>
       <c r="D210" t="s">
+        <v>457</v>
+      </c>
+      <c r="E210" t="s">
         <v>485</v>
-      </c>
-      <c r="E210" t="s">
-        <v>458</v>
       </c>
       <c r="F210" t="s">
         <v>25</v>
@@ -11909,10 +11909,10 @@
         <v>188</v>
       </c>
       <c r="D211" t="s">
+        <v>457</v>
+      </c>
+      <c r="E211" t="s">
         <v>485</v>
-      </c>
-      <c r="E211" t="s">
-        <v>458</v>
       </c>
       <c r="F211" t="s">
         <v>25</v>
@@ -11932,10 +11932,10 @@
         <v>9</v>
       </c>
       <c r="D212" t="s">
+        <v>457</v>
+      </c>
+      <c r="E212" t="s">
         <v>500</v>
-      </c>
-      <c r="E212" t="s">
-        <v>458</v>
       </c>
       <c r="F212" t="s">
         <v>34</v>
@@ -11955,10 +11955,10 @@
         <v>9</v>
       </c>
       <c r="D213" t="s">
+        <v>457</v>
+      </c>
+      <c r="E213" t="s">
         <v>462</v>
-      </c>
-      <c r="E213" t="s">
-        <v>458</v>
       </c>
       <c r="F213" t="s">
         <v>25</v>
@@ -11978,10 +11978,10 @@
         <v>9</v>
       </c>
       <c r="D214" t="s">
+        <v>457</v>
+      </c>
+      <c r="E214" t="s">
         <v>506</v>
-      </c>
-      <c r="E214" t="s">
-        <v>458</v>
       </c>
       <c r="F214" t="s">
         <v>34</v>
@@ -12001,10 +12001,10 @@
         <v>9</v>
       </c>
       <c r="D215" t="s">
+        <v>457</v>
+      </c>
+      <c r="E215" t="s">
         <v>485</v>
-      </c>
-      <c r="E215" t="s">
-        <v>458</v>
       </c>
       <c r="F215" t="s">
         <v>25</v>
@@ -12024,10 +12024,10 @@
         <v>188</v>
       </c>
       <c r="D216" t="s">
+        <v>457</v>
+      </c>
+      <c r="E216" t="s">
         <v>485</v>
-      </c>
-      <c r="E216" t="s">
-        <v>458</v>
       </c>
       <c r="F216" t="s">
         <v>25</v>
@@ -12047,10 +12047,10 @@
         <v>9</v>
       </c>
       <c r="D217" t="s">
+        <v>457</v>
+      </c>
+      <c r="E217" t="s">
         <v>462</v>
-      </c>
-      <c r="E217" t="s">
-        <v>458</v>
       </c>
       <c r="F217" t="s">
         <v>25</v>
@@ -12070,10 +12070,10 @@
         <v>9</v>
       </c>
       <c r="D218" t="s">
+        <v>457</v>
+      </c>
+      <c r="E218" t="s">
         <v>516</v>
-      </c>
-      <c r="E218" t="s">
-        <v>458</v>
       </c>
       <c r="F218" t="s">
         <v>34</v>
@@ -12093,10 +12093,10 @@
         <v>9</v>
       </c>
       <c r="D219" t="s">
+        <v>457</v>
+      </c>
+      <c r="E219" t="s">
         <v>519</v>
-      </c>
-      <c r="E219" t="s">
-        <v>458</v>
       </c>
       <c r="F219" t="s">
         <v>19</v>
@@ -12116,10 +12116,10 @@
         <v>9</v>
       </c>
       <c r="D220" t="s">
+        <v>457</v>
+      </c>
+      <c r="E220" t="s">
         <v>462</v>
-      </c>
-      <c r="E220" t="s">
-        <v>458</v>
       </c>
       <c r="F220" t="s">
         <v>25</v>
@@ -12139,10 +12139,10 @@
         <v>188</v>
       </c>
       <c r="D221" t="s">
+        <v>457</v>
+      </c>
+      <c r="E221" t="s">
         <v>462</v>
-      </c>
-      <c r="E221" t="s">
-        <v>458</v>
       </c>
       <c r="F221" t="s">
         <v>34</v>
@@ -12162,10 +12162,10 @@
         <v>9</v>
       </c>
       <c r="D222" t="s">
+        <v>457</v>
+      </c>
+      <c r="E222" t="s">
         <v>462</v>
-      </c>
-      <c r="E222" t="s">
-        <v>458</v>
       </c>
       <c r="F222" t="s">
         <v>34</v>
@@ -12185,10 +12185,10 @@
         <v>9</v>
       </c>
       <c r="D223" t="s">
+        <v>457</v>
+      </c>
+      <c r="E223" t="s">
         <v>462</v>
-      </c>
-      <c r="E223" t="s">
-        <v>458</v>
       </c>
       <c r="F223" t="s">
         <v>25</v>
@@ -12208,10 +12208,10 @@
         <v>9</v>
       </c>
       <c r="D224" t="s">
+        <v>457</v>
+      </c>
+      <c r="E224" t="s">
         <v>462</v>
-      </c>
-      <c r="E224" t="s">
-        <v>458</v>
       </c>
       <c r="F224" t="s">
         <v>25</v>
@@ -12231,10 +12231,10 @@
         <v>9</v>
       </c>
       <c r="D225" t="s">
+        <v>457</v>
+      </c>
+      <c r="E225" t="s">
         <v>462</v>
-      </c>
-      <c r="E225" t="s">
-        <v>458</v>
       </c>
       <c r="F225" t="s">
         <v>25</v>
@@ -12254,10 +12254,10 @@
         <v>9</v>
       </c>
       <c r="D226" t="s">
+        <v>457</v>
+      </c>
+      <c r="E226" t="s">
         <v>535</v>
-      </c>
-      <c r="E226" t="s">
-        <v>458</v>
       </c>
       <c r="F226" t="s">
         <v>19</v>
@@ -12277,10 +12277,10 @@
         <v>9</v>
       </c>
       <c r="D227" t="s">
+        <v>457</v>
+      </c>
+      <c r="E227" t="s">
         <v>538</v>
-      </c>
-      <c r="E227" t="s">
-        <v>458</v>
       </c>
       <c r="F227" t="s">
         <v>19</v>
@@ -12300,10 +12300,10 @@
         <v>9</v>
       </c>
       <c r="D228" t="s">
+        <v>457</v>
+      </c>
+      <c r="E228" t="s">
         <v>462</v>
-      </c>
-      <c r="E228" t="s">
-        <v>458</v>
       </c>
       <c r="F228" t="s">
         <v>25</v>
@@ -12323,10 +12323,10 @@
         <v>9</v>
       </c>
       <c r="D229" t="s">
+        <v>457</v>
+      </c>
+      <c r="E229" t="s">
         <v>462</v>
-      </c>
-      <c r="E229" t="s">
-        <v>458</v>
       </c>
       <c r="F229" t="s">
         <v>25</v>
@@ -12346,10 +12346,10 @@
         <v>9</v>
       </c>
       <c r="D230" t="s">
+        <v>457</v>
+      </c>
+      <c r="E230" t="s">
         <v>538</v>
-      </c>
-      <c r="E230" t="s">
-        <v>458</v>
       </c>
       <c r="F230" t="s">
         <v>34</v>
@@ -12369,10 +12369,10 @@
         <v>188</v>
       </c>
       <c r="D231" t="s">
+        <v>457</v>
+      </c>
+      <c r="E231" t="s">
         <v>538</v>
-      </c>
-      <c r="E231" t="s">
-        <v>458</v>
       </c>
       <c r="F231" t="s">
         <v>19</v>
@@ -12392,10 +12392,10 @@
         <v>9</v>
       </c>
       <c r="D232" t="s">
+        <v>457</v>
+      </c>
+      <c r="E232" t="s">
         <v>462</v>
-      </c>
-      <c r="E232" t="s">
-        <v>458</v>
       </c>
       <c r="F232" t="s">
         <v>25</v>
@@ -12415,10 +12415,10 @@
         <v>9</v>
       </c>
       <c r="D233" t="s">
+        <v>457</v>
+      </c>
+      <c r="E233" t="s">
         <v>462</v>
-      </c>
-      <c r="E233" t="s">
-        <v>458</v>
       </c>
       <c r="F233" t="s">
         <v>25</v>
@@ -12438,10 +12438,10 @@
         <v>9</v>
       </c>
       <c r="D234" t="s">
+        <v>457</v>
+      </c>
+      <c r="E234" t="s">
         <v>462</v>
-      </c>
-      <c r="E234" t="s">
-        <v>458</v>
       </c>
       <c r="F234" t="s">
         <v>16</v>
@@ -12461,10 +12461,10 @@
         <v>9</v>
       </c>
       <c r="D235" t="s">
+        <v>457</v>
+      </c>
+      <c r="E235" t="s">
         <v>462</v>
-      </c>
-      <c r="E235" t="s">
-        <v>458</v>
       </c>
       <c r="F235" t="s">
         <v>16</v>
@@ -12484,10 +12484,10 @@
         <v>9</v>
       </c>
       <c r="D236" t="s">
+        <v>457</v>
+      </c>
+      <c r="E236" t="s">
         <v>462</v>
-      </c>
-      <c r="E236" t="s">
-        <v>458</v>
       </c>
       <c r="F236" t="s">
         <v>25</v>
@@ -12507,10 +12507,10 @@
         <v>9</v>
       </c>
       <c r="D237" t="s">
+        <v>457</v>
+      </c>
+      <c r="E237" t="s">
         <v>462</v>
-      </c>
-      <c r="E237" t="s">
-        <v>458</v>
       </c>
       <c r="F237" t="s">
         <v>25</v>
@@ -12530,10 +12530,10 @@
         <v>9</v>
       </c>
       <c r="D238" t="s">
+        <v>457</v>
+      </c>
+      <c r="E238" t="s">
         <v>462</v>
-      </c>
-      <c r="E238" t="s">
-        <v>458</v>
       </c>
       <c r="F238" t="s">
         <v>16</v>
@@ -12553,10 +12553,10 @@
         <v>9</v>
       </c>
       <c r="D239" t="s">
+        <v>457</v>
+      </c>
+      <c r="E239" t="s">
         <v>462</v>
-      </c>
-      <c r="E239" t="s">
-        <v>458</v>
       </c>
       <c r="F239" t="s">
         <v>25</v>
@@ -12576,10 +12576,10 @@
         <v>9</v>
       </c>
       <c r="D240" t="s">
+        <v>457</v>
+      </c>
+      <c r="E240" t="s">
         <v>462</v>
-      </c>
-      <c r="E240" t="s">
-        <v>458</v>
       </c>
       <c r="F240" t="s">
         <v>25</v>
@@ -12599,10 +12599,10 @@
         <v>9</v>
       </c>
       <c r="D241" t="s">
+        <v>457</v>
+      </c>
+      <c r="E241" t="s">
         <v>462</v>
-      </c>
-      <c r="E241" t="s">
-        <v>458</v>
       </c>
       <c r="F241" t="s">
         <v>16</v>
@@ -12622,10 +12622,10 @@
         <v>9</v>
       </c>
       <c r="D242" t="s">
+        <v>457</v>
+      </c>
+      <c r="E242" t="s">
         <v>462</v>
-      </c>
-      <c r="E242" t="s">
-        <v>458</v>
       </c>
       <c r="F242" t="s">
         <v>25</v>
@@ -12645,10 +12645,10 @@
         <v>9</v>
       </c>
       <c r="D243" t="s">
+        <v>457</v>
+      </c>
+      <c r="E243" t="s">
         <v>462</v>
-      </c>
-      <c r="E243" t="s">
-        <v>458</v>
       </c>
       <c r="F243" t="s">
         <v>25</v>
@@ -12668,10 +12668,10 @@
         <v>9</v>
       </c>
       <c r="D244" t="s">
+        <v>457</v>
+      </c>
+      <c r="E244" t="s">
         <v>462</v>
-      </c>
-      <c r="E244" t="s">
-        <v>458</v>
       </c>
       <c r="F244" t="s">
         <v>25</v>
@@ -12691,10 +12691,10 @@
         <v>9</v>
       </c>
       <c r="D245" t="s">
+        <v>457</v>
+      </c>
+      <c r="E245" t="s">
         <v>462</v>
-      </c>
-      <c r="E245" t="s">
-        <v>458</v>
       </c>
       <c r="F245" t="s">
         <v>25</v>
@@ -12737,10 +12737,10 @@
         <v>9</v>
       </c>
       <c r="D247" t="s">
+        <v>576</v>
+      </c>
+      <c r="E247" t="s">
         <v>581</v>
-      </c>
-      <c r="E247" t="s">
-        <v>577</v>
       </c>
       <c r="F247" t="s">
         <v>19</v>
@@ -12783,10 +12783,10 @@
         <v>9</v>
       </c>
       <c r="D249" t="s">
+        <v>576</v>
+      </c>
+      <c r="E249" t="s">
         <v>581</v>
-      </c>
-      <c r="E249" t="s">
-        <v>577</v>
       </c>
       <c r="F249" t="s">
         <v>19</v>
@@ -12875,10 +12875,10 @@
         <v>9</v>
       </c>
       <c r="D253" t="s">
+        <v>576</v>
+      </c>
+      <c r="E253" t="s">
         <v>594</v>
-      </c>
-      <c r="E253" t="s">
-        <v>577</v>
       </c>
       <c r="F253" t="s">
         <v>19</v>
@@ -12921,10 +12921,10 @@
         <v>9</v>
       </c>
       <c r="D255" t="s">
+        <v>576</v>
+      </c>
+      <c r="E255" t="s">
         <v>599</v>
-      </c>
-      <c r="E255" t="s">
-        <v>577</v>
       </c>
       <c r="F255" t="s">
         <v>25</v>
@@ -12990,10 +12990,10 @@
         <v>9</v>
       </c>
       <c r="D258" t="s">
+        <v>576</v>
+      </c>
+      <c r="E258" t="s">
         <v>581</v>
-      </c>
-      <c r="E258" t="s">
-        <v>577</v>
       </c>
       <c r="F258" t="s">
         <v>19</v>
@@ -13013,10 +13013,10 @@
         <v>9</v>
       </c>
       <c r="D259" t="s">
+        <v>576</v>
+      </c>
+      <c r="E259" t="s">
         <v>581</v>
-      </c>
-      <c r="E259" t="s">
-        <v>577</v>
       </c>
       <c r="F259" t="s">
         <v>19</v>
@@ -13036,10 +13036,10 @@
         <v>188</v>
       </c>
       <c r="D260" t="s">
+        <v>576</v>
+      </c>
+      <c r="E260" t="s">
         <v>610</v>
-      </c>
-      <c r="E260" t="s">
-        <v>577</v>
       </c>
       <c r="F260" t="s">
         <v>25</v>
@@ -13105,10 +13105,10 @@
         <v>9</v>
       </c>
       <c r="D263" t="s">
+        <v>576</v>
+      </c>
+      <c r="E263" t="s">
         <v>617</v>
-      </c>
-      <c r="E263" t="s">
-        <v>577</v>
       </c>
       <c r="F263" t="s">
         <v>34</v>
@@ -13128,10 +13128,10 @@
         <v>9</v>
       </c>
       <c r="D264" t="s">
+        <v>576</v>
+      </c>
+      <c r="E264" t="s">
         <v>581</v>
-      </c>
-      <c r="E264" t="s">
-        <v>577</v>
       </c>
       <c r="F264" t="s">
         <v>19</v>
@@ -13151,10 +13151,10 @@
         <v>188</v>
       </c>
       <c r="D265" t="s">
+        <v>576</v>
+      </c>
+      <c r="E265" t="s">
         <v>581</v>
-      </c>
-      <c r="E265" t="s">
-        <v>577</v>
       </c>
       <c r="F265" t="s">
         <v>19</v>
@@ -13197,10 +13197,10 @@
         <v>9</v>
       </c>
       <c r="D267" t="s">
+        <v>576</v>
+      </c>
+      <c r="E267" t="s">
         <v>581</v>
-      </c>
-      <c r="E267" t="s">
-        <v>577</v>
       </c>
       <c r="F267" t="s">
         <v>19</v>
@@ -13243,10 +13243,10 @@
         <v>9</v>
       </c>
       <c r="D269" t="s">
+        <v>576</v>
+      </c>
+      <c r="E269" t="s">
         <v>581</v>
-      </c>
-      <c r="E269" t="s">
-        <v>577</v>
       </c>
       <c r="F269" t="s">
         <v>19</v>
@@ -13266,10 +13266,10 @@
         <v>9</v>
       </c>
       <c r="D270" t="s">
+        <v>576</v>
+      </c>
+      <c r="E270" t="s">
         <v>610</v>
-      </c>
-      <c r="E270" t="s">
-        <v>577</v>
       </c>
       <c r="F270" t="s">
         <v>19</v>
@@ -13289,10 +13289,10 @@
         <v>188</v>
       </c>
       <c r="D271" t="s">
+        <v>576</v>
+      </c>
+      <c r="E271" t="s">
         <v>581</v>
-      </c>
-      <c r="E271" t="s">
-        <v>577</v>
       </c>
       <c r="F271" t="s">
         <v>19</v>
@@ -13312,10 +13312,10 @@
         <v>9</v>
       </c>
       <c r="D272" t="s">
+        <v>576</v>
+      </c>
+      <c r="E272" t="s">
         <v>581</v>
-      </c>
-      <c r="E272" t="s">
-        <v>577</v>
       </c>
       <c r="F272" t="s">
         <v>19</v>
@@ -13358,10 +13358,10 @@
         <v>9</v>
       </c>
       <c r="D274" t="s">
+        <v>576</v>
+      </c>
+      <c r="E274" t="s">
         <v>581</v>
-      </c>
-      <c r="E274" t="s">
-        <v>577</v>
       </c>
       <c r="F274" t="s">
         <v>19</v>
@@ -13404,10 +13404,10 @@
         <v>9</v>
       </c>
       <c r="D276" t="s">
+        <v>576</v>
+      </c>
+      <c r="E276" t="s">
         <v>581</v>
-      </c>
-      <c r="E276" t="s">
-        <v>577</v>
       </c>
       <c r="F276" t="s">
         <v>19</v>
@@ -13427,10 +13427,10 @@
         <v>9</v>
       </c>
       <c r="D277" t="s">
+        <v>576</v>
+      </c>
+      <c r="E277" t="s">
         <v>647</v>
-      </c>
-      <c r="E277" t="s">
-        <v>577</v>
       </c>
       <c r="F277" t="s">
         <v>19</v>
@@ -13450,10 +13450,10 @@
         <v>9</v>
       </c>
       <c r="D278" t="s">
+        <v>576</v>
+      </c>
+      <c r="E278" t="s">
         <v>650</v>
-      </c>
-      <c r="E278" t="s">
-        <v>577</v>
       </c>
       <c r="F278" t="s">
         <v>34</v>
@@ -13473,10 +13473,10 @@
         <v>9</v>
       </c>
       <c r="D279" t="s">
+        <v>576</v>
+      </c>
+      <c r="E279" t="s">
         <v>581</v>
-      </c>
-      <c r="E279" t="s">
-        <v>577</v>
       </c>
       <c r="F279" t="s">
         <v>19</v>
@@ -13496,10 +13496,10 @@
         <v>9</v>
       </c>
       <c r="D280" t="s">
+        <v>576</v>
+      </c>
+      <c r="E280" t="s">
         <v>656</v>
-      </c>
-      <c r="E280" t="s">
-        <v>577</v>
       </c>
       <c r="F280" t="s">
         <v>34</v>
@@ -13519,10 +13519,10 @@
         <v>9</v>
       </c>
       <c r="D281" t="s">
+        <v>576</v>
+      </c>
+      <c r="E281" t="s">
         <v>581</v>
-      </c>
-      <c r="E281" t="s">
-        <v>577</v>
       </c>
       <c r="F281" t="s">
         <v>19</v>
@@ -13588,10 +13588,10 @@
         <v>9</v>
       </c>
       <c r="D284" t="s">
+        <v>576</v>
+      </c>
+      <c r="E284" t="s">
         <v>581</v>
-      </c>
-      <c r="E284" t="s">
-        <v>577</v>
       </c>
       <c r="F284" t="s">
         <v>19</v>
@@ -13703,10 +13703,10 @@
         <v>9</v>
       </c>
       <c r="D289" t="s">
+        <v>576</v>
+      </c>
+      <c r="E289" t="s">
         <v>647</v>
-      </c>
-      <c r="E289" t="s">
-        <v>577</v>
       </c>
       <c r="F289" t="s">
         <v>19</v>
@@ -13726,10 +13726,10 @@
         <v>9</v>
       </c>
       <c r="D290" t="s">
+        <v>576</v>
+      </c>
+      <c r="E290" t="s">
         <v>581</v>
-      </c>
-      <c r="E290" t="s">
-        <v>577</v>
       </c>
       <c r="F290" t="s">
         <v>19</v>
@@ -13795,10 +13795,10 @@
         <v>9</v>
       </c>
       <c r="D293" t="s">
+        <v>576</v>
+      </c>
+      <c r="E293" t="s">
         <v>647</v>
-      </c>
-      <c r="E293" t="s">
-        <v>577</v>
       </c>
       <c r="F293" t="s">
         <v>19</v>
@@ -13818,10 +13818,10 @@
         <v>9</v>
       </c>
       <c r="D294" t="s">
+        <v>576</v>
+      </c>
+      <c r="E294" t="s">
         <v>581</v>
-      </c>
-      <c r="E294" t="s">
-        <v>577</v>
       </c>
       <c r="F294" t="s">
         <v>19</v>
@@ -13979,10 +13979,10 @@
         <v>9</v>
       </c>
       <c r="D301" t="s">
+        <v>576</v>
+      </c>
+      <c r="E301" t="s">
         <v>581</v>
-      </c>
-      <c r="E301" t="s">
-        <v>577</v>
       </c>
       <c r="F301" t="s">
         <v>19</v>
@@ -14002,10 +14002,10 @@
         <v>9</v>
       </c>
       <c r="D302" t="s">
+        <v>576</v>
+      </c>
+      <c r="E302" t="s">
         <v>581</v>
-      </c>
-      <c r="E302" t="s">
-        <v>577</v>
       </c>
       <c r="F302" t="s">
         <v>19</v>
@@ -14025,10 +14025,10 @@
         <v>9</v>
       </c>
       <c r="D303" t="s">
+        <v>576</v>
+      </c>
+      <c r="E303" t="s">
         <v>581</v>
-      </c>
-      <c r="E303" t="s">
-        <v>577</v>
       </c>
       <c r="F303" t="s">
         <v>19</v>
@@ -14071,10 +14071,10 @@
         <v>9</v>
       </c>
       <c r="D305" t="s">
+        <v>576</v>
+      </c>
+      <c r="E305" t="s">
         <v>581</v>
-      </c>
-      <c r="E305" t="s">
-        <v>577</v>
       </c>
       <c r="F305" t="s">
         <v>19</v>
@@ -14140,10 +14140,10 @@
         <v>9</v>
       </c>
       <c r="D308" t="s">
+        <v>576</v>
+      </c>
+      <c r="E308" t="s">
         <v>714</v>
-      </c>
-      <c r="E308" t="s">
-        <v>577</v>
       </c>
       <c r="F308" t="s">
         <v>19</v>
@@ -14163,10 +14163,10 @@
         <v>9</v>
       </c>
       <c r="D309" t="s">
+        <v>576</v>
+      </c>
+      <c r="E309" t="s">
         <v>581</v>
-      </c>
-      <c r="E309" t="s">
-        <v>577</v>
       </c>
       <c r="F309" t="s">
         <v>19</v>
@@ -14508,10 +14508,10 @@
         <v>9</v>
       </c>
       <c r="D324" t="s">
+        <v>721</v>
+      </c>
+      <c r="E324" t="s">
         <v>750</v>
-      </c>
-      <c r="E324" t="s">
-        <v>722</v>
       </c>
       <c r="F324" t="s">
         <v>19</v>
@@ -14968,10 +14968,10 @@
         <v>9</v>
       </c>
       <c r="D344" t="s">
+        <v>721</v>
+      </c>
+      <c r="E344" t="s">
         <v>793</v>
-      </c>
-      <c r="E344" t="s">
-        <v>722</v>
       </c>
       <c r="F344" t="s">
         <v>34</v>
@@ -14991,10 +14991,10 @@
         <v>188</v>
       </c>
       <c r="D345" t="s">
+        <v>721</v>
+      </c>
+      <c r="E345" t="s">
         <v>797</v>
-      </c>
-      <c r="E345" t="s">
-        <v>722</v>
       </c>
       <c r="F345" t="s">
         <v>34</v>
@@ -15037,10 +15037,10 @@
         <v>188</v>
       </c>
       <c r="D347" t="s">
+        <v>800</v>
+      </c>
+      <c r="E347" t="s">
         <v>805</v>
-      </c>
-      <c r="E347" t="s">
-        <v>801</v>
       </c>
       <c r="F347" t="s">
         <v>19</v>
@@ -15267,10 +15267,10 @@
         <v>9</v>
       </c>
       <c r="D357" t="s">
+        <v>800</v>
+      </c>
+      <c r="E357" t="s">
         <v>826</v>
-      </c>
-      <c r="E357" t="s">
-        <v>801</v>
       </c>
       <c r="F357" t="s">
         <v>19</v>
@@ -15497,10 +15497,10 @@
         <v>9</v>
       </c>
       <c r="D367" t="s">
+        <v>800</v>
+      </c>
+      <c r="E367" t="s">
         <v>847</v>
-      </c>
-      <c r="E367" t="s">
-        <v>801</v>
       </c>
       <c r="F367" t="s">
         <v>19</v>
@@ -15520,10 +15520,10 @@
         <v>9</v>
       </c>
       <c r="D368" t="s">
+        <v>800</v>
+      </c>
+      <c r="E368" t="s">
         <v>805</v>
-      </c>
-      <c r="E368" t="s">
-        <v>801</v>
       </c>
       <c r="F368" t="s">
         <v>16</v>
@@ -15635,10 +15635,10 @@
         <v>9</v>
       </c>
       <c r="D373" t="s">
+        <v>800</v>
+      </c>
+      <c r="E373" t="s">
         <v>861</v>
-      </c>
-      <c r="E373" t="s">
-        <v>801</v>
       </c>
       <c r="F373" t="s">
         <v>25</v>
@@ -15681,10 +15681,10 @@
         <v>188</v>
       </c>
       <c r="D375" t="s">
+        <v>800</v>
+      </c>
+      <c r="E375" t="s">
         <v>861</v>
-      </c>
-      <c r="E375" t="s">
-        <v>801</v>
       </c>
       <c r="F375" t="s">
         <v>25</v>
@@ -15819,10 +15819,10 @@
         <v>188</v>
       </c>
       <c r="D381" t="s">
+        <v>875</v>
+      </c>
+      <c r="E381" t="s">
         <v>882</v>
-      </c>
-      <c r="E381" t="s">
-        <v>876</v>
       </c>
       <c r="F381" t="s">
         <v>16</v>
@@ -15957,10 +15957,10 @@
         <v>9</v>
       </c>
       <c r="D387" t="s">
+        <v>875</v>
+      </c>
+      <c r="E387" t="s">
         <v>895</v>
-      </c>
-      <c r="E387" t="s">
-        <v>876</v>
       </c>
       <c r="F387" t="s">
         <v>19</v>
@@ -15980,10 +15980,10 @@
         <v>9</v>
       </c>
       <c r="D388" t="s">
+        <v>875</v>
+      </c>
+      <c r="E388" t="s">
         <v>898</v>
-      </c>
-      <c r="E388" t="s">
-        <v>876</v>
       </c>
       <c r="F388" t="s">
         <v>25</v>
@@ -16026,10 +16026,10 @@
         <v>9</v>
       </c>
       <c r="D390" t="s">
+        <v>875</v>
+      </c>
+      <c r="E390" t="s">
         <v>903</v>
-      </c>
-      <c r="E390" t="s">
-        <v>876</v>
       </c>
       <c r="F390" t="s">
         <v>34</v>
@@ -16118,10 +16118,10 @@
         <v>188</v>
       </c>
       <c r="D394" t="s">
+        <v>875</v>
+      </c>
+      <c r="E394" t="s">
         <v>913</v>
-      </c>
-      <c r="E394" t="s">
-        <v>876</v>
       </c>
       <c r="F394" t="s">
         <v>19</v>
@@ -16164,10 +16164,10 @@
         <v>9</v>
       </c>
       <c r="D396" t="s">
+        <v>875</v>
+      </c>
+      <c r="E396" t="s">
         <v>918</v>
-      </c>
-      <c r="E396" t="s">
-        <v>876</v>
       </c>
       <c r="F396" t="s">
         <v>34</v>
@@ -16210,10 +16210,10 @@
         <v>9</v>
       </c>
       <c r="D398" t="s">
+        <v>875</v>
+      </c>
+      <c r="E398" t="s">
         <v>924</v>
-      </c>
-      <c r="E398" t="s">
-        <v>876</v>
       </c>
       <c r="F398" t="s">
         <v>34</v>
@@ -16279,10 +16279,10 @@
         <v>9</v>
       </c>
       <c r="D401" t="s">
+        <v>875</v>
+      </c>
+      <c r="E401" t="s">
         <v>932</v>
-      </c>
-      <c r="E401" t="s">
-        <v>876</v>
       </c>
       <c r="F401" t="s">
         <v>34</v>
@@ -16417,10 +16417,10 @@
         <v>9</v>
       </c>
       <c r="D407" t="s">
+        <v>875</v>
+      </c>
+      <c r="E407" t="s">
         <v>946</v>
-      </c>
-      <c r="E407" t="s">
-        <v>876</v>
       </c>
       <c r="F407" t="s">
         <v>34</v>
@@ -16440,10 +16440,10 @@
         <v>9</v>
       </c>
       <c r="D408" t="s">
+        <v>875</v>
+      </c>
+      <c r="E408" t="s">
         <v>950</v>
-      </c>
-      <c r="E408" t="s">
-        <v>876</v>
       </c>
       <c r="F408" t="s">
         <v>25</v>
@@ -16463,10 +16463,10 @@
         <v>9</v>
       </c>
       <c r="D409" t="s">
+        <v>875</v>
+      </c>
+      <c r="E409" t="s">
         <v>913</v>
-      </c>
-      <c r="E409" t="s">
-        <v>876</v>
       </c>
       <c r="F409" t="s">
         <v>16</v>
@@ -16486,10 +16486,10 @@
         <v>9</v>
       </c>
       <c r="D410" t="s">
+        <v>875</v>
+      </c>
+      <c r="E410" t="s">
         <v>882</v>
-      </c>
-      <c r="E410" t="s">
-        <v>876</v>
       </c>
       <c r="F410" t="s">
         <v>16</v>
@@ -16762,10 +16762,10 @@
         <v>9</v>
       </c>
       <c r="D422" t="s">
+        <v>972</v>
+      </c>
+      <c r="E422" t="s">
         <v>979</v>
-      </c>
-      <c r="E422" t="s">
-        <v>973</v>
       </c>
       <c r="F422" t="s">
         <v>34</v>
@@ -16808,10 +16808,10 @@
         <v>9</v>
       </c>
       <c r="D424" t="s">
+        <v>972</v>
+      </c>
+      <c r="E424" t="s">
         <v>984</v>
-      </c>
-      <c r="E424" t="s">
-        <v>973</v>
       </c>
       <c r="F424" t="s">
         <v>25</v>
@@ -16969,10 +16969,10 @@
         <v>9</v>
       </c>
       <c r="D431" t="s">
+        <v>972</v>
+      </c>
+      <c r="E431" t="s">
         <v>999</v>
-      </c>
-      <c r="E431" t="s">
-        <v>973</v>
       </c>
       <c r="F431" t="s">
         <v>34</v>
@@ -16992,10 +16992,10 @@
         <v>9</v>
       </c>
       <c r="D432" t="s">
+        <v>972</v>
+      </c>
+      <c r="E432" t="s">
         <v>1003</v>
-      </c>
-      <c r="E432" t="s">
-        <v>973</v>
       </c>
       <c r="F432" t="s">
         <v>34</v>
@@ -17084,10 +17084,10 @@
         <v>9</v>
       </c>
       <c r="D436" t="s">
+        <v>972</v>
+      </c>
+      <c r="E436" t="s">
         <v>1013</v>
-      </c>
-      <c r="E436" t="s">
-        <v>973</v>
       </c>
       <c r="F436" t="s">
         <v>34</v>
@@ -17153,10 +17153,10 @@
         <v>9</v>
       </c>
       <c r="D439" t="s">
+        <v>972</v>
+      </c>
+      <c r="E439" t="s">
         <v>1020</v>
-      </c>
-      <c r="E439" t="s">
-        <v>973</v>
       </c>
       <c r="F439" t="s">
         <v>34</v>
@@ -17176,10 +17176,10 @@
         <v>9</v>
       </c>
       <c r="D440" t="s">
+        <v>972</v>
+      </c>
+      <c r="E440" t="s">
         <v>1023</v>
-      </c>
-      <c r="E440" t="s">
-        <v>973</v>
       </c>
       <c r="F440" t="s">
         <v>25</v>
@@ -17245,10 +17245,10 @@
         <v>9</v>
       </c>
       <c r="D443" t="s">
+        <v>972</v>
+      </c>
+      <c r="E443" t="s">
         <v>1030</v>
-      </c>
-      <c r="E443" t="s">
-        <v>973</v>
       </c>
       <c r="F443" t="s">
         <v>34</v>
@@ -17613,10 +17613,10 @@
         <v>9</v>
       </c>
       <c r="D459" t="s">
+        <v>972</v>
+      </c>
+      <c r="E459" t="s">
         <v>1062</v>
-      </c>
-      <c r="E459" t="s">
-        <v>973</v>
       </c>
       <c r="F459" t="s">
         <v>25</v>
@@ -17843,10 +17843,10 @@
         <v>9</v>
       </c>
       <c r="D469" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E469" t="s">
         <v>1088</v>
-      </c>
-      <c r="E469" t="s">
-        <v>1067</v>
       </c>
       <c r="F469" t="s">
         <v>34</v>
@@ -17866,10 +17866,10 @@
         <v>9</v>
       </c>
       <c r="D470" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E470" t="s">
         <v>1092</v>
-      </c>
-      <c r="E470" t="s">
-        <v>1067</v>
       </c>
       <c r="F470" t="s">
         <v>34</v>
@@ -17889,10 +17889,10 @@
         <v>9</v>
       </c>
       <c r="D471" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E471" t="s">
         <v>1095</v>
-      </c>
-      <c r="E471" t="s">
-        <v>1067</v>
       </c>
       <c r="F471" t="s">
         <v>34</v>
@@ -17912,10 +17912,10 @@
         <v>9</v>
       </c>
       <c r="D472" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E472" t="s">
         <v>1098</v>
-      </c>
-      <c r="E472" t="s">
-        <v>1067</v>
       </c>
       <c r="F472" t="s">
         <v>34</v>
@@ -17958,10 +17958,10 @@
         <v>9</v>
       </c>
       <c r="D474" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E474" t="s">
         <v>1104</v>
-      </c>
-      <c r="E474" t="s">
-        <v>1067</v>
       </c>
       <c r="F474" t="s">
         <v>34</v>
@@ -18050,10 +18050,10 @@
         <v>9</v>
       </c>
       <c r="D478" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E478" t="s">
         <v>1114</v>
-      </c>
-      <c r="E478" t="s">
-        <v>1067</v>
       </c>
       <c r="F478" t="s">
         <v>34</v>
@@ -18418,10 +18418,10 @@
         <v>9</v>
       </c>
       <c r="D494" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E494" t="s">
         <v>1149</v>
-      </c>
-      <c r="E494" t="s">
-        <v>1145</v>
       </c>
       <c r="F494" t="s">
         <v>1068</v>
@@ -18556,10 +18556,10 @@
         <v>9</v>
       </c>
       <c r="D500" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E500" t="s">
         <v>1104</v>
-      </c>
-      <c r="E500" t="s">
-        <v>1145</v>
       </c>
       <c r="F500" t="s">
         <v>16</v>
@@ -18579,10 +18579,10 @@
         <v>188</v>
       </c>
       <c r="D501" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E501" t="s">
         <v>1104</v>
-      </c>
-      <c r="E501" t="s">
-        <v>1145</v>
       </c>
       <c r="F501" t="s">
         <v>19</v>
@@ -18648,10 +18648,10 @@
         <v>9</v>
       </c>
       <c r="D504" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E504" t="s">
         <v>1172</v>
-      </c>
-      <c r="E504" t="s">
-        <v>1145</v>
       </c>
       <c r="F504" t="s">
         <v>1068</v>
@@ -18740,10 +18740,10 @@
         <v>188</v>
       </c>
       <c r="D508" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E508" t="s">
         <v>1181</v>
-      </c>
-      <c r="E508" t="s">
-        <v>1145</v>
       </c>
       <c r="F508" t="s">
         <v>25</v>
@@ -18855,10 +18855,10 @@
         <v>9</v>
       </c>
       <c r="D513" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E513" t="s">
         <v>1192</v>
-      </c>
-      <c r="E513" t="s">
-        <v>1145</v>
       </c>
       <c r="F513" t="s">
         <v>34</v>
@@ -18878,10 +18878,10 @@
         <v>9</v>
       </c>
       <c r="D514" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E514" t="s">
         <v>1196</v>
-      </c>
-      <c r="E514" t="s">
-        <v>1145</v>
       </c>
       <c r="F514" t="s">
         <v>1068</v>
@@ -18901,10 +18901,10 @@
         <v>188</v>
       </c>
       <c r="D515" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E515" t="s">
         <v>1196</v>
-      </c>
-      <c r="E515" t="s">
-        <v>1145</v>
       </c>
       <c r="F515" t="s">
         <v>25</v>
@@ -18924,10 +18924,10 @@
         <v>9</v>
       </c>
       <c r="D516" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E516" t="s">
         <v>1203</v>
-      </c>
-      <c r="E516" t="s">
-        <v>1145</v>
       </c>
       <c r="F516" t="s">
         <v>34</v>
@@ -18970,10 +18970,10 @@
         <v>9</v>
       </c>
       <c r="D518" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E518" t="s">
         <v>1209</v>
-      </c>
-      <c r="E518" t="s">
-        <v>1145</v>
       </c>
       <c r="F518" t="s">
         <v>19</v>
@@ -19200,10 +19200,10 @@
         <v>188</v>
       </c>
       <c r="D528" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E528" t="s">
         <v>1230</v>
-      </c>
-      <c r="E528" t="s">
-        <v>1145</v>
       </c>
       <c r="F528" t="s">
         <v>25</v>
@@ -19223,10 +19223,10 @@
         <v>188</v>
       </c>
       <c r="D529" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E529" t="s">
         <v>1233</v>
-      </c>
-      <c r="E529" t="s">
-        <v>1145</v>
       </c>
       <c r="F529" t="s">
         <v>16</v>
@@ -19246,10 +19246,10 @@
         <v>9</v>
       </c>
       <c r="D530" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E530" t="s">
         <v>1236</v>
-      </c>
-      <c r="E530" t="s">
-        <v>1145</v>
       </c>
       <c r="F530" t="s">
         <v>34</v>
@@ -19292,10 +19292,10 @@
         <v>9</v>
       </c>
       <c r="D532" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E532" t="s">
         <v>1149</v>
-      </c>
-      <c r="E532" t="s">
-        <v>1241</v>
       </c>
       <c r="F532" t="s">
         <v>1242</v>
@@ -19315,10 +19315,10 @@
         <v>9</v>
       </c>
       <c r="D533" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E533" t="s">
         <v>1149</v>
-      </c>
-      <c r="E533" t="s">
-        <v>1241</v>
       </c>
       <c r="F533" t="s">
         <v>1242</v>
@@ -19338,10 +19338,10 @@
         <v>9</v>
       </c>
       <c r="D534" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E534" t="s">
         <v>1149</v>
-      </c>
-      <c r="E534" t="s">
-        <v>1241</v>
       </c>
       <c r="F534" t="s">
         <v>1242</v>
@@ -19361,10 +19361,10 @@
         <v>9</v>
       </c>
       <c r="D535" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E535" t="s">
         <v>1149</v>
-      </c>
-      <c r="E535" t="s">
-        <v>1241</v>
       </c>
       <c r="F535" t="s">
         <v>1242</v>
@@ -19384,10 +19384,10 @@
         <v>9</v>
       </c>
       <c r="D536" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E536" t="s">
         <v>1252</v>
-      </c>
-      <c r="E536" t="s">
-        <v>1241</v>
       </c>
       <c r="F536" t="s">
         <v>19</v>
@@ -19407,10 +19407,10 @@
         <v>9</v>
       </c>
       <c r="D537" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E537" t="s">
         <v>1149</v>
-      </c>
-      <c r="E537" t="s">
-        <v>1241</v>
       </c>
       <c r="F537" t="s">
         <v>1242</v>
@@ -19430,10 +19430,10 @@
         <v>9</v>
       </c>
       <c r="D538" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E538" t="s">
         <v>1149</v>
-      </c>
-      <c r="E538" t="s">
-        <v>1241</v>
       </c>
       <c r="F538" t="s">
         <v>1242</v>
@@ -19453,10 +19453,10 @@
         <v>9</v>
       </c>
       <c r="D539" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E539" t="s">
         <v>1149</v>
-      </c>
-      <c r="E539" t="s">
-        <v>1241</v>
       </c>
       <c r="F539" t="s">
         <v>1242</v>
@@ -19476,10 +19476,10 @@
         <v>9</v>
       </c>
       <c r="D540" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E540" t="s">
         <v>1149</v>
-      </c>
-      <c r="E540" t="s">
-        <v>1241</v>
       </c>
       <c r="F540" t="s">
         <v>1242</v>
@@ -19499,10 +19499,10 @@
         <v>9</v>
       </c>
       <c r="D541" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E541" t="s">
         <v>1149</v>
-      </c>
-      <c r="E541" t="s">
-        <v>1241</v>
       </c>
       <c r="F541" t="s">
         <v>1242</v>
@@ -19522,10 +19522,10 @@
         <v>9</v>
       </c>
       <c r="D542" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E542" t="s">
         <v>1149</v>
-      </c>
-      <c r="E542" t="s">
-        <v>1241</v>
       </c>
       <c r="F542" t="s">
         <v>1242</v>
@@ -19545,10 +19545,10 @@
         <v>9</v>
       </c>
       <c r="D543" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E543" t="s">
         <v>1268</v>
-      </c>
-      <c r="E543" t="s">
-        <v>1241</v>
       </c>
       <c r="F543" t="s">
         <v>19</v>
@@ -19568,10 +19568,10 @@
         <v>9</v>
       </c>
       <c r="D544" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E544" t="s">
         <v>1271</v>
-      </c>
-      <c r="E544" t="s">
-        <v>1241</v>
       </c>
       <c r="F544" t="s">
         <v>19</v>
@@ -19591,10 +19591,10 @@
         <v>9</v>
       </c>
       <c r="D545" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E545" t="s">
         <v>1149</v>
-      </c>
-      <c r="E545" t="s">
-        <v>1241</v>
       </c>
       <c r="F545" t="s">
         <v>1242</v>
@@ -19614,10 +19614,10 @@
         <v>9</v>
       </c>
       <c r="D546" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E546" t="s">
         <v>1149</v>
-      </c>
-      <c r="E546" t="s">
-        <v>1241</v>
       </c>
       <c r="F546" t="s">
         <v>1242</v>
@@ -19637,10 +19637,10 @@
         <v>9</v>
       </c>
       <c r="D547" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E547" t="s">
         <v>1149</v>
-      </c>
-      <c r="E547" t="s">
-        <v>1241</v>
       </c>
       <c r="F547" t="s">
         <v>1242</v>
@@ -19660,10 +19660,10 @@
         <v>9</v>
       </c>
       <c r="D548" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E548" t="s">
         <v>1149</v>
-      </c>
-      <c r="E548" t="s">
-        <v>1241</v>
       </c>
       <c r="F548" t="s">
         <v>1242</v>
@@ -19683,10 +19683,10 @@
         <v>9</v>
       </c>
       <c r="D549" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E549" t="s">
         <v>1149</v>
-      </c>
-      <c r="E549" t="s">
-        <v>1241</v>
       </c>
       <c r="F549" t="s">
         <v>1242</v>
@@ -19706,10 +19706,10 @@
         <v>9</v>
       </c>
       <c r="D550" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E550" t="s">
         <v>1149</v>
-      </c>
-      <c r="E550" t="s">
-        <v>1241</v>
       </c>
       <c r="F550" t="s">
         <v>1242</v>
@@ -19729,10 +19729,10 @@
         <v>9</v>
       </c>
       <c r="D551" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E551" t="s">
         <v>1149</v>
-      </c>
-      <c r="E551" t="s">
-        <v>1241</v>
       </c>
       <c r="F551" t="s">
         <v>1242</v>
@@ -19752,10 +19752,10 @@
         <v>9</v>
       </c>
       <c r="D552" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E552" t="s">
         <v>1149</v>
-      </c>
-      <c r="E552" t="s">
-        <v>1241</v>
       </c>
       <c r="F552" t="s">
         <v>16</v>
@@ -19775,10 +19775,10 @@
         <v>9</v>
       </c>
       <c r="D553" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E553" t="s">
         <v>1149</v>
-      </c>
-      <c r="E553" t="s">
-        <v>1241</v>
       </c>
       <c r="F553" t="s">
         <v>1242</v>
@@ -19798,10 +19798,10 @@
         <v>9</v>
       </c>
       <c r="D554" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E554" t="s">
         <v>1149</v>
-      </c>
-      <c r="E554" t="s">
-        <v>1241</v>
       </c>
       <c r="F554" t="s">
         <v>19</v>
@@ -19844,10 +19844,10 @@
         <v>9</v>
       </c>
       <c r="D556" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E556" t="s">
         <v>1300</v>
-      </c>
-      <c r="E556" t="s">
-        <v>1296</v>
       </c>
       <c r="F556" t="s">
         <v>1242</v>
@@ -19867,10 +19867,10 @@
         <v>9</v>
       </c>
       <c r="D557" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E557" t="s">
         <v>1303</v>
-      </c>
-      <c r="E557" t="s">
-        <v>1296</v>
       </c>
       <c r="F557" t="s">
         <v>1242</v>
@@ -20051,10 +20051,10 @@
         <v>9</v>
       </c>
       <c r="D565" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E565" t="s">
         <v>1321</v>
-      </c>
-      <c r="E565" t="s">
-        <v>1296</v>
       </c>
       <c r="F565" t="s">
         <v>34</v>
@@ -20097,10 +20097,10 @@
         <v>9</v>
       </c>
       <c r="D567" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E567" t="s">
         <v>1327</v>
-      </c>
-      <c r="E567" t="s">
-        <v>1296</v>
       </c>
       <c r="F567" t="s">
         <v>1242</v>
@@ -20120,10 +20120,10 @@
         <v>9</v>
       </c>
       <c r="D568" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E568" t="s">
         <v>1327</v>
-      </c>
-      <c r="E568" t="s">
-        <v>1296</v>
       </c>
       <c r="F568" t="s">
         <v>1242</v>
@@ -20304,10 +20304,10 @@
         <v>9</v>
       </c>
       <c r="D576" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E576" t="s">
         <v>1347</v>
-      </c>
-      <c r="E576" t="s">
-        <v>1296</v>
       </c>
       <c r="F576" t="s">
         <v>1242</v>
@@ -20511,10 +20511,10 @@
         <v>9</v>
       </c>
       <c r="D585" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E585" t="s">
         <v>1370</v>
-      </c>
-      <c r="E585" t="s">
-        <v>1358</v>
       </c>
       <c r="F585" t="s">
         <v>1242</v>
@@ -20534,10 +20534,10 @@
         <v>9</v>
       </c>
       <c r="D586" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E586" t="s">
         <v>1373</v>
-      </c>
-      <c r="E586" t="s">
-        <v>1358</v>
       </c>
       <c r="F586" t="s">
         <v>34</v>
@@ -20557,10 +20557,10 @@
         <v>9</v>
       </c>
       <c r="D587" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E587" t="s">
         <v>1377</v>
-      </c>
-      <c r="E587" t="s">
-        <v>1358</v>
       </c>
       <c r="F587" t="s">
         <v>1242</v>
@@ -20580,10 +20580,10 @@
         <v>9</v>
       </c>
       <c r="D588" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E588" t="s">
         <v>1380</v>
-      </c>
-      <c r="E588" t="s">
-        <v>1358</v>
       </c>
       <c r="F588" t="s">
         <v>19</v>
@@ -20626,10 +20626,10 @@
         <v>9</v>
       </c>
       <c r="D590" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E590" t="s">
         <v>1385</v>
-      </c>
-      <c r="E590" t="s">
-        <v>1358</v>
       </c>
       <c r="F590" t="s">
         <v>34</v>
@@ -20649,10 +20649,10 @@
         <v>9</v>
       </c>
       <c r="D591" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E591" t="s">
         <v>1389</v>
-      </c>
-      <c r="E591" t="s">
-        <v>1358</v>
       </c>
       <c r="F591" t="s">
         <v>34</v>
@@ -20695,10 +20695,10 @@
         <v>9</v>
       </c>
       <c r="D593" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E593" t="s">
         <v>1395</v>
-      </c>
-      <c r="E593" t="s">
-        <v>1358</v>
       </c>
       <c r="F593" t="s">
         <v>34</v>
@@ -20718,10 +20718,10 @@
         <v>9</v>
       </c>
       <c r="D594" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E594" t="s">
         <v>1399</v>
-      </c>
-      <c r="E594" t="s">
-        <v>1358</v>
       </c>
       <c r="F594" t="s">
         <v>16</v>
@@ -20741,10 +20741,10 @@
         <v>9</v>
       </c>
       <c r="D595" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E595" t="s">
         <v>1402</v>
-      </c>
-      <c r="E595" t="s">
-        <v>1358</v>
       </c>
       <c r="F595" t="s">
         <v>1242</v>
@@ -20971,10 +20971,10 @@
         <v>9</v>
       </c>
       <c r="D605" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E605" t="s">
         <v>1427</v>
-      </c>
-      <c r="E605" t="s">
-        <v>1423</v>
       </c>
       <c r="F605" t="s">
         <v>19</v>
@@ -21063,10 +21063,10 @@
         <v>9</v>
       </c>
       <c r="D609" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E609" t="s">
         <v>1437</v>
-      </c>
-      <c r="E609" t="s">
-        <v>1423</v>
       </c>
       <c r="F609" t="s">
         <v>34</v>
@@ -21086,10 +21086,10 @@
         <v>9</v>
       </c>
       <c r="D610" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E610" t="s">
         <v>1441</v>
-      </c>
-      <c r="E610" t="s">
-        <v>1423</v>
       </c>
       <c r="F610" t="s">
         <v>34</v>
@@ -21109,10 +21109,10 @@
         <v>9</v>
       </c>
       <c r="D611" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E611" t="s">
         <v>1445</v>
-      </c>
-      <c r="E611" t="s">
-        <v>1423</v>
       </c>
       <c r="F611" t="s">
         <v>1242</v>
@@ -21132,10 +21132,10 @@
         <v>9</v>
       </c>
       <c r="D612" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E612" t="s">
         <v>1449</v>
-      </c>
-      <c r="E612" t="s">
-        <v>1423</v>
       </c>
       <c r="F612" t="s">
         <v>34</v>
@@ -21224,10 +21224,10 @@
         <v>9</v>
       </c>
       <c r="D616" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E616" t="s">
         <v>1457</v>
-      </c>
-      <c r="E616" t="s">
-        <v>1423</v>
       </c>
       <c r="F616" t="s">
         <v>34</v>
@@ -21247,10 +21247,10 @@
         <v>9</v>
       </c>
       <c r="D617" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E617" t="s">
         <v>1461</v>
-      </c>
-      <c r="E617" t="s">
-        <v>1423</v>
       </c>
       <c r="F617" t="s">
         <v>1242</v>
@@ -21293,10 +21293,10 @@
         <v>9</v>
       </c>
       <c r="D619" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E619" t="s">
         <v>1427</v>
-      </c>
-      <c r="E619" t="s">
-        <v>1423</v>
       </c>
       <c r="F619" t="s">
         <v>34</v>
@@ -21316,10 +21316,10 @@
         <v>9</v>
       </c>
       <c r="D620" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E620" t="s">
         <v>1469</v>
-      </c>
-      <c r="E620" t="s">
-        <v>1423</v>
       </c>
       <c r="F620" t="s">
         <v>1242</v>
@@ -21339,10 +21339,10 @@
         <v>188</v>
       </c>
       <c r="D621" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E621" t="s">
         <v>1469</v>
-      </c>
-      <c r="E621" t="s">
-        <v>1423</v>
       </c>
       <c r="F621" t="s">
         <v>19</v>
@@ -21385,10 +21385,10 @@
         <v>9</v>
       </c>
       <c r="D623" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E623" t="s">
         <v>1475</v>
-      </c>
-      <c r="E623" t="s">
-        <v>1423</v>
       </c>
       <c r="F623" t="s">
         <v>1242</v>
@@ -21661,10 +21661,10 @@
         <v>9</v>
       </c>
       <c r="D635" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E635" t="s">
         <v>1501</v>
-      </c>
-      <c r="E635" t="s">
-        <v>1497</v>
       </c>
       <c r="F635" t="s">
         <v>34</v>
@@ -21776,10 +21776,10 @@
         <v>9</v>
       </c>
       <c r="D640" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E640" t="s">
         <v>1514</v>
-      </c>
-      <c r="E640" t="s">
-        <v>1497</v>
       </c>
       <c r="F640" t="s">
         <v>34</v>
@@ -21868,10 +21868,10 @@
         <v>9</v>
       </c>
       <c r="D644" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E644" t="s">
         <v>1514</v>
-      </c>
-      <c r="E644" t="s">
-        <v>1497</v>
       </c>
       <c r="F644" t="s">
         <v>34</v>
@@ -21891,10 +21891,10 @@
         <v>9</v>
       </c>
       <c r="D645" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E645" t="s">
         <v>1525</v>
-      </c>
-      <c r="E645" t="s">
-        <v>1497</v>
       </c>
       <c r="F645" t="s">
         <v>34</v>
@@ -21914,10 +21914,10 @@
         <v>9</v>
       </c>
       <c r="D646" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E646" t="s">
         <v>1529</v>
-      </c>
-      <c r="E646" t="s">
-        <v>1497</v>
       </c>
       <c r="F646" t="s">
         <v>34</v>
@@ -21960,10 +21960,10 @@
         <v>9</v>
       </c>
       <c r="D648" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E648" t="s">
         <v>1535</v>
-      </c>
-      <c r="E648" t="s">
-        <v>1497</v>
       </c>
       <c r="F648" t="s">
         <v>1242</v>
@@ -21983,10 +21983,10 @@
         <v>9</v>
       </c>
       <c r="D649" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E649" t="s">
         <v>1538</v>
-      </c>
-      <c r="E649" t="s">
-        <v>1497</v>
       </c>
       <c r="F649" t="s">
         <v>34</v>
@@ -22075,10 +22075,10 @@
         <v>9</v>
       </c>
       <c r="D653" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E653" t="s">
         <v>1548</v>
-      </c>
-      <c r="E653" t="s">
-        <v>1497</v>
       </c>
       <c r="F653" t="s">
         <v>19</v>
@@ -22098,10 +22098,10 @@
         <v>9</v>
       </c>
       <c r="D654" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E654" t="s">
         <v>1552</v>
-      </c>
-      <c r="E654" t="s">
-        <v>1497</v>
       </c>
       <c r="F654" t="s">
         <v>19</v>
@@ -22121,10 +22121,10 @@
         <v>9</v>
       </c>
       <c r="D655" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E655" t="s">
         <v>1555</v>
-      </c>
-      <c r="E655" t="s">
-        <v>1497</v>
       </c>
       <c r="F655" t="s">
         <v>19</v>
@@ -22213,10 +22213,10 @@
         <v>9</v>
       </c>
       <c r="D659" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E659" t="s">
         <v>1563</v>
-      </c>
-      <c r="E659" t="s">
-        <v>1497</v>
       </c>
       <c r="F659" t="s">
         <v>34</v>
@@ -22305,10 +22305,10 @@
         <v>9</v>
       </c>
       <c r="D663" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E663" t="s">
         <v>1575</v>
-      </c>
-      <c r="E663" t="s">
-        <v>1571</v>
       </c>
       <c r="F663" t="s">
         <v>19</v>
@@ -22351,10 +22351,10 @@
         <v>9</v>
       </c>
       <c r="D665" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E665" t="s">
         <v>1582</v>
-      </c>
-      <c r="E665" t="s">
-        <v>1571</v>
       </c>
       <c r="F665" t="s">
         <v>1242</v>
@@ -22374,10 +22374,10 @@
         <v>9</v>
       </c>
       <c r="D666" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E666" t="s">
         <v>1582</v>
-      </c>
-      <c r="E666" t="s">
-        <v>1571</v>
       </c>
       <c r="F666" t="s">
         <v>1242</v>
@@ -22397,10 +22397,10 @@
         <v>9</v>
       </c>
       <c r="D667" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E667" t="s">
         <v>1555</v>
-      </c>
-      <c r="E667" t="s">
-        <v>1571</v>
       </c>
       <c r="F667" t="s">
         <v>19</v>
@@ -22420,10 +22420,10 @@
         <v>9</v>
       </c>
       <c r="D668" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E668" t="s">
         <v>1582</v>
-      </c>
-      <c r="E668" t="s">
-        <v>1571</v>
       </c>
       <c r="F668" t="s">
         <v>1242</v>
@@ -22443,10 +22443,10 @@
         <v>9</v>
       </c>
       <c r="D669" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E669" t="s">
         <v>1582</v>
-      </c>
-      <c r="E669" t="s">
-        <v>1571</v>
       </c>
       <c r="F669" t="s">
         <v>1242</v>
@@ -22466,10 +22466,10 @@
         <v>9</v>
       </c>
       <c r="D670" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E670" t="s">
         <v>1594</v>
-      </c>
-      <c r="E670" t="s">
-        <v>1571</v>
       </c>
       <c r="F670" t="s">
         <v>19</v>
@@ -22489,10 +22489,10 @@
         <v>9</v>
       </c>
       <c r="D671" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E671" t="s">
         <v>1598</v>
-      </c>
-      <c r="E671" t="s">
-        <v>1571</v>
       </c>
       <c r="F671" t="s">
         <v>34</v>
@@ -22512,10 +22512,10 @@
         <v>9</v>
       </c>
       <c r="D672" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E672" t="s">
         <v>1535</v>
-      </c>
-      <c r="E672" t="s">
-        <v>1571</v>
       </c>
       <c r="F672" t="s">
         <v>34</v>
@@ -22535,10 +22535,10 @@
         <v>9</v>
       </c>
       <c r="D673" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E673" t="s">
         <v>1605</v>
-      </c>
-      <c r="E673" t="s">
-        <v>1571</v>
       </c>
       <c r="F673" t="s">
         <v>34</v>
@@ -22558,10 +22558,10 @@
         <v>9</v>
       </c>
       <c r="D674" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E674" t="s">
         <v>1582</v>
-      </c>
-      <c r="E674" t="s">
-        <v>1571</v>
       </c>
       <c r="F674" t="s">
         <v>1242</v>
@@ -22581,10 +22581,10 @@
         <v>9</v>
       </c>
       <c r="D675" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E675" t="s">
         <v>1582</v>
-      </c>
-      <c r="E675" t="s">
-        <v>1571</v>
       </c>
       <c r="F675" t="s">
         <v>34</v>
@@ -22604,10 +22604,10 @@
         <v>9</v>
       </c>
       <c r="D676" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E676" t="s">
         <v>1613</v>
-      </c>
-      <c r="E676" t="s">
-        <v>1571</v>
       </c>
       <c r="F676" t="s">
         <v>34</v>
@@ -22627,10 +22627,10 @@
         <v>9</v>
       </c>
       <c r="D677" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E677" t="s">
         <v>1555</v>
-      </c>
-      <c r="E677" t="s">
-        <v>1571</v>
       </c>
       <c r="F677" t="s">
         <v>19</v>
@@ -22650,10 +22650,10 @@
         <v>9</v>
       </c>
       <c r="D678" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E678" t="s">
         <v>1620</v>
-      </c>
-      <c r="E678" t="s">
-        <v>1571</v>
       </c>
       <c r="F678" t="s">
         <v>19</v>
@@ -22673,10 +22673,10 @@
         <v>188</v>
       </c>
       <c r="D679" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E679" t="s">
         <v>1620</v>
-      </c>
-      <c r="E679" t="s">
-        <v>1571</v>
       </c>
       <c r="F679" t="s">
         <v>1242</v>
@@ -22696,10 +22696,10 @@
         <v>9</v>
       </c>
       <c r="D680" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E680" t="s">
         <v>1620</v>
-      </c>
-      <c r="E680" t="s">
-        <v>1571</v>
       </c>
       <c r="F680" t="s">
         <v>34</v>
@@ -22719,10 +22719,10 @@
         <v>9</v>
       </c>
       <c r="D681" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E681" t="s">
         <v>1626</v>
-      </c>
-      <c r="E681" t="s">
-        <v>1571</v>
       </c>
       <c r="F681" t="s">
         <v>34</v>
@@ -22742,10 +22742,10 @@
         <v>9</v>
       </c>
       <c r="D682" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E682" t="s">
         <v>1582</v>
-      </c>
-      <c r="E682" t="s">
-        <v>1571</v>
       </c>
       <c r="F682" t="s">
         <v>19</v>
@@ -22765,10 +22765,10 @@
         <v>9</v>
       </c>
       <c r="D683" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E683" t="s">
         <v>1555</v>
-      </c>
-      <c r="E683" t="s">
-        <v>1571</v>
       </c>
       <c r="F683" t="s">
         <v>19</v>
@@ -22788,10 +22788,10 @@
         <v>9</v>
       </c>
       <c r="D684" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E684" t="s">
         <v>1582</v>
-      </c>
-      <c r="E684" t="s">
-        <v>1571</v>
       </c>
       <c r="F684" t="s">
         <v>1242</v>
@@ -22834,10 +22834,10 @@
         <v>9</v>
       </c>
       <c r="D686" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E686" t="s">
         <v>1582</v>
-      </c>
-      <c r="E686" t="s">
-        <v>1571</v>
       </c>
       <c r="F686" t="s">
         <v>19</v>
@@ -22857,10 +22857,10 @@
         <v>9</v>
       </c>
       <c r="D687" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E687" t="s">
         <v>1582</v>
-      </c>
-      <c r="E687" t="s">
-        <v>1571</v>
       </c>
       <c r="F687" t="s">
         <v>1242</v>
@@ -22880,10 +22880,10 @@
         <v>9</v>
       </c>
       <c r="D688" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E688" t="s">
         <v>1555</v>
-      </c>
-      <c r="E688" t="s">
-        <v>1571</v>
       </c>
       <c r="F688" t="s">
         <v>19</v>
@@ -22926,10 +22926,10 @@
         <v>9</v>
       </c>
       <c r="D690" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E690" t="s">
         <v>1647</v>
-      </c>
-      <c r="E690" t="s">
-        <v>1571</v>
       </c>
       <c r="F690" t="s">
         <v>19</v>
@@ -22949,10 +22949,10 @@
         <v>9</v>
       </c>
       <c r="D691" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E691" t="s">
         <v>1582</v>
-      </c>
-      <c r="E691" t="s">
-        <v>1571</v>
       </c>
       <c r="F691" t="s">
         <v>1242</v>
@@ -22972,10 +22972,10 @@
         <v>9</v>
       </c>
       <c r="D692" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E692" t="s">
         <v>1582</v>
-      </c>
-      <c r="E692" t="s">
-        <v>1571</v>
       </c>
       <c r="F692" t="s">
         <v>16</v>
@@ -22995,10 +22995,10 @@
         <v>188</v>
       </c>
       <c r="D693" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E693" t="s">
         <v>1582</v>
-      </c>
-      <c r="E693" t="s">
-        <v>1571</v>
       </c>
       <c r="F693" t="s">
         <v>1242</v>
@@ -23018,10 +23018,10 @@
         <v>9</v>
       </c>
       <c r="D694" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E694" t="s">
         <v>1605</v>
-      </c>
-      <c r="E694" t="s">
-        <v>1571</v>
       </c>
       <c r="F694" t="s">
         <v>34</v>
@@ -23041,10 +23041,10 @@
         <v>9</v>
       </c>
       <c r="D695" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E695" t="s">
         <v>1582</v>
-      </c>
-      <c r="E695" t="s">
-        <v>1571</v>
       </c>
       <c r="F695" t="s">
         <v>1242</v>
@@ -23064,10 +23064,10 @@
         <v>9</v>
       </c>
       <c r="D696" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E696" t="s">
         <v>1582</v>
-      </c>
-      <c r="E696" t="s">
-        <v>1571</v>
       </c>
       <c r="F696" t="s">
         <v>1242</v>
@@ -23110,10 +23110,10 @@
         <v>9</v>
       </c>
       <c r="D698" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E698" t="s">
         <v>1666</v>
-      </c>
-      <c r="E698" t="s">
-        <v>1662</v>
       </c>
       <c r="F698" t="s">
         <v>34</v>
@@ -23133,10 +23133,10 @@
         <v>9</v>
       </c>
       <c r="D699" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E699" t="s">
         <v>1670</v>
-      </c>
-      <c r="E699" t="s">
-        <v>1662</v>
       </c>
       <c r="F699" t="s">
         <v>1242</v>
@@ -23156,10 +23156,10 @@
         <v>9</v>
       </c>
       <c r="D700" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E700" t="s">
         <v>1670</v>
-      </c>
-      <c r="E700" t="s">
-        <v>1662</v>
       </c>
       <c r="F700" t="s">
         <v>1242</v>
@@ -23179,10 +23179,10 @@
         <v>9</v>
       </c>
       <c r="D701" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E701" t="s">
         <v>1670</v>
-      </c>
-      <c r="E701" t="s">
-        <v>1662</v>
       </c>
       <c r="F701" t="s">
         <v>1242</v>
@@ -23202,10 +23202,10 @@
         <v>9</v>
       </c>
       <c r="D702" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E702" t="s">
         <v>1670</v>
-      </c>
-      <c r="E702" t="s">
-        <v>1662</v>
       </c>
       <c r="F702" t="s">
         <v>1242</v>
@@ -23225,10 +23225,10 @@
         <v>9</v>
       </c>
       <c r="D703" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E703" t="s">
         <v>1670</v>
-      </c>
-      <c r="E703" t="s">
-        <v>1662</v>
       </c>
       <c r="F703" t="s">
         <v>1242</v>
@@ -23248,10 +23248,10 @@
         <v>9</v>
       </c>
       <c r="D704" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E704" t="s">
         <v>1666</v>
-      </c>
-      <c r="E704" t="s">
-        <v>1662</v>
       </c>
       <c r="F704" t="s">
         <v>34</v>
@@ -23271,10 +23271,10 @@
         <v>9</v>
       </c>
       <c r="D705" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E705" t="s">
         <v>1685</v>
-      </c>
-      <c r="E705" t="s">
-        <v>1662</v>
       </c>
       <c r="F705" t="s">
         <v>34</v>
@@ -23294,10 +23294,10 @@
         <v>9</v>
       </c>
       <c r="D706" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E706" t="s">
         <v>1670</v>
-      </c>
-      <c r="E706" t="s">
-        <v>1662</v>
       </c>
       <c r="F706" t="s">
         <v>16</v>
@@ -23317,10 +23317,10 @@
         <v>9</v>
       </c>
       <c r="D707" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E707" t="s">
         <v>1691</v>
-      </c>
-      <c r="E707" t="s">
-        <v>1662</v>
       </c>
       <c r="F707" t="s">
         <v>16</v>
@@ -23340,10 +23340,10 @@
         <v>9</v>
       </c>
       <c r="D708" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E708" t="s">
         <v>1694</v>
-      </c>
-      <c r="E708" t="s">
-        <v>1662</v>
       </c>
       <c r="F708" t="s">
         <v>34</v>
@@ -23363,10 +23363,10 @@
         <v>9</v>
       </c>
       <c r="D709" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E709" t="s">
         <v>1698</v>
-      </c>
-      <c r="E709" t="s">
-        <v>1662</v>
       </c>
       <c r="F709" t="s">
         <v>19</v>
@@ -23386,10 +23386,10 @@
         <v>9</v>
       </c>
       <c r="D710" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E710" t="s">
         <v>1702</v>
-      </c>
-      <c r="E710" t="s">
-        <v>1662</v>
       </c>
       <c r="F710" t="s">
         <v>34</v>
@@ -23409,10 +23409,10 @@
         <v>9</v>
       </c>
       <c r="D711" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E711" t="s">
         <v>1670</v>
-      </c>
-      <c r="E711" t="s">
-        <v>1662</v>
       </c>
       <c r="F711" t="s">
         <v>1242</v>
@@ -23432,10 +23432,10 @@
         <v>9</v>
       </c>
       <c r="D712" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E712" t="s">
         <v>1708</v>
-      </c>
-      <c r="E712" t="s">
-        <v>1662</v>
       </c>
       <c r="F712" t="s">
         <v>34</v>
@@ -23455,10 +23455,10 @@
         <v>9</v>
       </c>
       <c r="D713" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E713" t="s">
         <v>1712</v>
-      </c>
-      <c r="E713" t="s">
-        <v>1662</v>
       </c>
       <c r="F713" t="s">
         <v>34</v>
@@ -23478,10 +23478,10 @@
         <v>9</v>
       </c>
       <c r="D714" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E714" t="s">
         <v>1670</v>
-      </c>
-      <c r="E714" t="s">
-        <v>1662</v>
       </c>
       <c r="F714" t="s">
         <v>19</v>
@@ -23501,10 +23501,10 @@
         <v>9</v>
       </c>
       <c r="D715" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E715" t="s">
         <v>1718</v>
-      </c>
-      <c r="E715" t="s">
-        <v>1662</v>
       </c>
       <c r="F715" t="s">
         <v>34</v>
@@ -23524,10 +23524,10 @@
         <v>9</v>
       </c>
       <c r="D716" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E716" t="s">
         <v>1670</v>
-      </c>
-      <c r="E716" t="s">
-        <v>1662</v>
       </c>
       <c r="F716" t="s">
         <v>19</v>
@@ -23547,10 +23547,10 @@
         <v>9</v>
       </c>
       <c r="D717" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E717" t="s">
         <v>1724</v>
-      </c>
-      <c r="E717" t="s">
-        <v>1662</v>
       </c>
       <c r="F717" t="s">
         <v>34</v>
@@ -23570,10 +23570,10 @@
         <v>9</v>
       </c>
       <c r="D718" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E718" t="s">
         <v>1728</v>
-      </c>
-      <c r="E718" t="s">
-        <v>1662</v>
       </c>
       <c r="F718" t="s">
         <v>34</v>
@@ -23593,10 +23593,10 @@
         <v>9</v>
       </c>
       <c r="D719" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E719" t="s">
         <v>1670</v>
-      </c>
-      <c r="E719" t="s">
-        <v>1662</v>
       </c>
       <c r="F719" t="s">
         <v>1242</v>
@@ -23616,10 +23616,10 @@
         <v>9</v>
       </c>
       <c r="D720" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E720" t="s">
         <v>1733</v>
-      </c>
-      <c r="E720" t="s">
-        <v>1662</v>
       </c>
       <c r="F720" t="s">
         <v>19</v>
@@ -23639,10 +23639,10 @@
         <v>9</v>
       </c>
       <c r="D721" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E721" t="s">
         <v>1670</v>
-      </c>
-      <c r="E721" t="s">
-        <v>1662</v>
       </c>
       <c r="F721" t="s">
         <v>1242</v>
@@ -23662,10 +23662,10 @@
         <v>9</v>
       </c>
       <c r="D722" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E722" t="s">
         <v>1670</v>
-      </c>
-      <c r="E722" t="s">
-        <v>1662</v>
       </c>
       <c r="F722" t="s">
         <v>1242</v>
@@ -23685,10 +23685,10 @@
         <v>188</v>
       </c>
       <c r="D723" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E723" t="s">
         <v>1670</v>
-      </c>
-      <c r="E723" t="s">
-        <v>1662</v>
       </c>
       <c r="F723" t="s">
         <v>19</v>
@@ -23708,10 +23708,10 @@
         <v>9</v>
       </c>
       <c r="D724" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E724" t="s">
         <v>1741</v>
-      </c>
-      <c r="E724" t="s">
-        <v>1662</v>
       </c>
       <c r="F724" t="s">
         <v>34</v>
@@ -23731,10 +23731,10 @@
         <v>9</v>
       </c>
       <c r="D725" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E725" t="s">
         <v>1670</v>
-      </c>
-      <c r="E725" t="s">
-        <v>1662</v>
       </c>
       <c r="F725" t="s">
         <v>1242</v>
@@ -23754,10 +23754,10 @@
         <v>9</v>
       </c>
       <c r="D726" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E726" t="s">
         <v>1746</v>
-      </c>
-      <c r="E726" t="s">
-        <v>1662</v>
       </c>
       <c r="F726" t="s">
         <v>34</v>
@@ -23777,10 +23777,10 @@
         <v>9</v>
       </c>
       <c r="D727" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E727" t="s">
         <v>1670</v>
-      </c>
-      <c r="E727" t="s">
-        <v>1662</v>
       </c>
       <c r="F727" t="s">
         <v>1242</v>
@@ -23800,10 +23800,10 @@
         <v>9</v>
       </c>
       <c r="D728" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E728" t="s">
         <v>1670</v>
-      </c>
-      <c r="E728" t="s">
-        <v>1662</v>
       </c>
       <c r="F728" t="s">
         <v>1242</v>
@@ -23823,10 +23823,10 @@
         <v>9</v>
       </c>
       <c r="D729" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E729" t="s">
         <v>1685</v>
-      </c>
-      <c r="E729" t="s">
-        <v>1662</v>
       </c>
       <c r="F729" t="s">
         <v>34</v>
@@ -23846,10 +23846,10 @@
         <v>9</v>
       </c>
       <c r="D730" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E730" t="s">
         <v>1670</v>
-      </c>
-      <c r="E730" t="s">
-        <v>1662</v>
       </c>
       <c r="F730" t="s">
         <v>16</v>
@@ -23869,10 +23869,10 @@
         <v>188</v>
       </c>
       <c r="D731" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E731" t="s">
         <v>1670</v>
-      </c>
-      <c r="E731" t="s">
-        <v>1662</v>
       </c>
       <c r="F731" t="s">
         <v>1242</v>
@@ -23892,10 +23892,10 @@
         <v>9</v>
       </c>
       <c r="D732" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E732" t="s">
         <v>1708</v>
-      </c>
-      <c r="E732" t="s">
-        <v>1662</v>
       </c>
       <c r="F732" t="s">
         <v>34</v>
@@ -23915,10 +23915,10 @@
         <v>9</v>
       </c>
       <c r="D733" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E733" t="s">
         <v>1670</v>
-      </c>
-      <c r="E733" t="s">
-        <v>1662</v>
       </c>
       <c r="F733" t="s">
         <v>1242</v>
@@ -23938,10 +23938,10 @@
         <v>9</v>
       </c>
       <c r="D734" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E734" t="s">
         <v>1670</v>
-      </c>
-      <c r="E734" t="s">
-        <v>1662</v>
       </c>
       <c r="F734" t="s">
         <v>1242</v>
@@ -23984,10 +23984,10 @@
         <v>9</v>
       </c>
       <c r="D736" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E736" t="s">
         <v>1770</v>
-      </c>
-      <c r="E736" t="s">
-        <v>1766</v>
       </c>
       <c r="F736" t="s">
         <v>1242</v>
@@ -24007,10 +24007,10 @@
         <v>9</v>
       </c>
       <c r="D737" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E737" t="s">
         <v>1770</v>
-      </c>
-      <c r="E737" t="s">
-        <v>1766</v>
       </c>
       <c r="F737" t="s">
         <v>1242</v>
@@ -24030,10 +24030,10 @@
         <v>9</v>
       </c>
       <c r="D738" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E738" t="s">
         <v>1770</v>
-      </c>
-      <c r="E738" t="s">
-        <v>1766</v>
       </c>
       <c r="F738" t="s">
         <v>1242</v>
@@ -24053,10 +24053,10 @@
         <v>9</v>
       </c>
       <c r="D739" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E739" t="s">
         <v>1770</v>
-      </c>
-      <c r="E739" t="s">
-        <v>1766</v>
       </c>
       <c r="F739" t="s">
         <v>1242</v>
@@ -24076,10 +24076,10 @@
         <v>9</v>
       </c>
       <c r="D740" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E740" t="s">
         <v>1770</v>
-      </c>
-      <c r="E740" t="s">
-        <v>1766</v>
       </c>
       <c r="F740" t="s">
         <v>1242</v>
@@ -24099,10 +24099,10 @@
         <v>9</v>
       </c>
       <c r="D741" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E741" t="s">
         <v>1770</v>
-      </c>
-      <c r="E741" t="s">
-        <v>1766</v>
       </c>
       <c r="F741" t="s">
         <v>19</v>
@@ -24122,10 +24122,10 @@
         <v>9</v>
       </c>
       <c r="D742" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E742" t="s">
         <v>1783</v>
-      </c>
-      <c r="E742" t="s">
-        <v>1766</v>
       </c>
       <c r="F742" t="s">
         <v>19</v>
@@ -24145,10 +24145,10 @@
         <v>9</v>
       </c>
       <c r="D743" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E743" t="s">
         <v>1787</v>
-      </c>
-      <c r="E743" t="s">
-        <v>1766</v>
       </c>
       <c r="F743" t="s">
         <v>19</v>
@@ -24168,10 +24168,10 @@
         <v>9</v>
       </c>
       <c r="D744" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E744" t="s">
         <v>1770</v>
-      </c>
-      <c r="E744" t="s">
-        <v>1766</v>
       </c>
       <c r="F744" t="s">
         <v>1242</v>
@@ -24191,10 +24191,10 @@
         <v>9</v>
       </c>
       <c r="D745" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E745" t="s">
         <v>1770</v>
-      </c>
-      <c r="E745" t="s">
-        <v>1766</v>
       </c>
       <c r="F745" t="s">
         <v>1242</v>
@@ -24214,10 +24214,10 @@
         <v>9</v>
       </c>
       <c r="D746" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E746" t="s">
         <v>1795</v>
-      </c>
-      <c r="E746" t="s">
-        <v>1766</v>
       </c>
       <c r="F746" t="s">
         <v>34</v>
@@ -24237,10 +24237,10 @@
         <v>9</v>
       </c>
       <c r="D747" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E747" t="s">
         <v>1770</v>
-      </c>
-      <c r="E747" t="s">
-        <v>1766</v>
       </c>
       <c r="F747" t="s">
         <v>16</v>
@@ -24260,10 +24260,10 @@
         <v>9</v>
       </c>
       <c r="D748" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E748" t="s">
         <v>1795</v>
-      </c>
-      <c r="E748" t="s">
-        <v>1766</v>
       </c>
       <c r="F748" t="s">
         <v>34</v>
@@ -24283,10 +24283,10 @@
         <v>9</v>
       </c>
       <c r="D749" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E749" t="s">
         <v>1803</v>
-      </c>
-      <c r="E749" t="s">
-        <v>1766</v>
       </c>
       <c r="F749" t="s">
         <v>34</v>
@@ -24306,10 +24306,10 @@
         <v>9</v>
       </c>
       <c r="D750" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E750" t="s">
         <v>1807</v>
-      </c>
-      <c r="E750" t="s">
-        <v>1766</v>
       </c>
       <c r="F750" t="s">
         <v>34</v>
@@ -24329,10 +24329,10 @@
         <v>9</v>
       </c>
       <c r="D751" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E751" t="s">
         <v>1810</v>
-      </c>
-      <c r="E751" t="s">
-        <v>1766</v>
       </c>
       <c r="F751" t="s">
         <v>34</v>
@@ -24352,10 +24352,10 @@
         <v>9</v>
       </c>
       <c r="D752" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E752" t="s">
         <v>1770</v>
-      </c>
-      <c r="E752" t="s">
-        <v>1766</v>
       </c>
       <c r="F752" t="s">
         <v>1242</v>
@@ -24375,10 +24375,10 @@
         <v>9</v>
       </c>
       <c r="D753" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E753" t="s">
         <v>1816</v>
-      </c>
-      <c r="E753" t="s">
-        <v>1766</v>
       </c>
       <c r="F753" t="s">
         <v>1242</v>
@@ -24398,10 +24398,10 @@
         <v>9</v>
       </c>
       <c r="D754" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E754" t="s">
         <v>1770</v>
-      </c>
-      <c r="E754" t="s">
-        <v>1766</v>
       </c>
       <c r="F754" t="s">
         <v>19</v>
@@ -24421,10 +24421,10 @@
         <v>9</v>
       </c>
       <c r="D755" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E755" t="s">
         <v>1821</v>
-      </c>
-      <c r="E755" t="s">
-        <v>1766</v>
       </c>
       <c r="F755" t="s">
         <v>19</v>
@@ -24444,10 +24444,10 @@
         <v>9</v>
       </c>
       <c r="D756" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E756" t="s">
         <v>1770</v>
-      </c>
-      <c r="E756" t="s">
-        <v>1766</v>
       </c>
       <c r="F756" t="s">
         <v>1242</v>
@@ -24467,10 +24467,10 @@
         <v>9</v>
       </c>
       <c r="D757" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E757" t="s">
         <v>1770</v>
-      </c>
-      <c r="E757" t="s">
-        <v>1766</v>
       </c>
       <c r="F757" t="s">
         <v>1242</v>
@@ -24490,10 +24490,10 @@
         <v>9</v>
       </c>
       <c r="D758" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E758" t="s">
         <v>1828</v>
-      </c>
-      <c r="E758" t="s">
-        <v>1766</v>
       </c>
       <c r="F758" t="s">
         <v>34</v>
@@ -24513,10 +24513,10 @@
         <v>9</v>
       </c>
       <c r="D759" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E759" t="s">
         <v>1832</v>
-      </c>
-      <c r="E759" t="s">
-        <v>1766</v>
       </c>
       <c r="F759" t="s">
         <v>19</v>
@@ -24536,10 +24536,10 @@
         <v>9</v>
       </c>
       <c r="D760" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E760" t="s">
         <v>1770</v>
-      </c>
-      <c r="E760" t="s">
-        <v>1766</v>
       </c>
       <c r="F760" t="s">
         <v>1242</v>
@@ -24582,10 +24582,10 @@
         <v>9</v>
       </c>
       <c r="D762" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E762" t="s">
         <v>1839</v>
-      </c>
-      <c r="E762" t="s">
-        <v>1766</v>
       </c>
       <c r="F762" t="s">
         <v>34</v>
@@ -24605,10 +24605,10 @@
         <v>9</v>
       </c>
       <c r="D763" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E763" t="s">
         <v>1770</v>
-      </c>
-      <c r="E763" t="s">
-        <v>1766</v>
       </c>
       <c r="F763" t="s">
         <v>1242</v>
@@ -24628,10 +24628,10 @@
         <v>9</v>
       </c>
       <c r="D764" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E764" t="s">
         <v>1770</v>
-      </c>
-      <c r="E764" t="s">
-        <v>1766</v>
       </c>
       <c r="F764" t="s">
         <v>16</v>
@@ -24651,10 +24651,10 @@
         <v>188</v>
       </c>
       <c r="D765" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E765" t="s">
         <v>1770</v>
-      </c>
-      <c r="E765" t="s">
-        <v>1766</v>
       </c>
       <c r="F765" t="s">
         <v>1242</v>
@@ -24674,10 +24674,10 @@
         <v>9</v>
       </c>
       <c r="D766" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E766" t="s">
         <v>1770</v>
-      </c>
-      <c r="E766" t="s">
-        <v>1766</v>
       </c>
       <c r="F766" t="s">
         <v>1242</v>
@@ -24697,10 +24697,10 @@
         <v>9</v>
       </c>
       <c r="D767" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E767" t="s">
         <v>1770</v>
-      </c>
-      <c r="E767" t="s">
-        <v>1766</v>
       </c>
       <c r="F767" t="s">
         <v>1242</v>
@@ -24743,10 +24743,10 @@
         <v>9</v>
       </c>
       <c r="D769" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E769" t="s">
         <v>1856</v>
-      </c>
-      <c r="E769" t="s">
-        <v>1852</v>
       </c>
       <c r="F769" t="s">
         <v>34</v>
@@ -24766,10 +24766,10 @@
         <v>9</v>
       </c>
       <c r="D770" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E770" t="s">
         <v>1860</v>
-      </c>
-      <c r="E770" t="s">
-        <v>1852</v>
       </c>
       <c r="F770" t="s">
         <v>1242</v>
@@ -24789,10 +24789,10 @@
         <v>9</v>
       </c>
       <c r="D771" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E771" t="s">
         <v>1860</v>
-      </c>
-      <c r="E771" t="s">
-        <v>1852</v>
       </c>
       <c r="F771" t="s">
         <v>1242</v>
@@ -24812,10 +24812,10 @@
         <v>9</v>
       </c>
       <c r="D772" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E772" t="s">
         <v>1860</v>
-      </c>
-      <c r="E772" t="s">
-        <v>1852</v>
       </c>
       <c r="F772" t="s">
         <v>1242</v>
@@ -24835,10 +24835,10 @@
         <v>9</v>
       </c>
       <c r="D773" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E773" t="s">
         <v>1860</v>
-      </c>
-      <c r="E773" t="s">
-        <v>1852</v>
       </c>
       <c r="F773" t="s">
         <v>1242</v>
@@ -24858,10 +24858,10 @@
         <v>9</v>
       </c>
       <c r="D774" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E774" t="s">
         <v>1860</v>
-      </c>
-      <c r="E774" t="s">
-        <v>1852</v>
       </c>
       <c r="F774" t="s">
         <v>1242</v>
@@ -24881,10 +24881,10 @@
         <v>9</v>
       </c>
       <c r="D775" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E775" t="s">
         <v>1860</v>
-      </c>
-      <c r="E775" t="s">
-        <v>1852</v>
       </c>
       <c r="F775" t="s">
         <v>1242</v>
@@ -24927,10 +24927,10 @@
         <v>9</v>
       </c>
       <c r="D777" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E777" t="s">
         <v>1816</v>
-      </c>
-      <c r="E777" t="s">
-        <v>1852</v>
       </c>
       <c r="F777" t="s">
         <v>19</v>
@@ -24950,10 +24950,10 @@
         <v>9</v>
       </c>
       <c r="D778" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E778" t="s">
         <v>1860</v>
-      </c>
-      <c r="E778" t="s">
-        <v>1852</v>
       </c>
       <c r="F778" t="s">
         <v>1242</v>
@@ -24973,10 +24973,10 @@
         <v>9</v>
       </c>
       <c r="D779" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E779" t="s">
         <v>1860</v>
-      </c>
-      <c r="E779" t="s">
-        <v>1852</v>
       </c>
       <c r="F779" t="s">
         <v>16</v>
@@ -24996,10 +24996,10 @@
         <v>188</v>
       </c>
       <c r="D780" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E780" t="s">
         <v>1860</v>
-      </c>
-      <c r="E780" t="s">
-        <v>1852</v>
       </c>
       <c r="F780" t="s">
         <v>1242</v>
@@ -25019,10 +25019,10 @@
         <v>9</v>
       </c>
       <c r="D781" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E781" t="s">
         <v>1816</v>
-      </c>
-      <c r="E781" t="s">
-        <v>1852</v>
       </c>
       <c r="F781" t="s">
         <v>34</v>
@@ -25042,10 +25042,10 @@
         <v>9</v>
       </c>
       <c r="D782" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E782" t="s">
         <v>1860</v>
-      </c>
-      <c r="E782" t="s">
-        <v>1852</v>
       </c>
       <c r="F782" t="s">
         <v>1242</v>
@@ -25065,10 +25065,10 @@
         <v>9</v>
       </c>
       <c r="D783" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E783" t="s">
         <v>1889</v>
-      </c>
-      <c r="E783" t="s">
-        <v>1852</v>
       </c>
       <c r="F783" t="s">
         <v>34</v>
@@ -25088,10 +25088,10 @@
         <v>188</v>
       </c>
       <c r="D784" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E784" t="s">
         <v>1860</v>
-      </c>
-      <c r="E784" t="s">
-        <v>1852</v>
       </c>
       <c r="F784" t="s">
         <v>34</v>
@@ -25111,10 +25111,10 @@
         <v>9</v>
       </c>
       <c r="D785" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E785" t="s">
         <v>1894</v>
-      </c>
-      <c r="E785" t="s">
-        <v>1852</v>
       </c>
       <c r="F785" t="s">
         <v>34</v>
@@ -25134,10 +25134,10 @@
         <v>9</v>
       </c>
       <c r="D786" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E786" t="s">
         <v>1897</v>
-      </c>
-      <c r="E786" t="s">
-        <v>1852</v>
       </c>
       <c r="F786" t="s">
         <v>34</v>
@@ -25157,10 +25157,10 @@
         <v>9</v>
       </c>
       <c r="D787" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E787" t="s">
         <v>1860</v>
-      </c>
-      <c r="E787" t="s">
-        <v>1852</v>
       </c>
       <c r="F787" t="s">
         <v>1242</v>
@@ -25180,10 +25180,10 @@
         <v>9</v>
       </c>
       <c r="D788" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E788" t="s">
         <v>1860</v>
-      </c>
-      <c r="E788" t="s">
-        <v>1852</v>
       </c>
       <c r="F788" t="s">
         <v>1242</v>
@@ -25203,10 +25203,10 @@
         <v>9</v>
       </c>
       <c r="D789" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E789" t="s">
         <v>1905</v>
-      </c>
-      <c r="E789" t="s">
-        <v>1852</v>
       </c>
       <c r="F789" t="s">
         <v>16</v>
@@ -25226,10 +25226,10 @@
         <v>9</v>
       </c>
       <c r="D790" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E790" t="s">
         <v>1860</v>
-      </c>
-      <c r="E790" t="s">
-        <v>1852</v>
       </c>
       <c r="F790" t="s">
         <v>19</v>
@@ -25249,10 +25249,10 @@
         <v>188</v>
       </c>
       <c r="D791" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E791" t="s">
         <v>1911</v>
-      </c>
-      <c r="E791" t="s">
-        <v>1852</v>
       </c>
       <c r="F791" t="s">
         <v>34</v>
@@ -25272,10 +25272,10 @@
         <v>188</v>
       </c>
       <c r="D792" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E792" t="s">
         <v>1860</v>
-      </c>
-      <c r="E792" t="s">
-        <v>1852</v>
       </c>
       <c r="F792" t="s">
         <v>1242</v>
@@ -25295,10 +25295,10 @@
         <v>9</v>
       </c>
       <c r="D793" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E793" t="s">
         <v>1860</v>
-      </c>
-      <c r="E793" t="s">
-        <v>1852</v>
       </c>
       <c r="F793" t="s">
         <v>1242</v>
@@ -25318,10 +25318,10 @@
         <v>9</v>
       </c>
       <c r="D794" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E794" t="s">
         <v>1860</v>
-      </c>
-      <c r="E794" t="s">
-        <v>1852</v>
       </c>
       <c r="F794" t="s">
         <v>16</v>
@@ -25341,10 +25341,10 @@
         <v>188</v>
       </c>
       <c r="D795" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E795" t="s">
         <v>1905</v>
-      </c>
-      <c r="E795" t="s">
-        <v>1852</v>
       </c>
       <c r="F795" t="s">
         <v>34</v>
@@ -25364,10 +25364,10 @@
         <v>9</v>
       </c>
       <c r="D796" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E796" t="s">
         <v>1860</v>
-      </c>
-      <c r="E796" t="s">
-        <v>1852</v>
       </c>
       <c r="F796" t="s">
         <v>1242</v>
@@ -25410,10 +25410,10 @@
         <v>9</v>
       </c>
       <c r="D798" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E798" t="s">
         <v>1928</v>
-      </c>
-      <c r="E798" t="s">
-        <v>1924</v>
       </c>
       <c r="F798" t="s">
         <v>1242</v>
@@ -25433,10 +25433,10 @@
         <v>9</v>
       </c>
       <c r="D799" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E799" t="s">
         <v>1931</v>
-      </c>
-      <c r="E799" t="s">
-        <v>1924</v>
       </c>
       <c r="F799" t="s">
         <v>34</v>
@@ -25456,10 +25456,10 @@
         <v>9</v>
       </c>
       <c r="D800" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E800" t="s">
         <v>1935</v>
-      </c>
-      <c r="E800" t="s">
-        <v>1924</v>
       </c>
       <c r="F800" t="s">
         <v>34</v>
@@ -25479,10 +25479,10 @@
         <v>9</v>
       </c>
       <c r="D801" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E801" t="s">
         <v>1928</v>
-      </c>
-      <c r="E801" t="s">
-        <v>1924</v>
       </c>
       <c r="F801" t="s">
         <v>1242</v>
@@ -25502,10 +25502,10 @@
         <v>9</v>
       </c>
       <c r="D802" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E802" t="s">
         <v>1928</v>
-      </c>
-      <c r="E802" t="s">
-        <v>1924</v>
       </c>
       <c r="F802" t="s">
         <v>1242</v>
@@ -25525,10 +25525,10 @@
         <v>9</v>
       </c>
       <c r="D803" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E803" t="s">
         <v>1943</v>
-      </c>
-      <c r="E803" t="s">
-        <v>1924</v>
       </c>
       <c r="F803" t="s">
         <v>1242</v>
@@ -25548,10 +25548,10 @@
         <v>9</v>
       </c>
       <c r="D804" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E804" t="s">
         <v>1928</v>
-      </c>
-      <c r="E804" t="s">
-        <v>1924</v>
       </c>
       <c r="F804" t="s">
         <v>1242</v>
@@ -25571,10 +25571,10 @@
         <v>9</v>
       </c>
       <c r="D805" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E805" t="s">
         <v>1928</v>
-      </c>
-      <c r="E805" t="s">
-        <v>1924</v>
       </c>
       <c r="F805" t="s">
         <v>16</v>
@@ -25594,10 +25594,10 @@
         <v>188</v>
       </c>
       <c r="D806" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E806" t="s">
         <v>1928</v>
-      </c>
-      <c r="E806" t="s">
-        <v>1924</v>
       </c>
       <c r="F806" t="s">
         <v>1242</v>
@@ -25617,10 +25617,10 @@
         <v>9</v>
       </c>
       <c r="D807" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E807" t="s">
         <v>1928</v>
-      </c>
-      <c r="E807" t="s">
-        <v>1924</v>
       </c>
       <c r="F807" t="s">
         <v>1242</v>
@@ -25640,10 +25640,10 @@
         <v>9</v>
       </c>
       <c r="D808" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E808" t="s">
         <v>1928</v>
-      </c>
-      <c r="E808" t="s">
-        <v>1924</v>
       </c>
       <c r="F808" t="s">
         <v>1242</v>
@@ -25663,10 +25663,10 @@
         <v>9</v>
       </c>
       <c r="D809" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E809" t="s">
         <v>1928</v>
-      </c>
-      <c r="E809" t="s">
-        <v>1924</v>
       </c>
       <c r="F809" t="s">
         <v>1242</v>
@@ -25686,10 +25686,10 @@
         <v>188</v>
       </c>
       <c r="D810" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E810" t="s">
         <v>1928</v>
-      </c>
-      <c r="E810" t="s">
-        <v>1924</v>
       </c>
       <c r="F810" t="s">
         <v>1242</v>
@@ -25732,10 +25732,10 @@
         <v>9</v>
       </c>
       <c r="D812" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E812" t="s">
         <v>1928</v>
-      </c>
-      <c r="E812" t="s">
-        <v>1924</v>
       </c>
       <c r="F812" t="s">
         <v>1242</v>
@@ -25755,10 +25755,10 @@
         <v>9</v>
       </c>
       <c r="D813" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E813" t="s">
         <v>1943</v>
-      </c>
-      <c r="E813" t="s">
-        <v>1924</v>
       </c>
       <c r="F813" t="s">
         <v>34</v>
@@ -25778,10 +25778,10 @@
         <v>9</v>
       </c>
       <c r="D814" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E814" t="s">
         <v>1968</v>
-      </c>
-      <c r="E814" t="s">
-        <v>1924</v>
       </c>
       <c r="F814" t="s">
         <v>34</v>
@@ -25801,10 +25801,10 @@
         <v>9</v>
       </c>
       <c r="D815" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E815" t="s">
         <v>1928</v>
-      </c>
-      <c r="E815" t="s">
-        <v>1924</v>
       </c>
       <c r="F815" t="s">
         <v>1242</v>
@@ -25824,10 +25824,10 @@
         <v>9</v>
       </c>
       <c r="D816" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E816" t="s">
         <v>1928</v>
-      </c>
-      <c r="E816" t="s">
-        <v>1924</v>
       </c>
       <c r="F816" t="s">
         <v>34</v>
@@ -25847,10 +25847,10 @@
         <v>9</v>
       </c>
       <c r="D817" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E817" t="s">
         <v>1976</v>
-      </c>
-      <c r="E817" t="s">
-        <v>1924</v>
       </c>
       <c r="F817" t="s">
         <v>34</v>
@@ -25870,10 +25870,10 @@
         <v>9</v>
       </c>
       <c r="D818" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E818" t="s">
         <v>1928</v>
-      </c>
-      <c r="E818" t="s">
-        <v>1924</v>
       </c>
       <c r="F818" t="s">
         <v>1242</v>
@@ -25893,10 +25893,10 @@
         <v>9</v>
       </c>
       <c r="D819" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E819" t="s">
         <v>1981</v>
-      </c>
-      <c r="E819" t="s">
-        <v>1924</v>
       </c>
       <c r="F819" t="s">
         <v>34</v>
@@ -25916,10 +25916,10 @@
         <v>9</v>
       </c>
       <c r="D820" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E820" t="s">
         <v>1985</v>
-      </c>
-      <c r="E820" t="s">
-        <v>1924</v>
       </c>
       <c r="F820" t="s">
         <v>34</v>
@@ -25939,10 +25939,10 @@
         <v>9</v>
       </c>
       <c r="D821" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E821" t="s">
         <v>1928</v>
-      </c>
-      <c r="E821" t="s">
-        <v>1924</v>
       </c>
       <c r="F821" t="s">
         <v>1242</v>
@@ -25962,10 +25962,10 @@
         <v>9</v>
       </c>
       <c r="D822" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E822" t="s">
         <v>1928</v>
-      </c>
-      <c r="E822" t="s">
-        <v>1924</v>
       </c>
       <c r="F822" t="s">
         <v>1242</v>
@@ -25985,10 +25985,10 @@
         <v>9</v>
       </c>
       <c r="D823" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E823" t="s">
         <v>1928</v>
-      </c>
-      <c r="E823" t="s">
-        <v>1924</v>
       </c>
       <c r="F823" t="s">
         <v>1242</v>
@@ -26008,10 +26008,10 @@
         <v>9</v>
       </c>
       <c r="D824" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E824" t="s">
         <v>1928</v>
-      </c>
-      <c r="E824" t="s">
-        <v>1924</v>
       </c>
       <c r="F824" t="s">
         <v>1242</v>
@@ -26031,10 +26031,10 @@
         <v>9</v>
       </c>
       <c r="D825" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E825" t="s">
         <v>1928</v>
-      </c>
-      <c r="E825" t="s">
-        <v>1924</v>
       </c>
       <c r="F825" t="s">
         <v>1242</v>
@@ -26054,10 +26054,10 @@
         <v>9</v>
       </c>
       <c r="D826" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E826" t="s">
         <v>1928</v>
-      </c>
-      <c r="E826" t="s">
-        <v>1924</v>
       </c>
       <c r="F826" t="s">
         <v>1242</v>
@@ -26077,10 +26077,10 @@
         <v>188</v>
       </c>
       <c r="D827" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E827" t="s">
         <v>1928</v>
-      </c>
-      <c r="E827" t="s">
-        <v>1924</v>
       </c>
       <c r="F827" t="s">
         <v>1242</v>
@@ -26100,10 +26100,10 @@
         <v>9</v>
       </c>
       <c r="D828" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E828" t="s">
         <v>1928</v>
-      </c>
-      <c r="E828" t="s">
-        <v>1924</v>
       </c>
       <c r="F828" t="s">
         <v>1242</v>
@@ -26123,10 +26123,10 @@
         <v>9</v>
       </c>
       <c r="D829" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E829" t="s">
         <v>1928</v>
-      </c>
-      <c r="E829" t="s">
-        <v>1924</v>
       </c>
       <c r="F829" t="s">
         <v>1242</v>
@@ -26215,10 +26215,10 @@
         <v>9</v>
       </c>
       <c r="D833" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E833" t="s">
         <v>2016</v>
-      </c>
-      <c r="E833" t="s">
-        <v>2007</v>
       </c>
       <c r="F833" t="s">
         <v>34</v>
@@ -26284,10 +26284,10 @@
         <v>9</v>
       </c>
       <c r="D836" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E836" t="s">
         <v>2016</v>
-      </c>
-      <c r="E836" t="s">
-        <v>2007</v>
       </c>
       <c r="F836" t="s">
         <v>16</v>
@@ -26307,10 +26307,10 @@
         <v>9</v>
       </c>
       <c r="D837" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E837" t="s">
         <v>2026</v>
-      </c>
-      <c r="E837" t="s">
-        <v>2007</v>
       </c>
       <c r="F837" t="s">
         <v>16</v>
@@ -26330,10 +26330,10 @@
         <v>188</v>
       </c>
       <c r="D838" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E838" t="s">
         <v>2016</v>
-      </c>
-      <c r="E838" t="s">
-        <v>2007</v>
       </c>
       <c r="F838" t="s">
         <v>1242</v>
@@ -26353,10 +26353,10 @@
         <v>188</v>
       </c>
       <c r="D839" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E839" t="s">
         <v>2026</v>
-      </c>
-      <c r="E839" t="s">
-        <v>2007</v>
       </c>
       <c r="F839" t="s">
         <v>34</v>
@@ -26514,10 +26514,10 @@
         <v>9</v>
       </c>
       <c r="D846" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E846" t="s">
         <v>2043</v>
-      </c>
-      <c r="E846" t="s">
-        <v>2007</v>
       </c>
       <c r="F846" t="s">
         <v>19</v>
@@ -26537,10 +26537,10 @@
         <v>9</v>
       </c>
       <c r="D847" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E847" t="s">
         <v>2047</v>
-      </c>
-      <c r="E847" t="s">
-        <v>2007</v>
       </c>
       <c r="F847" t="s">
         <v>2011</v>
@@ -26560,10 +26560,10 @@
         <v>9</v>
       </c>
       <c r="D848" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E848" t="s">
         <v>2047</v>
-      </c>
-      <c r="E848" t="s">
-        <v>2007</v>
       </c>
       <c r="F848" t="s">
         <v>2011</v>
@@ -26583,10 +26583,10 @@
         <v>9</v>
       </c>
       <c r="D849" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E849" t="s">
         <v>2047</v>
-      </c>
-      <c r="E849" t="s">
-        <v>2007</v>
       </c>
       <c r="F849" t="s">
         <v>2011</v>
@@ -26606,10 +26606,10 @@
         <v>9</v>
       </c>
       <c r="D850" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E850" t="s">
         <v>2047</v>
-      </c>
-      <c r="E850" t="s">
-        <v>2007</v>
       </c>
       <c r="F850" t="s">
         <v>16</v>
@@ -26629,10 +26629,10 @@
         <v>188</v>
       </c>
       <c r="D851" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E851" t="s">
         <v>2047</v>
-      </c>
-      <c r="E851" t="s">
-        <v>2007</v>
       </c>
       <c r="F851" t="s">
         <v>1242</v>
@@ -26652,10 +26652,10 @@
         <v>9</v>
       </c>
       <c r="D852" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E852" t="s">
         <v>2047</v>
-      </c>
-      <c r="E852" t="s">
-        <v>2007</v>
       </c>
       <c r="F852" t="s">
         <v>2011</v>
@@ -26675,10 +26675,10 @@
         <v>9</v>
       </c>
       <c r="D853" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E853" t="s">
         <v>2047</v>
-      </c>
-      <c r="E853" t="s">
-        <v>2007</v>
       </c>
       <c r="F853" t="s">
         <v>2011</v>
@@ -26698,10 +26698,10 @@
         <v>9</v>
       </c>
       <c r="D854" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E854" t="s">
         <v>2047</v>
-      </c>
-      <c r="E854" t="s">
-        <v>2007</v>
       </c>
       <c r="F854" t="s">
         <v>2011</v>
@@ -26744,10 +26744,10 @@
         <v>9</v>
       </c>
       <c r="D856" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E856" t="s">
         <v>2016</v>
-      </c>
-      <c r="E856" t="s">
-        <v>2007</v>
       </c>
       <c r="F856" t="s">
         <v>34</v>
@@ -26767,10 +26767,10 @@
         <v>188</v>
       </c>
       <c r="D857" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E857" t="s">
         <v>2016</v>
-      </c>
-      <c r="E857" t="s">
-        <v>2007</v>
       </c>
       <c r="F857" t="s">
         <v>2011</v>
@@ -26997,10 +26997,10 @@
         <v>9</v>
       </c>
       <c r="D867" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E867" t="s">
         <v>2090</v>
-      </c>
-      <c r="E867" t="s">
-        <v>2086</v>
       </c>
       <c r="F867" t="s">
         <v>2011</v>
@@ -27020,10 +27020,10 @@
         <v>9</v>
       </c>
       <c r="D868" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E868" t="s">
         <v>2090</v>
-      </c>
-      <c r="E868" t="s">
-        <v>2086</v>
       </c>
       <c r="F868" t="s">
         <v>2011</v>
@@ -27043,10 +27043,10 @@
         <v>9</v>
       </c>
       <c r="D869" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E869" t="s">
         <v>2090</v>
-      </c>
-      <c r="E869" t="s">
-        <v>2086</v>
       </c>
       <c r="F869" t="s">
         <v>2011</v>
@@ -27066,10 +27066,10 @@
         <v>9</v>
       </c>
       <c r="D870" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E870" t="s">
         <v>2090</v>
-      </c>
-      <c r="E870" t="s">
-        <v>2086</v>
       </c>
       <c r="F870" t="s">
         <v>2011</v>
@@ -27089,10 +27089,10 @@
         <v>9</v>
       </c>
       <c r="D871" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E871" t="s">
         <v>2090</v>
-      </c>
-      <c r="E871" t="s">
-        <v>2086</v>
       </c>
       <c r="F871" t="s">
         <v>2011</v>
@@ -27112,10 +27112,10 @@
         <v>9</v>
       </c>
       <c r="D872" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E872" t="s">
         <v>2090</v>
-      </c>
-      <c r="E872" t="s">
-        <v>2086</v>
       </c>
       <c r="F872" t="s">
         <v>16</v>
@@ -27135,10 +27135,10 @@
         <v>188</v>
       </c>
       <c r="D873" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E873" t="s">
         <v>2090</v>
-      </c>
-      <c r="E873" t="s">
-        <v>2086</v>
       </c>
       <c r="F873" t="s">
         <v>1242</v>
@@ -27158,10 +27158,10 @@
         <v>9</v>
       </c>
       <c r="D874" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E874" t="s">
         <v>2090</v>
-      </c>
-      <c r="E874" t="s">
-        <v>2086</v>
       </c>
       <c r="F874" t="s">
         <v>2011</v>
@@ -27181,10 +27181,10 @@
         <v>9</v>
       </c>
       <c r="D875" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E875" t="s">
         <v>2107</v>
-      </c>
-      <c r="E875" t="s">
-        <v>2086</v>
       </c>
       <c r="F875" t="s">
         <v>2011</v>
@@ -27204,10 +27204,10 @@
         <v>9</v>
       </c>
       <c r="D876" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E876" t="s">
         <v>2107</v>
-      </c>
-      <c r="E876" t="s">
-        <v>2086</v>
       </c>
       <c r="F876" t="s">
         <v>2011</v>
@@ -27227,10 +27227,10 @@
         <v>9</v>
       </c>
       <c r="D877" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E877" t="s">
         <v>2107</v>
-      </c>
-      <c r="E877" t="s">
-        <v>2086</v>
       </c>
       <c r="F877" t="s">
         <v>16</v>
@@ -27250,10 +27250,10 @@
         <v>188</v>
       </c>
       <c r="D878" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E878" t="s">
         <v>2107</v>
-      </c>
-      <c r="E878" t="s">
-        <v>2086</v>
       </c>
       <c r="F878" t="s">
         <v>1242</v>
@@ -27273,10 +27273,10 @@
         <v>9</v>
       </c>
       <c r="D879" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E879" t="s">
         <v>2107</v>
-      </c>
-      <c r="E879" t="s">
-        <v>2086</v>
       </c>
       <c r="F879" t="s">
         <v>2011</v>
@@ -27296,10 +27296,10 @@
         <v>9</v>
       </c>
       <c r="D880" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E880" t="s">
         <v>2107</v>
-      </c>
-      <c r="E880" t="s">
-        <v>2086</v>
       </c>
       <c r="F880" t="s">
         <v>2011</v>
@@ -27319,10 +27319,10 @@
         <v>9</v>
       </c>
       <c r="D881" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E881" t="s">
         <v>2107</v>
-      </c>
-      <c r="E881" t="s">
-        <v>2086</v>
       </c>
       <c r="F881" t="s">
         <v>2011</v>
@@ -27342,10 +27342,10 @@
         <v>9</v>
       </c>
       <c r="D882" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E882" t="s">
         <v>2090</v>
-      </c>
-      <c r="E882" t="s">
-        <v>2086</v>
       </c>
       <c r="F882" t="s">
         <v>2011</v>
@@ -27365,10 +27365,10 @@
         <v>9</v>
       </c>
       <c r="D883" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E883" t="s">
         <v>2090</v>
-      </c>
-      <c r="E883" t="s">
-        <v>2086</v>
       </c>
       <c r="F883" t="s">
         <v>19</v>
@@ -27388,10 +27388,10 @@
         <v>9</v>
       </c>
       <c r="D884" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E884" t="s">
         <v>2090</v>
-      </c>
-      <c r="E884" t="s">
-        <v>2086</v>
       </c>
       <c r="F884" t="s">
         <v>19</v>
@@ -27411,10 +27411,10 @@
         <v>9</v>
       </c>
       <c r="D885" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E885" t="s">
         <v>2090</v>
-      </c>
-      <c r="E885" t="s">
-        <v>2086</v>
       </c>
       <c r="F885" t="s">
         <v>19</v>
@@ -27434,10 +27434,10 @@
         <v>9</v>
       </c>
       <c r="D886" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E886" t="s">
         <v>2090</v>
-      </c>
-      <c r="E886" t="s">
-        <v>2086</v>
       </c>
       <c r="F886" t="s">
         <v>2011</v>
@@ -27457,10 +27457,10 @@
         <v>9</v>
       </c>
       <c r="D887" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E887" t="s">
         <v>2090</v>
-      </c>
-      <c r="E887" t="s">
-        <v>2086</v>
       </c>
       <c r="F887" t="s">
         <v>2011</v>
@@ -27480,10 +27480,10 @@
         <v>9</v>
       </c>
       <c r="D888" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E888" t="s">
         <v>2090</v>
-      </c>
-      <c r="E888" t="s">
-        <v>2086</v>
       </c>
       <c r="F888" t="s">
         <v>19</v>
@@ -27503,10 +27503,10 @@
         <v>9</v>
       </c>
       <c r="D889" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E889" t="s">
         <v>2090</v>
-      </c>
-      <c r="E889" t="s">
-        <v>2086</v>
       </c>
       <c r="F889" t="s">
         <v>2011</v>
@@ -27526,10 +27526,10 @@
         <v>9</v>
       </c>
       <c r="D890" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E890" t="s">
         <v>2090</v>
-      </c>
-      <c r="E890" t="s">
-        <v>2086</v>
       </c>
       <c r="F890" t="s">
         <v>2011</v>
@@ -27549,10 +27549,10 @@
         <v>188</v>
       </c>
       <c r="D891" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E891" t="s">
         <v>2090</v>
-      </c>
-      <c r="E891" t="s">
-        <v>2086</v>
       </c>
       <c r="F891" t="s">
         <v>1242</v>
@@ -27572,10 +27572,10 @@
         <v>9</v>
       </c>
       <c r="D892" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E892" t="s">
         <v>2090</v>
-      </c>
-      <c r="E892" t="s">
-        <v>2086</v>
       </c>
       <c r="F892" t="s">
         <v>2011</v>
@@ -27595,10 +27595,10 @@
         <v>9</v>
       </c>
       <c r="D893" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E893" t="s">
         <v>2090</v>
-      </c>
-      <c r="E893" t="s">
-        <v>2086</v>
       </c>
       <c r="F893" t="s">
         <v>2011</v>
@@ -27618,10 +27618,10 @@
         <v>9</v>
       </c>
       <c r="D894" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E894" t="s">
         <v>2090</v>
-      </c>
-      <c r="E894" t="s">
-        <v>2086</v>
       </c>
       <c r="F894" t="s">
         <v>2011</v>
@@ -27641,10 +27641,10 @@
         <v>188</v>
       </c>
       <c r="D895" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E895" t="s">
         <v>2090</v>
-      </c>
-      <c r="E895" t="s">
-        <v>2086</v>
       </c>
       <c r="F895" t="s">
         <v>1242</v>
@@ -28331,10 +28331,10 @@
         <v>9</v>
       </c>
       <c r="D925" t="s">
+        <v>2200</v>
+      </c>
+      <c r="E925" t="s">
         <v>2213</v>
-      </c>
-      <c r="E925" t="s">
-        <v>2201</v>
       </c>
       <c r="F925" t="s">
         <v>2011</v>
@@ -28354,10 +28354,10 @@
         <v>188</v>
       </c>
       <c r="D926" t="s">
+        <v>2200</v>
+      </c>
+      <c r="E926" t="s">
         <v>2213</v>
-      </c>
-      <c r="E926" t="s">
-        <v>2201</v>
       </c>
       <c r="F926" t="s">
         <v>1242</v>
@@ -28561,10 +28561,10 @@
         <v>9</v>
       </c>
       <c r="D935" t="s">
+        <v>2200</v>
+      </c>
+      <c r="E935" t="s">
         <v>2233</v>
-      </c>
-      <c r="E935" t="s">
-        <v>2201</v>
       </c>
       <c r="F935" t="s">
         <v>2011</v>
@@ -28607,10 +28607,10 @@
         <v>9</v>
       </c>
       <c r="D937" t="s">
+        <v>2200</v>
+      </c>
+      <c r="E937" t="s">
         <v>2237</v>
-      </c>
-      <c r="E937" t="s">
-        <v>2201</v>
       </c>
       <c r="F937" t="s">
         <v>2011</v>
@@ -28630,10 +28630,10 @@
         <v>9</v>
       </c>
       <c r="D938" t="s">
+        <v>2200</v>
+      </c>
+      <c r="E938" t="s">
         <v>2233</v>
-      </c>
-      <c r="E938" t="s">
-        <v>2201</v>
       </c>
       <c r="F938" t="s">
         <v>2011</v>
